--- a/china-notion-sync.xlsx
+++ b/china-notion-sync.xlsx
@@ -17,9 +17,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$T$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Schedule'!$A$1:$T$239</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ideas (parked)'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ideas (parked)'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Moves'!$A$1:$F$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Legs'!$A$1:$I$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Legs'!$A$1:$I$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I37" s="6" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 07:30 → 08:00</t>
         </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I38" s="6" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 08:50 → 08:10</t>
+          <t>MOVE day 4 → 2; RETIME 08:50 → 09:10</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I39" s="6" t="n">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 10:17 → 09:37</t>
+          <t>MOVE day 4 → 2; RETIME 10:17 → 10:37</t>
         </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I40" s="6" t="n">
@@ -4269,23 +4269,23 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Shuhe Old Town</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L40" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O40" s="6" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 12:26 → 10:26</t>
+          <t>MOVE day 4 → 2; RETIME 12:26 → 11:26</t>
         </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
@@ -4334,67 +4334,67 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
           <t>Shuhe Old Town</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="J41" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O41" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 14:47 → 11:17</t>
+          <t>RETIME 14:31 → 12:04</t>
         </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>Guides recommend 3-4 h for a full Shuhe visit, but for travellers who have already walked Dayan, 2 h covers the core lanes, canals and Qinglong Bridge; museum and lunch are separate stops.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T41" s="6" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Shuhe Old Town</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -4437,11 +4437,11 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I42" s="6" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -4465,24 +4465,24 @@
         </is>
       </c>
       <c r="O42" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:31 → 13:25; ORDER 50 → 60</t>
+          <t>MOVE day 4 → 2; RETIME 14:47 → 13:25; ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Guides recommend 3-4 h for a full Shuhe visit, but for travellers who have already walked Dayan, 2 h covers the core lanes, canals and Qinglong Bridge; museum and lunch are separate stops.</t>
         </is>
       </c>
       <c r="T42" s="6" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="I43" s="6" t="n">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 17:26 → 14:46</t>
+          <t>MOVE day 4 → 2; RETIME 17:26 → 15:46</t>
         </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I44" s="6" t="n">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 00:18 → 15:50; ORDER 100 → 80</t>
+          <t>MOVE day 4 → 2; RETIME 00:18 → 19:00; ORDER 100 → 80</t>
         </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="I45" s="6" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>ORDER 70 → 90</t>
+          <t>RETIME 18:00 → 20:23; ORDER 70 → 90</t>
         </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
@@ -4806,14 +4806,14 @@
         </is>
       </c>
       <c r="L46" s="6" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>26.06</v>
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I47" s="6" t="n">
@@ -4890,18 +4890,18 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>31.28</v>
+        <v>0</v>
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:51 → 08:11</t>
+          <t>RETIME 08:51 → 08:29</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I48" s="6" t="n">
@@ -4973,23 +4973,23 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Impression Lijiang</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>RETIME 11:19 → 11:13</t>
+          <t>RETIME 11:19 → 10:37</t>
         </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
@@ -5038,46 +5038,46 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
+          <t>Impression Lijiang</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>Impression Lijiang</t>
-        </is>
-      </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>8.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -5085,25 +5085,25 @@
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:02 → 12:51; ORDER 50 → 40</t>
+          <t>RETIME 13:47 → 13:00</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>The show itself is exactly 60 min, but standard tickets are unreserved first-come seating and operators advise arriving up to an hour early; 30-35 min pre-show plus exiting the amphitheatre is realistic.</t>
         </is>
       </c>
       <c r="T49" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -5126,26 +5126,26 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Impression Lijiang</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I50" s="6" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -5173,25 +5173,25 @@
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:47 → 14:19; ORDER 40 → 50</t>
+          <t>RETIME 16:02 → 14:53</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>The show itself is exactly 60 min, but standard tickets are unreserved first-come seating and operators advise arriving up to an hour early; 30-35 min pre-show plus exiting the amphitheatre is realistic.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T50" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -5224,12 +5224,12 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I51" s="6" t="n">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:11 → 16:23</t>
+          <t>RETIME 17:11 → 16:12</t>
         </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I52" s="6" t="n">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:20 → 18:01</t>
+          <t>RETIME 19:20 → 18:00</t>
         </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
@@ -23779,12 +23779,12 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I41" s="6" t="n">
@@ -23824,7 +23824,7 @@
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 07:30 → 08:00</t>
         </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
@@ -23867,12 +23867,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I42" s="6" t="n">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 08:50 → 08:10</t>
+          <t>MOVE day 4 → 2; RETIME 08:50 → 09:10</t>
         </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
@@ -23955,12 +23955,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I43" s="6" t="n">
@@ -24000,7 +24000,7 @@
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 10:17 → 09:37</t>
+          <t>MOVE day 4 → 2; RETIME 10:17 → 10:37</t>
         </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
@@ -24043,12 +24043,12 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I44" s="6" t="n">
@@ -24056,23 +24056,23 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Shuhe Old Town</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L44" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O44" s="6" t="n">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 12:26 → 10:26</t>
+          <t>MOVE day 4 → 2; RETIME 12:26 → 11:26</t>
         </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
@@ -24121,67 +24121,67 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
           <t>Shuhe Old Town</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="Q45" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 14:47 → 11:17</t>
+          <t>RETIME 14:31 → 12:04</t>
         </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>Guides recommend 3-4 h for a full Shuhe visit, but for travellers who have already walked Dayan, 2 h covers the core lanes, canals and Qinglong Bridge; museum and lunch are separate stops.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T45" s="6" t="inlineStr">
@@ -24209,12 +24209,12 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Shuhe Old Town</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -24224,11 +24224,11 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I46" s="6" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -24252,24 +24252,24 @@
         </is>
       </c>
       <c r="O46" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:31 → 13:25; ORDER 50 → 60</t>
+          <t>MOVE day 4 → 2; RETIME 14:47 → 13:25; ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Guides recommend 3-4 h for a full Shuhe visit, but for travellers who have already walked Dayan, 2 h covers the core lanes, canals and Qinglong Bridge; museum and lunch are separate stops.</t>
         </is>
       </c>
       <c r="T46" s="6" t="inlineStr">
@@ -24307,12 +24307,12 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="I47" s="6" t="n">
@@ -24352,7 +24352,7 @@
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 17:26 → 14:46</t>
+          <t>MOVE day 4 → 2; RETIME 17:26 → 15:46</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
@@ -24395,12 +24395,12 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I48" s="6" t="n">
@@ -24440,7 +24440,7 @@
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 00:18 → 15:50; ORDER 100 → 80</t>
+          <t>MOVE day 4 → 2; RETIME 00:18 → 19:00; ORDER 100 → 80</t>
         </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
@@ -24483,12 +24483,12 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="I49" s="6" t="n">
@@ -24528,7 +24528,7 @@
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>ORDER 70 → 90</t>
+          <t>RETIME 18:00 → 20:23; ORDER 70 → 90</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
@@ -24593,14 +24593,14 @@
         </is>
       </c>
       <c r="L50" s="6" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>26.06</v>
       </c>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
@@ -24659,12 +24659,12 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I51" s="6" t="n">
@@ -24677,18 +24677,18 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>31.28</v>
+        <v>0</v>
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
@@ -24704,7 +24704,7 @@
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:51 → 08:11</t>
+          <t>RETIME 08:51 → 08:29</t>
         </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
@@ -24747,12 +24747,12 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I52" s="6" t="n">
@@ -24760,23 +24760,23 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Impression Lijiang</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
@@ -24792,7 +24792,7 @@
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>RETIME 11:19 → 11:13</t>
+          <t>RETIME 11:19 → 10:37</t>
         </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
@@ -24825,46 +24825,46 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
+          <t>Impression Lijiang</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>Impression Lijiang</t>
-        </is>
-      </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>8.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
@@ -24872,25 +24872,25 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:02 → 12:51; ORDER 50 → 40</t>
+          <t>RETIME 13:47 → 13:00</t>
         </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>The show itself is exactly 60 min, but standard tickets are unreserved first-come seating and operators advise arriving up to an hour early; 30-35 min pre-show plus exiting the amphitheatre is realistic.</t>
         </is>
       </c>
       <c r="T53" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -24913,26 +24913,26 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Impression Lijiang</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I54" s="6" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -24960,25 +24960,25 @@
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="Q54" s="6" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:47 → 14:19; ORDER 40 → 50</t>
+          <t>RETIME 16:02 → 14:53</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>The show itself is exactly 60 min, but standard tickets are unreserved first-come seating and operators advise arriving up to an hour early; 30-35 min pre-show plus exiting the amphitheatre is realistic.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T54" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -25011,12 +25011,12 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I55" s="6" t="n">
@@ -25056,7 +25056,7 @@
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:11 → 16:23</t>
+          <t>RETIME 17:11 → 16:12</t>
         </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
@@ -25099,12 +25099,12 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I56" s="6" t="n">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:20 → 18:01</t>
+          <t>RETIME 19:20 → 18:00</t>
         </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
@@ -41140,7 +41140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -41559,20 +41559,20 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Check in at KS Kongshang</t>
+          <t>Chongqing West (alt station)</t>
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
@@ -41581,31 +41581,31 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Not a sight — logistics, kept out of the stop list per the no-hotels rule. Practically: the hotel is on the 52nd floor of the Xinhua International Building at Jiefangbei, formal check-in is after 14:00, so on arrival day drop bags around 12:15, eat, and collect the room later in the afternoon. Passport needed at the desk.</t>
+          <t>Not a sight — it is the contingency departure station, 40–60 min from Jiefangbei in morning traffic versus roughly 30 for Chongqing North. Only relevant if the day-3 ticket turns out to leave from West rather than North, in which case the 06:45 hotel departure has to become 06:00. Confirm which station the ticket is for before booking anything else on day 3.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Fenghuang</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Chongqing West (alt station)</t>
+          <t>Bar street</t>
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>Not a sight — it is the contingency departure station, 40–60 min from Jiefangbei in morning traffic versus roughly 30 for Chongqing North. Only relevant if the day-3 ticket turns out to leave from West rather than North, in which case the 06:45 hotel departure has to become 06:00. Confirm which station the ticket is for before booking anything else on day 3.</t>
+          <t>Flagged bonus, 45 min, and it sits right on the route home past Hong Bridge. With a 05:45 wake-up for the dawn session and a 07:45 train, walk through it and keep walking. Only worth sitting down if you abandon the sunrise.</t>
         </is>
       </c>
     </row>
@@ -41634,11 +41634,11 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Bar street</t>
+          <t>Station shuttle / taxi</t>
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Flagged bonus, 45 min, and it sits right on the route home past Hong Bridge. With a 05:45 wake-up for the dawn session and a 07:45 train, walk through it and keep walking. Only worth sitting down if you abandon the sunrise.</t>
+          <t>Logistics, not a sight — the station transfer is inserted automatically. Listed here because it is the hidden cost that guts this stop: ~25 min each way, which is what turns day 2 into a 25-minute dawn and nothing else.</t>
         </is>
       </c>
     </row>
@@ -41658,20 +41658,20 @@
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Station shuttle / taxi</t>
+          <t>Nanhua Bridge</t>
         </is>
       </c>
       <c r="E16" s="10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>Logistics, not a sight — the station transfer is inserted automatically. Listed here because it is the hidden cost that guts this stop: ~25 min each way, which is what turns day 2 into a 25-minute dawn and nothing else.</t>
+          <t>The best elevated sweep of the stilted houses and the classic dawn frame, but it is ~1 km upriver from the hotel — 12 min each way. A 25-minute pre-departure window cannot reach it and get back. It is the first thing a second night buys you.</t>
         </is>
       </c>
     </row>
@@ -41691,20 +41691,20 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Check in at Jinshuian</t>
+          <t>Shen Congwen Residence</t>
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Logistics, not a sight — the hotel block is inserted automatically. Budgeted at 20 min between the taxi and the 17:05 start of the walk. Booking required.</t>
+          <t>Fenghuang's one real cultural stop, and it is simply not open while you are here: doors ~08:00, your train leaves at 07:45. Not a scheduling choice — a consequence of the one-night stay.</t>
         </is>
       </c>
     </row>
@@ -41733,11 +41733,11 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Nanhua Bridge</t>
+          <t>Miao batik &amp; silver lanes</t>
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>The best elevated sweep of the stilted houses and the classic dawn frame, but it is ~1 km upriver from the hotel — 12 min each way. A 25-minute pre-departure window cannot reach it and get back. It is the first thing a second night buys you.</t>
+          <t>Shops open ~09:00. The only free window is day 1's evening, and that window is spent on the lit river, which is the entire reason to come. Browse whatever is still open as you walk home past Hong Bridge instead of scheduling it.</t>
         </is>
       </c>
     </row>
@@ -41766,11 +41766,11 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Shen Congwen Residence</t>
+          <t>Ginger candy stalls</t>
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
@@ -41779,18 +41779,18 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Fenghuang's one real cultural stop, and it is simply not open while you are here: doors ~08:00, your train leaves at 07:45. Not a scheduling choice — a consequence of the one-night stay.</t>
+          <t>Daytime stalls with the hand-pulling demonstration. Some shops stay open late — pick up a bag in passing on the day 1 walk for the train, but do not give it a slot.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Fenghuang</t>
+          <t>Guilin</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
@@ -41799,11 +41799,11 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Miao batik &amp; silver lanes</t>
+          <t>Reed Flute Cave</t>
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
@@ -41812,31 +41812,31 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>Shops open ~09:00. The only free window is day 1's evening, and that window is spent on the lit river, which is the entire reason to come. Browse whatever is still open as you walk home past Hong Bridge instead of scheduling it.</t>
+          <t>Does not fit and should not be forced. It closes at 18:00 (Apr 1–Oct 31 07:30–18:00) with last guided entry ~30 min before, and it is out of town to the northwest. Even the optimistic line — clear the station 14:50, straight there without checking in, 75 min inside — lands you back downtown around 17:00 having dragged luggage to a cave, and it only works at all from Guilin North (~3.5 km away). If the arrival is actually Guilin West, it is ~20 km further and the maths collapses entirely. The sight's own note already says to skip it in favour of the stronger Silver Cave later in the trip — take that advice. Keep it as a wet-weather substitute only if a later Guilin morning materialises.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Fenghuang</t>
+          <t>Lijiang</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Ginger candy stalls</t>
+          <t>Lashi Lake wetland</t>
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
@@ -41845,14 +41845,14 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Daytime stalls with the hand-pulling demonstration. Some shops stay open late — pick up a bag in passing on the day 1 walk for the train, but do not give it a slot.</t>
+          <t>The only genuine cut. It is a third separate cluster (25–30 min west, the opposite direction from Baisha and Shuhe) and 2.5 h of horse ride plus boat — adding it to day 2 pushes that day past 10 h right before the 06:30 mountain start, and it is the weakest nature stop on a list that already has a 4,680 m glacier and one of the deepest gorges on earth. The horse guides are also the most consistently complained-about hard sell in Lijiang. Swap it in only if the mountain is rained out and day 3 or 4 collapses — it makes a decent gentle half-day paired with the massage.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
@@ -41860,16 +41860,16 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Liu Xiaoqing rice tofu</t>
+          <t>Check in — J Hotel (Tower)</t>
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
@@ -41878,14 +41878,14 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>Did not fit the reworked day</t>
+          <t>Hotel admin — the day 5 evening move from Puxi to Lujiazui, roughly 17:00–18:00.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="B23" s="10" t="n">
@@ -41893,16 +41893,16 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Check in at Waterfall Bay</t>
+          <t>Dinner alt · Donghu Rd</t>
         </is>
       </c>
       <c r="E23" s="10" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
@@ -41911,14 +41911,14 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Logistics, not a sight — the hotel block is inserted automatically. Budget 30 min because it is also where you buy the ¥108 ticket, which is valid 2-3 days and covers the waterfall, Tuwang Palace and every Baishetang performance. Booking required; do not schedule anything else until it is done.</t>
+          <t>Flagged as a dinner alternate, not a stop — use it for day 3's Concession dinner.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Guilin</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
@@ -41926,16 +41926,16 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Reed Flute Cave</t>
+          <t>Dinner alt · Fumin Rd</t>
         </is>
       </c>
       <c r="E24" s="10" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
@@ -41944,31 +41944,31 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>Does not fit and should not be forced. It closes at 18:00 (Apr 1–Oct 31 07:30–18:00) with last guided entry ~30 min before, and it is out of town to the northwest. Even the optimistic line — clear the station 14:50, straight there without checking in, 75 min inside — lands you back downtown around 17:00 having dragged luggage to a cave, and it only works at all from Guilin North (~3.5 km away). If the arrival is actually Guilin West, it is ~20 km further and the maths collapses entirely. The sight's own note already says to skip it in favour of the stronger Silver Cave later in the trip — take that advice. Keep it as a wet-weather substitute only if a later Guilin morning materialises.</t>
+          <t>Second Concession dinner alternate — backup to Donghu Rd on the same evening.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Guilin</t>
+          <t>Yangshuo</t>
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Check in at RongShi</t>
+          <t>Sunrise balloon flight</t>
         </is>
       </c>
       <c r="E25" s="10" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
@@ -41977,31 +41977,31 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Not a sight — logistics, kept out of the stop list per the no-hotels rule. Budget 30 min around 15:40, on the cruise-wharf side of downtown, which is why both real stops are within walking distance of it.</t>
+          <t>The best thing here that does not fit. It is a second dawn (04:00-06:00 pickup) in a stay with room for exactly one, and it collides head-on with Xianggong — same hour, same light, same karst. At ~USD 260-300 pp it is flagged as a big-budget swap, so treat it that way: fly it INSTEAD of Xianggong on day 2 morning if the spend appeals and the forecast is clear, rather than as an addition. Note the current plan had it at 21:20, which is not a thing — balloons only fly at dawn. Weather-dependent either way, and a scrub with no backup dawn left is the real risk.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Lijiang</t>
+          <t>Zhangjiajie</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Lashi Lake wetland</t>
+          <t>Yangjiajie cableway</t>
         </is>
       </c>
       <c r="E26" s="10" t="n">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
@@ -42010,31 +42010,31 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>The only genuine cut. It is a third separate cluster (25–30 min west, the opposite direction from Baisha and Shuhe) and 2.5 h of horse ride plus boat — adding it to day 2 pushes that day past 10 h right before the 06:30 mountain start, and it is the weakest nature stop on a list that already has a 4,680 m glacier and one of the deepest gorges on earth. The horse guides are also the most consistently complained-about hard sell in Lijiang. Swap it in only if the mountain is rained out and day 3 or 4 collapses — it makes a decent gentle half-day paired with the massage.</t>
+          <t>The lift that makes Yangjiajie reachable — cut with the area it serves. Only worth restoring if you add a fifth day or trade away the entire Tianzi/Ten-Mile half of day 2.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Lijiang</t>
+          <t>Zhangjiajie</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Check in at Anyin</t>
+          <t>Yangjiajie</t>
         </is>
       </c>
       <c r="E27" s="10" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
@@ -42043,276 +42043,12 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Hotel logistics rather than a sight, so it is left out of the stop list for the builder to place. Worth protecting the hour though: reach the courtyard around 14:15, drop bags, and sit still for an hour before going out — the first afternoon at 2,400 m is where altitude headaches get made.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Check in at Marriott</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>REMOVE from this day in Notion — keep the page, mark it unscheduled/idea</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>Hotel admin, not a sight — slots itself between the Maglev and Nanjing Rd East on day 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Check in — J Hotel (Tower)</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>REMOVE from this day in Notion — keep the page, mark it unscheduled/idea</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>Hotel admin — the day 5 evening move from Puxi to Lujiazui, roughly 17:00–18:00.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>Dinner alt · Donghu Rd</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>REMOVE from this day in Notion — keep the page, mark it unscheduled/idea</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>Flagged as a dinner alternate, not a stop — use it for day 3's Concession dinner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Dinner alt · Fumin Rd</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>REMOVE from this day in Notion — keep the page, mark it unscheduled/idea</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>Second Concession dinner alternate — backup to Donghu Rd on the same evening.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Yangshuo</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>Sunrise balloon flight</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>120</v>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>REMOVE from this day in Notion — keep the page, mark it unscheduled/idea</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>The best thing here that does not fit. It is a second dawn (04:00-06:00 pickup) in a stay with room for exactly one, and it collides head-on with Xianggong — same hour, same light, same karst. At ~USD 260-300 pp it is flagged as a big-budget swap, so treat it that way: fly it INSTEAD of Xianggong on day 2 morning if the spend appeals and the forecast is clear, rather than as an addition. Note the current plan had it at 21:20, which is not a thing — balloons only fly at dawn. Weather-dependent either way, and a scrub with no backup dawn left is the real risk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Yangshuo</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Fengqi Homestay</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>REMOVE from this day in Notion — keep the page, mark it unscheduled/idea</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>Not a sight — this is the lodging itself (3 nights, check-in on arrival ~14:15 after clearing the wharf at 13:45). Deliberately kept out of the day plans so it does not consume a stop slot; it is simply where each day starts and ends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Zhangjiajie</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Yangjiajie cableway</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>REMOVE from this day in Notion — keep the page, mark it unscheduled/idea</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>The lift that makes Yangjiajie reachable — cut with the area it serves. Only worth restoring if you add a fifth day or trade away the entire Tianzi/Ten-Mile half of day 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Zhangjiajie</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Yangjiajie</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>REMOVE from this day in Notion — keep the page, mark it unscheduled/idea</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
           <t>Genuinely excellent and much quieter than Yuanjiajie — Natural Great Wall and One Step to Heaven — but it sits at the far western end of the plateau. Reaching it costs its own cable car plus roughly an hour of extra shuttle each way, about 4 h of marginal cost against Ten-Mile Gallery's 90 min for zero extra transfer. With one afternoon and two full days it is the correct thing to lose. If you would rather have it than Tianmen, swap the whole of day 3 for it — do not try to squeeze it into day 2.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G35"/>
+  <autoFilter ref="A1:G27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43054,7 +42790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I161"/>
+  <dimension ref="A1:I160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -44320,7 +44056,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Baisha embroidery</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -44361,7 +44097,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Shuhe Old Town</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -44498,14 +44234,14 @@
         </is>
       </c>
       <c r="G35" s="8" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>8.800000000000001</v>
+        <v>26.06</v>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -44525,12 +44261,12 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Glacier Park cable car</t>
+          <t>Jade Dragon summit</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Jade Dragon summit</t>
+          <t>Impression Lijiang</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -44539,10 +44275,10 @@
         </is>
       </c>
       <c r="G36" s="8" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>31.28</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
@@ -44571,7 +44307,7 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Impression Lijiang</t>
+          <t>Blue Moon Valley</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -44580,10 +44316,10 @@
         </is>
       </c>
       <c r="G37" s="8" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>8.869999999999999</v>
+        <v>2.87</v>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
@@ -44607,12 +44343,12 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Impression Lijiang</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Blue Moon Valley</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -44621,10 +44357,10 @@
         </is>
       </c>
       <c r="G38" s="8" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>2.87</v>
+        <v>24.39</v>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
@@ -44639,21 +44375,21 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Depart for the gorge</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -44662,14 +44398,14 @@
         </is>
       </c>
       <c r="G39" s="8" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>24.39</v>
+        <v>4.2</v>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -44689,12 +44425,12 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Depart for the gorge</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Depart for the gorge</t>
+          <t>Qiaotou gateway</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -44703,10 +44439,10 @@
         </is>
       </c>
       <c r="G40" s="8" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>4.2</v>
+        <v>80.2</v>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
@@ -44730,12 +44466,12 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Depart for the gorge</t>
+          <t>Qiaotou gateway</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Qiaotou gateway</t>
+          <t>Tiger Leaping Gorge</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -44744,10 +44480,10 @@
         </is>
       </c>
       <c r="G41" s="8" t="n">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>80.2</v>
+        <v>4.7</v>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
@@ -44771,12 +44507,12 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Qiaotou gateway</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Tiger Leaping Gorge</t>
+          <t>Middle Gorge descent</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -44785,14 +44521,14 @@
         </is>
       </c>
       <c r="G42" s="8" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>4.7</v>
+        <v>16.05</v>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -44812,12 +44548,12 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Middle Gorge descent</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -44826,10 +44562,10 @@
         </is>
       </c>
       <c r="G43" s="8" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>16.05</v>
+        <v>25.44</v>
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
@@ -44844,21 +44580,21 @@
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Black Dragon Pool</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -44867,10 +44603,10 @@
         </is>
       </c>
       <c r="G44" s="8" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>25.44</v>
+        <v>1.79</v>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
@@ -44894,12 +44630,12 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Black Dragon Pool</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Black Dragon Pool</t>
+          <t>Last Dayan loop</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -44935,12 +44671,12 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Black Dragon Pool</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Last Dayan loop</t>
+          <t>Fly from LJG</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -44949,10 +44685,10 @@
         </is>
       </c>
       <c r="G46" s="8" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>1.79</v>
+        <v>21.42</v>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
@@ -44963,11 +44699,11 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Lijiang</t>
+          <t>Chengdu</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
@@ -44976,12 +44712,12 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Fly from LJG</t>
+          <t>Check in at Minyoun Dongda</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -44990,14 +44726,14 @@
         </is>
       </c>
       <c r="G47" s="8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>21.42</v>
+        <v>25.9</v>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -45008,21 +44744,21 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Check in at Minyoun Dongda</t>
+          <t>Chengdu Panda Base</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -45031,10 +44767,10 @@
         </is>
       </c>
       <c r="G48" s="8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>25.9</v>
+        <v>27.8</v>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
@@ -45058,12 +44794,12 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Chengdu Panda Base</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Chengdu Panda Base</t>
+          <t>People’s Park</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -45072,14 +44808,14 @@
         </is>
       </c>
       <c r="G49" s="8" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>27.8</v>
+        <v>11.92</v>
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -45099,28 +44835,28 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Chengdu Panda Base</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>People’s Park</t>
+          <t>Heming Teahouse</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G50" s="8" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>11.92</v>
+        <v>0.3</v>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -45140,24 +44876,24 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Heming Teahouse</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Heming Teahouse</t>
+          <t>Kuanzhai Alleys</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G51" s="8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
@@ -45181,28 +44917,28 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Heming Teahouse</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Kuanzhai Alleys</t>
+          <t>Sichuan opera</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G52" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -45222,24 +44958,24 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Sichuan opera</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Sichuan opera</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G53" s="8" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0.8</v>
+        <v>4.52</v>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
@@ -45254,21 +44990,21 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Sichuan opera</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Sanxingdui Museum</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -45277,10 +45013,10 @@
         </is>
       </c>
       <c r="G54" s="8" t="n">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>4.52</v>
+        <v>48.94</v>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
@@ -45304,12 +45040,12 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Sanxingdui Museum</t>
+          <t>Wuhou Shrine</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -45318,10 +45054,10 @@
         </is>
       </c>
       <c r="G55" s="8" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>48.94</v>
+        <v>41.53</v>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
@@ -45345,28 +45081,28 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Wuhou Shrine</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Wuhou Shrine</t>
+          <t>Jinli Old Street</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G56" s="8" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>41.53</v>
+        <v>0.9</v>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -45386,28 +45122,28 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Wuhou Shrine</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Jinli Old Street</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G57" s="8" t="n">
         <v>13</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0.9</v>
+        <v>3.94</v>
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -45418,48 +45154,48 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Train from Chengdu East</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G58" s="8" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>3.94</v>
+        <v>14.7</v>
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>Chongqing</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
@@ -45468,12 +45204,12 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Arrive Chongqing North</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Train from Chengdu East</t>
+          <t>Check in at KS Kongshang</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -45482,10 +45218,10 @@
         </is>
       </c>
       <c r="G59" s="8" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>14.7</v>
+        <v>8.1</v>
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
@@ -45509,12 +45245,12 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Arrive Chongqing North</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Check in at KS Kongshang</t>
+          <t>Jiefangbei</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -45523,10 +45259,10 @@
         </is>
       </c>
       <c r="G60" s="8" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>8.1</v>
+        <v>1.7</v>
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
@@ -45550,28 +45286,28 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Jiefangbei</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Jiefangbei</t>
+          <t>Raffles Crystal deck</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G61" s="8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -45591,12 +45327,12 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Jiefangbei</t>
+          <t>Raffles Crystal deck</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Raffles Crystal deck</t>
+          <t>Chaotianmen Docks</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -45605,14 +45341,14 @@
         </is>
       </c>
       <c r="G62" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>1.28</v>
+        <v>4.1</v>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -45632,12 +45368,12 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Raffles Crystal deck</t>
+          <t>Chaotianmen Docks</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Chaotianmen Docks</t>
+          <t>Kuixinglou Plaza</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -45646,14 +45382,14 @@
         </is>
       </c>
       <c r="G63" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>4.1</v>
+        <v>1.38</v>
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -45673,28 +45409,28 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Chaotianmen Docks</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Kuixinglou Plaza</t>
+          <t>Qiansimen Bridge</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G64" s="8" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>1.38</v>
+        <v>4.7</v>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -45714,28 +45450,28 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Qiansimen Bridge</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Qiansimen Bridge</t>
+          <t>Hongya Cave</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G65" s="8" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>4.7</v>
+        <v>0.52</v>
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -45746,37 +45482,37 @@
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Qiansimen Bridge</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Hongya Cave</t>
+          <t>Liziba monorail</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G66" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>0.52</v>
+        <v>4.3</v>
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -45796,24 +45532,24 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Liziba monorail</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Liziba monorail</t>
+          <t>Eling Park</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G67" s="8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
@@ -45837,24 +45573,24 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Liziba monorail</t>
+          <t>Eling Park</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Eling Park</t>
+          <t>Testbed 2</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G68" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
@@ -45878,28 +45614,28 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Eling Park</t>
+          <t>Testbed 2</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Testbed 2</t>
+          <t>Baixiang Ju</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G69" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>0.8</v>
+        <v>4.28</v>
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -45919,28 +45655,28 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Testbed 2</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Baixiang Ju</t>
+          <t>Yangtze Cableway</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G70" s="8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>4.28</v>
+        <v>3.5</v>
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -45960,24 +45696,24 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Yangtze Cableway</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Yangtze Cableway</t>
+          <t>Longmenhao Old Street</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G71" s="8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
@@ -46001,12 +45737,12 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Yangtze Cableway</t>
+          <t>Longmenhao Old Street</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Longmenhao Old Street</t>
+          <t>Two Rivers night cruise</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -46015,14 +45751,14 @@
         </is>
       </c>
       <c r="G72" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -46042,24 +45778,24 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Longmenhao Old Street</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Two Rivers night cruise</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G73" s="8" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
@@ -46074,33 +45810,33 @@
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Chongqing North station</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G74" s="8" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>0.96</v>
+        <v>5.39</v>
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
@@ -46111,11 +45847,11 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Zhangjiajie</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
@@ -46124,12 +45860,12 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Chongqing North station</t>
+          <t>Check in at Yuji Hotel</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -46138,10 +45874,10 @@
         </is>
       </c>
       <c r="G75" s="8" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>5.39</v>
+        <v>21.76</v>
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
@@ -46165,12 +45901,12 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Check in at Yuji Hotel</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Check in at Yuji Hotel</t>
+          <t>Wulingyuan East Gate</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -46179,14 +45915,14 @@
         </is>
       </c>
       <c r="G76" s="8" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>21.76</v>
+        <v>1.8</v>
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -46206,12 +45942,12 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Check in at Yuji Hotel</t>
+          <t>Wulingyuan East Gate</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Wulingyuan East Gate</t>
+          <t>Golden Whip Stream</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -46220,10 +45956,10 @@
         </is>
       </c>
       <c r="G77" s="8" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>1.8</v>
+        <v>13.9</v>
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
@@ -46247,12 +45983,12 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Wulingyuan East Gate</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Golden Whip Stream</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -46261,14 +45997,14 @@
         </is>
       </c>
       <c r="G78" s="8" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>13.9</v>
+        <v>10.41</v>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -46279,21 +46015,21 @@
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Bailong Elevator</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
@@ -46302,14 +46038,14 @@
         </is>
       </c>
       <c r="G79" s="8" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>10.41</v>
+        <v>38.8</v>
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -46329,24 +46065,24 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Bailong Elevator</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Bailong Elevator</t>
+          <t>Yuanjiajie (Avatar)</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G80" s="8" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>38.8</v>
+        <v>0.1</v>
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
@@ -46370,28 +46106,28 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Bailong Elevator</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Yuanjiajie (Avatar)</t>
+          <t>Tianzi Mountain</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G81" s="8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>0.1</v>
+        <v>4.25</v>
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -46411,28 +46147,28 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Tianzi Mountain</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Tianzi Mountain</t>
+          <t>Tianzi cableway down</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G82" s="8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>4.25</v>
+        <v>0.7</v>
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -46452,24 +46188,24 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Tianzi Mountain</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Tianzi cableway down</t>
+          <t>Ten-Mile Gallery</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G83" s="8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>0.7</v>
+        <v>11.1</v>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
@@ -46493,12 +46229,12 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Ten-Mile Gallery</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Ten-Mile Gallery</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
@@ -46507,14 +46243,14 @@
         </is>
       </c>
       <c r="G84" s="8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>11.1</v>
+        <v>6.14</v>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -46525,33 +46261,33 @@
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Ten-Mile Gallery</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Bus to Zhangjiajie city</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G85" s="8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>6.14</v>
+        <v>0.93</v>
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
@@ -46575,12 +46311,12 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Bus to Zhangjiajie city</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Bus to Zhangjiajie city</t>
+          <t>Tianmen cableway</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -46589,14 +46325,14 @@
         </is>
       </c>
       <c r="G86" s="8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -46616,24 +46352,24 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Bus to Zhangjiajie city</t>
+          <t>Tianmen cableway</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Tianmen cableway</t>
+          <t>Tianmen Mountain</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G87" s="8" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>0.8</v>
+        <v>27.2</v>
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
@@ -46657,12 +46393,12 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Tianmen cableway</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Tianmen Mountain</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -46671,14 +46407,14 @@
         </is>
       </c>
       <c r="G88" s="8" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>27.2</v>
+        <v>34.04</v>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -46689,21 +46425,21 @@
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Head to the station</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -46712,25 +46448,25 @@
         </is>
       </c>
       <c r="G89" s="8" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>34.04</v>
+        <v>1.9</v>
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>Zhangjiajie</t>
+          <t>Furong (Hibiscus)</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
@@ -46739,12 +46475,12 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Arrive Furongzhen</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Head to the station</t>
+          <t>Check in at Waterfall Bay</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -46753,10 +46489,10 @@
         </is>
       </c>
       <c r="G90" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
@@ -46780,24 +46516,24 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Arrive Furongzhen</t>
+          <t>Check in at Waterfall Bay</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Check in at Waterfall Bay</t>
+          <t>Liu Xiaoqing rice tofu</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G91" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>4.9</v>
+        <v>0.1</v>
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
@@ -46821,12 +46557,12 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Check in at Waterfall Bay</t>
+          <t>Liu Xiaoqing rice tofu</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Liu Xiaoqing rice tofu</t>
+          <t>Wuli Stone Street</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -46862,12 +46598,12 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Liu Xiaoqing rice tofu</t>
+          <t>Wuli Stone Street</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Wuli Stone Street</t>
+          <t>Tuwang Palace</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
@@ -46879,7 +46615,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
@@ -46903,12 +46639,12 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Wuli Stone Street</t>
+          <t>Furong waterfall</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Tuwang Palace</t>
+          <t>Youshui River cruise</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
@@ -46944,12 +46680,12 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Furong waterfall</t>
+          <t>Baishetang Square</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Youshui River cruise</t>
+          <t>Shenpu Camp Square</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
@@ -46985,12 +46721,12 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Baishetang Square</t>
+          <t>Shenpu Camp Square</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Shenpu Camp Square</t>
+          <t>Far-bank platform</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
@@ -47017,48 +46753,48 @@
         </is>
       </c>
       <c r="B97" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Shenpu Camp Square</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Far-bank platform</t>
+          <t>Train from Furongzhen</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G97" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Fenghuang</t>
         </is>
       </c>
       <c r="B98" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
@@ -47067,12 +46803,12 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Fenghuang HSR station</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Train from Furongzhen</t>
+          <t>Check in at Jinshuian</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -47081,14 +46817,14 @@
         </is>
       </c>
       <c r="G98" s="8" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>3.83</v>
+        <v>11.3</v>
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -47108,28 +46844,28 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Fenghuang HSR station</t>
+          <t>Check in at Jinshuian</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Check in at Jinshuian</t>
+          <t>East Gate Tower</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G99" s="8" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>11.3</v>
+        <v>0.43</v>
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -47149,12 +46885,12 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Check in at Jinshuian</t>
+          <t>East Gate Tower</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>East Gate Tower</t>
+          <t>Hong Bridge</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
@@ -47163,14 +46899,14 @@
         </is>
       </c>
       <c r="G100" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -47190,12 +46926,12 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>East Gate Tower</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Hong Bridge</t>
+          <t>Fenghuang Ancient Town</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
@@ -47204,14 +46940,14 @@
         </is>
       </c>
       <c r="G101" s="8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>0.1</v>
+        <v>0.77</v>
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -47231,12 +46967,12 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Fenghuang Ancient Town</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Fenghuang Ancient Town</t>
+          <t>Jumping stones</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
@@ -47245,10 +46981,10 @@
         </is>
       </c>
       <c r="G102" s="8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>0.77</v>
+        <v>0.37</v>
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
@@ -47272,12 +47008,12 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Fenghuang Ancient Town</t>
+          <t>Jumping stones</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Jumping stones</t>
+          <t>Snow Bridge (Xueqiao)</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -47286,10 +47022,10 @@
         </is>
       </c>
       <c r="G103" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
@@ -47313,12 +47049,12 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Jumping stones</t>
+          <t>Tuojiang night boat</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Snow Bridge (Xueqiao)</t>
+          <t>Wanming Pagoda</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
@@ -47327,14 +47063,14 @@
         </is>
       </c>
       <c r="G104" s="8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -47354,12 +47090,12 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Tuojiang night boat</t>
+          <t>Wanming Pagoda</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Wanming Pagoda</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
@@ -47368,14 +47104,14 @@
         </is>
       </c>
       <c r="G105" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -47386,33 +47122,33 @@
         </is>
       </c>
       <c r="B106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Wanming Pagoda</t>
+          <t>Sunrise / mist session</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Train from Gucheng</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G106" s="8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>0.6</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
@@ -47423,11 +47159,11 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>Fenghuang</t>
+          <t>Guilin</t>
         </is>
       </c>
       <c r="B107" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
@@ -47436,12 +47172,12 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Sunrise / mist session</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Train from Gucheng</t>
+          <t>Check in at RongShi</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
@@ -47450,10 +47186,10 @@
         </is>
       </c>
       <c r="G107" s="8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>8.050000000000001</v>
+        <v>6.68</v>
       </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
@@ -47477,24 +47213,24 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Check in at RongShi</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Check in at RongShi</t>
+          <t>Elephant Trunk Hill</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G108" s="8" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>6.68</v>
+        <v>0.23</v>
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
@@ -47518,12 +47254,12 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Check in at RongShi</t>
+          <t>Elephant Trunk Hill</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Elephant Trunk Hill</t>
+          <t>Two Rivers &amp; Four Lakes</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
@@ -47532,10 +47268,10 @@
         </is>
       </c>
       <c r="G109" s="8" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>0.23</v>
+        <v>0.68</v>
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
@@ -47559,12 +47295,12 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Elephant Trunk Hill</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Two Rivers &amp; Four Lakes</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr">
@@ -47573,10 +47309,10 @@
         </is>
       </c>
       <c r="G110" s="8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
@@ -47587,7 +47323,7 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>Guilin</t>
+          <t>Yangshuo</t>
         </is>
       </c>
       <c r="B111" s="8" t="n">
@@ -47595,17 +47331,17 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Fengqi Homestay</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
@@ -47614,10 +47350,10 @@
         </is>
       </c>
       <c r="G111" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
@@ -47641,28 +47377,28 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Fengqi Homestay</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Fengqi Homestay</t>
+          <t>West Street</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G112" s="8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -47682,28 +47418,28 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Fengqi Homestay</t>
+          <t>West Street</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>West Street</t>
+          <t>Li River night walk</t>
         </is>
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G113" s="8" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -47714,33 +47450,33 @@
         </is>
       </c>
       <c r="B114" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>West Street</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Li River night walk</t>
+          <t>Xingping Ancient Town</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G114" s="8" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>0.68</v>
+        <v>3.03</v>
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
@@ -47764,12 +47500,12 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Xingping Ancient Town</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Xingping Ancient Town</t>
+          <t>20-RMB viewpoint</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
@@ -47778,14 +47514,14 @@
         </is>
       </c>
       <c r="G115" s="8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>3.03</v>
+        <v>2.4</v>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -47805,12 +47541,12 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Xingping Ancient Town</t>
+          <t>20-RMB viewpoint</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>20-RMB viewpoint</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -47819,14 +47555,14 @@
         </is>
       </c>
       <c r="G116" s="8" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>2.4</v>
+        <v>17.39</v>
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -47846,12 +47582,12 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>20-RMB viewpoint</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
@@ -47860,10 +47596,10 @@
         </is>
       </c>
       <c r="G117" s="8" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>17.39</v>
+        <v>1.42</v>
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
@@ -47878,21 +47614,21 @@
         </is>
       </c>
       <c r="B118" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Yulong bamboo rafting</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -47901,14 +47637,14 @@
         </is>
       </c>
       <c r="G118" s="8" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>1.42</v>
+        <v>12.1</v>
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -47928,12 +47664,12 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Yulong bamboo rafting</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="F119" s="8" t="inlineStr">
@@ -47942,14 +47678,14 @@
         </is>
       </c>
       <c r="G119" s="8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>12.1</v>
+        <v>6.53</v>
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -47969,12 +47705,12 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Yulong valley cycling</t>
+          <t>Moon Hill</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
@@ -47983,14 +47719,14 @@
         </is>
       </c>
       <c r="G120" s="8" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>6.53</v>
+        <v>10.4</v>
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48010,12 +47746,12 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Moon Hill</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F121" s="8" t="inlineStr">
@@ -48024,14 +47760,14 @@
         </is>
       </c>
       <c r="G121" s="8" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>10.4</v>
+        <v>6.23</v>
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48042,21 +47778,21 @@
         </is>
       </c>
       <c r="B122" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Fly from KWL</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
@@ -48065,25 +47801,25 @@
         </is>
       </c>
       <c r="G122" s="8" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>6.23</v>
+        <v>89.8</v>
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>Yangshuo</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="B123" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
@@ -48092,12 +47828,12 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Fly from KWL</t>
+          <t>Check in at Marriott</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr">
@@ -48106,14 +47842,14 @@
         </is>
       </c>
       <c r="G123" s="8" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>89.8</v>
+        <v>33.89</v>
       </c>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48133,12 +47869,12 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Check in at Marriott</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Check in at Marriott</t>
+          <t>Shanghai Maglev</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
@@ -48147,10 +47883,10 @@
         </is>
       </c>
       <c r="G124" s="8" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>33.89</v>
+        <v>9.23</v>
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
@@ -48174,12 +47910,12 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Check in at Marriott</t>
+          <t>Shanghai Maglev</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Maglev</t>
+          <t>Nanjing Road East</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
@@ -48188,10 +47924,10 @@
         </is>
       </c>
       <c r="G125" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>9.23</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
@@ -48215,28 +47951,28 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Maglev</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Nanjing Road East</t>
+          <t>The Bund</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G126" s="8" t="n">
         <v>19</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>8.449999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48256,28 +47992,28 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>The Bund</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>The Bund</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G127" s="8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>3.5</v>
+        <v>0.34</v>
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48297,24 +48033,24 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>The Bund</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Old Jazz Bar</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G128" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>0.34</v>
+        <v>1.72</v>
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
@@ -48329,21 +48065,21 @@
         </is>
       </c>
       <c r="B129" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>Old Jazz Bar</t>
+          <t>Recovery massage / spa</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>M50 Creative Park</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr">
@@ -48352,10 +48088,10 @@
         </is>
       </c>
       <c r="G129" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>1.72</v>
+        <v>3.34</v>
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
@@ -48379,12 +48115,12 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Recovery massage / spa</t>
+          <t>M50 Creative Park</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>M50 Creative Park</t>
+          <t>Jing’an Temple</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
@@ -48393,10 +48129,10 @@
         </is>
       </c>
       <c r="G130" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
@@ -48420,24 +48156,24 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>M50 Creative Park</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Jing’an Temple</t>
+          <t>Nanjing Road West</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G131" s="8" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H131" s="8" t="n">
-        <v>2.83</v>
+        <v>0.96</v>
       </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
@@ -48461,12 +48197,12 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Nanjing Road West</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Nanjing Road West</t>
+          <t>Zhangyuan</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
@@ -48475,14 +48211,14 @@
         </is>
       </c>
       <c r="G132" s="8" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>0.96</v>
+        <v>0.5</v>
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48502,28 +48238,28 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Nanjing Road West</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Zhangyuan</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G133" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>0.5</v>
+        <v>4.38</v>
       </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48534,37 +48270,37 @@
         </is>
       </c>
       <c r="B134" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Wukang Building</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G134" s="8" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>4.38</v>
+        <v>6.5</v>
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48584,24 +48320,24 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Wukang Building</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Wukang Building</t>
+          <t>Wukang Road</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G135" s="8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
@@ -48625,12 +48361,12 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Wukang Building</t>
+          <t>Wukang Road</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Wukang Road</t>
+          <t>Ferguson Lane</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr">
@@ -48639,10 +48375,10 @@
         </is>
       </c>
       <c r="G136" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
@@ -48666,24 +48402,24 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Wukang Road</t>
+          <t>Ferguson Lane</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Ferguson Lane</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G137" s="8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="I137" s="8" t="inlineStr">
         <is>
@@ -48707,12 +48443,12 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Ferguson Lane</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Anfu Road</t>
+          <t>Wulumuqi Road</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
@@ -48724,7 +48460,7 @@
         <v>14</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
@@ -48748,28 +48484,28 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Anfu Road</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Wulumuqi Road</t>
+          <t>Fuxing Park</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G139" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48789,28 +48525,28 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Fuxing Park</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Fuxing Park</t>
+          <t>Sinan Mansions</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G140" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48830,28 +48566,28 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Fuxing Park</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Sinan Mansions</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G141" s="8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>0.3</v>
+        <v>3.97</v>
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48862,37 +48598,37 @@
         </is>
       </c>
       <c r="B142" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Yu Garden</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G142" s="8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>3.97</v>
+        <v>3.1</v>
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48912,28 +48648,28 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Yu Garden</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G143" s="8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H143" s="8" t="n">
-        <v>3.1</v>
+        <v>0.47</v>
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48953,12 +48689,12 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Mid-Lake Teahouse</t>
+          <t>Yuyuan Bazaar</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
@@ -48967,14 +48703,14 @@
         </is>
       </c>
       <c r="G144" s="8" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48994,12 +48730,12 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Mid-Lake Teahouse</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Yuyuan Bazaar</t>
+          <t>City God Temple</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr">
@@ -49008,14 +48744,14 @@
         </is>
       </c>
       <c r="G145" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -49035,24 +48771,24 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>City God Temple</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>City God Temple</t>
+          <t>People’s Square</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G146" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>0.26</v>
+        <v>1.83</v>
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
@@ -49076,12 +48812,12 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>City God Temple</t>
+          <t>People’s Square</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>People’s Square</t>
+          <t>Huangpu night cruise</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
@@ -49090,10 +48826,10 @@
         </is>
       </c>
       <c r="G147" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H147" s="8" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
@@ -49117,24 +48853,24 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>People’s Square</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Huangpu night cruise</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G148" s="8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>2.45</v>
+        <v>0.77</v>
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
@@ -49149,33 +48885,33 @@
         </is>
       </c>
       <c r="B149" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>TANK Shanghai</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G149" s="8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H149" s="8" t="n">
-        <v>0.77</v>
+        <v>7.16</v>
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
@@ -49199,24 +48935,24 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>TANK Shanghai</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>TANK Shanghai</t>
+          <t>West Bund Museum</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G150" s="8" t="n">
         <v>17</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>7.16</v>
+        <v>0.64</v>
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
@@ -49240,28 +48976,28 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>TANK Shanghai</t>
+          <t>West Bund Museum</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>West Bund Museum</t>
+          <t>West Bund riverside</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G151" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H151" s="8" t="n">
-        <v>0.64</v>
+        <v>1.8</v>
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -49281,28 +49017,28 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>West Bund Museum</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>West Bund riverside</t>
+          <t>Long Museum West Bund</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G152" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H152" s="8" t="n">
-        <v>1.8</v>
+        <v>0.66</v>
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -49322,24 +49058,24 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Long Museum West Bund</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G153" s="8" t="n">
         <v>17</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>0.66</v>
+        <v>6.75</v>
       </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
@@ -49354,21 +49090,21 @@
         </is>
       </c>
       <c r="B154" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Shanghai Museum East</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr">
@@ -49377,10 +49113,10 @@
         </is>
       </c>
       <c r="G154" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H154" s="8" t="n">
-        <v>6.75</v>
+        <v>5.97</v>
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
@@ -49404,12 +49140,12 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Shanghai Museum East</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Museum East</t>
+          <t>Shanghai Tower base</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr">
@@ -49418,10 +49154,10 @@
         </is>
       </c>
       <c r="G155" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H155" s="8" t="n">
-        <v>5.97</v>
+        <v>3.63</v>
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
@@ -49445,24 +49181,24 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Museum East</t>
+          <t>Shanghai Tower base</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Tower base</t>
+          <t>World Financial Center</t>
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G156" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H156" s="8" t="n">
-        <v>3.63</v>
+        <v>0.17</v>
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
@@ -49486,12 +49222,12 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Tower base</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>World Financial Center</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr">
@@ -49503,11 +49239,11 @@
         <v>8</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>0.17</v>
+        <v>0.6</v>
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -49527,12 +49263,12 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Jin Mao Tower</t>
+          <t>Oriental Pearl Tower</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr">
@@ -49541,14 +49277,14 @@
         </is>
       </c>
       <c r="G158" s="8" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H158" s="8" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -49568,12 +49304,12 @@
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>Jin Mao Tower</t>
+          <t>Oriental Pearl Tower</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Oriental Pearl Tower</t>
+          <t>Pudong promenade</t>
         </is>
       </c>
       <c r="F159" s="8" t="inlineStr">
@@ -49582,14 +49318,14 @@
         </is>
       </c>
       <c r="G159" s="8" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H159" s="8" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -49609,74 +49345,33 @@
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Oriental Pearl Tower</t>
+          <t>Pudong promenade</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Pudong promenade</t>
+          <t>Fly from PVG</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G160" s="8" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="H160" s="8" t="n">
-        <v>0</v>
+        <v>31.45</v>
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="8" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="B161" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C161" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D161" s="8" t="inlineStr">
-        <is>
-          <t>Pudong promenade</t>
-        </is>
-      </c>
-      <c r="E161" s="8" t="inlineStr">
-        <is>
-          <t>Fly from PVG</t>
-        </is>
-      </c>
-      <c r="F161" s="8" t="inlineStr">
-        <is>
-          <t>didi</t>
-        </is>
-      </c>
-      <c r="G161" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="H161" s="8" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="I161" s="8" t="inlineStr">
-        <is>
           <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I161"/>
+  <autoFilter ref="A1:I160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/china-notion-sync.xlsx
+++ b/china-notion-sync.xlsx
@@ -8393,23 +8393,23 @@
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>Kuixinglou Plaza</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L87" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M87" s="6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="N87" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O87" s="6" t="n">
@@ -8458,46 +8458,46 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
           <t>Kuixinglou Plaza</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>18:37</t>
-        </is>
-      </c>
-      <c r="I88" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J88" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L88" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M88" s="6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="N88" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O88" s="6" t="n">
@@ -8505,20 +8505,20 @@
       </c>
       <c r="P88" s="6" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="Q88" s="6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:12 → 18:07; ORDER 80 → 70</t>
+          <t>RETIME 18:33 → 17:58</t>
         </is>
       </c>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>Meet Chongqing describes a small free square experienced by crossing one elevated walkway, roughly 30min to an hour with no ticket or lift queue.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T88" s="6" t="inlineStr">
@@ -8546,17 +8546,17 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Kuixinglou Plaza</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="I89" s="6" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -8593,20 +8593,20 @@
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="Q89" s="6" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:33 → 18:45; ORDER 70 → 80</t>
+          <t>RETIME 20:12 → 19:45</t>
         </is>
       </c>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Meet Chongqing describes a small free square experienced by crossing one elevated walkway, roughly 30min to an hour with no ticket or lift queue.</t>
         </is>
       </c>
       <c r="T89" s="6" t="inlineStr">
@@ -8737,11 +8737,11 @@
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="I91" s="6" t="n">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -8777,12 +8777,12 @@
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>RETIME 00:11 → 21:37; ORDER 110 → 100</t>
+          <t>RETIME 00:11 → 21:37; DURATION 105m → 83m; ORDER 110 → 100</t>
         </is>
       </c>
       <c r="S91" s="7" t="inlineStr">
         <is>
-          <t>Guides put a full walk-through at 2-3h across 11 levels with the 19:30-22:00 window the most crowded and lift queues of 30-45min (stairs advised); trimmed because the bridge and riverbank photo stops are separate.</t>
+          <t>CUT SHORT BY CLOSING TIME: closes 23:00, last entry 22:30; 22 min less than the 105 min advice. Guides put a full walk-through at 2-3h across 11 levels with the 19:30-22:00 window the most crowded and lift queues of 30-45min (stairs advised); trimmed because the bridge and riverbank photo stops are separate.</t>
         </is>
       </c>
       <c r="T91" s="6" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I92" s="6" t="n">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="R92" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 07:30 → 08:00</t>
         </is>
       </c>
       <c r="S92" s="7" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I93" s="6" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:43 → 08:03</t>
+          <t>RETIME 08:43 → 09:03</t>
         </is>
       </c>
       <c r="S93" s="7" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I94" s="6" t="n">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:01 → 08:51</t>
+          <t>RETIME 10:01 → 09:51</t>
         </is>
       </c>
       <c r="S94" s="7" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="I95" s="6" t="n">
@@ -9097,23 +9097,23 @@
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>Baixiang Ju</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L95" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M95" s="6" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N95" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>RETIME 11:23 → 10:28</t>
+          <t>RETIME 11:23 → 11:28</t>
         </is>
       </c>
       <c r="S95" s="7" t="inlineStr">
@@ -9162,46 +9162,46 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
           <t>Baixiang Ju</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="I96" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J96" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L96" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N96" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
@@ -9209,20 +9209,20 @@
       </c>
       <c r="P96" s="6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q96" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:20 → 12:19; ORDER 60 → 50</t>
+          <t>RETIME 14:10 → 13:06</t>
         </is>
       </c>
       <c r="S96" s="7" t="inlineStr">
         <is>
-          <t>Guides report most visitors spend 40min to 1.5h, with the main corridors and the three street-level exits coverable in about 20min.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T96" s="6" t="inlineStr">
@@ -9250,26 +9250,26 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Baixiang Ju</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I97" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -9297,20 +9297,20 @@
       </c>
       <c r="P97" s="6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="Q97" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:10 → 13:12; ORDER 50 → 60</t>
+          <t>RETIME 15:20 → 14:27</t>
         </is>
       </c>
       <c r="S97" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Guides report most visitors spend 40min to 1.5h, with the main corridors and the three street-level exits coverable in about 20min.</t>
         </is>
       </c>
       <c r="T97" s="6" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I98" s="6" t="n">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:17 → 14:39</t>
+          <t>RETIME 17:17 → 15:39</t>
         </is>
       </c>
       <c r="S98" s="7" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I99" s="6" t="n">
@@ -9449,23 +9449,23 @@
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>Two Rivers night cruise</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L99" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M99" s="6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N99" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:21 → 15:58</t>
+          <t>RETIME 18:21 → 16:58</t>
         </is>
       </c>
       <c r="S99" s="7" t="inlineStr">
@@ -9514,46 +9514,46 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
           <t>Two Rivers night cruise</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="I100" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="J100" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L100" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M100" s="6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N100" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O100" s="6" t="n">
@@ -9561,25 +9561,25 @@
       </c>
       <c r="P100" s="6" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="Q100" s="6" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:49 → 17:29; ORDER 100 → 90</t>
+          <t>RETIME 20:03 → 18:21</t>
         </is>
       </c>
       <c r="S100" s="7" t="inlineStr">
         <is>
-          <t>Operators state a fixed 45-50min sailing over the 16-20km loop, and Chinese booking guides advise arriving 30min before departure for ticket check and seating.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T100" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -9602,26 +9602,26 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Two Rivers night cruise</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I101" s="6" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
@@ -9649,25 +9649,25 @@
       </c>
       <c r="P101" s="6" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="Q101" s="6" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:03 → 18:52; ORDER 90 → 100</t>
+          <t>RETIME 21:49 → 20:07</t>
         </is>
       </c>
       <c r="S101" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Operators state a fixed 45-50min sailing over the 16-20km loop, and Chinese booking guides advise arriving 30min before departure for ticket check and seating.</t>
         </is>
       </c>
       <c r="T101" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -9700,12 +9700,12 @@
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="I102" s="6" t="n">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>RETIME 05:30 → 07:00</t>
+          <t>RETIME 05:30 → 06:30</t>
         </is>
       </c>
       <c r="S102" s="7" t="inlineStr">
@@ -28512,23 +28512,23 @@
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>Kuixinglou Plaza</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L95" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M95" s="6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="N95" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
@@ -28577,46 +28577,46 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
           <t>Kuixinglou Plaza</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>18:37</t>
-        </is>
-      </c>
-      <c r="I96" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J96" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L96" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="N96" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
@@ -28624,20 +28624,20 @@
       </c>
       <c r="P96" s="6" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="Q96" s="6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:12 → 18:07; ORDER 80 → 70</t>
+          <t>RETIME 18:33 → 17:58</t>
         </is>
       </c>
       <c r="S96" s="7" t="inlineStr">
         <is>
-          <t>Meet Chongqing describes a small free square experienced by crossing one elevated walkway, roughly 30min to an hour with no ticket or lift queue.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T96" s="6" t="inlineStr">
@@ -28665,17 +28665,17 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Kuixinglou Plaza</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
@@ -28684,7 +28684,7 @@
         </is>
       </c>
       <c r="I97" s="6" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -28712,20 +28712,20 @@
       </c>
       <c r="P97" s="6" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="Q97" s="6" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:33 → 18:45; ORDER 70 → 80</t>
+          <t>RETIME 20:12 → 19:45</t>
         </is>
       </c>
       <c r="S97" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Meet Chongqing describes a small free square experienced by crossing one elevated walkway, roughly 30min to an hour with no ticket or lift queue.</t>
         </is>
       </c>
       <c r="T97" s="6" t="inlineStr">
@@ -28856,11 +28856,11 @@
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="I99" s="6" t="n">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -28896,12 +28896,12 @@
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>RETIME 00:11 → 21:37; ORDER 110 → 100</t>
+          <t>RETIME 00:11 → 21:37; DURATION 105m → 83m; ORDER 110 → 100</t>
         </is>
       </c>
       <c r="S99" s="7" t="inlineStr">
         <is>
-          <t>Guides put a full walk-through at 2-3h across 11 levels with the 19:30-22:00 window the most crowded and lift queues of 30-45min (stairs advised); trimmed because the bridge and riverbank photo stops are separate.</t>
+          <t>CUT SHORT BY CLOSING TIME: closes 23:00, last entry 22:30; 22 min less than the 105 min advice. Guides put a full walk-through at 2-3h across 11 levels with the 19:30-22:00 window the most crowded and lift queues of 30-45min (stairs advised); trimmed because the bridge and riverbank photo stops are separate.</t>
         </is>
       </c>
       <c r="T99" s="6" t="inlineStr">
@@ -28939,12 +28939,12 @@
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I100" s="6" t="n">
@@ -28984,7 +28984,7 @@
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 07:30 → 08:00</t>
         </is>
       </c>
       <c r="S100" s="7" t="inlineStr">
@@ -29027,12 +29027,12 @@
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I101" s="6" t="n">
@@ -29072,7 +29072,7 @@
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:43 → 08:03</t>
+          <t>RETIME 08:43 → 09:03</t>
         </is>
       </c>
       <c r="S101" s="7" t="inlineStr">
@@ -29115,12 +29115,12 @@
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I102" s="6" t="n">
@@ -29160,7 +29160,7 @@
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:01 → 08:51</t>
+          <t>RETIME 10:01 → 09:51</t>
         </is>
       </c>
       <c r="S102" s="7" t="inlineStr">
@@ -29203,12 +29203,12 @@
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="I103" s="6" t="n">
@@ -29216,23 +29216,23 @@
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>Baixiang Ju</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L103" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M103" s="6" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N103" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O103" s="6" t="n">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>RETIME 11:23 → 10:28</t>
+          <t>RETIME 11:23 → 11:28</t>
         </is>
       </c>
       <c r="S103" s="7" t="inlineStr">
@@ -29281,46 +29281,46 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
           <t>Baixiang Ju</t>
         </is>
       </c>
-      <c r="F104" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="H104" s="6" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="I104" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J104" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L104" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M104" s="6" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N104" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
@@ -29328,20 +29328,20 @@
       </c>
       <c r="P104" s="6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q104" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:20 → 12:19; ORDER 60 → 50</t>
+          <t>RETIME 14:10 → 13:06</t>
         </is>
       </c>
       <c r="S104" s="7" t="inlineStr">
         <is>
-          <t>Guides report most visitors spend 40min to 1.5h, with the main corridors and the three street-level exits coverable in about 20min.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T104" s="6" t="inlineStr">
@@ -29369,26 +29369,26 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Baixiang Ju</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I105" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
@@ -29416,20 +29416,20 @@
       </c>
       <c r="P105" s="6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="Q105" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:10 → 13:12; ORDER 50 → 60</t>
+          <t>RETIME 15:20 → 14:27</t>
         </is>
       </c>
       <c r="S105" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Guides report most visitors spend 40min to 1.5h, with the main corridors and the three street-level exits coverable in about 20min.</t>
         </is>
       </c>
       <c r="T105" s="6" t="inlineStr">
@@ -29467,12 +29467,12 @@
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I106" s="6" t="n">
@@ -29512,7 +29512,7 @@
       </c>
       <c r="R106" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:17 → 14:39</t>
+          <t>RETIME 17:17 → 15:39</t>
         </is>
       </c>
       <c r="S106" s="7" t="inlineStr">
@@ -29555,12 +29555,12 @@
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I107" s="6" t="n">
@@ -29568,23 +29568,23 @@
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>Two Rivers night cruise</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L107" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M107" s="6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N107" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O107" s="6" t="n">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:21 → 15:58</t>
+          <t>RETIME 18:21 → 16:58</t>
         </is>
       </c>
       <c r="S107" s="7" t="inlineStr">
@@ -29633,46 +29633,46 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
           <t>Two Rivers night cruise</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="inlineStr">
-        <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="I108" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="J108" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L108" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N108" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O108" s="6" t="n">
@@ -29680,25 +29680,25 @@
       </c>
       <c r="P108" s="6" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="Q108" s="6" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:49 → 17:29; ORDER 100 → 90</t>
+          <t>RETIME 20:03 → 18:21</t>
         </is>
       </c>
       <c r="S108" s="7" t="inlineStr">
         <is>
-          <t>Operators state a fixed 45-50min sailing over the 16-20km loop, and Chinese booking guides advise arriving 30min before departure for ticket check and seating.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T108" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -29721,26 +29721,26 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Two Rivers night cruise</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I109" s="6" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
@@ -29768,25 +29768,25 @@
       </c>
       <c r="P109" s="6" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="Q109" s="6" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:03 → 18:52; ORDER 90 → 100</t>
+          <t>RETIME 21:49 → 20:07</t>
         </is>
       </c>
       <c r="S109" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Operators state a fixed 45-50min sailing over the 16-20km loop, and Chinese booking guides advise arriving 30min before departure for ticket check and seating.</t>
         </is>
       </c>
       <c r="T109" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -29819,12 +29819,12 @@
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="I110" s="6" t="n">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>RETIME 05:30 → 07:00</t>
+          <t>RETIME 05:30 → 06:30</t>
         </is>
       </c>
       <c r="S110" s="7" t="inlineStr">
@@ -45240,7 +45240,7 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Chaotianmen Docks</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -45281,7 +45281,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Kuixinglou Plaza</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -45486,7 +45486,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Testbed 2</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -45527,7 +45527,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Baixiang Ju</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -45609,7 +45609,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Longmenhao Old Street</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -45650,7 +45650,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Two Rivers night cruise</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">

--- a/china-notion-sync.xlsx
+++ b/china-notion-sync.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Schedule'!$A$1:$T$240</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ideas (parked)'!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Moves'!$A$1:$F$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Legs'!$A$1:$I$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Legs'!$A$1:$I$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1634,18 +1634,18 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L10" s="6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>3.5</v>
+        <v>2.17</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I11" s="6" t="n">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:42 → 07:32</t>
+          <t>RETIME 08:42 → 07:23</t>
         </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I12" s="6" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:36 → 09:11</t>
+          <t>RETIME 10:36 → 09:02</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="I13" s="6" t="n">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:26 → 12:49</t>
+          <t>RETIME 12:26 → 12:40</t>
         </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
@@ -1968,36 +1968,36 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I14" s="6" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Jingshan Park</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:08 → 14:06; DURATION 180m → 174m; ORDER 60 → 50</t>
+          <t>RETIME 15:08 → 13:57; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>CUT SHORT BY CLOSING TIME: closes 17:00, last entry 16:00; 6 min less than the 180 min advice. TripAdvisor reviewers and museum guides say most people spend 2-3h and enthusiasts 4-6h, with the Ancient China galleries alone quoted at 2-3h; add the passport/security check on entry.</t>
+          <t>TripAdvisor reviewers and museum guides say most people spend 2-3h and enthusiasts 4-6h, with the Ancient China galleries alone quoted at 2-3h; add the passport/security check on entry.</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -2046,46 +2046,46 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
+          <t>Jingshan Park</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Jingshan Park</t>
-        </is>
-      </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -2093,20 +2093,20 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:04 → 17:08; ORDER 70 → 60</t>
+          <t>RETIME 13:40 → 17:25; ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Trip.com and TripAdvisor reports give a 5-15 min climb each way (about 150 steps) and an average visit around 30 min, stretching to 2h only for dedicated photographers.</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -2134,26 +2134,26 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Jingshan Park</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I16" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -2181,20 +2181,20 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:40 → 19:06; ORDER 50 → 70</t>
+          <t>RETIME 18:04 → 18:18</t>
         </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>Trip.com and TripAdvisor reports give a 5-15 min climb each way (about 150 steps) and an average visit around 30 min, stretching to 2h only for dedicated photographers.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -2254,14 +2254,14 @@
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>74.90000000000001</v>
+        <v>58.69</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O17" s="6" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="I18" s="6" t="n">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Toboggan down</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L18" s="6" t="n">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O18" s="6" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>RETIME 09:45 → 09:05</t>
+          <t>RETIME 09:45 → 09:18</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
@@ -2398,35 +2398,35 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
           <t>Toboggan down</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
@@ -2445,20 +2445,20 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:16 → 11:58; ORDER 40 → 30</t>
+          <t>RETIME 12:41 → 12:11</t>
         </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>Rider reports and operator guides put the descent itself at 5-10 min depending on braking; the rest is the walk to the launch platform, the safety briefing and the summer queue.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Toboggan down</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="I20" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -2533,20 +2533,20 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:41 → 12:26; ORDER 30 → 40</t>
+          <t>RETIME 14:16 → 13:19</t>
         </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Rider reports and operator guides put the descent itself at 5-10 min depending on braking; the rest is the walk to the launch platform, the safety briefing and the summer queue.</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I21" s="6" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:51 → 15:05</t>
+          <t>RETIME 16:51 → 15:18</t>
         </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I22" s="6" t="n">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:50 → 17:43</t>
+          <t>RETIME 18:50 → 17:56</t>
         </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="I23" s="6" t="n">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:33 → 19:31</t>
+          <t>RETIME 20:33 → 19:44</t>
         </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
@@ -2870,14 +2870,14 @@
         </is>
       </c>
       <c r="L24" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>23.6</v>
+        <v>15.32</v>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I25" s="6" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>RETIME 09:01 → 08:21</t>
+          <t>RETIME 09:01 → 08:13</t>
         </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I26" s="6" t="n">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 11:59</t>
+          <t>RETIME 12:00 → 11:51</t>
         </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="I27" s="6" t="n">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:09 → 13:43</t>
+          <t>RETIME 13:09 → 13:35</t>
         </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I28" s="6" t="n">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:25 → 16:29</t>
+          <t>RETIME 15:25 → 16:21</t>
         </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
@@ -4014,14 +4014,14 @@
         </is>
       </c>
       <c r="L37" s="6" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>11.9</v>
+        <v>9.17</v>
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I38" s="6" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 08:50 → 09:10</t>
+          <t>MOVE day 4 → 2; RETIME 08:50 → 09:03</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I39" s="6" t="n">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 10:17 → 10:37</t>
+          <t>MOVE day 4 → 2; RETIME 10:17 → 10:30</t>
         </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I40" s="6" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 12:26 → 11:26</t>
+          <t>MOVE day 4 → 2; RETIME 12:26 → 11:19</t>
         </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I41" s="6" t="n">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:31 → 12:04</t>
+          <t>RETIME 14:31 → 11:57</t>
         </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="I42" s="6" t="n">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 14:47 → 13:25; ORDER 50 → 60</t>
+          <t>MOVE day 4 → 2; RETIME 14:47 → 13:18; ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I43" s="6" t="n">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 17:26 → 15:46</t>
+          <t>MOVE day 4 → 2; RETIME 17:26 → 15:39</t>
         </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
@@ -4809,7 +4809,7 @@
         <v>46</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>26.06</v>
+        <v>26.28</v>
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
@@ -5418,18 +5418,18 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>4.2</v>
+        <v>0.93</v>
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I54" s="6" t="n">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 4; RETIME 08:40 → 08:00</t>
+          <t>MOVE day 2 → 4; RETIME 08:40 → 08:05</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I55" s="6" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 4; RETIME 10:58 → 10:03</t>
+          <t>MOVE day 2 → 4; RETIME 10:58 → 10:08</t>
         </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="I56" s="6" t="n">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 4; RETIME 11:59 → 10:49</t>
+          <t>MOVE day 2 → 4; RETIME 11:59 → 10:54</t>
         </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I57" s="6" t="n">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:17 → 12:57; ORDER 60 → 50</t>
+          <t>RETIME 16:17 → 13:02; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I58" s="6" t="n">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 4; RETIME 15:48 → 14:36</t>
+          <t>MOVE day 2 → 4; RETIME 15:48 → 14:41</t>
         </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
@@ -6730,14 +6730,14 @@
         </is>
       </c>
       <c r="L68" s="6" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>27.8</v>
+        <v>10.85</v>
       </c>
       <c r="N68" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O68" s="6" t="n">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I69" s="6" t="n">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>RETIME 09:02 → 08:22</t>
+          <t>RETIME 09:02 → 08:06</t>
         </is>
       </c>
       <c r="S69" s="7" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I70" s="6" t="n">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:53 → 12:24; ORDER 50 → 30</t>
+          <t>RETIME 15:53 → 12:08; ORDER 50 → 30</t>
         </is>
       </c>
       <c r="S70" s="7" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="I71" s="6" t="n">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 13:17; ORDER 30 → 40</t>
+          <t>RETIME 12:00 → 13:01; ORDER 30 → 40</t>
         </is>
       </c>
       <c r="S71" s="7" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I72" s="6" t="n">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:06 → 14:30; ORDER 60 → 50</t>
+          <t>RETIME 18:06 → 14:14; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S72" s="7" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I73" s="6" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:29 → 16:23; ORDER 70 → 60</t>
+          <t>RETIME 19:29 → 16:07; ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S73" s="7" t="inlineStr">
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="L76" s="6" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>48.94</v>
+        <v>40.16</v>
       </c>
       <c r="N76" s="6" t="inlineStr">
         <is>
@@ -7500,12 +7500,12 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I77" s="6" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="R77" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:30 → 09:03; ORDER 40 → 20</t>
+          <t>RETIME 12:30 → 08:50; ORDER 40 → 20</t>
         </is>
       </c>
       <c r="S77" s="7" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="I78" s="6" t="n">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:23 → 12:41; ORDER 50 → 30</t>
+          <t>RETIME 16:23 → 12:28; ORDER 50 → 30</t>
         </is>
       </c>
       <c r="S78" s="7" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I79" s="6" t="n">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:48 → 14:58; ORDER 70 → 40</t>
+          <t>RETIME 19:48 → 14:45; ORDER 70 → 40</t>
         </is>
       </c>
       <c r="S79" s="7" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I80" s="6" t="n">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:39 → 17:19; ORDER 80 → 50</t>
+          <t>RETIME 21:39 → 17:06; ORDER 80 → 50</t>
         </is>
       </c>
       <c r="S80" s="7" t="inlineStr">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I81" s="6" t="n">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>RETIME 23:53 → 18:57; ORDER 90 → 60</t>
+          <t>RETIME 23:53 → 18:44; ORDER 90 → 60</t>
         </is>
       </c>
       <c r="S81" s="7" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="I82" s="6" t="n">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 1 → 3; RETIME 00:17 → 20:46; ORDER 40 → 70</t>
+          <t>MOVE day 1 → 3; RETIME 00:17 → 20:33; ORDER 40 → 70</t>
         </is>
       </c>
       <c r="S82" s="7" t="inlineStr">
@@ -8838,18 +8838,18 @@
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>4.3</v>
+        <v>4.14</v>
       </c>
       <c r="N92" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I93" s="6" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:43 → 09:03</t>
+          <t>RETIME 08:43 → 08:56</t>
         </is>
       </c>
       <c r="S93" s="7" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I94" s="6" t="n">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:01 → 09:51</t>
+          <t>RETIME 10:01 → 09:44</t>
         </is>
       </c>
       <c r="S94" s="7" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I95" s="6" t="n">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>RETIME 11:23 → 11:28</t>
+          <t>RETIME 11:23 → 11:21</t>
         </is>
       </c>
       <c r="S95" s="7" t="inlineStr">
@@ -9172,12 +9172,12 @@
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="I96" s="6" t="n">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:10 → 13:06</t>
+          <t>RETIME 14:10 → 12:59</t>
         </is>
       </c>
       <c r="S96" s="7" t="inlineStr">
@@ -9260,12 +9260,12 @@
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="I97" s="6" t="n">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:20 → 14:27</t>
+          <t>RETIME 15:20 → 14:20</t>
         </is>
       </c>
       <c r="S97" s="7" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I98" s="6" t="n">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:17 → 15:39</t>
+          <t>RETIME 17:17 → 15:32</t>
         </is>
       </c>
       <c r="S98" s="7" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I99" s="6" t="n">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:21 → 16:58</t>
+          <t>RETIME 18:21 → 16:51</t>
         </is>
       </c>
       <c r="S99" s="7" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I100" s="6" t="n">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:03 → 18:21</t>
+          <t>RETIME 20:03 → 18:14</t>
         </is>
       </c>
       <c r="S100" s="7" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I101" s="6" t="n">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:49 → 20:07</t>
+          <t>RETIME 21:49 → 20:00</t>
         </is>
       </c>
       <c r="S101" s="7" t="inlineStr">
@@ -10145,11 +10145,11 @@
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I107" s="6" t="n">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:00 → 16:57</t>
+          <t>RETIME 18:00 → 16:57; DURATION 165m → 123m</t>
         </is>
       </c>
       <c r="S107" s="7" t="inlineStr">
         <is>
-          <t>Trail guides and trip reports put the full 7.5 km flat walk at 2.5-3 h at a relaxed pace with photo stops (some quote 3-4 h).</t>
+          <t>CUT SHORT BY CLOSING TIME: closes 19:00, last entry 17:30; 42 min less than the 165 min advice. Trail guides and trip reports put the full 7.5 km flat walk at 2.5-3 h at a relaxed pace with photo stops (some quote 3-4 h).</t>
         </is>
       </c>
       <c r="T107" s="6" t="inlineStr">
@@ -10228,12 +10228,12 @@
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I108" s="6" t="n">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:21 → 19:50</t>
+          <t>RETIME 20:21 → 19:08</t>
         </is>
       </c>
       <c r="S108" s="7" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="I109" s="6" t="n">
@@ -10338,14 +10338,14 @@
         </is>
       </c>
       <c r="L109" s="6" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="M109" s="6" t="n">
-        <v>38.8</v>
+        <v>7.45</v>
       </c>
       <c r="N109" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O109" s="6" t="n">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 07:30 → 06:30</t>
         </is>
       </c>
       <c r="S109" s="7" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I110" s="6" t="n">
@@ -10422,18 +10422,18 @@
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L110" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M110" s="6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N110" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O110" s="6" t="n">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>RETIME 09:17 → 08:37</t>
+          <t>RETIME 09:17 → 07:31</t>
         </is>
       </c>
       <c r="S110" s="7" t="inlineStr">
@@ -10492,12 +10492,12 @@
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I111" s="6" t="n">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="R111" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:12 → 09:47</t>
+          <t>RETIME 10:12 → 08:39</t>
         </is>
       </c>
       <c r="S111" s="7" t="inlineStr">
@@ -10580,12 +10580,12 @@
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I112" s="6" t="n">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:58 → 12:55</t>
+          <t>RETIME 12:58 → 11:47</t>
         </is>
       </c>
       <c r="S112" s="7" t="inlineStr">
@@ -10668,12 +10668,12 @@
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I113" s="6" t="n">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="R113" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:08 → 14:16</t>
+          <t>RETIME 14:08 → 13:08</t>
         </is>
       </c>
       <c r="S113" s="7" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I114" s="6" t="n">
@@ -10769,23 +10769,23 @@
       </c>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Ten-Mile Gallery</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L114" s="6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M114" s="6" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="N114" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O114" s="6" t="n">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="R114" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:33 → 17:11</t>
+          <t>RETIME 16:33 → 16:03</t>
         </is>
       </c>
       <c r="S114" s="7" t="inlineStr">
@@ -10834,22 +10834,22 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Ten-Mile Gallery</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I115" s="6" t="n">
@@ -10857,23 +10857,23 @@
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>Ten-Mile Gallery</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L115" s="6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M115" s="6" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="N115" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O115" s="6" t="n">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="P115" s="6" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="Q115" s="6" t="n">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:57 → 18:19; ORDER 80 → 70</t>
+          <t>RETIME 17:48 → 17:33</t>
         </is>
       </c>
       <c r="S115" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Official guidance is ~1 h for the 2 km gallery; tram is 10-15 min each way and the walk-out ~40 min, so tram queue plus walk lands near 1.5 h in August.</t>
         </is>
       </c>
       <c r="T115" s="6" t="inlineStr">
@@ -10922,22 +10922,22 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Ten-Mile Gallery</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I116" s="6" t="n">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="P116" s="6" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="Q116" s="6" t="n">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:48 → 20:19; ORDER 70 → 80</t>
+          <t>RETIME 19:57 → 19:11</t>
         </is>
       </c>
       <c r="S116" s="7" t="inlineStr">
         <is>
-          <t>Official guidance is ~1 h for the 2 km gallery; tram is 10-15 min each way and the walk-out ~40 min, so tram queue plus walk lands near 1.5 h in August.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T116" s="6" t="inlineStr">
@@ -11038,14 +11038,14 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L117" s="6" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="M117" s="6" t="n">
-        <v>0.93</v>
+        <v>27.77</v>
       </c>
       <c r="N117" s="6" t="inlineStr">
         <is>
@@ -11108,12 +11108,12 @@
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I118" s="6" t="n">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:47 → 08:05; ORDER 50 → 20</t>
+          <t>RETIME 14:47 → 08:31; ORDER 50 → 20</t>
         </is>
       </c>
       <c r="S118" s="7" t="inlineStr">
@@ -11196,12 +11196,12 @@
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I119" s="6" t="n">
@@ -11214,18 +11214,18 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L119" s="6" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M119" s="6" t="n">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="N119" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:52 → 08:55; ORDER 60 → 30</t>
+          <t>RETIME 15:52 → 09:21; ORDER 60 → 30</t>
         </is>
       </c>
       <c r="S119" s="7" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I120" s="6" t="n">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:36 → 11:09; ORDER 70 → 40</t>
+          <t>RETIME 17:36 → 10:44; ORDER 70 → 40</t>
         </is>
       </c>
       <c r="S120" s="7" t="inlineStr">
@@ -11372,12 +11372,12 @@
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I121" s="6" t="n">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:35 → 15:32; ORDER 40 → 50</t>
+          <t>RETIME 13:35 → 15:07; ORDER 40 → 50</t>
         </is>
       </c>
       <c r="S121" s="7" t="inlineStr">
@@ -15150,14 +15150,14 @@
         </is>
       </c>
       <c r="L164" s="6" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M164" s="6" t="n">
-        <v>12.1</v>
+        <v>6.53</v>
       </c>
       <c r="N164" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O164" s="6" t="n">
@@ -15216,12 +15216,12 @@
       </c>
       <c r="G165" s="6" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="H165" s="6" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="I165" s="6" t="n">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="R165" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 08:55 → 08:05; ORDER 30 → 20</t>
+          <t>MOVE day 2 → 3; RETIME 08:55 → 07:59; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S165" s="7" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I166" s="6" t="n">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="R166" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 13:28 → 09:59; ORDER 50 → 30</t>
+          <t>MOVE day 2 → 3; RETIME 13:28 → 09:53; ORDER 50 → 30</t>
         </is>
       </c>
       <c r="S166" s="7" t="inlineStr">
@@ -15392,12 +15392,12 @@
       </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I167" s="6" t="n">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="R167" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 12:37</t>
+          <t>RETIME 12:00 → 12:31</t>
         </is>
       </c>
       <c r="S167" s="7" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="G168" s="6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I168" s="6" t="n">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="R168" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 16:01 → 14:10; ORDER 60 → 50</t>
+          <t>MOVE day 2 → 3; RETIME 16:01 → 14:04; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S168" s="7" t="inlineStr">
@@ -16466,18 +16466,18 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L179" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M179" s="6" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="N179" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O179" s="6" t="n">
@@ -16536,12 +16536,12 @@
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="H180" s="6" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I180" s="6" t="n">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="R180" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:28 → 07:43; ORDER 30 → 20</t>
+          <t>RETIME 13:28 → 07:54; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S180" s="7" t="inlineStr">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="G181" s="6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I181" s="6" t="n">
@@ -16669,7 +16669,7 @@
       </c>
       <c r="R181" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 18:37 → 09:33; ORDER 80 → 30</t>
+          <t>MOVE day 4 → 2; RETIME 18:37 → 09:44; ORDER 80 → 30</t>
         </is>
       </c>
       <c r="S181" s="7" t="inlineStr">
@@ -16712,12 +16712,12 @@
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="H182" s="6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I182" s="6" t="n">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="R182" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:55 → 11:52</t>
+          <t>RETIME 15:55 → 12:03</t>
         </is>
       </c>
       <c r="S182" s="7" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I183" s="6" t="n">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="R183" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 13:00; ORDER 20 → 50</t>
+          <t>RETIME 12:00 → 13:11; ORDER 20 → 50</t>
         </is>
       </c>
       <c r="S183" s="7" t="inlineStr">
@@ -16888,12 +16888,12 @@
       </c>
       <c r="G184" s="6" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I184" s="6" t="n">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="R184" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:32 → 14:31</t>
+          <t>RETIME 19:32 → 14:42</t>
         </is>
       </c>
       <c r="S184" s="7" t="inlineStr">
@@ -16976,12 +16976,12 @@
       </c>
       <c r="G185" s="6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I185" s="6" t="n">
@@ -17021,7 +17021,7 @@
       </c>
       <c r="R185" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:47 → 16:01; ORDER 50 → 70</t>
+          <t>RETIME 17:47 → 16:12; ORDER 50 → 70</t>
         </is>
       </c>
       <c r="S185" s="7" t="inlineStr">
@@ -17170,18 +17170,18 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L187" s="6" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M187" s="6" t="n">
-        <v>6.5</v>
+        <v>7.18</v>
       </c>
       <c r="N187" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O187" s="6" t="n">
@@ -17240,12 +17240,12 @@
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H188" s="6" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="I188" s="6" t="n">
@@ -17285,7 +17285,7 @@
       </c>
       <c r="R188" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:18 → 08:08</t>
+          <t>RETIME 10:18 → 08:00</t>
         </is>
       </c>
       <c r="S188" s="7" t="inlineStr">
@@ -17328,12 +17328,12 @@
       </c>
       <c r="G189" s="6" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="H189" s="6" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I189" s="6" t="n">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="R189" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:06 → 08:46</t>
+          <t>RETIME 12:06 → 08:38</t>
         </is>
       </c>
       <c r="S189" s="7" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="H190" s="6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I190" s="6" t="n">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="R190" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:33 → 09:58</t>
+          <t>RETIME 13:33 → 09:50</t>
         </is>
       </c>
       <c r="S190" s="7" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="G191" s="6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="H191" s="6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I191" s="6" t="n">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="R191" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:25 → 11:05</t>
+          <t>RETIME 15:25 → 10:57</t>
         </is>
       </c>
       <c r="S191" s="7" t="inlineStr">
@@ -17592,12 +17592,12 @@
       </c>
       <c r="G192" s="6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="H192" s="6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I192" s="6" t="n">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="R192" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:02 → 12:12</t>
+          <t>RETIME 17:02 → 12:04</t>
         </is>
       </c>
       <c r="S192" s="7" t="inlineStr">
@@ -17680,12 +17680,12 @@
       </c>
       <c r="G193" s="6" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="H193" s="6" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I193" s="6" t="n">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="R193" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:46 → 12:50</t>
+          <t>RETIME 18:46 → 12:42</t>
         </is>
       </c>
       <c r="S193" s="7" t="inlineStr">
@@ -17768,12 +17768,12 @@
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H194" s="6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I194" s="6" t="n">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="R194" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:42 → 14:08; ORDER 90 → 80</t>
+          <t>RETIME 21:42 → 14:00; ORDER 90 → 80</t>
         </is>
       </c>
       <c r="S194" s="7" t="inlineStr">
@@ -17856,12 +17856,12 @@
       </c>
       <c r="G195" s="6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="H195" s="6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I195" s="6" t="n">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="R195" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:59 → 15:06; ORDER 80 → 90</t>
+          <t>RETIME 19:59 → 14:58; ORDER 80 → 90</t>
         </is>
       </c>
       <c r="S195" s="7" t="inlineStr">
@@ -18050,18 +18050,18 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L197" s="6" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="M197" s="6" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="N197" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O197" s="6" t="n">
@@ -18120,12 +18120,12 @@
       </c>
       <c r="G198" s="6" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="H198" s="6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I198" s="6" t="n">
@@ -18165,7 +18165,7 @@
       </c>
       <c r="R198" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:41 → 08:01</t>
+          <t>RETIME 08:41 → 07:51</t>
         </is>
       </c>
       <c r="S198" s="7" t="inlineStr">
@@ -18208,12 +18208,12 @@
       </c>
       <c r="G199" s="6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="H199" s="6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I199" s="6" t="n">
@@ -18253,7 +18253,7 @@
       </c>
       <c r="R199" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:21 → 09:53; ORDER 40 → 30</t>
+          <t>RETIME 12:21 → 09:43; ORDER 40 → 30</t>
         </is>
       </c>
       <c r="S199" s="7" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="G200" s="6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="H200" s="6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I200" s="6" t="n">
@@ -18309,23 +18309,23 @@
       </c>
       <c r="J200" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>City God Temple</t>
         </is>
       </c>
       <c r="K200" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L200" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M200" s="6" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="N200" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O200" s="6" t="n">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="R200" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:52 → 11:07; ORDER 30 → 40</t>
+          <t>RETIME 10:52 → 10:57; ORDER 30 → 40</t>
         </is>
       </c>
       <c r="S200" s="7" t="inlineStr">
@@ -18374,46 +18374,46 @@
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
+          <t>City God Temple</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G201" s="6" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="I201" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J201" s="6" t="inlineStr">
+        <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F201" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G201" s="6" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="H201" s="6" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="I201" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J201" s="6" t="inlineStr">
-        <is>
-          <t>City God Temple</t>
-        </is>
-      </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L201" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M201" s="6" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="N201" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O201" s="6" t="n">
@@ -18421,20 +18421,20 @@
       </c>
       <c r="P201" s="6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="Q201" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R201" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:27 → 12:15; ORDER 60 → 50</t>
+          <t>RETIME 13:31 → 12:15</t>
         </is>
       </c>
       <c r="S201" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Guides quote 1-2h but that usually bundles the surrounding market; the walled temple itself (CNY10, 09:00-17:00) is compact and reads in ~45min.</t>
         </is>
       </c>
       <c r="T201" s="6" t="inlineStr">
@@ -18462,26 +18462,26 @@
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>City God Temple</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="H202" s="6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="I202" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J202" s="6" t="inlineStr">
         <is>
@@ -18509,20 +18509,20 @@
       </c>
       <c r="P202" s="6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="Q202" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R202" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:31 → 13:33; ORDER 50 → 60</t>
+          <t>RETIME 15:27 → 13:08</t>
         </is>
       </c>
       <c r="S202" s="7" t="inlineStr">
         <is>
-          <t>Guides quote 1-2h but that usually bundles the surrounding market; the walled temple itself (CNY10, 09:00-17:00) is compact and reads in ~45min.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T202" s="6" t="inlineStr">
@@ -18560,12 +18560,12 @@
       </c>
       <c r="G203" s="6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="H203" s="6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I203" s="6" t="n">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="R203" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:39 → 14:35</t>
+          <t>RETIME 16:39 → 14:25</t>
         </is>
       </c>
       <c r="S203" s="7" t="inlineStr">
@@ -18648,12 +18648,12 @@
       </c>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="H204" s="6" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I204" s="6" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="R204" s="7" t="inlineStr">
         <is>
-          <t>RETIME 22:52 → 15:38; ORDER 100 → 80</t>
+          <t>RETIME 22:52 → 15:28; ORDER 100 → 80</t>
         </is>
       </c>
       <c r="S204" s="7" t="inlineStr">
@@ -18846,10 +18846,10 @@
         </is>
       </c>
       <c r="L206" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M206" s="6" t="n">
-        <v>7.16</v>
+        <v>8.6</v>
       </c>
       <c r="N206" s="6" t="inlineStr">
         <is>
@@ -18912,12 +18912,12 @@
       </c>
       <c r="G207" s="6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="H207" s="6" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="I207" s="6" t="n">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="R207" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:02 → 08:00; ORDER 50 → 20</t>
+          <t>RETIME 17:02 → 08:02; ORDER 50 → 20</t>
         </is>
       </c>
       <c r="S207" s="7" t="inlineStr">
@@ -19000,12 +19000,12 @@
       </c>
       <c r="G208" s="6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="H208" s="6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I208" s="6" t="n">
@@ -19045,7 +19045,7 @@
       </c>
       <c r="R208" s="7" t="inlineStr">
         <is>
-          <t>RETIME 11:13 → 09:40</t>
+          <t>RETIME 11:13 → 09:42</t>
         </is>
       </c>
       <c r="S208" s="7" t="inlineStr">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="G209" s="6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="H209" s="6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I209" s="6" t="n">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="R209" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:50 → 11:33; ORDER 20 → 40</t>
+          <t>RETIME 08:50 → 11:35; ORDER 20 → 40</t>
         </is>
       </c>
       <c r="S209" s="7" t="inlineStr">
@@ -19176,12 +19176,12 @@
       </c>
       <c r="G210" s="6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="H210" s="6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="I210" s="6" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="R210" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:48 → 12:26; ORDER 60 → 50</t>
+          <t>RETIME 19:48 → 12:28; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S210" s="7" t="inlineStr">
@@ -19264,12 +19264,12 @@
       </c>
       <c r="G211" s="6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="H211" s="6" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I211" s="6" t="n">
@@ -19309,7 +19309,7 @@
       </c>
       <c r="R211" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:06 → 13:51; ORDER 40 → 60</t>
+          <t>RETIME 14:06 → 13:53; ORDER 40 → 60</t>
         </is>
       </c>
       <c r="S211" s="7" t="inlineStr">
@@ -21257,18 +21257,18 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L12" s="6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>3.5</v>
+        <v>2.17</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -21327,12 +21327,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I13" s="6" t="n">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:42 → 07:32</t>
+          <t>RETIME 08:42 → 07:23</t>
         </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
@@ -21415,12 +21415,12 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I14" s="6" t="n">
@@ -21460,7 +21460,7 @@
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:36 → 09:11</t>
+          <t>RETIME 10:36 → 09:02</t>
         </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
@@ -21503,12 +21503,12 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="I15" s="6" t="n">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:26 → 12:49</t>
+          <t>RETIME 12:26 → 12:40</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
@@ -21591,36 +21591,36 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I16" s="6" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Jingshan Park</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:08 → 14:06; DURATION 180m → 174m; ORDER 60 → 50</t>
+          <t>RETIME 15:08 → 13:57; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>CUT SHORT BY CLOSING TIME: closes 17:00, last entry 16:00; 6 min less than the 180 min advice. TripAdvisor reviewers and museum guides say most people spend 2-3h and enthusiasts 4-6h, with the Ancient China galleries alone quoted at 2-3h; add the passport/security check on entry.</t>
+          <t>TripAdvisor reviewers and museum guides say most people spend 2-3h and enthusiasts 4-6h, with the Ancient China galleries alone quoted at 2-3h; add the passport/security check on entry.</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -21669,46 +21669,46 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
+          <t>Jingshan Park</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Jingshan Park</t>
-        </is>
-      </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O17" s="6" t="n">
@@ -21716,20 +21716,20 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:04 → 17:08; ORDER 70 → 60</t>
+          <t>RETIME 13:40 → 17:25; ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Trip.com and TripAdvisor reports give a 5-15 min climb each way (about 150 steps) and an average visit around 30 min, stretching to 2h only for dedicated photographers.</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -21757,26 +21757,26 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Jingshan Park</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I18" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -21804,20 +21804,20 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:40 → 19:06; ORDER 50 → 70</t>
+          <t>RETIME 18:04 → 18:18</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>Trip.com and TripAdvisor reports give a 5-15 min climb each way (about 150 steps) and an average visit around 30 min, stretching to 2h only for dedicated photographers.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -21877,14 +21877,14 @@
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>74.90000000000001</v>
+        <v>58.69</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
@@ -21943,12 +21943,12 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="I20" s="6" t="n">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Toboggan down</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L20" s="6" t="n">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O20" s="6" t="n">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>RETIME 09:45 → 09:05</t>
+          <t>RETIME 09:45 → 09:18</t>
         </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
@@ -22021,35 +22021,35 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
           <t>Toboggan down</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
@@ -22060,7 +22060,7 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O21" s="6" t="n">
@@ -22068,20 +22068,20 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:16 → 11:58; ORDER 40 → 30</t>
+          <t>RETIME 12:41 → 12:11</t>
         </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>Rider reports and operator guides put the descent itself at 5-10 min depending on braking; the rest is the walk to the launch platform, the safety briefing and the summer queue.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -22109,26 +22109,26 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Toboggan down</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="I22" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -22156,20 +22156,20 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:41 → 12:26; ORDER 30 → 40</t>
+          <t>RETIME 14:16 → 13:19</t>
         </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Rider reports and operator guides put the descent itself at 5-10 min depending on braking; the rest is the walk to the launch platform, the safety briefing and the summer queue.</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -22207,12 +22207,12 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I23" s="6" t="n">
@@ -22252,7 +22252,7 @@
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:51 → 15:05</t>
+          <t>RETIME 16:51 → 15:18</t>
         </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
@@ -22295,12 +22295,12 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I24" s="6" t="n">
@@ -22340,7 +22340,7 @@
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:50 → 17:43</t>
+          <t>RETIME 18:50 → 17:56</t>
         </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
@@ -22383,12 +22383,12 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="I25" s="6" t="n">
@@ -22428,7 +22428,7 @@
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:33 → 19:31</t>
+          <t>RETIME 20:33 → 19:44</t>
         </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
@@ -22493,14 +22493,14 @@
         </is>
       </c>
       <c r="L26" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>23.6</v>
+        <v>15.32</v>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O26" s="6" t="n">
@@ -22559,12 +22559,12 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I27" s="6" t="n">
@@ -22604,7 +22604,7 @@
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>RETIME 09:01 → 08:21</t>
+          <t>RETIME 09:01 → 08:13</t>
         </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
@@ -22647,12 +22647,12 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I28" s="6" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 11:59</t>
+          <t>RETIME 12:00 → 11:51</t>
         </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
@@ -22735,12 +22735,12 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="I29" s="6" t="n">
@@ -22780,7 +22780,7 @@
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:09 → 13:43</t>
+          <t>RETIME 13:09 → 13:35</t>
         </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
@@ -22823,12 +22823,12 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I30" s="6" t="n">
@@ -22868,7 +22868,7 @@
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:25 → 16:29</t>
+          <t>RETIME 15:25 → 16:21</t>
         </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
@@ -23801,14 +23801,14 @@
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.9</v>
+        <v>9.17</v>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O41" s="6" t="n">
@@ -23867,12 +23867,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I42" s="6" t="n">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 08:50 → 09:10</t>
+          <t>MOVE day 4 → 2; RETIME 08:50 → 09:03</t>
         </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
@@ -23955,12 +23955,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I43" s="6" t="n">
@@ -24000,7 +24000,7 @@
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 10:17 → 10:37</t>
+          <t>MOVE day 4 → 2; RETIME 10:17 → 10:30</t>
         </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
@@ -24043,12 +24043,12 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I44" s="6" t="n">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 12:26 → 11:26</t>
+          <t>MOVE day 4 → 2; RETIME 12:26 → 11:19</t>
         </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
@@ -24131,12 +24131,12 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I45" s="6" t="n">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:31 → 12:04</t>
+          <t>RETIME 14:31 → 11:57</t>
         </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
@@ -24219,12 +24219,12 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="I46" s="6" t="n">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 14:47 → 13:25; ORDER 50 → 60</t>
+          <t>MOVE day 4 → 2; RETIME 14:47 → 13:18; ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
@@ -24307,12 +24307,12 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I47" s="6" t="n">
@@ -24352,7 +24352,7 @@
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 17:26 → 15:46</t>
+          <t>MOVE day 4 → 2; RETIME 17:26 → 15:39</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
@@ -24596,7 +24596,7 @@
         <v>46</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>26.06</v>
+        <v>26.28</v>
       </c>
       <c r="N50" s="6" t="inlineStr">
         <is>
@@ -25205,18 +25205,18 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L57" s="6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>4.2</v>
+        <v>0.93</v>
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O57" s="6" t="n">
@@ -25275,12 +25275,12 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I58" s="6" t="n">
@@ -25320,7 +25320,7 @@
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 4; RETIME 08:40 → 08:00</t>
+          <t>MOVE day 2 → 4; RETIME 08:40 → 08:05</t>
         </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
@@ -25363,12 +25363,12 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I59" s="6" t="n">
@@ -25408,7 +25408,7 @@
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 4; RETIME 10:58 → 10:03</t>
+          <t>MOVE day 2 → 4; RETIME 10:58 → 10:08</t>
         </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
@@ -25451,12 +25451,12 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="I60" s="6" t="n">
@@ -25496,7 +25496,7 @@
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 4; RETIME 11:59 → 10:49</t>
+          <t>MOVE day 2 → 4; RETIME 11:59 → 10:54</t>
         </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
@@ -25539,12 +25539,12 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I61" s="6" t="n">
@@ -25584,7 +25584,7 @@
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:17 → 12:57; ORDER 60 → 50</t>
+          <t>RETIME 16:17 → 13:02; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
@@ -25627,12 +25627,12 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I62" s="6" t="n">
@@ -25672,7 +25672,7 @@
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 4; RETIME 15:48 → 14:36</t>
+          <t>MOVE day 2 → 4; RETIME 15:48 → 14:41</t>
         </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
@@ -26605,14 +26605,14 @@
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>27.8</v>
+        <v>10.85</v>
       </c>
       <c r="N73" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
@@ -26671,12 +26671,12 @@
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I74" s="6" t="n">
@@ -26716,7 +26716,7 @@
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>RETIME 09:02 → 08:22</t>
+          <t>RETIME 09:02 → 08:06</t>
         </is>
       </c>
       <c r="S74" s="7" t="inlineStr">
@@ -26759,12 +26759,12 @@
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I75" s="6" t="n">
@@ -26804,7 +26804,7 @@
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:53 → 12:24; ORDER 50 → 30</t>
+          <t>RETIME 15:53 → 12:08; ORDER 50 → 30</t>
         </is>
       </c>
       <c r="S75" s="7" t="inlineStr">
@@ -26847,12 +26847,12 @@
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="I76" s="6" t="n">
@@ -26892,7 +26892,7 @@
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 13:17; ORDER 30 → 40</t>
+          <t>RETIME 12:00 → 13:01; ORDER 30 → 40</t>
         </is>
       </c>
       <c r="S76" s="7" t="inlineStr">
@@ -26935,12 +26935,12 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I77" s="6" t="n">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="R77" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:06 → 14:30; ORDER 60 → 50</t>
+          <t>RETIME 18:06 → 14:14; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S77" s="7" t="inlineStr">
@@ -27023,12 +27023,12 @@
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I78" s="6" t="n">
@@ -27068,7 +27068,7 @@
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:29 → 16:23; ORDER 70 → 60</t>
+          <t>RETIME 19:29 → 16:07; ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S78" s="7" t="inlineStr">
@@ -27309,10 +27309,10 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>48.94</v>
+        <v>40.16</v>
       </c>
       <c r="N81" s="6" t="inlineStr">
         <is>
@@ -27375,12 +27375,12 @@
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I82" s="6" t="n">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:30 → 09:03; ORDER 40 → 20</t>
+          <t>RETIME 12:30 → 08:50; ORDER 40 → 20</t>
         </is>
       </c>
       <c r="S82" s="7" t="inlineStr">
@@ -27463,12 +27463,12 @@
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="I83" s="6" t="n">
@@ -27508,7 +27508,7 @@
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:23 → 12:41; ORDER 50 → 30</t>
+          <t>RETIME 16:23 → 12:28; ORDER 50 → 30</t>
         </is>
       </c>
       <c r="S83" s="7" t="inlineStr">
@@ -27551,12 +27551,12 @@
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I84" s="6" t="n">
@@ -27596,7 +27596,7 @@
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:48 → 14:58; ORDER 70 → 40</t>
+          <t>RETIME 19:48 → 14:45; ORDER 70 → 40</t>
         </is>
       </c>
       <c r="S84" s="7" t="inlineStr">
@@ -27639,12 +27639,12 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I85" s="6" t="n">
@@ -27684,7 +27684,7 @@
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:39 → 17:19; ORDER 80 → 50</t>
+          <t>RETIME 21:39 → 17:06; ORDER 80 → 50</t>
         </is>
       </c>
       <c r="S85" s="7" t="inlineStr">
@@ -27727,12 +27727,12 @@
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I86" s="6" t="n">
@@ -27772,7 +27772,7 @@
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>RETIME 23:53 → 18:57; ORDER 90 → 60</t>
+          <t>RETIME 23:53 → 18:44; ORDER 90 → 60</t>
         </is>
       </c>
       <c r="S86" s="7" t="inlineStr">
@@ -27815,12 +27815,12 @@
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="I87" s="6" t="n">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 1 → 3; RETIME 00:17 → 20:46; ORDER 40 → 70</t>
+          <t>MOVE day 1 → 3; RETIME 00:17 → 20:33; ORDER 40 → 70</t>
         </is>
       </c>
       <c r="S87" s="7" t="inlineStr">
@@ -28957,18 +28957,18 @@
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L100" s="6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M100" s="6" t="n">
-        <v>4.3</v>
+        <v>4.14</v>
       </c>
       <c r="N100" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O100" s="6" t="n">
@@ -29027,12 +29027,12 @@
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I101" s="6" t="n">
@@ -29072,7 +29072,7 @@
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:43 → 09:03</t>
+          <t>RETIME 08:43 → 08:56</t>
         </is>
       </c>
       <c r="S101" s="7" t="inlineStr">
@@ -29115,12 +29115,12 @@
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I102" s="6" t="n">
@@ -29160,7 +29160,7 @@
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:01 → 09:51</t>
+          <t>RETIME 10:01 → 09:44</t>
         </is>
       </c>
       <c r="S102" s="7" t="inlineStr">
@@ -29203,12 +29203,12 @@
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I103" s="6" t="n">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>RETIME 11:23 → 11:28</t>
+          <t>RETIME 11:23 → 11:21</t>
         </is>
       </c>
       <c r="S103" s="7" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="I104" s="6" t="n">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:10 → 13:06</t>
+          <t>RETIME 14:10 → 12:59</t>
         </is>
       </c>
       <c r="S104" s="7" t="inlineStr">
@@ -29379,12 +29379,12 @@
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="I105" s="6" t="n">
@@ -29424,7 +29424,7 @@
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:20 → 14:27</t>
+          <t>RETIME 15:20 → 14:20</t>
         </is>
       </c>
       <c r="S105" s="7" t="inlineStr">
@@ -29467,12 +29467,12 @@
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I106" s="6" t="n">
@@ -29512,7 +29512,7 @@
       </c>
       <c r="R106" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:17 → 15:39</t>
+          <t>RETIME 17:17 → 15:32</t>
         </is>
       </c>
       <c r="S106" s="7" t="inlineStr">
@@ -29555,12 +29555,12 @@
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I107" s="6" t="n">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:21 → 16:58</t>
+          <t>RETIME 18:21 → 16:51</t>
         </is>
       </c>
       <c r="S107" s="7" t="inlineStr">
@@ -29643,12 +29643,12 @@
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I108" s="6" t="n">
@@ -29688,7 +29688,7 @@
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:03 → 18:21</t>
+          <t>RETIME 20:03 → 18:14</t>
         </is>
       </c>
       <c r="S108" s="7" t="inlineStr">
@@ -29731,12 +29731,12 @@
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I109" s="6" t="n">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:49 → 20:07</t>
+          <t>RETIME 21:49 → 20:00</t>
         </is>
       </c>
       <c r="S109" s="7" t="inlineStr">
@@ -30340,11 +30340,11 @@
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I116" s="6" t="n">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="J116" s="6" t="inlineStr">
         <is>
@@ -30380,12 +30380,12 @@
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:00 → 16:57</t>
+          <t>RETIME 18:00 → 16:57; DURATION 165m → 123m</t>
         </is>
       </c>
       <c r="S116" s="7" t="inlineStr">
         <is>
-          <t>Trail guides and trip reports put the full 7.5 km flat walk at 2.5-3 h at a relaxed pace with photo stops (some quote 3-4 h).</t>
+          <t>CUT SHORT BY CLOSING TIME: closes 19:00, last entry 17:30; 42 min less than the 165 min advice. Trail guides and trip reports put the full 7.5 km flat walk at 2.5-3 h at a relaxed pace with photo stops (some quote 3-4 h).</t>
         </is>
       </c>
       <c r="T116" s="6" t="inlineStr">
@@ -30423,12 +30423,12 @@
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I117" s="6" t="n">
@@ -30468,7 +30468,7 @@
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:21 → 19:50</t>
+          <t>RETIME 20:21 → 19:08</t>
         </is>
       </c>
       <c r="S117" s="7" t="inlineStr">
@@ -30511,12 +30511,12 @@
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="I118" s="6" t="n">
@@ -30533,14 +30533,14 @@
         </is>
       </c>
       <c r="L118" s="6" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="M118" s="6" t="n">
-        <v>38.8</v>
+        <v>7.45</v>
       </c>
       <c r="N118" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O118" s="6" t="n">
@@ -30556,7 +30556,7 @@
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 07:30 → 06:30</t>
         </is>
       </c>
       <c r="S118" s="7" t="inlineStr">
@@ -30599,12 +30599,12 @@
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I119" s="6" t="n">
@@ -30617,18 +30617,18 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L119" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M119" s="6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N119" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
@@ -30644,7 +30644,7 @@
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>RETIME 09:17 → 08:37</t>
+          <t>RETIME 09:17 → 07:31</t>
         </is>
       </c>
       <c r="S119" s="7" t="inlineStr">
@@ -30687,12 +30687,12 @@
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I120" s="6" t="n">
@@ -30732,7 +30732,7 @@
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:12 → 09:47</t>
+          <t>RETIME 10:12 → 08:39</t>
         </is>
       </c>
       <c r="S120" s="7" t="inlineStr">
@@ -30775,12 +30775,12 @@
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I121" s="6" t="n">
@@ -30820,7 +30820,7 @@
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:58 → 12:55</t>
+          <t>RETIME 12:58 → 11:47</t>
         </is>
       </c>
       <c r="S121" s="7" t="inlineStr">
@@ -30863,12 +30863,12 @@
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I122" s="6" t="n">
@@ -30908,7 +30908,7 @@
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:08 → 14:16</t>
+          <t>RETIME 14:08 → 13:08</t>
         </is>
       </c>
       <c r="S122" s="7" t="inlineStr">
@@ -30951,12 +30951,12 @@
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I123" s="6" t="n">
@@ -30964,23 +30964,23 @@
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Ten-Mile Gallery</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L123" s="6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M123" s="6" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="N123" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O123" s="6" t="n">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:33 → 17:11</t>
+          <t>RETIME 16:33 → 16:03</t>
         </is>
       </c>
       <c r="S123" s="7" t="inlineStr">
@@ -31029,22 +31029,22 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Ten-Mile Gallery</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I124" s="6" t="n">
@@ -31052,23 +31052,23 @@
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>Ten-Mile Gallery</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L124" s="6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M124" s="6" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="N124" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O124" s="6" t="n">
@@ -31076,7 +31076,7 @@
       </c>
       <c r="P124" s="6" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="Q124" s="6" t="n">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:57 → 18:19; ORDER 80 → 70</t>
+          <t>RETIME 17:48 → 17:33</t>
         </is>
       </c>
       <c r="S124" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Official guidance is ~1 h for the 2 km gallery; tram is 10-15 min each way and the walk-out ~40 min, so tram queue plus walk lands near 1.5 h in August.</t>
         </is>
       </c>
       <c r="T124" s="6" t="inlineStr">
@@ -31117,22 +31117,22 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>Ten-Mile Gallery</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I125" s="6" t="n">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="P125" s="6" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="Q125" s="6" t="n">
@@ -31172,12 +31172,12 @@
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:48 → 20:19; ORDER 70 → 80</t>
+          <t>RETIME 19:57 → 19:11</t>
         </is>
       </c>
       <c r="S125" s="7" t="inlineStr">
         <is>
-          <t>Official guidance is ~1 h for the 2 km gallery; tram is 10-15 min each way and the walk-out ~40 min, so tram queue plus walk lands near 1.5 h in August.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T125" s="6" t="inlineStr">
@@ -31233,14 +31233,14 @@
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L126" s="6" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="M126" s="6" t="n">
-        <v>0.93</v>
+        <v>27.77</v>
       </c>
       <c r="N126" s="6" t="inlineStr">
         <is>
@@ -31303,12 +31303,12 @@
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I127" s="6" t="n">
@@ -31348,7 +31348,7 @@
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:47 → 08:05; ORDER 50 → 20</t>
+          <t>RETIME 14:47 → 08:31; ORDER 50 → 20</t>
         </is>
       </c>
       <c r="S127" s="7" t="inlineStr">
@@ -31391,12 +31391,12 @@
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I128" s="6" t="n">
@@ -31409,18 +31409,18 @@
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L128" s="6" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M128" s="6" t="n">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="N128" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O128" s="6" t="n">
@@ -31436,7 +31436,7 @@
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:52 → 08:55; ORDER 60 → 30</t>
+          <t>RETIME 15:52 → 09:21; ORDER 60 → 30</t>
         </is>
       </c>
       <c r="S128" s="7" t="inlineStr">
@@ -31479,12 +31479,12 @@
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I129" s="6" t="n">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:36 → 11:09; ORDER 70 → 40</t>
+          <t>RETIME 17:36 → 10:44; ORDER 70 → 40</t>
         </is>
       </c>
       <c r="S129" s="7" t="inlineStr">
@@ -31567,12 +31567,12 @@
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I130" s="6" t="n">
@@ -31612,7 +31612,7 @@
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:35 → 15:32; ORDER 40 → 50</t>
+          <t>RETIME 13:35 → 15:07; ORDER 40 → 50</t>
         </is>
       </c>
       <c r="S130" s="7" t="inlineStr">
@@ -36099,14 +36099,14 @@
         </is>
       </c>
       <c r="L182" s="6" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M182" s="6" t="n">
-        <v>12.1</v>
+        <v>6.53</v>
       </c>
       <c r="N182" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O182" s="6" t="n">
@@ -36165,12 +36165,12 @@
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="I183" s="6" t="n">
@@ -36210,7 +36210,7 @@
       </c>
       <c r="R183" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 08:55 → 08:05; ORDER 30 → 20</t>
+          <t>MOVE day 2 → 3; RETIME 08:55 → 07:59; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S183" s="7" t="inlineStr">
@@ -36253,12 +36253,12 @@
       </c>
       <c r="G184" s="6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I184" s="6" t="n">
@@ -36298,7 +36298,7 @@
       </c>
       <c r="R184" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 13:28 → 09:59; ORDER 50 → 30</t>
+          <t>MOVE day 2 → 3; RETIME 13:28 → 09:53; ORDER 50 → 30</t>
         </is>
       </c>
       <c r="S184" s="7" t="inlineStr">
@@ -36341,12 +36341,12 @@
       </c>
       <c r="G185" s="6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I185" s="6" t="n">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="R185" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 12:37</t>
+          <t>RETIME 12:00 → 12:31</t>
         </is>
       </c>
       <c r="S185" s="7" t="inlineStr">
@@ -36429,12 +36429,12 @@
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="H186" s="6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I186" s="6" t="n">
@@ -36474,7 +36474,7 @@
       </c>
       <c r="R186" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 16:01 → 14:10; ORDER 60 → 50</t>
+          <t>MOVE day 2 → 3; RETIME 16:01 → 14:04; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S186" s="7" t="inlineStr">
@@ -37491,18 +37491,18 @@
       </c>
       <c r="K198" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L198" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M198" s="6" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="N198" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O198" s="6" t="n">
@@ -37561,12 +37561,12 @@
       </c>
       <c r="G199" s="6" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="H199" s="6" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I199" s="6" t="n">
@@ -37606,7 +37606,7 @@
       </c>
       <c r="R199" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:28 → 07:43; ORDER 30 → 20</t>
+          <t>RETIME 13:28 → 07:54; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S199" s="7" t="inlineStr">
@@ -37649,12 +37649,12 @@
       </c>
       <c r="G200" s="6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="H200" s="6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I200" s="6" t="n">
@@ -37694,7 +37694,7 @@
       </c>
       <c r="R200" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 18:37 → 09:33; ORDER 80 → 30</t>
+          <t>MOVE day 4 → 2; RETIME 18:37 → 09:44; ORDER 80 → 30</t>
         </is>
       </c>
       <c r="S200" s="7" t="inlineStr">
@@ -37737,12 +37737,12 @@
       </c>
       <c r="G201" s="6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="H201" s="6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I201" s="6" t="n">
@@ -37782,7 +37782,7 @@
       </c>
       <c r="R201" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:55 → 11:52</t>
+          <t>RETIME 15:55 → 12:03</t>
         </is>
       </c>
       <c r="S201" s="7" t="inlineStr">
@@ -37825,12 +37825,12 @@
       </c>
       <c r="G202" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="H202" s="6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I202" s="6" t="n">
@@ -37870,7 +37870,7 @@
       </c>
       <c r="R202" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 13:00; ORDER 20 → 50</t>
+          <t>RETIME 12:00 → 13:11; ORDER 20 → 50</t>
         </is>
       </c>
       <c r="S202" s="7" t="inlineStr">
@@ -37913,12 +37913,12 @@
       </c>
       <c r="G203" s="6" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="H203" s="6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I203" s="6" t="n">
@@ -37958,7 +37958,7 @@
       </c>
       <c r="R203" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:32 → 14:31</t>
+          <t>RETIME 19:32 → 14:42</t>
         </is>
       </c>
       <c r="S203" s="7" t="inlineStr">
@@ -38001,12 +38001,12 @@
       </c>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="H204" s="6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I204" s="6" t="n">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="R204" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:47 → 16:01; ORDER 50 → 70</t>
+          <t>RETIME 17:47 → 16:12; ORDER 50 → 70</t>
         </is>
       </c>
       <c r="S204" s="7" t="inlineStr">
@@ -38195,18 +38195,18 @@
       </c>
       <c r="K206" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L206" s="6" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M206" s="6" t="n">
-        <v>6.5</v>
+        <v>7.18</v>
       </c>
       <c r="N206" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O206" s="6" t="n">
@@ -38265,12 +38265,12 @@
       </c>
       <c r="G207" s="6" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H207" s="6" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="I207" s="6" t="n">
@@ -38310,7 +38310,7 @@
       </c>
       <c r="R207" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:18 → 08:08</t>
+          <t>RETIME 10:18 → 08:00</t>
         </is>
       </c>
       <c r="S207" s="7" t="inlineStr">
@@ -38353,12 +38353,12 @@
       </c>
       <c r="G208" s="6" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="H208" s="6" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I208" s="6" t="n">
@@ -38398,7 +38398,7 @@
       </c>
       <c r="R208" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:06 → 08:46</t>
+          <t>RETIME 12:06 → 08:38</t>
         </is>
       </c>
       <c r="S208" s="7" t="inlineStr">
@@ -38441,12 +38441,12 @@
       </c>
       <c r="G209" s="6" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="H209" s="6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I209" s="6" t="n">
@@ -38486,7 +38486,7 @@
       </c>
       <c r="R209" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:33 → 09:58</t>
+          <t>RETIME 13:33 → 09:50</t>
         </is>
       </c>
       <c r="S209" s="7" t="inlineStr">
@@ -38529,12 +38529,12 @@
       </c>
       <c r="G210" s="6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="H210" s="6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I210" s="6" t="n">
@@ -38574,7 +38574,7 @@
       </c>
       <c r="R210" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:25 → 11:05</t>
+          <t>RETIME 15:25 → 10:57</t>
         </is>
       </c>
       <c r="S210" s="7" t="inlineStr">
@@ -38617,12 +38617,12 @@
       </c>
       <c r="G211" s="6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="H211" s="6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I211" s="6" t="n">
@@ -38662,7 +38662,7 @@
       </c>
       <c r="R211" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:02 → 12:12</t>
+          <t>RETIME 17:02 → 12:04</t>
         </is>
       </c>
       <c r="S211" s="7" t="inlineStr">
@@ -38705,12 +38705,12 @@
       </c>
       <c r="G212" s="6" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="H212" s="6" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I212" s="6" t="n">
@@ -38750,7 +38750,7 @@
       </c>
       <c r="R212" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:46 → 12:50</t>
+          <t>RETIME 18:46 → 12:42</t>
         </is>
       </c>
       <c r="S212" s="7" t="inlineStr">
@@ -38793,12 +38793,12 @@
       </c>
       <c r="G213" s="6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H213" s="6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I213" s="6" t="n">
@@ -38838,7 +38838,7 @@
       </c>
       <c r="R213" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:42 → 14:08; ORDER 90 → 80</t>
+          <t>RETIME 21:42 → 14:00; ORDER 90 → 80</t>
         </is>
       </c>
       <c r="S213" s="7" t="inlineStr">
@@ -38881,12 +38881,12 @@
       </c>
       <c r="G214" s="6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="H214" s="6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I214" s="6" t="n">
@@ -38926,7 +38926,7 @@
       </c>
       <c r="R214" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:59 → 15:06; ORDER 80 → 90</t>
+          <t>RETIME 19:59 → 14:58; ORDER 80 → 90</t>
         </is>
       </c>
       <c r="S214" s="7" t="inlineStr">
@@ -39075,18 +39075,18 @@
       </c>
       <c r="K216" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L216" s="6" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="M216" s="6" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="N216" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O216" s="6" t="n">
@@ -39145,12 +39145,12 @@
       </c>
       <c r="G217" s="6" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="H217" s="6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I217" s="6" t="n">
@@ -39190,7 +39190,7 @@
       </c>
       <c r="R217" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:41 → 08:01</t>
+          <t>RETIME 08:41 → 07:51</t>
         </is>
       </c>
       <c r="S217" s="7" t="inlineStr">
@@ -39233,12 +39233,12 @@
       </c>
       <c r="G218" s="6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="H218" s="6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I218" s="6" t="n">
@@ -39278,7 +39278,7 @@
       </c>
       <c r="R218" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:21 → 09:53; ORDER 40 → 30</t>
+          <t>RETIME 12:21 → 09:43; ORDER 40 → 30</t>
         </is>
       </c>
       <c r="S218" s="7" t="inlineStr">
@@ -39321,12 +39321,12 @@
       </c>
       <c r="G219" s="6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="H219" s="6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I219" s="6" t="n">
@@ -39334,23 +39334,23 @@
       </c>
       <c r="J219" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>City God Temple</t>
         </is>
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L219" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M219" s="6" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="N219" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O219" s="6" t="n">
@@ -39366,7 +39366,7 @@
       </c>
       <c r="R219" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:52 → 11:07; ORDER 30 → 40</t>
+          <t>RETIME 10:52 → 10:57; ORDER 30 → 40</t>
         </is>
       </c>
       <c r="S219" s="7" t="inlineStr">
@@ -39399,46 +39399,46 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
+          <t>City God Temple</t>
+        </is>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G220" s="6" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="H220" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="I220" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J220" s="6" t="inlineStr">
+        <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F220" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G220" s="6" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="H220" s="6" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="I220" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J220" s="6" t="inlineStr">
-        <is>
-          <t>City God Temple</t>
-        </is>
-      </c>
       <c r="K220" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L220" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M220" s="6" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="N220" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O220" s="6" t="n">
@@ -39446,20 +39446,20 @@
       </c>
       <c r="P220" s="6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="Q220" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R220" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:27 → 12:15; ORDER 60 → 50</t>
+          <t>RETIME 13:31 → 12:15</t>
         </is>
       </c>
       <c r="S220" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Guides quote 1-2h but that usually bundles the surrounding market; the walled temple itself (CNY10, 09:00-17:00) is compact and reads in ~45min.</t>
         </is>
       </c>
       <c r="T220" s="6" t="inlineStr">
@@ -39487,26 +39487,26 @@
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>City God Temple</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G221" s="6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="I221" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J221" s="6" t="inlineStr">
         <is>
@@ -39534,20 +39534,20 @@
       </c>
       <c r="P221" s="6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="Q221" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R221" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:31 → 13:33; ORDER 50 → 60</t>
+          <t>RETIME 15:27 → 13:08</t>
         </is>
       </c>
       <c r="S221" s="7" t="inlineStr">
         <is>
-          <t>Guides quote 1-2h but that usually bundles the surrounding market; the walled temple itself (CNY10, 09:00-17:00) is compact and reads in ~45min.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T221" s="6" t="inlineStr">
@@ -39585,12 +39585,12 @@
       </c>
       <c r="G222" s="6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="H222" s="6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I222" s="6" t="n">
@@ -39630,7 +39630,7 @@
       </c>
       <c r="R222" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:39 → 14:35</t>
+          <t>RETIME 16:39 → 14:25</t>
         </is>
       </c>
       <c r="S222" s="7" t="inlineStr">
@@ -39673,12 +39673,12 @@
       </c>
       <c r="G223" s="6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="H223" s="6" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I223" s="6" t="n">
@@ -39718,7 +39718,7 @@
       </c>
       <c r="R223" s="7" t="inlineStr">
         <is>
-          <t>RETIME 22:52 → 15:38; ORDER 100 → 80</t>
+          <t>RETIME 22:52 → 15:28; ORDER 100 → 80</t>
         </is>
       </c>
       <c r="S223" s="7" t="inlineStr">
@@ -39871,10 +39871,10 @@
         </is>
       </c>
       <c r="L225" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M225" s="6" t="n">
-        <v>7.16</v>
+        <v>8.6</v>
       </c>
       <c r="N225" s="6" t="inlineStr">
         <is>
@@ -39937,12 +39937,12 @@
       </c>
       <c r="G226" s="6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="H226" s="6" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="I226" s="6" t="n">
@@ -39982,7 +39982,7 @@
       </c>
       <c r="R226" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:02 → 08:00; ORDER 50 → 20</t>
+          <t>RETIME 17:02 → 08:02; ORDER 50 → 20</t>
         </is>
       </c>
       <c r="S226" s="7" t="inlineStr">
@@ -40025,12 +40025,12 @@
       </c>
       <c r="G227" s="6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="H227" s="6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I227" s="6" t="n">
@@ -40070,7 +40070,7 @@
       </c>
       <c r="R227" s="7" t="inlineStr">
         <is>
-          <t>RETIME 11:13 → 09:40</t>
+          <t>RETIME 11:13 → 09:42</t>
         </is>
       </c>
       <c r="S227" s="7" t="inlineStr">
@@ -40113,12 +40113,12 @@
       </c>
       <c r="G228" s="6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="H228" s="6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I228" s="6" t="n">
@@ -40158,7 +40158,7 @@
       </c>
       <c r="R228" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:50 → 11:33; ORDER 20 → 40</t>
+          <t>RETIME 08:50 → 11:35; ORDER 20 → 40</t>
         </is>
       </c>
       <c r="S228" s="7" t="inlineStr">
@@ -40201,12 +40201,12 @@
       </c>
       <c r="G229" s="6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="H229" s="6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="I229" s="6" t="n">
@@ -40246,7 +40246,7 @@
       </c>
       <c r="R229" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:48 → 12:26; ORDER 60 → 50</t>
+          <t>RETIME 19:48 → 12:28; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S229" s="7" t="inlineStr">
@@ -40289,12 +40289,12 @@
       </c>
       <c r="G230" s="6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="H230" s="6" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I230" s="6" t="n">
@@ -40334,7 +40334,7 @@
       </c>
       <c r="R230" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:06 → 13:51; ORDER 40 → 60</t>
+          <t>RETIME 14:06 → 13:53; ORDER 40 → 60</t>
         </is>
       </c>
       <c r="S230" s="7" t="inlineStr">
@@ -42621,7 +42621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I161"/>
+  <dimension ref="A1:I160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -42995,18 +42995,18 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G9" s="8" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>3.5</v>
+        <v>2.17</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>National Museum</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Jingshan Park</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -43204,14 +43204,14 @@
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>58.69</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -43231,7 +43231,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Toboggan down</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -43368,14 +43368,14 @@
         </is>
       </c>
       <c r="G18" s="8" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>23.6</v>
+        <v>15.32</v>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -43778,14 +43778,14 @@
         </is>
       </c>
       <c r="G28" s="8" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>11.9</v>
+        <v>9.17</v>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -44068,7 +44068,7 @@
         <v>46</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>26.06</v>
+        <v>26.28</v>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
@@ -44225,18 +44225,18 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G39" s="8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>4.2</v>
+        <v>0.93</v>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -44598,14 +44598,14 @@
         </is>
       </c>
       <c r="G48" s="8" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>27.8</v>
+        <v>10.85</v>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -44844,10 +44844,10 @@
         </is>
       </c>
       <c r="G54" s="8" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>48.94</v>
+        <v>40.16</v>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
@@ -45373,18 +45373,18 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G67" s="8" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>4.3</v>
+        <v>4.14</v>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -45910,14 +45910,14 @@
         </is>
       </c>
       <c r="G80" s="8" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>38.8</v>
+        <v>7.45</v>
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -45937,28 +45937,28 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Bailong Elevator</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Yuanjiajie (Avatar)</t>
+          <t>Tianzi Mountain</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G81" s="8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>0.1</v>
+        <v>4.25</v>
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -45978,28 +45978,28 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Tianzi Mountain</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Tianzi Mountain</t>
+          <t>Tianzi cableway down</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G82" s="8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>4.25</v>
+        <v>0.7</v>
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -46019,24 +46019,24 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Tianzi Mountain</t>
+          <t>Tianzi cableway down</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Tianzi cableway down</t>
+          <t>Ten-Mile Gallery</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G83" s="8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>0.7</v>
+        <v>11.1</v>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Ten-Mile Gallery</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
@@ -46074,14 +46074,14 @@
         </is>
       </c>
       <c r="G84" s="8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>11.1</v>
+        <v>6.14</v>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -46092,21 +46092,21 @@
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Ten-Mile Gallery</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Bus to Zhangjiajie city</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -46115,10 +46115,10 @@
         </is>
       </c>
       <c r="G85" s="8" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>6.14</v>
+        <v>27.77</v>
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
@@ -46142,12 +46142,12 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Bus to Zhangjiajie city</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Bus to Zhangjiajie city</t>
+          <t>Tianmen cableway</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -46156,14 +46156,14 @@
         </is>
       </c>
       <c r="G86" s="8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -46183,28 +46183,28 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Bus to Zhangjiajie city</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Tianmen cableway</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G87" s="8" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>0.8</v>
+        <v>34.04</v>
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -46215,21 +46215,21 @@
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Tianmen cableway</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Tianmen Mountain</t>
+          <t>Head to the station</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -46238,10 +46238,10 @@
         </is>
       </c>
       <c r="G88" s="8" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>27.2</v>
+        <v>1.9</v>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
@@ -46252,25 +46252,25 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>Zhangjiajie</t>
+          <t>Furong (Hibiscus)</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Arrive Furongzhen</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Check in at Waterfall Bay</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -46279,25 +46279,25 @@
         </is>
       </c>
       <c r="G89" s="8" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>34.04</v>
+        <v>4.9</v>
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>Zhangjiajie</t>
+          <t>Furong (Hibiscus)</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
@@ -46306,24 +46306,24 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Check in at Waterfall Bay</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Head to the station</t>
+          <t>Liu Xiaoqing rice tofu</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G90" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
@@ -46347,24 +46347,24 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Arrive Furongzhen</t>
+          <t>Liu Xiaoqing rice tofu</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Check in at Waterfall Bay</t>
+          <t>Wuli Stone Street</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G91" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>4.9</v>
+        <v>0.1</v>
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
@@ -46388,12 +46388,12 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Check in at Waterfall Bay</t>
+          <t>Wuli Stone Street</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Liu Xiaoqing rice tofu</t>
+          <t>Tuwang Palace</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -46405,7 +46405,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
@@ -46429,12 +46429,12 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Liu Xiaoqing rice tofu</t>
+          <t>Furong waterfall</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Wuli Stone Street</t>
+          <t>Youshui River cruise</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
@@ -46446,7 +46446,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
@@ -46470,12 +46470,12 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Wuli Stone Street</t>
+          <t>Baishetang Square</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Tuwang Palace</t>
+          <t>Shenpu Camp Square</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
@@ -46511,12 +46511,12 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Furong waterfall</t>
+          <t>Shenpu Camp Square</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Youshui River cruise</t>
+          <t>Far-bank platform</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
@@ -46543,44 +46543,44 @@
         </is>
       </c>
       <c r="B96" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Baishetang Square</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Shenpu Camp Square</t>
+          <t>Train from Furongzhen</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G96" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Fenghuang</t>
         </is>
       </c>
       <c r="B97" s="8" t="n">
@@ -46588,29 +46588,29 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Shenpu Camp Square</t>
+          <t>Fenghuang HSR station</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Far-bank platform</t>
+          <t>Check in at Jinshuian</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G97" s="8" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
@@ -46621,11 +46621,11 @@
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Fenghuang</t>
         </is>
       </c>
       <c r="B98" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
@@ -46634,24 +46634,24 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Check in at Jinshuian</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Train from Furongzhen</t>
+          <t>East Gate Tower</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G98" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>3.83</v>
+        <v>0.43</v>
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
@@ -46675,24 +46675,24 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Fenghuang HSR station</t>
+          <t>East Gate Tower</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Check in at Jinshuian</t>
+          <t>Hong Bridge</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G99" s="8" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>11.3</v>
+        <v>0.1</v>
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
@@ -46716,12 +46716,12 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Check in at Jinshuian</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>East Gate Tower</t>
+          <t>Fenghuang Ancient Town</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
@@ -46730,10 +46730,10 @@
         </is>
       </c>
       <c r="G100" s="8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>0.43</v>
+        <v>0.77</v>
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
@@ -46757,12 +46757,12 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>East Gate Tower</t>
+          <t>Fenghuang Ancient Town</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Hong Bridge</t>
+          <t>Jumping stones</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
@@ -46771,14 +46771,14 @@
         </is>
       </c>
       <c r="G101" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>0.1</v>
+        <v>0.37</v>
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -46798,12 +46798,12 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Jumping stones</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Fenghuang Ancient Town</t>
+          <t>Snow Bridge (Xueqiao)</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
@@ -46812,10 +46812,10 @@
         </is>
       </c>
       <c r="G102" s="8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
@@ -46839,12 +46839,12 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Fenghuang Ancient Town</t>
+          <t>Tuojiang night boat</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Jumping stones</t>
+          <t>Wanming Pagoda</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -46853,14 +46853,14 @@
         </is>
       </c>
       <c r="G103" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>0.37</v>
+        <v>0.8</v>
       </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -46880,12 +46880,12 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Jumping stones</t>
+          <t>Wanming Pagoda</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Snow Bridge (Xueqiao)</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
@@ -46894,10 +46894,10 @@
         </is>
       </c>
       <c r="G104" s="8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
@@ -46912,44 +46912,44 @@
         </is>
       </c>
       <c r="B105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Tuojiang night boat</t>
+          <t>Sunrise / mist session</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Wanming Pagoda</t>
+          <t>Train from Gucheng</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G105" s="8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>0.8</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>Fenghuang</t>
+          <t>Guilin</t>
         </is>
       </c>
       <c r="B106" s="8" t="n">
@@ -46957,29 +46957,29 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Wanming Pagoda</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Check in at RongShi</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G106" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>0.6</v>
+        <v>6.68</v>
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
@@ -46990,11 +46990,11 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>Fenghuang</t>
+          <t>Guilin</t>
         </is>
       </c>
       <c r="B107" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
@@ -47003,24 +47003,24 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Sunrise / mist session</t>
+          <t>Check in at RongShi</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Train from Gucheng</t>
+          <t>Elephant Trunk Hill</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G107" s="8" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>8.050000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
@@ -47044,24 +47044,24 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Elephant Trunk Hill</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Check in at RongShi</t>
+          <t>Two Rivers &amp; Four Lakes</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G108" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>6.68</v>
+        <v>0.68</v>
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
@@ -47085,12 +47085,12 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Check in at RongShi</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Elephant Trunk Hill</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
@@ -47099,10 +47099,10 @@
         </is>
       </c>
       <c r="G109" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>Guilin</t>
+          <t>Yangshuo</t>
         </is>
       </c>
       <c r="B110" s="8" t="n">
@@ -47121,17 +47121,17 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Elephant Trunk Hill</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Two Rivers &amp; Four Lakes</t>
+          <t>Fengqi Homestay</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr">
@@ -47140,10 +47140,10 @@
         </is>
       </c>
       <c r="G110" s="8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>Guilin</t>
+          <t>Yangshuo</t>
         </is>
       </c>
       <c r="B111" s="8" t="n">
@@ -47162,33 +47162,33 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Fengqi Homestay</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>West Street</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G111" s="8" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -47208,12 +47208,12 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>West Street</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Fengqi Homestay</t>
+          <t>Li River night walk</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
@@ -47222,10 +47222,10 @@
         </is>
       </c>
       <c r="G112" s="8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>0.52</v>
+        <v>0.68</v>
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
@@ -47240,21 +47240,21 @@
         </is>
       </c>
       <c r="B113" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Fengqi Homestay</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>West Street</t>
+          <t>Xingping Ancient Town</t>
         </is>
       </c>
       <c r="F113" s="8" t="inlineStr">
@@ -47263,14 +47263,14 @@
         </is>
       </c>
       <c r="G113" s="8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>0.8</v>
+        <v>3.03</v>
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -47281,37 +47281,37 @@
         </is>
       </c>
       <c r="B114" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>West Street</t>
+          <t>Xingping Ancient Town</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Li River night walk</t>
+          <t>20-RMB viewpoint</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G114" s="8" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>0.68</v>
+        <v>2.4</v>
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -47331,12 +47331,12 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>20-RMB viewpoint</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Xingping Ancient Town</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
@@ -47345,10 +47345,10 @@
         </is>
       </c>
       <c r="G115" s="8" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>3.03</v>
+        <v>17.39</v>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
@@ -47372,12 +47372,12 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Xingping Ancient Town</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>20-RMB viewpoint</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -47386,14 +47386,14 @@
         </is>
       </c>
       <c r="G116" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -47404,21 +47404,21 @@
         </is>
       </c>
       <c r="B117" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>20-RMB viewpoint</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Yulong bamboo rafting</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
@@ -47427,10 +47427,10 @@
         </is>
       </c>
       <c r="G117" s="8" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>17.39</v>
+        <v>6.53</v>
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
@@ -47445,21 +47445,21 @@
         </is>
       </c>
       <c r="B118" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Yulong bamboo rafting</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -47468,10 +47468,10 @@
         </is>
       </c>
       <c r="G118" s="8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>1.42</v>
+        <v>6.53</v>
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
@@ -47495,12 +47495,12 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Moon Hill</t>
         </is>
       </c>
       <c r="F119" s="8" t="inlineStr">
@@ -47509,10 +47509,10 @@
         </is>
       </c>
       <c r="G119" s="8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>12.1</v>
+        <v>10.4</v>
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
@@ -47536,12 +47536,12 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Yulong valley cycling</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
@@ -47553,7 +47553,7 @@
         <v>16</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>6.53</v>
+        <v>6.23</v>
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
@@ -47568,21 +47568,21 @@
         </is>
       </c>
       <c r="B121" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Moon Hill</t>
+          <t>Fly from KWL</t>
         </is>
       </c>
       <c r="F121" s="8" t="inlineStr">
@@ -47591,10 +47591,10 @@
         </is>
       </c>
       <c r="G121" s="8" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>10.4</v>
+        <v>89.8</v>
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
@@ -47605,25 +47605,25 @@
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>Yangshuo</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="B122" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Check in at Marriott</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
@@ -47632,10 +47632,10 @@
         </is>
       </c>
       <c r="G122" s="8" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>6.23</v>
+        <v>33.89</v>
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
@@ -47646,11 +47646,11 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>Yangshuo</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="B123" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
@@ -47659,12 +47659,12 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Check in at Marriott</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Fly from KWL</t>
+          <t>Shanghai Maglev</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr">
@@ -47673,14 +47673,14 @@
         </is>
       </c>
       <c r="G123" s="8" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>89.8</v>
+        <v>9.23</v>
       </c>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -47700,12 +47700,12 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Shanghai Maglev</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Check in at Marriott</t>
+          <t>Nanjing Road East</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
@@ -47714,10 +47714,10 @@
         </is>
       </c>
       <c r="G124" s="8" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>33.89</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
@@ -47741,28 +47741,28 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Check in at Marriott</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Maglev</t>
+          <t>The Bund</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G125" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>9.23</v>
+        <v>3.5</v>
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -47782,24 +47782,24 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Maglev</t>
+          <t>The Bund</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Nanjing Road East</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G126" s="8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>8.449999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
@@ -47823,28 +47823,28 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>The Bund</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G127" s="8" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>3.5</v>
+        <v>1.72</v>
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -47855,33 +47855,33 @@
         </is>
       </c>
       <c r="B128" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>The Bund</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Old Jazz Bar</t>
+          <t>Recovery massage / spa</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G128" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>0.34</v>
+        <v>2.67</v>
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
@@ -47896,21 +47896,21 @@
         </is>
       </c>
       <c r="B129" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>Old Jazz Bar</t>
+          <t>Recovery massage / spa</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>M50 Creative Park</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr">
@@ -47919,10 +47919,10 @@
         </is>
       </c>
       <c r="G129" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>1.72</v>
+        <v>3.34</v>
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
@@ -47946,12 +47946,12 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Recovery massage / spa</t>
+          <t>M50 Creative Park</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>M50 Creative Park</t>
+          <t>Jing’an Temple</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
@@ -47960,10 +47960,10 @@
         </is>
       </c>
       <c r="G130" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
@@ -47987,24 +47987,24 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>M50 Creative Park</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Jing’an Temple</t>
+          <t>Nanjing Road West</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G131" s="8" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H131" s="8" t="n">
-        <v>2.83</v>
+        <v>0.96</v>
       </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
@@ -48028,12 +48028,12 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Nanjing Road West</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Nanjing Road West</t>
+          <t>Zhangyuan</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
@@ -48042,14 +48042,14 @@
         </is>
       </c>
       <c r="G132" s="8" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>0.96</v>
+        <v>0.5</v>
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48069,28 +48069,28 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Nanjing Road West</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Zhangyuan</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G133" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>0.5</v>
+        <v>4.38</v>
       </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48101,21 +48101,21 @@
         </is>
       </c>
       <c r="B134" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Wukang Building</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
@@ -48124,10 +48124,10 @@
         </is>
       </c>
       <c r="G134" s="8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>4.38</v>
+        <v>7.18</v>
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
@@ -48151,24 +48151,24 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Wukang Building</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Wukang Building</t>
+          <t>Wukang Road</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G135" s="8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
@@ -48192,12 +48192,12 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Wukang Building</t>
+          <t>Wukang Road</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Wukang Road</t>
+          <t>Ferguson Lane</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr">
@@ -48206,10 +48206,10 @@
         </is>
       </c>
       <c r="G136" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
@@ -48233,24 +48233,24 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Wukang Road</t>
+          <t>Ferguson Lane</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Ferguson Lane</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G137" s="8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="I137" s="8" t="inlineStr">
         <is>
@@ -48274,12 +48274,12 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Ferguson Lane</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Anfu Road</t>
+          <t>Wulumuqi Road</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
@@ -48291,7 +48291,7 @@
         <v>14</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
@@ -48315,28 +48315,28 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Anfu Road</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Wulumuqi Road</t>
+          <t>Fuxing Park</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G139" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48356,28 +48356,28 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Fuxing Park</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Fuxing Park</t>
+          <t>Sinan Mansions</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G140" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48397,28 +48397,28 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Fuxing Park</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Sinan Mansions</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G141" s="8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>0.3</v>
+        <v>3.97</v>
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48429,21 +48429,21 @@
         </is>
       </c>
       <c r="B142" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Yu Garden</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
@@ -48452,10 +48452,10 @@
         </is>
       </c>
       <c r="G142" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>3.97</v>
+        <v>1.27</v>
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
@@ -48479,28 +48479,28 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Yu Garden</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G143" s="8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H143" s="8" t="n">
-        <v>3.1</v>
+        <v>0.47</v>
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48520,12 +48520,12 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Mid-Lake Teahouse</t>
+          <t>Yuyuan Bazaar</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
@@ -48534,14 +48534,14 @@
         </is>
       </c>
       <c r="G144" s="8" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48561,12 +48561,12 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Mid-Lake Teahouse</t>
+          <t>Yuyuan Bazaar</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Yuyuan Bazaar</t>
+          <t>City God Temple</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr">
@@ -48575,14 +48575,14 @@
         </is>
       </c>
       <c r="G145" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48607,19 +48607,19 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>City God Temple</t>
+          <t>People’s Square</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G146" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>0.26</v>
+        <v>1.83</v>
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
@@ -48643,12 +48643,12 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>City God Temple</t>
+          <t>People’s Square</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>People’s Square</t>
+          <t>Huangpu night cruise</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
@@ -48657,10 +48657,10 @@
         </is>
       </c>
       <c r="G147" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H147" s="8" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
@@ -48684,24 +48684,24 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>People’s Square</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Huangpu night cruise</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G148" s="8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>2.45</v>
+        <v>0.77</v>
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
@@ -48716,33 +48716,33 @@
         </is>
       </c>
       <c r="B149" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>TANK Shanghai</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G149" s="8" t="n">
         <v>19</v>
       </c>
       <c r="H149" s="8" t="n">
-        <v>0.77</v>
+        <v>8.6</v>
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
@@ -48766,24 +48766,24 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>TANK Shanghai</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>TANK Shanghai</t>
+          <t>West Bund Museum</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G150" s="8" t="n">
         <v>17</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>7.16</v>
+        <v>0.64</v>
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
@@ -48807,28 +48807,28 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>TANK Shanghai</t>
+          <t>West Bund Museum</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>West Bund Museum</t>
+          <t>West Bund riverside</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G151" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H151" s="8" t="n">
-        <v>0.64</v>
+        <v>1.8</v>
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48848,28 +48848,28 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>West Bund Museum</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>West Bund riverside</t>
+          <t>Long Museum West Bund</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G152" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H152" s="8" t="n">
-        <v>1.8</v>
+        <v>0.66</v>
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48889,24 +48889,24 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Long Museum West Bund</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G153" s="8" t="n">
         <v>17</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>0.66</v>
+        <v>6.75</v>
       </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
@@ -48921,21 +48921,21 @@
         </is>
       </c>
       <c r="B154" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Shanghai Museum East</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr">
@@ -48944,10 +48944,10 @@
         </is>
       </c>
       <c r="G154" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H154" s="8" t="n">
-        <v>6.75</v>
+        <v>5.97</v>
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
@@ -48971,12 +48971,12 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Shanghai Museum East</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Museum East</t>
+          <t>Shanghai Tower base</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr">
@@ -48985,10 +48985,10 @@
         </is>
       </c>
       <c r="G155" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H155" s="8" t="n">
-        <v>5.97</v>
+        <v>3.63</v>
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
@@ -49012,24 +49012,24 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Museum East</t>
+          <t>Shanghai Tower base</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Tower base</t>
+          <t>World Financial Center</t>
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G156" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H156" s="8" t="n">
-        <v>3.63</v>
+        <v>0.17</v>
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
@@ -49053,12 +49053,12 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Tower base</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>World Financial Center</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr">
@@ -49070,11 +49070,11 @@
         <v>8</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>0.17</v>
+        <v>0.6</v>
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -49094,12 +49094,12 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Jin Mao Tower</t>
+          <t>Oriental Pearl Tower</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr">
@@ -49108,14 +49108,14 @@
         </is>
       </c>
       <c r="G158" s="8" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H158" s="8" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -49135,12 +49135,12 @@
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>Jin Mao Tower</t>
+          <t>Oriental Pearl Tower</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Oriental Pearl Tower</t>
+          <t>Pudong promenade</t>
         </is>
       </c>
       <c r="F159" s="8" t="inlineStr">
@@ -49149,14 +49149,14 @@
         </is>
       </c>
       <c r="G159" s="8" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H159" s="8" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -49176,74 +49176,33 @@
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Oriental Pearl Tower</t>
+          <t>Pudong promenade</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Pudong promenade</t>
+          <t>Fly from PVG</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G160" s="8" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="H160" s="8" t="n">
-        <v>0</v>
+        <v>31.45</v>
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="8" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="B161" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C161" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D161" s="8" t="inlineStr">
-        <is>
-          <t>Pudong promenade</t>
-        </is>
-      </c>
-      <c r="E161" s="8" t="inlineStr">
-        <is>
-          <t>Fly from PVG</t>
-        </is>
-      </c>
-      <c r="F161" s="8" t="inlineStr">
-        <is>
-          <t>didi</t>
-        </is>
-      </c>
-      <c r="G161" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="H161" s="8" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="I161" s="8" t="inlineStr">
-        <is>
           <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I161"/>
+  <autoFilter ref="A1:I160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/china-notion-sync.xlsx
+++ b/china-notion-sync.xlsx
@@ -13993,23 +13993,23 @@
       </c>
       <c r="J151" s="6" t="inlineStr">
         <is>
-          <t>Two Rivers &amp; Four Lakes</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L151" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M151" s="6" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="N151" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O151" s="6" t="n">
@@ -14058,22 +14058,22 @@
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>Two Rivers &amp; Four Lakes</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="H152" s="6" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I152" s="6" t="n">
@@ -14081,23 +14081,23 @@
       </c>
       <c r="J152" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Two Rivers &amp; Four Lakes</t>
         </is>
       </c>
       <c r="K152" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L152" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M152" s="6" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="N152" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O152" s="6" t="n">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="P152" s="6" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q152" s="6" t="n">
@@ -14113,17 +14113,17 @@
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>RETIME 23:05 → 18:22; ORDER 70 → 50</t>
+          <t>RETIME 21:20 → 18:04; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S152" s="7" t="inlineStr">
         <is>
-          <t>Operators and review sites put the full Two Rivers &amp; Four Lakes night cruise at 80-90 min over ~7 km (the shorter Four Lakes-only loop is ~60 min).</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T152" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -14146,12 +14146,12 @@
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Two Rivers &amp; Four Lakes</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="P153" s="6" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="Q153" s="6" t="n">
@@ -14201,17 +14201,17 @@
       </c>
       <c r="R153" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:20 → 20:00</t>
+          <t>RETIME 23:05 → 20:00; ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S153" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Operators and review sites put the full Two Rivers &amp; Four Lakes night cruise at 80-90 min over ~7 km (the shorter Four Lakes-only loop is ~60 min).</t>
         </is>
       </c>
       <c r="T153" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -34684,23 +34684,23 @@
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>Two Rivers &amp; Four Lakes</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L165" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M165" s="6" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="N165" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O165" s="6" t="n">
@@ -34749,22 +34749,22 @@
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>Two Rivers &amp; Four Lakes</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I166" s="6" t="n">
@@ -34772,23 +34772,23 @@
       </c>
       <c r="J166" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Two Rivers &amp; Four Lakes</t>
         </is>
       </c>
       <c r="K166" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L166" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M166" s="6" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="N166" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O166" s="6" t="n">
@@ -34796,7 +34796,7 @@
       </c>
       <c r="P166" s="6" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q166" s="6" t="n">
@@ -34804,17 +34804,17 @@
       </c>
       <c r="R166" s="7" t="inlineStr">
         <is>
-          <t>RETIME 23:05 → 18:22; ORDER 70 → 50</t>
+          <t>RETIME 21:20 → 18:04; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S166" s="7" t="inlineStr">
         <is>
-          <t>Operators and review sites put the full Two Rivers &amp; Four Lakes night cruise at 80-90 min over ~7 km (the shorter Four Lakes-only loop is ~60 min).</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T166" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -34837,12 +34837,12 @@
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Two Rivers &amp; Four Lakes</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G167" s="6" t="inlineStr">
@@ -34884,7 +34884,7 @@
       </c>
       <c r="P167" s="6" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="Q167" s="6" t="n">
@@ -34892,17 +34892,17 @@
       </c>
       <c r="R167" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:20 → 20:00</t>
+          <t>RETIME 23:05 → 20:00; ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S167" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Operators and review sites put the full Two Rivers &amp; Four Lakes night cruise at 80-90 min over ~7 km (the shorter Four Lakes-only loop is ~60 min).</t>
         </is>
       </c>
       <c r="T167" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -47100,7 +47100,7 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Elephant Trunk Hill</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -47141,7 +47141,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Two Rivers &amp; Four Lakes</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">

--- a/china-notion-sync.xlsx
+++ b/china-notion-sync.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Legs" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$T$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$T$227</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Schedule'!$A$1:$T$242</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ideas (parked)'!$A$1:$G$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Moves'!$A$1:$F$26</definedName>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T226"/>
+  <dimension ref="A1:T227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>06:13</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="I29" s="6" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>RETIME 05:39 → 05:38</t>
+          <t>RETIME 05:39 → 05:30</t>
         </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="I83" s="6" t="n">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>RETIME 06:54 → 06:38</t>
+          <t>RETIME 06:54 → 06:30</t>
         </is>
       </c>
       <c r="S83" s="7" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="I102" s="6" t="n">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>RETIME 05:30 → 06:38</t>
+          <t>RETIME 05:30 → 06:30</t>
         </is>
       </c>
       <c r="S102" s="7" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I123" s="6" t="n">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:08</t>
+          <t>RETIME 07:30 → 07:00</t>
         </is>
       </c>
       <c r="S123" s="7" t="inlineStr">
@@ -14677,23 +14677,23 @@
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>Li River night walk</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L159" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M159" s="6" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="N159" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O159" s="6" t="n">
@@ -14742,72 +14742,72 @@
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="I160" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J160" s="6" t="inlineStr">
+        <is>
           <t>Li River night walk</t>
         </is>
       </c>
-      <c r="F160" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="H160" s="6" t="inlineStr">
-        <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="I160" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J160" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K160" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L160" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M160" s="6" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="N160" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O160" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P160" s="6" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="Q160" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R160" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 1; RETIME 19:58 → 17:53; ORDER 80 → 50</t>
+          <t>RETIME 20:09 → 17:35; ORDER 70 → 50</t>
         </is>
       </c>
       <c r="S160" s="7" t="inlineStr">
         <is>
-          <t>Optional after-dinner stroll on the Yangshuo riverfront promenade; no fixed route, and 30-45 min covers the illuminated stretch near West Street.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T160" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -14830,17 +14830,17 @@
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Li River night walk</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr">
@@ -14849,7 +14849,7 @@
         </is>
       </c>
       <c r="I161" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="J161" s="6" t="inlineStr">
         <is>
@@ -14873,29 +14873,29 @@
         </is>
       </c>
       <c r="O161" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P161" s="6" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="Q161" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="R161" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:09 → 18:46; ORDER 70 → 60</t>
+          <t>MOVE day 2 → 1; RETIME 19:58 → 19:31; ORDER 80 → 60</t>
         </is>
       </c>
       <c r="S161" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Optional after-dinner stroll on the Yangshuo riverfront promenade; no fixed route, and 30-45 min covers the illuminated stretch near West Street.</t>
         </is>
       </c>
       <c r="T161" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -15205,23 +15205,23 @@
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L165" s="6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M165" s="6" t="n">
-        <v>17.39</v>
+        <v>0</v>
       </c>
       <c r="N165" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O165" s="6" t="n">
@@ -15270,30 +15270,30 @@
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="I166" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J166" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K166" s="6" t="inlineStr">
@@ -15313,29 +15313,29 @@
         </is>
       </c>
       <c r="O166" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P166" s="6" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q166" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R166" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 1 → 2; RETIME 21:48 → 10:35; ORDER 80 → 50</t>
+          <t>ORDER 40 → 50</t>
         </is>
       </c>
       <c r="S166" s="7" t="inlineStr">
         <is>
-          <t>Show runs ~70 min (operators quote 60-70); the venue advises arriving well before curtain and the 2,000+ seat amphitheatre empties slowly, so allow ~20 min of seating and exit.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T166" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
@@ -15368,36 +15368,36 @@
       </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I167" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J167" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L167" s="6" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M167" s="6" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="N167" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O167" s="6" t="n">
@@ -15405,20 +15405,20 @@
       </c>
       <c r="P167" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q167" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R167" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 12:13; ORDER 40 → 60</t>
+          <t>ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S167" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T167" s="6" t="inlineStr">
@@ -15456,12 +15456,12 @@
       </c>
       <c r="G168" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I168" s="6" t="n">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="R168" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 07:30 → 08:00</t>
         </is>
       </c>
       <c r="S168" s="7" t="inlineStr">
@@ -15544,12 +15544,12 @@
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I169" s="6" t="n">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="R169" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 08:55 → 07:59; ORDER 30 → 20</t>
+          <t>MOVE day 2 → 3; RETIME 08:55 → 09:30; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S169" s="7" t="inlineStr">
@@ -15632,12 +15632,12 @@
       </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="H170" s="6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I170" s="6" t="n">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="R170" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 13:28 → 09:53; ORDER 50 → 30</t>
+          <t>MOVE day 2 → 3; RETIME 13:28 → 11:24; ORDER 50 → 30</t>
         </is>
       </c>
       <c r="S170" s="7" t="inlineStr">
@@ -15720,12 +15720,12 @@
       </c>
       <c r="G171" s="6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I171" s="6" t="n">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="R171" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 12:31</t>
+          <t>RETIME 12:00 → 14:02</t>
         </is>
       </c>
       <c r="S171" s="7" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="H172" s="6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I172" s="6" t="n">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="R172" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 16:01 → 14:04; ORDER 60 → 50</t>
+          <t>MOVE day 2 → 3; RETIME 16:01 → 15:35; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S172" s="7" t="inlineStr">
@@ -15896,12 +15896,12 @@
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="H173" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I173" s="6" t="n">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="J173" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="K173" s="6" t="inlineStr">
@@ -15918,10 +15918,10 @@
         </is>
       </c>
       <c r="L173" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M173" s="6" t="n">
-        <v>6.23</v>
+        <v>5.42</v>
       </c>
       <c r="N173" s="6" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
       </c>
       <c r="R173" s="7" t="inlineStr">
         <is>
-          <t>ORDER 50 → 60</t>
+          <t>RETIME 18:00 → 17:13; ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S173" s="7" t="inlineStr">
@@ -15962,42 +15962,42 @@
         </is>
       </c>
       <c r="B174" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D174" s="6" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="H174" s="6" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I174" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J174" s="6" t="inlineStr">
         <is>
-          <t>Fly from KWL</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K174" s="6" t="inlineStr">
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="L174" s="6" t="n">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="M174" s="6" t="n">
-        <v>67.09</v>
+        <v>1.42</v>
       </c>
       <c r="N174" s="6" t="inlineStr">
         <is>
@@ -16017,40 +16017,40 @@
         </is>
       </c>
       <c r="O174" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P174" s="6" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="Q174" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R174" s="7" t="inlineStr">
         <is>
-          <t>RETIME 06:09 → 05:50</t>
+          <t>MOVE day 1 → 3; RETIME 21:48 → 19:45; ORDER 80 → 70</t>
         </is>
       </c>
       <c r="S174" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Show runs ~70 min (operators quote 60-70); the venue advises arriving well before curtain and the 2,000+ seat amphitheatre empties slowly, so allow ~20 min of seating and exit.</t>
         </is>
       </c>
       <c r="T174" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Yangshuo</t>
         </is>
       </c>
       <c r="B175" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
@@ -16062,67 +16062,67 @@
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>Land at PVG</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="I175" s="6" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J175" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Fly from KWL</t>
         </is>
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L175" s="6" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="M175" s="6" t="n">
-        <v>0</v>
+        <v>67.09</v>
       </c>
       <c r="N175" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O175" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P175" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="Q175" s="6" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="R175" s="7" t="inlineStr">
         <is>
-          <t>DURATION 40m → 45m</t>
+          <t>RETIME 06:09 → 05:30</t>
         </is>
       </c>
       <c r="S175" s="7" t="inlineStr">
         <is>
-          <t>PVG guides put full international arrival at ~60min; a domestic arrival (HO1148 from Guilin, T2) skips immigration, leaving deplane, long terminal walk and belt wait at ~35-45min.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T175" s="6" t="inlineStr">
@@ -16146,50 +16146,50 @@
         </is>
       </c>
       <c r="D176" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
+          <t>Land at PVG</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="I176" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J176" s="6" t="inlineStr">
+        <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F176" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G176" s="6" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="H176" s="6" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="I176" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J176" s="6" t="inlineStr">
-        <is>
-          <t>Check in at Marriott</t>
-        </is>
-      </c>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L176" s="6" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M176" s="6" t="n">
-        <v>33.89</v>
+        <v>0</v>
       </c>
       <c r="N176" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O176" s="6" t="n">
@@ -16197,20 +16197,20 @@
       </c>
       <c r="P176" s="6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="Q176" s="6" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="R176" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:46 → 13:53; ORDER 30 → 20</t>
+          <t>DURATION 40m → 45m</t>
         </is>
       </c>
       <c r="S176" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>PVG guides put full international arrival at ~60min; a domestic arrival (HO1148 from Guilin, T2) skips immigration, leaving deplane, long terminal walk and belt wait at ~35-45min.</t>
         </is>
       </c>
       <c r="T176" s="6" t="inlineStr">
@@ -16234,46 +16234,46 @@
         </is>
       </c>
       <c r="D177" s="6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="I177" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J177" s="6" t="inlineStr">
+        <is>
           <t>Check in at Marriott</t>
         </is>
       </c>
-      <c r="F177" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G177" s="6" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="H177" s="6" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="I177" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J177" s="6" t="inlineStr">
-        <is>
-          <t>Shanghai Maglev</t>
-        </is>
-      </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="L177" s="6" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="M177" s="6" t="n">
-        <v>9.23</v>
+        <v>33.89</v>
       </c>
       <c r="N177" s="6" t="inlineStr">
         <is>
@@ -16285,20 +16285,20 @@
       </c>
       <c r="P177" s="6" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="Q177" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="R177" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:57 → 15:58; ORDER 40 → 30</t>
+          <t>RETIME 15:46 → 13:53; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S177" s="7" t="inlineStr">
         <is>
-          <t>Standard city-hotel check-in plus bag drop and a quick freshen-up; no evidence of unusual delays at this property.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T177" s="6" t="inlineStr">
@@ -16322,46 +16322,46 @@
         </is>
       </c>
       <c r="D178" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
+          <t>Check in at Marriott</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J178" s="6" t="inlineStr">
+        <is>
           <t>Shanghai Maglev</t>
         </is>
       </c>
-      <c r="F178" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G178" s="6" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="H178" s="6" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="I178" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="J178" s="6" t="inlineStr">
-        <is>
-          <t>Nanjing Road East</t>
-        </is>
-      </c>
       <c r="K178" s="6" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="L178" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M178" s="6" t="n">
-        <v>8.449999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="N178" s="6" t="inlineStr">
         <is>
@@ -16373,25 +16373,25 @@
       </c>
       <c r="P178" s="6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="Q178" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R178" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:30 → 16:56; ORDER 20 → 40</t>
+          <t>RETIME 16:57 → 15:58; ORDER 40 → 30</t>
         </is>
       </c>
       <c r="S178" s="7" t="inlineStr">
         <is>
-          <t>Operator and airport guides: 8-minute run PVG-Longyang Road with departures every 15-20min, so ticket, platform wait, ride and exit total roughly 25min.</t>
+          <t>Standard city-hotel check-in plus bag drop and a quick freshen-up; no evidence of unusual delays at this property.</t>
         </is>
       </c>
       <c r="T178" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -16410,50 +16410,50 @@
         </is>
       </c>
       <c r="D179" s="6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
+          <t>Shanghai Maglev</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J179" s="6" t="inlineStr">
+        <is>
           <t>Nanjing Road East</t>
         </is>
       </c>
-      <c r="F179" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G179" s="6" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="H179" s="6" t="inlineStr">
-        <is>
-          <t>18:48</t>
-        </is>
-      </c>
-      <c r="I179" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J179" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L179" s="6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M179" s="6" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N179" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O179" s="6" t="n">
@@ -16461,25 +16461,25 @@
       </c>
       <c r="P179" s="6" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="Q179" s="6" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="R179" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:51 → 17:48</t>
+          <t>RETIME 14:30 → 16:56; ORDER 20 → 40</t>
         </is>
       </c>
       <c r="S179" s="7" t="inlineStr">
         <is>
-          <t>Guides say the full pedestrian street takes about two hours and 2-3h combined with the Bund; a one-way walk toward the river with browsing stops is about an hour.</t>
+          <t>Operator and airport guides: 8-minute run PVG-Longyang Road with departures every 15-20min, so ticket, platform wait, ride and exit total roughly 25min.</t>
         </is>
       </c>
       <c r="T179" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -16498,50 +16498,50 @@
         </is>
       </c>
       <c r="D180" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>Nanjing Road East</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="J180" s="6" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F180" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G180" s="6" t="inlineStr">
-        <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="H180" s="6" t="inlineStr">
-        <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="I180" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J180" s="6" t="inlineStr">
-        <is>
-          <t>The Bund</t>
-        </is>
-      </c>
       <c r="K180" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L180" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M180" s="6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N180" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O180" s="6" t="n">
@@ -16549,20 +16549,20 @@
       </c>
       <c r="P180" s="6" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="Q180" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R180" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:16 → 18:56; ORDER 70 → 60</t>
+          <t>RETIME 17:51 → 17:48</t>
         </is>
       </c>
       <c r="S180" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Guides say the full pedestrian street takes about two hours and 2-3h combined with the Bund; a one-way walk toward the river with browsing stops is about an hour.</t>
         </is>
       </c>
       <c r="T180" s="6" t="inlineStr">
@@ -16586,50 +16586,50 @@
         </is>
       </c>
       <c r="D181" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J181" s="6" t="inlineStr">
+        <is>
           <t>The Bund</t>
         </is>
       </c>
-      <c r="F181" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G181" s="6" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
-      <c r="H181" s="6" t="inlineStr">
-        <is>
-          <t>21:53</t>
-        </is>
-      </c>
-      <c r="I181" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J181" s="6" t="inlineStr">
-        <is>
-          <t>Old Jazz Bar</t>
-        </is>
-      </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="L181" s="6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M181" s="6" t="n">
-        <v>0.34</v>
+        <v>3.5</v>
       </c>
       <c r="N181" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O181" s="6" t="n">
@@ -16637,25 +16637,25 @@
       </c>
       <c r="P181" s="6" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="Q181" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R181" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:33 → 20:53; ORDER 60 → 70</t>
+          <t>RETIME 21:16 → 18:56; ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S181" s="7" t="inlineStr">
         <is>
-          <t>GPSmyCity self-guided Bund route is 1.1km / about 1 hour, matching blog reports of 45-90min strolling the promenade.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T181" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -16674,46 +16674,46 @@
         </is>
       </c>
       <c r="D182" s="6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
+          <t>The Bund</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="I182" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J182" s="6" t="inlineStr">
+        <is>
           <t>Old Jazz Bar</t>
         </is>
       </c>
-      <c r="F182" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G182" s="6" t="inlineStr">
-        <is>
-          <t>22:13</t>
-        </is>
-      </c>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>23:43</t>
-        </is>
-      </c>
-      <c r="I182" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J182" s="6" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
       <c r="K182" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L182" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M182" s="6" t="n">
-        <v>1.72</v>
+        <v>0.34</v>
       </c>
       <c r="N182" s="6" t="inlineStr">
         <is>
@@ -16721,29 +16721,29 @@
         </is>
       </c>
       <c r="O182" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P182" s="6" t="inlineStr">
         <is>
-          <t>01:51</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="Q182" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R182" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 3 → 1; RETIME 01:51 → 22:13; ORDER 110 → 80</t>
+          <t>RETIME 19:33 → 20:53; ORDER 60 → 70</t>
         </is>
       </c>
       <c r="S182" s="7" t="inlineStr">
         <is>
-          <t>The Fairmont Peace Hotel Old Jazz Band plays a long nightly run (from ~18:30, sets through 23:30); reviewers describe staying for a couple of sets over drinks, roughly 90min.</t>
+          <t>GPSmyCity self-guided Bund route is 1.1km / about 1 hour, matching blog reports of 45-90min strolling the promenade.</t>
         </is>
       </c>
       <c r="T182" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -16754,42 +16754,42 @@
         </is>
       </c>
       <c r="B183" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D183" s="6" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>22:13</t>
         </is>
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>23:43</t>
         </is>
       </c>
       <c r="I183" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J183" s="6" t="inlineStr">
         <is>
-          <t>Recovery massage / spa</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K183" s="6" t="inlineStr">
@@ -16798,10 +16798,10 @@
         </is>
       </c>
       <c r="L183" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M183" s="6" t="n">
-        <v>2.67</v>
+        <v>1.72</v>
       </c>
       <c r="N183" s="6" t="inlineStr">
         <is>
@@ -16809,24 +16809,24 @@
         </is>
       </c>
       <c r="O183" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P183" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>01:51</t>
         </is>
       </c>
       <c r="Q183" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R183" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>MOVE day 3 → 1; RETIME 01:51 → 22:13; ORDER 110 → 80</t>
         </is>
       </c>
       <c r="S183" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>The Fairmont Peace Hotel Old Jazz Band plays a long nightly run (from ~18:30, sets through 23:30); reviewers describe staying for a couple of sets over drinks, roughly 90min.</t>
         </is>
       </c>
       <c r="T183" s="6" t="inlineStr">
@@ -16850,46 +16850,46 @@
         </is>
       </c>
       <c r="D184" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J184" s="6" t="inlineStr">
+        <is>
           <t>Recovery massage / spa</t>
         </is>
       </c>
-      <c r="F184" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G184" s="6" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="H184" s="6" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="I184" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J184" s="6" t="inlineStr">
-        <is>
-          <t>M50 Creative Park</t>
-        </is>
-      </c>
       <c r="K184" s="6" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="L184" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M184" s="6" t="n">
-        <v>3.34</v>
+        <v>2.67</v>
       </c>
       <c r="N184" s="6" t="inlineStr">
         <is>
@@ -16901,20 +16901,20 @@
       </c>
       <c r="P184" s="6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q184" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="R184" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:28 → 07:54; ORDER 30 → 20</t>
+          <t>RETIME 07:30 → 07:00</t>
         </is>
       </c>
       <c r="S184" s="7" t="inlineStr">
         <is>
-          <t>Shanghai spa listings (Time Out, SmartShanghai, Culture Trip) show 60-80min foot/body packages as the standard tourist option; add foot bath, changing and tea for ~90min door to door.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T184" s="6" t="inlineStr">
@@ -16938,46 +16938,46 @@
         </is>
       </c>
       <c r="D185" s="6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
+          <t>Recovery massage / spa</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J185" s="6" t="inlineStr">
+        <is>
           <t>M50 Creative Park</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G185" s="6" t="inlineStr">
-        <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="H185" s="6" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="I185" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="J185" s="6" t="inlineStr">
-        <is>
-          <t>Jing’an Temple</t>
-        </is>
-      </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="L185" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M185" s="6" t="n">
-        <v>2.83</v>
+        <v>3.34</v>
       </c>
       <c r="N185" s="6" t="inlineStr">
         <is>
@@ -16985,24 +16985,24 @@
         </is>
       </c>
       <c r="O185" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P185" s="6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="Q185" s="6" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="R185" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 18:37 → 09:44; ORDER 80 → 30</t>
+          <t>RETIME 13:28 → 07:54; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S185" s="7" t="inlineStr">
         <is>
-          <t>Travel guides budget 2-4h (about 3h recommended) for 140+ studios and galleries plus the graffiti wall; 2h is a highlights-plus pass through the better galleries.</t>
+          <t>Shanghai spa listings (Time Out, SmartShanghai, Culture Trip) show 60-80min foot/body packages as the standard tourist option; add foot bath, changing and tea for ~90min door to door.</t>
         </is>
       </c>
       <c r="T185" s="6" t="inlineStr">
@@ -17026,76 +17026,76 @@
         </is>
       </c>
       <c r="D186" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
+          <t>M50 Creative Park</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J186" s="6" t="inlineStr">
+        <is>
           <t>Jing’an Temple</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="H186" s="6" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="I186" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J186" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K186" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L186" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M186" s="6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N186" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O186" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P186" s="6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="Q186" s="6" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="R186" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:55 → 12:03</t>
+          <t>MOVE day 4 → 2; RETIME 18:37 → 09:44; ORDER 80 → 30</t>
         </is>
       </c>
       <c r="S186" s="7" t="inlineStr">
         <is>
-          <t>Multiple guides recommend about 1 hour for the compact walled complex (90min quoted as a generous middle ground); 45min is tight once you include ticketing and the Mahavira Hall.</t>
+          <t>Travel guides budget 2-4h (about 3h recommended) for 140+ studios and galleries plus the graffiti wall; 2h is a highlights-plus pass through the better galleries.</t>
         </is>
       </c>
       <c r="T186" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -17114,26 +17114,26 @@
         </is>
       </c>
       <c r="D187" s="6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Jing’an Temple</t>
         </is>
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I187" s="6" t="n">
@@ -17141,23 +17141,23 @@
       </c>
       <c r="J187" s="6" t="inlineStr">
         <is>
-          <t>Nanjing Road West</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L187" s="6" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M187" s="6" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="N187" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O187" s="6" t="n">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="P187" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="Q187" s="6" t="n">
@@ -17173,17 +17173,17 @@
       </c>
       <c r="R187" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 13:11; ORDER 20 → 50</t>
+          <t>RETIME 15:55 → 12:03</t>
         </is>
       </c>
       <c r="S187" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Multiple guides recommend about 1 hour for the compact walled complex (90min quoted as a generous middle ground); 45min is tight once you include ticketing and the Mahavira Hall.</t>
         </is>
       </c>
       <c r="T187" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -17202,50 +17202,50 @@
         </is>
       </c>
       <c r="D188" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="I188" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="J188" s="6" t="inlineStr">
         <is>
           <t>Nanjing Road West</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G188" s="6" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="H188" s="6" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="I188" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="J188" s="6" t="inlineStr">
-        <is>
-          <t>Zhangyuan</t>
-        </is>
-      </c>
       <c r="K188" s="6" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
       <c r="L188" s="6" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="M188" s="6" t="n">
-        <v>0.5</v>
+        <v>0.96</v>
       </c>
       <c r="N188" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O188" s="6" t="n">
@@ -17253,20 +17253,20 @@
       </c>
       <c r="P188" s="6" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q188" s="6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="R188" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:32 → 14:42</t>
+          <t>RETIME 12:00 → 13:11; ORDER 20 → 50</t>
         </is>
       </c>
       <c r="S188" s="7" t="inlineStr">
         <is>
-          <t>Shopping guides: most visitors spend 1-2h on West Nanjing Road, 2-3h if working through Plaza 66 / HKRI Taikoo Hui; 75min covers the strip plus one mall.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T188" s="6" t="inlineStr">
@@ -17290,50 +17290,50 @@
         </is>
       </c>
       <c r="D189" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
+          <t>Nanjing Road West</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="I189" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J189" s="6" t="inlineStr">
+        <is>
           <t>Zhangyuan</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G189" s="6" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="H189" s="6" t="inlineStr">
-        <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="I189" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J189" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L189" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M189" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N189" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O189" s="6" t="n">
@@ -17341,20 +17341,20 @@
       </c>
       <c r="P189" s="6" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="Q189" s="6" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="R189" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:47 → 16:12; ORDER 50 → 70</t>
+          <t>RETIME 19:32 → 14:42</t>
         </is>
       </c>
       <c r="S189" s="7" t="inlineStr">
         <is>
-          <t>Reviews describe a restored shikumen retail precinct 'similar to Xintiandi but much quieter'; an unhurried wander of the lanes with a pop-up or two runs about an hour.</t>
+          <t>Shopping guides: most visitors spend 1-2h on West Nanjing Road, 2-3h if working through Plaza 66 / HKRI Taikoo Hui; 75min covers the strip plus one mall.</t>
         </is>
       </c>
       <c r="T189" s="6" t="inlineStr">
@@ -17378,50 +17378,50 @@
         </is>
       </c>
       <c r="D190" s="6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
+          <t>Zhangyuan</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="I190" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J190" s="6" t="inlineStr">
+        <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G190" s="6" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="H190" s="6" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="I190" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J190" s="6" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
       <c r="K190" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L190" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M190" s="6" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="N190" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O190" s="6" t="n">
@@ -17429,20 +17429,20 @@
       </c>
       <c r="P190" s="6" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="Q190" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R190" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:15 → 18:00; ORDER 70 → 80</t>
+          <t>RETIME 17:47 → 16:12; ORDER 50 → 70</t>
         </is>
       </c>
       <c r="S190" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Reviews describe a restored shikumen retail precinct 'similar to Xintiandi but much quieter'; an unhurried wander of the lanes with a pop-up or two runs about an hour.</t>
         </is>
       </c>
       <c r="T190" s="6" t="inlineStr">
@@ -17458,19 +17458,19 @@
         </is>
       </c>
       <c r="B191" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D191" s="6" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F191" s="6" t="inlineStr">
@@ -17480,20 +17480,20 @@
       </c>
       <c r="G191" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H191" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I191" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J191" s="6" t="inlineStr">
         <is>
-          <t>Wukang Building</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K191" s="6" t="inlineStr">
@@ -17502,10 +17502,10 @@
         </is>
       </c>
       <c r="L191" s="6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M191" s="6" t="n">
-        <v>7.18</v>
+        <v>4.38</v>
       </c>
       <c r="N191" s="6" t="inlineStr">
         <is>
@@ -17513,24 +17513,24 @@
         </is>
       </c>
       <c r="O191" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P191" s="6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="Q191" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R191" s="7" t="inlineStr">
         <is>
-          <t>RETIME 09:00 → 07:00</t>
+          <t>RETIME 21:15 → 18:00; ORDER 70 → 80</t>
         </is>
       </c>
       <c r="S191" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T191" s="6" t="inlineStr">
@@ -17554,50 +17554,50 @@
         </is>
       </c>
       <c r="D192" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="I192" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J192" s="6" t="inlineStr">
+        <is>
           <t>Wukang Building</t>
         </is>
       </c>
-      <c r="F192" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G192" s="6" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H192" s="6" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="I192" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J192" s="6" t="inlineStr">
-        <is>
-          <t>Wukang Road</t>
-        </is>
-      </c>
       <c r="K192" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L192" s="6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M192" s="6" t="n">
-        <v>0.7</v>
+        <v>7.18</v>
       </c>
       <c r="N192" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O192" s="6" t="n">
@@ -17605,20 +17605,20 @@
       </c>
       <c r="P192" s="6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="Q192" s="6" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="R192" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:18 → 08:00</t>
+          <t>RETIME 09:00 → 07:00</t>
         </is>
       </c>
       <c r="S192" s="7" t="inlineStr">
         <is>
-          <t>Walking guides treat Wukang Mansion as a photo landmark on the corner (best 16:00-17:30); it is exterior-only, so 15-25min including crowd jostling.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T192" s="6" t="inlineStr">
@@ -17642,46 +17642,46 @@
         </is>
       </c>
       <c r="D193" s="6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
+          <t>Wukang Building</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J193" s="6" t="inlineStr">
+        <is>
           <t>Wukang Road</t>
         </is>
       </c>
-      <c r="F193" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G193" s="6" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="H193" s="6" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="I193" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J193" s="6" t="inlineStr">
-        <is>
-          <t>Ferguson Lane</t>
-        </is>
-      </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
       <c r="L193" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M193" s="6" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="N193" s="6" t="inlineStr">
         <is>
@@ -17693,20 +17693,20 @@
       </c>
       <c r="P193" s="6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="Q193" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="R193" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:06 → 08:38</t>
+          <t>RETIME 10:18 → 08:00</t>
         </is>
       </c>
       <c r="S193" s="7" t="inlineStr">
         <is>
-          <t>Guides quote 2-3h for Wukang Road with photos and coffee, but that bundles Ferguson Lane and cafes which are separate stops here; the 1.17km street alone walks in about an hour.</t>
+          <t>Walking guides treat Wukang Mansion as a photo landmark on the corner (best 16:00-17:30); it is exterior-only, so 15-25min including crowd jostling.</t>
         </is>
       </c>
       <c r="T193" s="6" t="inlineStr">
@@ -17730,46 +17730,46 @@
         </is>
       </c>
       <c r="D194" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
+          <t>Wukang Road</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="I194" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J194" s="6" t="inlineStr">
+        <is>
           <t>Ferguson Lane</t>
         </is>
       </c>
-      <c r="F194" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G194" s="6" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="H194" s="6" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="I194" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J194" s="6" t="inlineStr">
-        <is>
-          <t>Anfu Road</t>
-        </is>
-      </c>
       <c r="K194" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L194" s="6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M194" s="6" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="N194" s="6" t="inlineStr">
         <is>
@@ -17781,25 +17781,25 @@
       </c>
       <c r="P194" s="6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="Q194" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R194" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:33 → 09:50</t>
+          <t>RETIME 12:06 → 08:38</t>
         </is>
       </c>
       <c r="S194" s="7" t="inlineStr">
         <is>
-          <t>Ferguson Lane (376 Wukang Rd) is described as a small tucked-away courtyard of galleries and bistros — 15min to look, 45min if you actually sit for the coffee it exists for.</t>
+          <t>Guides quote 2-3h for Wukang Road with photos and coffee, but that bundles Ferguson Lane and cafes which are separate stops here; the 1.17km street alone walks in about an hour.</t>
         </is>
       </c>
       <c r="T194" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -17818,11 +17818,11 @@
         </is>
       </c>
       <c r="D195" s="6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Anfu Road</t>
+          <t>Ferguson Lane</t>
         </is>
       </c>
       <c r="F195" s="6" t="inlineStr">
@@ -17832,12 +17832,12 @@
       </c>
       <c r="G195" s="6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="H195" s="6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I195" s="6" t="n">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="J195" s="6" t="inlineStr">
         <is>
-          <t>Wulumuqi Road</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="K195" s="6" t="inlineStr">
@@ -17857,7 +17857,7 @@
         <v>14</v>
       </c>
       <c r="M195" s="6" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="N195" s="6" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
       </c>
       <c r="P195" s="6" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="Q195" s="6" t="n">
@@ -17877,17 +17877,17 @@
       </c>
       <c r="R195" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:25 → 10:57</t>
+          <t>RETIME 13:33 → 09:50</t>
         </is>
       </c>
       <c r="S195" s="7" t="inlineStr">
         <is>
-          <t>Wukang+Anfu combined walking routes are quoted at 3-4h over 2.5km; Anfu Road's own share, browsing a couple of shops, is roughly 45min.</t>
+          <t>Ferguson Lane (376 Wukang Rd) is described as a small tucked-away courtyard of galleries and bistros — 15min to look, 45min if you actually sit for the coffee it exists for.</t>
         </is>
       </c>
       <c r="T195" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -17906,50 +17906,50 @@
         </is>
       </c>
       <c r="D196" s="6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
+          <t>Anfu Road</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="H196" s="6" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="I196" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J196" s="6" t="inlineStr">
+        <is>
           <t>Wulumuqi Road</t>
         </is>
       </c>
-      <c r="F196" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G196" s="6" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="H196" s="6" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="I196" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J196" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K196" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="L196" s="6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M196" s="6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N196" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O196" s="6" t="n">
@@ -17957,25 +17957,25 @@
       </c>
       <c r="P196" s="6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="Q196" s="6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="R196" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:02 → 12:04</t>
+          <t>RETIME 15:25 → 10:57</t>
         </is>
       </c>
       <c r="S196" s="7" t="inlineStr">
         <is>
-          <t>Guides frame Wulumuqi Middle Road as a short local-life detour (markets, Art Deco corner at Fuxing West Rd) rather than a destination; ~30min walk-through.</t>
+          <t>Wukang+Anfu combined walking routes are quoted at 3-4h over 2.5km; Anfu Road's own share, browsing a couple of shops, is roughly 45min.</t>
         </is>
       </c>
       <c r="T196" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -17994,50 +17994,50 @@
         </is>
       </c>
       <c r="D197" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
+          <t>Wulumuqi Road</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J197" s="6" t="inlineStr">
+        <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F197" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G197" s="6" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="H197" s="6" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="I197" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J197" s="6" t="inlineStr">
-        <is>
-          <t>Fuxing Park</t>
-        </is>
-      </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L197" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M197" s="6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N197" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O197" s="6" t="n">
@@ -18045,25 +18045,25 @@
       </c>
       <c r="P197" s="6" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="Q197" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="R197" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:46 → 12:42</t>
+          <t>RETIME 17:02 → 12:04</t>
         </is>
       </c>
       <c r="S197" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Guides frame Wulumuqi Middle Road as a short local-life detour (markets, Art Deco corner at Fuxing West Rd) rather than a destination; ~30min walk-through.</t>
         </is>
       </c>
       <c r="T197" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -18082,50 +18082,50 @@
         </is>
       </c>
       <c r="D198" s="6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J198" s="6" t="inlineStr">
+        <is>
           <t>Fuxing Park</t>
         </is>
       </c>
-      <c r="F198" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G198" s="6" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="H198" s="6" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="I198" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J198" s="6" t="inlineStr">
-        <is>
-          <t>Sinan Mansions</t>
-        </is>
-      </c>
       <c r="K198" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L198" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M198" s="6" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="N198" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O198" s="6" t="n">
@@ -18133,20 +18133,20 @@
       </c>
       <c r="P198" s="6" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="Q198" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R198" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:42 → 14:00; ORDER 90 → 80</t>
+          <t>RETIME 18:46 → 12:42</t>
         </is>
       </c>
       <c r="S198" s="7" t="inlineStr">
         <is>
-          <t>Guides say Fuxing Park is 'worth a 30-60 minute walk'; 45min lets you watch the dancing and chess without circling twice.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T198" s="6" t="inlineStr">
@@ -18170,50 +18170,50 @@
         </is>
       </c>
       <c r="D199" s="6" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
+          <t>Fuxing Park</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H199" s="6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="I199" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J199" s="6" t="inlineStr">
+        <is>
           <t>Sinan Mansions</t>
         </is>
       </c>
-      <c r="F199" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G199" s="6" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="H199" s="6" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="I199" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J199" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L199" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M199" s="6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N199" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O199" s="6" t="n">
@@ -18221,20 +18221,20 @@
       </c>
       <c r="P199" s="6" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q199" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R199" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:59 → 14:58; ORDER 80 → 90</t>
+          <t>RETIME 21:42 → 14:00; ORDER 90 → 80</t>
         </is>
       </c>
       <c r="S199" s="7" t="inlineStr">
         <is>
-          <t>Travel guides advise 1-2h to walk the estate, admire the facades and browse boutiques/side galleries; 60min is the lower, unhurried-but-not-lingering end.</t>
+          <t>Guides say Fuxing Park is 'worth a 30-60 minute walk'; 45min lets you watch the dancing and chess without circling twice.</t>
         </is>
       </c>
       <c r="T199" s="6" t="inlineStr">
@@ -18258,50 +18258,50 @@
         </is>
       </c>
       <c r="D200" s="6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
+          <t>Sinan Mansions</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J200" s="6" t="inlineStr">
+        <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F200" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G200" s="6" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="H200" s="6" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="I200" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J200" s="6" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
       <c r="K200" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L200" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M200" s="6" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N200" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O200" s="6" t="n">
@@ -18309,20 +18309,20 @@
       </c>
       <c r="P200" s="6" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="Q200" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R200" s="7" t="inlineStr">
         <is>
-          <t>RETIME 00:10 → 18:00</t>
+          <t>RETIME 19:59 → 14:58; ORDER 80 → 90</t>
         </is>
       </c>
       <c r="S200" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Travel guides advise 1-2h to walk the estate, admire the facades and browse boutiques/side galleries; 60min is the lower, unhurried-but-not-lingering end.</t>
         </is>
       </c>
       <c r="T200" s="6" t="inlineStr">
@@ -18338,19 +18338,19 @@
         </is>
       </c>
       <c r="B201" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D201" s="6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F201" s="6" t="inlineStr">
@@ -18360,20 +18360,20 @@
       </c>
       <c r="G201" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H201" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I201" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J201" s="6" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K201" s="6" t="inlineStr">
@@ -18382,10 +18382,10 @@
         </is>
       </c>
       <c r="L201" s="6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M201" s="6" t="n">
-        <v>1.27</v>
+        <v>3.97</v>
       </c>
       <c r="N201" s="6" t="inlineStr">
         <is>
@@ -18393,24 +18393,24 @@
         </is>
       </c>
       <c r="O201" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P201" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="Q201" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R201" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 00:10 → 18:00</t>
         </is>
       </c>
       <c r="S201" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T201" s="6" t="inlineStr">
@@ -18434,46 +18434,46 @@
         </is>
       </c>
       <c r="D202" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="I202" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J202" s="6" t="inlineStr">
+        <is>
           <t>Yu Garden</t>
         </is>
       </c>
-      <c r="F202" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G202" s="6" t="inlineStr">
-        <is>
-          <t>07:51</t>
-        </is>
-      </c>
-      <c r="H202" s="6" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="I202" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J202" s="6" t="inlineStr">
-        <is>
-          <t>Mid-Lake Teahouse</t>
-        </is>
-      </c>
       <c r="K202" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L202" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M202" s="6" t="n">
-        <v>0.47</v>
+        <v>1.27</v>
       </c>
       <c r="N202" s="6" t="inlineStr">
         <is>
@@ -18485,25 +18485,25 @@
       </c>
       <c r="P202" s="6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q202" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="R202" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:41 → 07:51</t>
+          <t>RETIME 07:30 → 07:00</t>
         </is>
       </c>
       <c r="S202" s="7" t="inlineStr">
         <is>
-          <t>TripAdvisor/guide consensus is ~2h for a complete visit and 45-60min for a fast loop; at opening with fewer crowds, a highlights-plus circuit of the rockeries and pavilions is ~90min.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T202" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -18522,50 +18522,50 @@
         </is>
       </c>
       <c r="D203" s="6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
+          <t>Yu Garden</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G203" s="6" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="H203" s="6" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="I203" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J203" s="6" t="inlineStr">
+        <is>
           <t>Mid-Lake Teahouse</t>
         </is>
       </c>
-      <c r="F203" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G203" s="6" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="H203" s="6" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="I203" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J203" s="6" t="inlineStr">
-        <is>
-          <t>Yuyuan Bazaar</t>
-        </is>
-      </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
       <c r="L203" s="6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M203" s="6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="N203" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O203" s="6" t="n">
@@ -18573,25 +18573,25 @@
       </c>
       <c r="P203" s="6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q203" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R203" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:21 → 09:43; ORDER 40 → 30</t>
+          <t>RETIME 08:41 → 07:51</t>
         </is>
       </c>
       <c r="S203" s="7" t="inlineStr">
         <is>
-          <t>TripAdvisor reviewers report lingering 'an hour or two' over tea and the complimentary quail-egg/sweet snacks while watching the pond; 45min feels rushed for a set tea service.</t>
+          <t>TripAdvisor/guide consensus is ~2h for a complete visit and 45-60min for a fast loop; at opening with fewer crowds, a highlights-plus circuit of the rockeries and pavilions is ~90min.</t>
         </is>
       </c>
       <c r="T203" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -18610,11 +18610,11 @@
         </is>
       </c>
       <c r="D204" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>Yuyuan Bazaar</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
@@ -18624,12 +18624,12 @@
       </c>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="H204" s="6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I204" s="6" t="n">
@@ -18637,7 +18637,7 @@
       </c>
       <c r="J204" s="6" t="inlineStr">
         <is>
-          <t>City God Temple</t>
+          <t>Yuyuan Bazaar</t>
         </is>
       </c>
       <c r="K204" s="6" t="inlineStr">
@@ -18646,14 +18646,14 @@
         </is>
       </c>
       <c r="L204" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M204" s="6" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="N204" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O204" s="6" t="n">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="P204" s="6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q204" s="6" t="n">
@@ -18669,12 +18669,12 @@
       </c>
       <c r="R204" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:52 → 10:57; ORDER 30 → 40</t>
+          <t>RETIME 12:21 → 09:43; ORDER 40 → 30</t>
         </is>
       </c>
       <c r="S204" s="7" t="inlineStr">
         <is>
-          <t>Guides say you can 'easily spend an hour or two' in the bazaar alone (4h if you do garden, bazaar and dumpling houses together); 60min covers snacks and a souvenir sweep.</t>
+          <t>TripAdvisor reviewers report lingering 'an hour or two' over tea and the complimentary quail-egg/sweet snacks while watching the pond; 45min feels rushed for a set tea service.</t>
         </is>
       </c>
       <c r="T204" s="6" t="inlineStr">
@@ -18698,50 +18698,50 @@
         </is>
       </c>
       <c r="D205" s="6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
+          <t>Yuyuan Bazaar</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="I205" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J205" s="6" t="inlineStr">
+        <is>
           <t>City God Temple</t>
         </is>
       </c>
-      <c r="F205" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G205" s="6" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="H205" s="6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="I205" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J205" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L205" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M205" s="6" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="N205" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O205" s="6" t="n">
@@ -18749,20 +18749,20 @@
       </c>
       <c r="P205" s="6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="Q205" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R205" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:31 → 12:15</t>
+          <t>RETIME 10:52 → 10:57; ORDER 30 → 40</t>
         </is>
       </c>
       <c r="S205" s="7" t="inlineStr">
         <is>
-          <t>Guides quote 1-2h but that usually bundles the surrounding market; the walled temple itself (CNY10, 09:00-17:00) is compact and reads in ~45min.</t>
+          <t>Guides say you can 'easily spend an hour or two' in the bazaar alone (4h if you do garden, bazaar and dumpling houses together); 60min covers snacks and a souvenir sweep.</t>
         </is>
       </c>
       <c r="T205" s="6" t="inlineStr">
@@ -18786,50 +18786,50 @@
         </is>
       </c>
       <c r="D206" s="6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
+          <t>City God Temple</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="I206" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J206" s="6" t="inlineStr">
+        <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F206" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G206" s="6" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="H206" s="6" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="I206" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J206" s="6" t="inlineStr">
-        <is>
-          <t>People’s Square</t>
-        </is>
-      </c>
       <c r="K206" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L206" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M206" s="6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="N206" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O206" s="6" t="n">
@@ -18837,20 +18837,20 @@
       </c>
       <c r="P206" s="6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="Q206" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R206" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:27 → 13:08</t>
+          <t>RETIME 13:31 → 12:15</t>
         </is>
       </c>
       <c r="S206" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Guides quote 1-2h but that usually bundles the surrounding market; the walled temple itself (CNY10, 09:00-17:00) is compact and reads in ~45min.</t>
         </is>
       </c>
       <c r="T206" s="6" t="inlineStr">
@@ -18874,46 +18874,46 @@
         </is>
       </c>
       <c r="D207" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J207" s="6" t="inlineStr">
+        <is>
           <t>People’s Square</t>
         </is>
       </c>
-      <c r="F207" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G207" s="6" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="H207" s="6" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="I207" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J207" s="6" t="inlineStr">
-        <is>
-          <t>Huangpu night cruise</t>
-        </is>
-      </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="L207" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M207" s="6" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="N207" s="6" t="inlineStr">
         <is>
@@ -18925,20 +18925,20 @@
       </c>
       <c r="P207" s="6" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="Q207" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R207" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:39 → 14:25</t>
+          <t>RETIME 15:27 → 13:08</t>
         </is>
       </c>
       <c r="S207" s="7" t="inlineStr">
         <is>
-          <t>TripAdvisor reviews split between '10 minutes is plenty' for the plaza and 2-4h if you linger in People's Park; 45min suits its role here as a stroll-and-rest buffer.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T207" s="6" t="inlineStr">
@@ -18962,50 +18962,50 @@
         </is>
       </c>
       <c r="D208" s="6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
+          <t>People’s Square</t>
+        </is>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G208" s="6" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="H208" s="6" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J208" s="6" t="inlineStr">
+        <is>
           <t>Huangpu night cruise</t>
         </is>
       </c>
-      <c r="F208" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G208" s="6" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="H208" s="6" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="I208" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="J208" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K208" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L208" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M208" s="6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="N208" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O208" s="6" t="n">
@@ -19013,25 +19013,25 @@
       </c>
       <c r="P208" s="6" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="Q208" s="6" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="R208" s="7" t="inlineStr">
         <is>
-          <t>RETIME 22:52 → 15:28; ORDER 100 → 80</t>
+          <t>RETIME 16:39 → 14:25</t>
         </is>
       </c>
       <c r="S208" s="7" t="inlineStr">
         <is>
-          <t>Operators list the standard Shiliupu night cruise at 45-50min afloat; ticket redemption, security and boarding queues at the wharf add ~25min.</t>
+          <t>TripAdvisor reviews split between '10 minutes is plenty' for the plaza and 2-4h if you linger in People's Park; 45min suits its role here as a stroll-and-rest buffer.</t>
         </is>
       </c>
       <c r="T208" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -19050,50 +19050,50 @@
         </is>
       </c>
       <c r="D209" s="6" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
+          <t>Huangpu night cruise</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="H209" s="6" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="I209" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J209" s="6" t="inlineStr">
+        <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F209" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G209" s="6" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="H209" s="6" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="I209" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J209" s="6" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L209" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M209" s="6" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="N209" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O209" s="6" t="n">
@@ -19101,25 +19101,25 @@
       </c>
       <c r="P209" s="6" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="Q209" s="6" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="R209" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:13 → 18:00</t>
+          <t>RETIME 22:52 → 15:28; ORDER 100 → 80</t>
         </is>
       </c>
       <c r="S209" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Operators list the standard Shiliupu night cruise at 45-50min afloat; ticket redemption, security and boarding queues at the wharf add ~25min.</t>
         </is>
       </c>
       <c r="T209" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -19130,19 +19130,19 @@
         </is>
       </c>
       <c r="B210" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C210" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D210" s="6" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
@@ -19152,32 +19152,32 @@
       </c>
       <c r="G210" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H210" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I210" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J210" s="6" t="inlineStr">
         <is>
-          <t>TANK Shanghai</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K210" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L210" s="6" t="n">
         <v>19</v>
       </c>
       <c r="M210" s="6" t="n">
-        <v>8.6</v>
+        <v>0.77</v>
       </c>
       <c r="N210" s="6" t="inlineStr">
         <is>
@@ -19185,24 +19185,24 @@
         </is>
       </c>
       <c r="O210" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P210" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q210" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R210" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 21:13 → 18:00</t>
         </is>
       </c>
       <c r="S210" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T210" s="6" t="inlineStr">
@@ -19226,46 +19226,46 @@
         </is>
       </c>
       <c r="D211" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H211" s="6" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="I211" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J211" s="6" t="inlineStr">
+        <is>
           <t>TANK Shanghai</t>
         </is>
       </c>
-      <c r="F211" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G211" s="6" t="inlineStr">
-        <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="H211" s="6" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="I211" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="J211" s="6" t="inlineStr">
-        <is>
-          <t>West Bund Museum</t>
-        </is>
-      </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L211" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M211" s="6" t="n">
-        <v>0.64</v>
+        <v>8.6</v>
       </c>
       <c r="N211" s="6" t="inlineStr">
         <is>
@@ -19277,20 +19277,20 @@
       </c>
       <c r="P211" s="6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q211" s="6" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="R211" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:02 → 08:02; ORDER 50 → 20</t>
+          <t>RETIME 07:30 → 07:00</t>
         </is>
       </c>
       <c r="S211" s="7" t="inlineStr">
         <is>
-          <t>Some visitors suggest half a day, but TripAdvisor reviews repeatedly call the exhibits limited for the ticket price; the tanks plus the wrapping park read in about 75min.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T211" s="6" t="inlineStr">
@@ -19314,50 +19314,50 @@
         </is>
       </c>
       <c r="D212" s="6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
+          <t>TANK Shanghai</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="H212" s="6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="I212" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J212" s="6" t="inlineStr">
+        <is>
           <t>West Bund Museum</t>
         </is>
       </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G212" s="6" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="H212" s="6" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="I212" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J212" s="6" t="inlineStr">
-        <is>
-          <t>West Bund riverside</t>
-        </is>
-      </c>
       <c r="K212" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L212" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M212" s="6" t="n">
-        <v>1.8</v>
+        <v>0.64</v>
       </c>
       <c r="N212" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O212" s="6" t="n">
@@ -19365,20 +19365,20 @@
       </c>
       <c r="P212" s="6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="Q212" s="6" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="R212" s="7" t="inlineStr">
         <is>
-          <t>RETIME 11:13 → 09:42</t>
+          <t>RETIME 17:02 → 08:02; ORDER 50 → 20</t>
         </is>
       </c>
       <c r="S212" s="7" t="inlineStr">
         <is>
-          <t>Museum lists 11:00-18:00 with last entry 17:00 across a modest number of galleries; guides recommend several hours only for major shows, so a highlights-plus visit is ~90min.</t>
+          <t>Some visitors suggest half a day, but TripAdvisor reviews repeatedly call the exhibits limited for the ticket price; the tanks plus the wrapping park read in about 75min.</t>
         </is>
       </c>
       <c r="T212" s="6" t="inlineStr">
@@ -19402,50 +19402,50 @@
         </is>
       </c>
       <c r="D213" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
+          <t>West Bund Museum</t>
+        </is>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="H213" s="6" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="I213" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J213" s="6" t="inlineStr">
+        <is>
           <t>West Bund riverside</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G213" s="6" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="H213" s="6" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="I213" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J213" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="L213" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M213" s="6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="N213" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O213" s="6" t="n">
@@ -19453,25 +19453,25 @@
       </c>
       <c r="P213" s="6" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="Q213" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R213" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:50 → 11:35; ORDER 20 → 40</t>
+          <t>RETIME 11:13 → 09:42</t>
         </is>
       </c>
       <c r="S213" s="7" t="inlineStr">
         <is>
-          <t>No dedicated dwell figure found; the Xuhui riverside corridor linking the museums is a 10-15min walk each way, so ~45min allows an unhurried stroll with stops between venues.</t>
+          <t>Museum lists 11:00-18:00 with last entry 17:00 across a modest number of galleries; guides recommend several hours only for major shows, so a highlights-plus visit is ~90min.</t>
         </is>
       </c>
       <c r="T213" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -19490,50 +19490,50 @@
         </is>
       </c>
       <c r="D214" s="6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
+          <t>West Bund riverside</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="H214" s="6" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="I214" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J214" s="6" t="inlineStr">
+        <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G214" s="6" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="H214" s="6" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="I214" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J214" s="6" t="inlineStr">
-        <is>
-          <t>Long Museum West Bund</t>
-        </is>
-      </c>
       <c r="K214" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L214" s="6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M214" s="6" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="N214" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O214" s="6" t="n">
@@ -19541,25 +19541,25 @@
       </c>
       <c r="P214" s="6" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q214" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R214" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:48 → 12:28; ORDER 60 → 50</t>
+          <t>RETIME 08:50 → 11:35; ORDER 20 → 40</t>
         </is>
       </c>
       <c r="S214" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>No dedicated dwell figure found; the Xuhui riverside corridor linking the museums is a 10-15min walk each way, so ~45min allows an unhurried stroll with stops between venues.</t>
         </is>
       </c>
       <c r="T214" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -19578,50 +19578,50 @@
         </is>
       </c>
       <c r="D215" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="H215" s="6" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="I215" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="J215" s="6" t="inlineStr">
         <is>
           <t>Long Museum West Bund</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G215" s="6" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="H215" s="6" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="I215" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J215" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L215" s="6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M215" s="6" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="N215" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O215" s="6" t="n">
@@ -19629,20 +19629,20 @@
       </c>
       <c r="P215" s="6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="Q215" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R215" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:06 → 13:53; ORDER 40 → 60</t>
+          <t>RETIME 19:48 → 12:28; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S215" s="7" t="inlineStr">
         <is>
-          <t>TripAdvisor reviewers say 'about an hour to see it', some 'squeeze in two hours', and guides suggest 3-4h only for a blockbuster temporary show; 90min is the unhurried middle.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T215" s="6" t="inlineStr">
@@ -19666,26 +19666,26 @@
         </is>
       </c>
       <c r="D216" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Long Museum West Bund</t>
         </is>
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G216" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I216" s="6" t="n">
@@ -19693,23 +19693,23 @@
       </c>
       <c r="J216" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K216" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L216" s="6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M216" s="6" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="N216" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O216" s="6" t="n">
@@ -19717,7 +19717,7 @@
       </c>
       <c r="P216" s="6" t="inlineStr">
         <is>
-          <t>02:44</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="Q216" s="6" t="n">
@@ -19725,12 +19725,12 @@
       </c>
       <c r="R216" s="7" t="inlineStr">
         <is>
-          <t>RETIME 02:44 → 18:00; ORDER 110 → 70</t>
+          <t>RETIME 14:06 → 13:53; ORDER 40 → 60</t>
         </is>
       </c>
       <c r="S216" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>TripAdvisor reviewers say 'about an hour to see it', some 'squeeze in two hours', and guides suggest 3-4h only for a blockbuster temporary show; 90min is the unhurried middle.</t>
         </is>
       </c>
       <c r="T216" s="6" t="inlineStr">
@@ -19746,19 +19746,19 @@
         </is>
       </c>
       <c r="B217" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D217" s="6" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F217" s="6" t="inlineStr">
@@ -19768,20 +19768,20 @@
       </c>
       <c r="G217" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H217" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I217" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J217" s="6" t="inlineStr">
         <is>
-          <t>Shanghai Museum East</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K217" s="6" t="inlineStr">
@@ -19793,7 +19793,7 @@
         <v>17</v>
       </c>
       <c r="M217" s="6" t="n">
-        <v>6.62</v>
+        <v>6.75</v>
       </c>
       <c r="N217" s="6" t="inlineStr">
         <is>
@@ -19801,24 +19801,24 @@
         </is>
       </c>
       <c r="O217" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P217" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>02:44</t>
         </is>
       </c>
       <c r="Q217" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R217" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 02:44 → 18:00; ORDER 110 → 70</t>
         </is>
       </c>
       <c r="S217" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T217" s="6" t="inlineStr">
@@ -19842,46 +19842,46 @@
         </is>
       </c>
       <c r="D218" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G218" s="6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H218" s="6" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="I218" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J218" s="6" t="inlineStr">
+        <is>
           <t>Shanghai Museum East</t>
         </is>
       </c>
-      <c r="F218" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G218" s="6" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H218" s="6" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="I218" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="J218" s="6" t="inlineStr">
-        <is>
-          <t>Shanghai Tower base</t>
-        </is>
-      </c>
       <c r="K218" s="6" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="L218" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M218" s="6" t="n">
-        <v>3.63</v>
+        <v>6.62</v>
       </c>
       <c r="N218" s="6" t="inlineStr">
         <is>
@@ -19893,25 +19893,25 @@
       </c>
       <c r="P218" s="6" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q218" s="6" t="n">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="R218" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:21 → 08:00; ORDER 30 → 20</t>
+          <t>RETIME 07:30 → 07:00</t>
         </is>
       </c>
       <c r="S218" s="7" t="inlineStr">
         <is>
-          <t>Guides advise at least 2-3h and recommend 3-4h (3-5h thorough) for 20 halls; 3 focused hours covers the headline galleries plus one temporary show.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T218" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -19930,46 +19930,46 @@
         </is>
       </c>
       <c r="D219" s="6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
+          <t>Shanghai Museum East</t>
+        </is>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G219" s="6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="H219" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="I219" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="J219" s="6" t="inlineStr">
+        <is>
           <t>Shanghai Tower base</t>
         </is>
       </c>
-      <c r="F219" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G219" s="6" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="H219" s="6" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="I219" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J219" s="6" t="inlineStr">
-        <is>
-          <t>World Financial Center</t>
-        </is>
-      </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L219" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M219" s="6" t="n">
-        <v>0.17</v>
+        <v>3.63</v>
       </c>
       <c r="N219" s="6" t="inlineStr">
         <is>
@@ -19977,29 +19977,29 @@
         </is>
       </c>
       <c r="O219" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P219" s="6" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q219" s="6" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="R219" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 5 → 6; RETIME 21:36 → 11:20; ORDER 80 → 30</t>
+          <t>RETIME 13:21 → 08:00; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S219" s="7" t="inlineStr">
         <is>
-          <t>No published dwell time; the ground plaza and Exit 9A photo spot are the documented ground-level draws, and a walk around the base with photos is ~30min.</t>
+          <t>Guides advise at least 2-3h and recommend 3-4h (3-5h thorough) for 20 halls; 3 focused hours covers the headline galleries plus one temporary show.</t>
         </is>
       </c>
       <c r="T219" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -20018,11 +20018,11 @@
         </is>
       </c>
       <c r="D220" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>World Financial Center</t>
+          <t>Shanghai Tower base</t>
         </is>
       </c>
       <c r="F220" s="6" t="inlineStr">
@@ -20032,12 +20032,12 @@
       </c>
       <c r="G220" s="6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="H220" s="6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="I220" s="6" t="n">
@@ -20045,23 +20045,23 @@
       </c>
       <c r="J220" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>World Financial Center</t>
         </is>
       </c>
       <c r="K220" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L220" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M220" s="6" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="N220" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O220" s="6" t="n">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P220" s="6" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="Q220" s="6" t="n">
@@ -20077,17 +20077,17 @@
       </c>
       <c r="R220" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 5 → 6; RETIME 01:05 → 12:06; ORDER 100 → 40</t>
+          <t>MOVE day 5 → 6; RETIME 21:36 → 11:20; ORDER 80 → 30</t>
         </is>
       </c>
       <c r="S220" s="7" t="inlineStr">
         <is>
-          <t>Exterior stop per the note; the 94/97/100F observatory would instead need 1-2h (30min on 94F, 20min on 97F, 1-1.5h on 100F) plus ticket and lift queues.</t>
+          <t>No published dwell time; the ground plaza and Exit 9A photo spot are the documented ground-level draws, and a walk around the base with photos is ~30min.</t>
         </is>
       </c>
       <c r="T220" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -20106,71 +20106,71 @@
         </is>
       </c>
       <c r="D221" s="6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
+          <t>World Financial Center</t>
+        </is>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G221" s="6" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="H221" s="6" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="I221" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J221" s="6" t="inlineStr">
+        <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F221" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G221" s="6" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="H221" s="6" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="I221" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J221" s="6" t="inlineStr">
-        <is>
-          <t>Jin Mao Tower</t>
-        </is>
-      </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L221" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M221" s="6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N221" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O221" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P221" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="Q221" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="R221" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 12:44; ORDER 20 → 50</t>
+          <t>MOVE day 5 → 6; RETIME 01:05 → 12:06; ORDER 100 → 40</t>
         </is>
       </c>
       <c r="S221" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Exterior stop per the note; the 94/97/100F observatory would instead need 1-2h (30min on 94F, 20min on 97F, 1-1.5h on 100F) plus ticket and lift queues.</t>
         </is>
       </c>
       <c r="T221" s="6" t="inlineStr">
@@ -20194,71 +20194,71 @@
         </is>
       </c>
       <c r="D222" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F222" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G222" s="6" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="H222" s="6" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="I222" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="J222" s="6" t="inlineStr">
         <is>
           <t>Jin Mao Tower</t>
         </is>
       </c>
-      <c r="F222" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G222" s="6" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="H222" s="6" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="I222" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J222" s="6" t="inlineStr">
-        <is>
-          <t>Oriental Pearl Tower</t>
-        </is>
-      </c>
       <c r="K222" s="6" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
       <c r="L222" s="6" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M222" s="6" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="N222" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O222" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P222" s="6" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q222" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="R222" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 5 → 6; RETIME 23:19 → 14:00; ORDER 90 → 60</t>
+          <t>RETIME 12:00 → 12:44; ORDER 20 → 50</t>
         </is>
       </c>
       <c r="S222" s="7" t="inlineStr">
         <is>
-          <t>Treated per the note as an exterior stop; going up would be different — the 88F deck is quoted at 2-3h and the Skywalk session alone is 45min plus 30min security check-in.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T222" s="6" t="inlineStr">
@@ -20282,11 +20282,11 @@
         </is>
       </c>
       <c r="D223" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Oriental Pearl Tower</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="F223" s="6" t="inlineStr">
@@ -20296,12 +20296,12 @@
       </c>
       <c r="G223" s="6" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H223" s="6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="I223" s="6" t="n">
@@ -20309,7 +20309,7 @@
       </c>
       <c r="J223" s="6" t="inlineStr">
         <is>
-          <t>Pudong promenade</t>
+          <t>Oriental Pearl Tower</t>
         </is>
       </c>
       <c r="K223" s="6" t="inlineStr">
@@ -20318,22 +20318,22 @@
         </is>
       </c>
       <c r="L223" s="6" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="M223" s="6" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="N223" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O223" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P223" s="6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="Q223" s="6" t="n">
@@ -20341,12 +20341,12 @@
       </c>
       <c r="R223" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:30 → 14:57; ORDER 50 → 70</t>
+          <t>MOVE day 5 → 6; RETIME 23:19 → 14:00; ORDER 90 → 60</t>
         </is>
       </c>
       <c r="S223" s="7" t="inlineStr">
         <is>
-          <t>Exterior-only per the note, so a photo stop at the base; ascending instead runs 1-2h on the decks and 2-3h with the museum, plus 15-60min ticket and 10-60min lift queues.</t>
+          <t>Treated per the note as an exterior stop; going up would be different — the 88F deck is quoted at 2-3h and the Skywalk session alone is 45min plus 30min security check-in.</t>
         </is>
       </c>
       <c r="T223" s="6" t="inlineStr">
@@ -20370,50 +20370,50 @@
         </is>
       </c>
       <c r="D224" s="6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
+          <t>Oriental Pearl Tower</t>
+        </is>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G224" s="6" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="H224" s="6" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="I224" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J224" s="6" t="inlineStr">
+        <is>
           <t>Pudong promenade</t>
         </is>
       </c>
-      <c r="F224" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G224" s="6" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="H224" s="6" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
-      <c r="I224" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J224" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K224" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L224" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M224" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N224" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O224" s="6" t="n">
@@ -20421,20 +20421,20 @@
       </c>
       <c r="P224" s="6" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="Q224" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="R224" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:21 → 15:36; ORDER 40 → 80</t>
+          <t>RETIME 17:30 → 14:57; ORDER 50 → 70</t>
         </is>
       </c>
       <c r="S224" s="7" t="inlineStr">
         <is>
-          <t>Binjiang Avenue full route logs are 7.7km/2h, but the Lujiazui section fronting the towers is a fraction of that; TripAdvisor describes it as a short skyline stroll of ~45min.</t>
+          <t>Exterior-only per the note, so a photo stop at the base; ascending instead runs 1-2h on the decks and 2-3h with the museum, plus 15-60min ticket and 10-60min lift queues.</t>
         </is>
       </c>
       <c r="T224" s="6" t="inlineStr">
@@ -20458,50 +20458,50 @@
         </is>
       </c>
       <c r="D225" s="6" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
+          <t>Pudong promenade</t>
+        </is>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G225" s="6" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="H225" s="6" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="I225" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J225" s="6" t="inlineStr">
+        <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F225" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G225" s="6" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="H225" s="6" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="I225" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J225" s="6" t="inlineStr">
-        <is>
-          <t>Fly from PVG</t>
-        </is>
-      </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L225" s="6" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M225" s="6" t="n">
-        <v>31.45</v>
+        <v>0</v>
       </c>
       <c r="N225" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O225" s="6" t="n">
@@ -20509,20 +20509,20 @@
       </c>
       <c r="P225" s="6" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="Q225" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="R225" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:48 → 18:00; ORDER 60 → 90</t>
+          <t>RETIME 16:21 → 15:36; ORDER 40 → 80</t>
         </is>
       </c>
       <c r="S225" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Binjiang Avenue full route logs are 7.7km/2h, but the Lujiazui section fronting the towers is a fraction of that; TripAdvisor describes it as a short skyline stroll of ~45min.</t>
         </is>
       </c>
       <c r="T225" s="6" t="inlineStr">
@@ -20546,69 +20546,157 @@
         </is>
       </c>
       <c r="D226" s="6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G226" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H226" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="I226" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J226" s="6" t="inlineStr">
+        <is>
           <t>Fly from PVG</t>
         </is>
       </c>
-      <c r="F226" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="G226" s="6" t="inlineStr">
-        <is>
-          <t>23:10</t>
-        </is>
-      </c>
-      <c r="H226" s="6" t="inlineStr">
-        <is>
-          <t>02:10 (+1)</t>
-        </is>
-      </c>
-      <c r="I226" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="J226" s="6" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
-      <c r="K226" s="6" t="inlineStr"/>
-      <c r="L226" s="6" t="inlineStr"/>
-      <c r="M226" s="6" t="inlineStr"/>
-      <c r="N226" s="6" t="inlineStr"/>
+      <c r="K226" s="6" t="inlineStr">
+        <is>
+          <t>didi</t>
+        </is>
+      </c>
+      <c r="L226" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="M226" s="6" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="N226" s="6" t="inlineStr">
+        <is>
+          <t>estimated (fitted model)</t>
+        </is>
+      </c>
       <c r="O226" s="6" t="n">
         <v>6</v>
       </c>
       <c r="P226" s="6" t="inlineStr">
         <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="Q226" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="R226" s="7" t="inlineStr">
+        <is>
+          <t>RETIME 19:48 → 18:00; ORDER 60 → 90</t>
+        </is>
+      </c>
+      <c r="S226" s="7" t="inlineStr">
+        <is>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+        </is>
+      </c>
+      <c r="T226" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D227" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>Fly from PVG</t>
+        </is>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="G227" s="6" t="inlineStr">
+        <is>
           <t>23:10</t>
         </is>
       </c>
-      <c r="Q226" s="6" t="n">
+      <c r="H227" s="6" t="inlineStr">
+        <is>
+          <t>02:10 (+1)</t>
+        </is>
+      </c>
+      <c r="I227" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="R226" s="7" t="inlineStr">
+      <c r="J227" s="6" t="inlineStr">
+        <is>
+          <t>Hotel (home)</t>
+        </is>
+      </c>
+      <c r="K227" s="6" t="inlineStr"/>
+      <c r="L227" s="6" t="inlineStr"/>
+      <c r="M227" s="6" t="inlineStr"/>
+      <c r="N227" s="6" t="inlineStr"/>
+      <c r="O227" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P227" s="6" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="Q227" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="R227" s="7" t="inlineStr">
         <is>
           <t>ORDER 70 → 100</t>
         </is>
       </c>
-      <c r="S226" s="7" t="inlineStr">
+      <c r="S227" s="7" t="inlineStr">
         <is>
           <t>PVG guidance is to arrive 3h before an international departure (check-in closes 60min out), with Aug listed among the airport's busiest months; matches the note's 23:10 for a 02:10 flight.</t>
         </is>
       </c>
-      <c r="T226" s="6" t="inlineStr">
+      <c r="T227" s="6" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T226"/>
+  <autoFilter ref="A1:T227"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23415,12 +23503,12 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>06:13</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="I32" s="6" t="n">
@@ -23460,7 +23548,7 @@
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>RETIME 05:39 → 05:38</t>
+          <t>RETIME 05:39 → 05:30</t>
         </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
@@ -28319,12 +28407,12 @@
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="I88" s="6" t="n">
@@ -28364,7 +28452,7 @@
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>RETIME 06:54 → 06:38</t>
+          <t>RETIME 06:54 → 06:30</t>
         </is>
       </c>
       <c r="S88" s="7" t="inlineStr">
@@ -30235,12 +30323,12 @@
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="I110" s="6" t="n">
@@ -30280,7 +30368,7 @@
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>RETIME 05:30 → 06:38</t>
+          <t>RETIME 05:30 → 06:30</t>
         </is>
       </c>
       <c r="S110" s="7" t="inlineStr">
@@ -32159,12 +32247,12 @@
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I132" s="6" t="n">
@@ -32204,7 +32292,7 @@
       </c>
       <c r="R132" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:08</t>
+          <t>RETIME 07:30 → 07:00</t>
         </is>
       </c>
       <c r="S132" s="7" t="inlineStr">
@@ -35712,23 +35800,23 @@
       </c>
       <c r="J173" s="6" t="inlineStr">
         <is>
-          <t>Li River night walk</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L173" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M173" s="6" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="N173" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O173" s="6" t="n">
@@ -35777,72 +35865,72 @@
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="I174" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J174" s="6" t="inlineStr">
+        <is>
           <t>Li River night walk</t>
         </is>
       </c>
-      <c r="F174" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G174" s="6" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="H174" s="6" t="inlineStr">
-        <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="I174" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J174" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K174" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L174" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M174" s="6" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="N174" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O174" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P174" s="6" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="Q174" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R174" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 1; RETIME 19:58 → 17:53; ORDER 80 → 50</t>
+          <t>RETIME 20:09 → 17:35; ORDER 70 → 50</t>
         </is>
       </c>
       <c r="S174" s="7" t="inlineStr">
         <is>
-          <t>Optional after-dinner stroll on the Yangshuo riverfront promenade; no fixed route, and 30-45 min covers the illuminated stretch near West Street.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T174" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -35865,17 +35953,17 @@
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Li River night walk</t>
         </is>
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="H175" s="6" t="inlineStr">
@@ -35884,7 +35972,7 @@
         </is>
       </c>
       <c r="I175" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="J175" s="6" t="inlineStr">
         <is>
@@ -35908,29 +35996,29 @@
         </is>
       </c>
       <c r="O175" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P175" s="6" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="Q175" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="R175" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:09 → 18:46; ORDER 70 → 60</t>
+          <t>MOVE day 2 → 1; RETIME 19:58 → 19:31; ORDER 80 → 60</t>
         </is>
       </c>
       <c r="S175" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Optional after-dinner stroll on the Yangshuo riverfront promenade; no fixed route, and 30-45 min covers the illuminated stretch near West Street.</t>
         </is>
       </c>
       <c r="T175" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -36240,23 +36328,23 @@
       </c>
       <c r="J179" s="6" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L179" s="6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M179" s="6" t="n">
-        <v>17.39</v>
+        <v>0</v>
       </c>
       <c r="N179" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O179" s="6" t="n">
@@ -36305,30 +36393,30 @@
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="H180" s="6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="I180" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J180" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K180" s="6" t="inlineStr">
@@ -36348,29 +36436,29 @@
         </is>
       </c>
       <c r="O180" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P180" s="6" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q180" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R180" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 1 → 2; RETIME 21:48 → 10:35; ORDER 80 → 50</t>
+          <t>ORDER 40 → 50</t>
         </is>
       </c>
       <c r="S180" s="7" t="inlineStr">
         <is>
-          <t>Show runs ~70 min (operators quote 60-70); the venue advises arriving well before curtain and the 2,000+ seat amphitheatre empties slowly, so allow ~20 min of seating and exit.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T180" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -36393,7 +36481,7 @@
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F181" s="6" t="inlineStr">
@@ -36403,36 +36491,36 @@
       </c>
       <c r="G181" s="6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I181" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J181" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L181" s="6" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M181" s="6" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="N181" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O181" s="6" t="n">
@@ -36440,20 +36528,20 @@
       </c>
       <c r="P181" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q181" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R181" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 12:13; ORDER 40 → 60</t>
+          <t>ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S181" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T181" s="6" t="inlineStr">
@@ -36463,88 +36551,88 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="8" t="inlineStr">
+      <c r="A182" s="6" t="inlineStr">
         <is>
           <t>Yangshuo</t>
         </is>
       </c>
-      <c r="B182" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C182" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="D182" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="E182" s="8" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
-      <c r="F182" s="8" t="inlineStr">
+      <c r="B182" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="G182" s="8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="H182" s="8" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="I182" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="J182" s="8" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
-      <c r="K182" s="8" t="inlineStr">
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="I182" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J182" s="6" t="inlineStr">
+        <is>
+          <t>Yulong bamboo rafting</t>
+        </is>
+      </c>
+      <c r="K182" s="6" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
-      <c r="L182" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="M182" s="8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="N182" s="8" t="inlineStr">
+      <c r="L182" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="M182" s="6" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="N182" s="6" t="inlineStr">
         <is>
           <t>estimated (fitted model)</t>
         </is>
       </c>
-      <c r="O182" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P182" s="8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="Q182" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="R182" s="9" t="inlineStr">
-        <is>
-          <t>no change</t>
-        </is>
-      </c>
-      <c r="S182" s="9" t="inlineStr">
-        <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
-        </is>
-      </c>
-      <c r="T182" s="8" t="inlineStr">
+      <c r="O182" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P182" s="6" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Q182" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="R182" s="7" t="inlineStr">
+        <is>
+          <t>RETIME 07:30 → 08:00</t>
+        </is>
+      </c>
+      <c r="S182" s="7" t="inlineStr">
+        <is>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+        </is>
+      </c>
+      <c r="T182" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
@@ -36565,34 +36653,34 @@
         </is>
       </c>
       <c r="D183" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Yulong bamboo rafting</t>
         </is>
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I183" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J183" s="6" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="K183" s="6" t="inlineStr">
@@ -36612,29 +36700,29 @@
         </is>
       </c>
       <c r="O183" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P183" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="Q183" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R183" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>MOVE day 2 → 3; RETIME 08:55 → 09:30; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S183" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Route tables for Yulong rafting list Jinlong Bridge to Jiuxian as 6 km / 90 min, the longest and most popular section with its nine small weirs.</t>
         </is>
       </c>
       <c r="T183" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -36653,11 +36741,11 @@
         </is>
       </c>
       <c r="D184" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
@@ -36667,36 +36755,36 @@
       </c>
       <c r="G184" s="6" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I184" s="6" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="J184" s="6" t="inlineStr">
         <is>
-          <t>Yulong valley cycling</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K184" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L184" s="6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M184" s="6" t="n">
-        <v>6.53</v>
+        <v>0</v>
       </c>
       <c r="N184" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O184" s="6" t="n">
@@ -36704,20 +36792,20 @@
       </c>
       <c r="P184" s="6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="Q184" s="6" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="R184" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 08:55 → 07:59; ORDER 30 → 20</t>
+          <t>MOVE day 2 → 3; RETIME 13:28 → 11:24; ORDER 50 → 30</t>
         </is>
       </c>
       <c r="S184" s="7" t="inlineStr">
         <is>
-          <t>Route tables for Yulong rafting list Jinlong Bridge to Jiuxian as 6 km / 90 min, the longest and most popular section with its nine small weirs.</t>
+          <t>The West Street round-trip loop through the Shili Gallery / Jiuxian-Chaoyang Weir section is 19 km and quoted at 2-3 hrs by cycling guides, including photo and drink stops.</t>
         </is>
       </c>
       <c r="T184" s="6" t="inlineStr">
@@ -36741,76 +36829,76 @@
         </is>
       </c>
       <c r="D185" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>Yulong valley cycling</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G185" s="6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I185" s="6" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="J185" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Moon Hill</t>
         </is>
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L185" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M185" s="6" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="N185" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O185" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P185" s="6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q185" s="6" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="R185" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 13:28 → 09:53; ORDER 50 → 30</t>
+          <t>RETIME 12:00 → 14:02</t>
         </is>
       </c>
       <c r="S185" s="7" t="inlineStr">
         <is>
-          <t>The West Street round-trip loop through the Shili Gallery / Jiuxian-Chaoyang Weir section is 19 km and quoted at 2-3 hrs by cycling guides, including photo and drink stops.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T185" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -36829,71 +36917,71 @@
         </is>
       </c>
       <c r="D186" s="6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Moon Hill</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="H186" s="6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I186" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J186" s="6" t="inlineStr">
         <is>
-          <t>Moon Hill</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K186" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L186" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M186" s="6" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="N186" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O186" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P186" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="Q186" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R186" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 12:31</t>
+          <t>MOVE day 2 → 3; RETIME 16:01 → 15:35; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S186" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>800+ stone steps; guides quote ~30-40 min to the arch (China Highlights says ~1 hr to the top), plus time at the arch and the descent, and August heat slows everyone down.</t>
         </is>
       </c>
       <c r="T186" s="6" t="inlineStr">
@@ -36917,26 +37005,26 @@
         </is>
       </c>
       <c r="D187" s="6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>Moon Hill</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I187" s="6" t="n">
@@ -36944,31 +37032,31 @@
       </c>
       <c r="J187" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L187" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M187" s="6" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="N187" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O187" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P187" s="6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q187" s="6" t="n">
@@ -36976,12 +37064,12 @@
       </c>
       <c r="R187" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 16:01 → 14:04; ORDER 60 → 50</t>
+          <t>RETIME 18:00 → 17:13; ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S187" s="7" t="inlineStr">
         <is>
-          <t>800+ stone steps; guides quote ~30-40 min to the arch (China Highlights says ~1 hr to the top), plus time at the arch and the descent, and August heat slows everyone down.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T187" s="6" t="inlineStr">
@@ -37005,26 +37093,26 @@
         </is>
       </c>
       <c r="D188" s="6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="H188" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I188" s="6" t="n">
@@ -37041,10 +37129,10 @@
         </is>
       </c>
       <c r="L188" s="6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M188" s="6" t="n">
-        <v>6.23</v>
+        <v>1.42</v>
       </c>
       <c r="N188" s="6" t="inlineStr">
         <is>
@@ -37052,11 +37140,11 @@
         </is>
       </c>
       <c r="O188" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P188" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="Q188" s="6" t="n">
@@ -37064,17 +37152,17 @@
       </c>
       <c r="R188" s="7" t="inlineStr">
         <is>
-          <t>ORDER 50 → 60</t>
+          <t>MOVE day 1 → 3; RETIME 21:48 → 19:45; ORDER 80 → 70</t>
         </is>
       </c>
       <c r="S188" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Show runs ~70 min (operators quote 60-70); the venue advises arriving well before curtain and the 2,000+ seat amphitheatre empties slowly, so allow ~20 min of seating and exit.</t>
         </is>
       </c>
       <c r="T188" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -37107,12 +37195,12 @@
       </c>
       <c r="G189" s="6" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="H189" s="6" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="I189" s="6" t="n">
@@ -37152,7 +37240,7 @@
       </c>
       <c r="R189" s="7" t="inlineStr">
         <is>
-          <t>RETIME 06:09 → 05:50</t>
+          <t>RETIME 06:09 → 05:30</t>
         </is>
       </c>
       <c r="S189" s="7" t="inlineStr">
@@ -43098,14 +43186,14 @@
         <v>1</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>90</v>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 1 → 2</t>
+          <t>Change this page's day: 1 → 3</t>
         </is>
       </c>
     </row>
@@ -43117,21 +43205,21 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Xingping Ancient Town</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="E21" s="12" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 2 → 3</t>
+          <t>Change this page's day: 3 → 2</t>
         </is>
       </c>
     </row>
@@ -43143,21 +43231,21 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Yulong valley cycling</t>
+          <t>20-RMB viewpoint</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="E22" s="12" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 2 → 3</t>
+          <t>Change this page's day: 3 → 2</t>
         </is>
       </c>
     </row>
@@ -43169,7 +43257,7 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Moon Hill</t>
+          <t>Yulong bamboo rafting</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
@@ -43195,21 +43283,21 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Li River night walk</t>
+          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 2 → 1</t>
+          <t>Change this page's day: 2 → 3</t>
         </is>
       </c>
     </row>
@@ -43221,21 +43309,21 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Xingping Ancient Town</t>
+          <t>Moon Hill</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="E25" s="12" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 3 → 2</t>
+          <t>Change this page's day: 2 → 3</t>
         </is>
       </c>
     </row>
@@ -43247,21 +43335,21 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>20-RMB viewpoint</t>
+          <t>Li River night walk</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 3 → 2</t>
+          <t>Change this page's day: 2 → 1</t>
         </is>
       </c>
     </row>
@@ -47823,7 +47911,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>West Street</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -47946,12 +48034,12 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>20-RMB viewpoint</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
@@ -47960,10 +48048,10 @@
         </is>
       </c>
       <c r="G114" s="8" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>17.39</v>
+        <v>16.3</v>
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
@@ -47978,21 +48066,21 @@
         </is>
       </c>
       <c r="B115" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Yulong bamboo rafting</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
@@ -48001,10 +48089,10 @@
         </is>
       </c>
       <c r="G115" s="8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>1.42</v>
+        <v>6.53</v>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
@@ -48028,12 +48116,12 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Yulong bamboo rafting</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -48069,12 +48157,12 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Yulong valley cycling</t>
+          <t>Moon Hill</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
@@ -48083,14 +48171,14 @@
         </is>
       </c>
       <c r="G117" s="8" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>6.53</v>
+        <v>10.4</v>
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48110,12 +48198,12 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Moon Hill</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -48124,14 +48212,14 @@
         </is>
       </c>
       <c r="G118" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>10.4</v>
+        <v>5.42</v>
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48151,7 +48239,7 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -48165,10 +48253,10 @@
         </is>
       </c>
       <c r="G119" s="8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>6.23</v>
+        <v>1.42</v>
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>

--- a/china-notion-sync.xlsx
+++ b/china-notion-sync.xlsx
@@ -15280,12 +15280,12 @@
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I166" s="6" t="n">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="R166" s="7" t="inlineStr">
         <is>
-          <t>ORDER 40 → 50</t>
+          <t>RETIME 12:00 → 12:15; ORDER 40 → 50</t>
         </is>
       </c>
       <c r="S166" s="7" t="inlineStr">
@@ -15368,12 +15368,12 @@
       </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I167" s="6" t="n">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="J167" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="K167" s="6" t="inlineStr">
@@ -15390,10 +15390,10 @@
         </is>
       </c>
       <c r="L167" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M167" s="6" t="n">
-        <v>16.3</v>
+        <v>17.39</v>
       </c>
       <c r="N167" s="6" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
       </c>
       <c r="R167" s="7" t="inlineStr">
         <is>
-          <t>ORDER 70 → 60</t>
+          <t>RETIME 18:00 → 17:30; ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S167" s="7" t="inlineStr">
@@ -15434,42 +15434,42 @@
         </is>
       </c>
       <c r="B168" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I168" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J168" s="6" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K168" s="6" t="inlineStr">
@@ -15478,10 +15478,10 @@
         </is>
       </c>
       <c r="L168" s="6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M168" s="6" t="n">
-        <v>6.53</v>
+        <v>1.42</v>
       </c>
       <c r="N168" s="6" t="inlineStr">
         <is>
@@ -15489,29 +15489,29 @@
         </is>
       </c>
       <c r="O168" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P168" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="Q168" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R168" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 08:00</t>
+          <t>MOVE day 1 → 2; RETIME 21:48 → 19:45; ORDER 80 → 70</t>
         </is>
       </c>
       <c r="S168" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Show runs ~70 min (operators quote 60-70); the venue advises arriving well before curtain and the 2,000+ seat amphitheatre empties slowly, so allow ~20 min of seating and exit.</t>
         </is>
       </c>
       <c r="T168" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -15530,34 +15530,34 @@
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J169" s="6" t="inlineStr">
+        <is>
           <t>Yulong bamboo rafting</t>
-        </is>
-      </c>
-      <c r="F169" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G169" s="6" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="H169" s="6" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="I169" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J169" s="6" t="inlineStr">
-        <is>
-          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="K169" s="6" t="inlineStr">
@@ -15577,29 +15577,29 @@
         </is>
       </c>
       <c r="O169" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P169" s="6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q169" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="R169" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 08:55 → 09:30; ORDER 30 → 20</t>
+          <t>RETIME 07:30 → 08:00</t>
         </is>
       </c>
       <c r="S169" s="7" t="inlineStr">
         <is>
-          <t>Route tables for Yulong rafting list Jinlong Bridge to Jiuxian as 6 km / 90 min, the longest and most popular section with its nine small weirs.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T169" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -15618,50 +15618,50 @@
         </is>
       </c>
       <c r="D170" s="6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
+          <t>Yulong bamboo rafting</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="I170" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J170" s="6" t="inlineStr">
+        <is>
           <t>Yulong valley cycling</t>
         </is>
       </c>
-      <c r="F170" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G170" s="6" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="H170" s="6" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="I170" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="J170" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K170" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L170" s="6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M170" s="6" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="N170" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O170" s="6" t="n">
@@ -15669,20 +15669,20 @@
       </c>
       <c r="P170" s="6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="Q170" s="6" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="R170" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 13:28 → 11:24; ORDER 50 → 30</t>
+          <t>MOVE day 2 → 3; RETIME 08:55 → 09:30; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S170" s="7" t="inlineStr">
         <is>
-          <t>The West Street round-trip loop through the Shili Gallery / Jiuxian-Chaoyang Weir section is 19 km and quoted at 2-3 hrs by cycling guides, including photo and drink stops.</t>
+          <t>Route tables for Yulong rafting list Jinlong Bridge to Jiuxian as 6 km / 90 min, the longest and most popular section with its nine small weirs.</t>
         </is>
       </c>
       <c r="T170" s="6" t="inlineStr">
@@ -15706,76 +15706,76 @@
         </is>
       </c>
       <c r="D171" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
+          <t>Yulong valley cycling</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="I171" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="J171" s="6" t="inlineStr">
+        <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G171" s="6" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="H171" s="6" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="I171" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J171" s="6" t="inlineStr">
-        <is>
-          <t>Moon Hill</t>
-        </is>
-      </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L171" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M171" s="6" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="N171" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O171" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P171" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="Q171" s="6" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="R171" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 14:02</t>
+          <t>MOVE day 2 → 3; RETIME 13:28 → 11:24; ORDER 50 → 30</t>
         </is>
       </c>
       <c r="S171" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>The West Street round-trip loop through the Shili Gallery / Jiuxian-Chaoyang Weir section is 19 km and quoted at 2-3 hrs by cycling guides, including photo and drink stops.</t>
         </is>
       </c>
       <c r="T171" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -15794,71 +15794,71 @@
         </is>
       </c>
       <c r="D172" s="6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="I172" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J172" s="6" t="inlineStr">
+        <is>
           <t>Moon Hill</t>
         </is>
       </c>
-      <c r="F172" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G172" s="6" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="H172" s="6" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="I172" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J172" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K172" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L172" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M172" s="6" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="N172" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O172" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P172" s="6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q172" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R172" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 16:01 → 15:35; ORDER 60 → 50</t>
+          <t>RETIME 12:00 → 14:02</t>
         </is>
       </c>
       <c r="S172" s="7" t="inlineStr">
         <is>
-          <t>800+ stone steps; guides quote ~30-40 min to the arch (China Highlights says ~1 hr to the top), plus time at the arch and the descent, and August heat slows everyone down.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T172" s="6" t="inlineStr">
@@ -15882,26 +15882,26 @@
         </is>
       </c>
       <c r="D173" s="6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Moon Hill</t>
         </is>
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="H173" s="6" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I173" s="6" t="n">
@@ -15909,31 +15909,31 @@
       </c>
       <c r="J173" s="6" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L173" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M173" s="6" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="N173" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O173" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P173" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="Q173" s="6" t="n">
@@ -15941,12 +15941,12 @@
       </c>
       <c r="R173" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:00 → 17:13; ORDER 50 → 60</t>
+          <t>MOVE day 2 → 3; RETIME 16:01 → 15:35; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S173" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>800+ stone steps; guides quote ~30-40 min to the arch (China Highlights says ~1 hr to the top), plus time at the arch and the descent, and August heat slows everyone down.</t>
         </is>
       </c>
       <c r="T173" s="6" t="inlineStr">
@@ -15970,26 +15970,26 @@
         </is>
       </c>
       <c r="D174" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H174" s="6" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I174" s="6" t="n">
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="L174" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M174" s="6" t="n">
-        <v>1.42</v>
+        <v>6.23</v>
       </c>
       <c r="N174" s="6" t="inlineStr">
         <is>
@@ -16017,11 +16017,11 @@
         </is>
       </c>
       <c r="O174" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P174" s="6" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q174" s="6" t="n">
@@ -16029,17 +16029,17 @@
       </c>
       <c r="R174" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 1 → 3; RETIME 21:48 → 19:45; ORDER 80 → 70</t>
+          <t>ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S174" s="7" t="inlineStr">
         <is>
-          <t>Show runs ~70 min (operators quote 60-70); the venue advises arriving well before curtain and the 2,000+ seat amphitheatre empties slowly, so allow ~20 min of seating and exit.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T174" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -36403,12 +36403,12 @@
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="H180" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I180" s="6" t="n">
@@ -36448,7 +36448,7 @@
       </c>
       <c r="R180" s="7" t="inlineStr">
         <is>
-          <t>ORDER 40 → 50</t>
+          <t>RETIME 12:00 → 12:15; ORDER 40 → 50</t>
         </is>
       </c>
       <c r="S180" s="7" t="inlineStr">
@@ -36491,12 +36491,12 @@
       </c>
       <c r="G181" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I181" s="6" t="n">
@@ -36504,7 +36504,7 @@
       </c>
       <c r="J181" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="K181" s="6" t="inlineStr">
@@ -36513,10 +36513,10 @@
         </is>
       </c>
       <c r="L181" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M181" s="6" t="n">
-        <v>16.3</v>
+        <v>17.39</v>
       </c>
       <c r="N181" s="6" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
       </c>
       <c r="R181" s="7" t="inlineStr">
         <is>
-          <t>ORDER 70 → 60</t>
+          <t>RETIME 18:00 → 17:30; ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S181" s="7" t="inlineStr">
@@ -36557,42 +36557,42 @@
         </is>
       </c>
       <c r="B182" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D182" s="6" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="H182" s="6" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I182" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J182" s="6" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K182" s="6" t="inlineStr">
@@ -36601,10 +36601,10 @@
         </is>
       </c>
       <c r="L182" s="6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M182" s="6" t="n">
-        <v>6.53</v>
+        <v>1.42</v>
       </c>
       <c r="N182" s="6" t="inlineStr">
         <is>
@@ -36612,29 +36612,29 @@
         </is>
       </c>
       <c r="O182" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P182" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="Q182" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R182" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 08:00</t>
+          <t>MOVE day 1 → 2; RETIME 21:48 → 19:45; ORDER 80 → 70</t>
         </is>
       </c>
       <c r="S182" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Show runs ~70 min (operators quote 60-70); the venue advises arriving well before curtain and the 2,000+ seat amphitheatre empties slowly, so allow ~20 min of seating and exit.</t>
         </is>
       </c>
       <c r="T182" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -36653,34 +36653,34 @@
         </is>
       </c>
       <c r="D183" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J183" s="6" t="inlineStr">
+        <is>
           <t>Yulong bamboo rafting</t>
-        </is>
-      </c>
-      <c r="F183" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G183" s="6" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="H183" s="6" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="I183" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J183" s="6" t="inlineStr">
-        <is>
-          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="K183" s="6" t="inlineStr">
@@ -36700,29 +36700,29 @@
         </is>
       </c>
       <c r="O183" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P183" s="6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q183" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="R183" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 08:55 → 09:30; ORDER 30 → 20</t>
+          <t>RETIME 07:30 → 08:00</t>
         </is>
       </c>
       <c r="S183" s="7" t="inlineStr">
         <is>
-          <t>Route tables for Yulong rafting list Jinlong Bridge to Jiuxian as 6 km / 90 min, the longest and most popular section with its nine small weirs.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T183" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -36741,50 +36741,50 @@
         </is>
       </c>
       <c r="D184" s="6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
+          <t>Yulong bamboo rafting</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J184" s="6" t="inlineStr">
+        <is>
           <t>Yulong valley cycling</t>
         </is>
       </c>
-      <c r="F184" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G184" s="6" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="H184" s="6" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="I184" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="J184" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K184" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L184" s="6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M184" s="6" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="N184" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O184" s="6" t="n">
@@ -36792,20 +36792,20 @@
       </c>
       <c r="P184" s="6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="Q184" s="6" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="R184" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 13:28 → 11:24; ORDER 50 → 30</t>
+          <t>MOVE day 2 → 3; RETIME 08:55 → 09:30; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S184" s="7" t="inlineStr">
         <is>
-          <t>The West Street round-trip loop through the Shili Gallery / Jiuxian-Chaoyang Weir section is 19 km and quoted at 2-3 hrs by cycling guides, including photo and drink stops.</t>
+          <t>Route tables for Yulong rafting list Jinlong Bridge to Jiuxian as 6 km / 90 min, the longest and most popular section with its nine small weirs.</t>
         </is>
       </c>
       <c r="T184" s="6" t="inlineStr">
@@ -36829,76 +36829,76 @@
         </is>
       </c>
       <c r="D185" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
+          <t>Yulong valley cycling</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="J185" s="6" t="inlineStr">
+        <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G185" s="6" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="H185" s="6" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="I185" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J185" s="6" t="inlineStr">
-        <is>
-          <t>Moon Hill</t>
-        </is>
-      </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L185" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M185" s="6" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="N185" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O185" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P185" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="Q185" s="6" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="R185" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 14:02</t>
+          <t>MOVE day 2 → 3; RETIME 13:28 → 11:24; ORDER 50 → 30</t>
         </is>
       </c>
       <c r="S185" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>The West Street round-trip loop through the Shili Gallery / Jiuxian-Chaoyang Weir section is 19 km and quoted at 2-3 hrs by cycling guides, including photo and drink stops.</t>
         </is>
       </c>
       <c r="T185" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -36917,71 +36917,71 @@
         </is>
       </c>
       <c r="D186" s="6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J186" s="6" t="inlineStr">
+        <is>
           <t>Moon Hill</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="H186" s="6" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="I186" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J186" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K186" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L186" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M186" s="6" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="N186" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O186" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P186" s="6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q186" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R186" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 2 → 3; RETIME 16:01 → 15:35; ORDER 60 → 50</t>
+          <t>RETIME 12:00 → 14:02</t>
         </is>
       </c>
       <c r="S186" s="7" t="inlineStr">
         <is>
-          <t>800+ stone steps; guides quote ~30-40 min to the arch (China Highlights says ~1 hr to the top), plus time at the arch and the descent, and August heat slows everyone down.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T186" s="6" t="inlineStr">
@@ -37005,26 +37005,26 @@
         </is>
       </c>
       <c r="D187" s="6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Moon Hill</t>
         </is>
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I187" s="6" t="n">
@@ -37032,31 +37032,31 @@
       </c>
       <c r="J187" s="6" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L187" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M187" s="6" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="N187" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O187" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P187" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="Q187" s="6" t="n">
@@ -37064,12 +37064,12 @@
       </c>
       <c r="R187" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:00 → 17:13; ORDER 50 → 60</t>
+          <t>MOVE day 2 → 3; RETIME 16:01 → 15:35; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S187" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>800+ stone steps; guides quote ~30-40 min to the arch (China Highlights says ~1 hr to the top), plus time at the arch and the descent, and August heat slows everyone down.</t>
         </is>
       </c>
       <c r="T187" s="6" t="inlineStr">
@@ -37093,26 +37093,26 @@
         </is>
       </c>
       <c r="D188" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H188" s="6" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I188" s="6" t="n">
@@ -37129,10 +37129,10 @@
         </is>
       </c>
       <c r="L188" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M188" s="6" t="n">
-        <v>1.42</v>
+        <v>6.23</v>
       </c>
       <c r="N188" s="6" t="inlineStr">
         <is>
@@ -37140,11 +37140,11 @@
         </is>
       </c>
       <c r="O188" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P188" s="6" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q188" s="6" t="n">
@@ -37152,17 +37152,17 @@
       </c>
       <c r="R188" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 1 → 3; RETIME 21:48 → 19:45; ORDER 80 → 70</t>
+          <t>ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S188" s="7" t="inlineStr">
         <is>
-          <t>Show runs ~70 min (operators quote 60-70); the venue advises arriving well before curtain and the 2,000+ seat amphitheatre empties slowly, so allow ~20 min of seating and exit.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T188" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -43186,14 +43186,14 @@
         <v>1</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>90</v>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 1 → 3</t>
+          <t>Change this page's day: 1 → 2</t>
         </is>
       </c>
     </row>
@@ -43205,21 +43205,21 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Xingping Ancient Town</t>
+          <t>Yulong bamboo rafting</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="E21" s="12" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 3 → 2</t>
+          <t>Change this page's day: 2 → 3</t>
         </is>
       </c>
     </row>
@@ -43231,21 +43231,21 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>20-RMB viewpoint</t>
+          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="E22" s="12" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 3 → 2</t>
+          <t>Change this page's day: 2 → 3</t>
         </is>
       </c>
     </row>
@@ -43257,7 +43257,7 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Moon Hill</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
@@ -43283,21 +43283,21 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Yulong valley cycling</t>
+          <t>Li River night walk</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 2 → 3</t>
+          <t>Change this page's day: 2 → 1</t>
         </is>
       </c>
     </row>
@@ -43309,21 +43309,21 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Moon Hill</t>
+          <t>Xingping Ancient Town</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="E25" s="12" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 2 → 3</t>
+          <t>Change this page's day: 3 → 2</t>
         </is>
       </c>
     </row>
@@ -43335,21 +43335,21 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Li River night walk</t>
+          <t>20-RMB viewpoint</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="E26" s="12" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 2 → 1</t>
+          <t>Change this page's day: 3 → 2</t>
         </is>
       </c>
     </row>
@@ -48039,7 +48039,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
@@ -48048,10 +48048,10 @@
         </is>
       </c>
       <c r="G114" s="8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>16.3</v>
+        <v>17.39</v>
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
@@ -48066,21 +48066,21 @@
         </is>
       </c>
       <c r="B115" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
@@ -48089,10 +48089,10 @@
         </is>
       </c>
       <c r="G115" s="8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>6.53</v>
+        <v>1.42</v>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
@@ -48116,12 +48116,12 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
           <t>Yulong bamboo rafting</t>
-        </is>
-      </c>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -48157,12 +48157,12 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Yulong bamboo rafting</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Moon Hill</t>
+          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
@@ -48171,14 +48171,14 @@
         </is>
       </c>
       <c r="G117" s="8" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>10.4</v>
+        <v>6.53</v>
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48198,12 +48198,12 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Moon Hill</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -48212,14 +48212,14 @@
         </is>
       </c>
       <c r="G118" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>5.42</v>
+        <v>10.4</v>
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48239,7 +48239,7 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -48253,10 +48253,10 @@
         </is>
       </c>
       <c r="G119" s="8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>1.42</v>
+        <v>6.23</v>
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>

--- a/china-notion-sync.xlsx
+++ b/china-notion-sync.xlsx
@@ -15,11 +15,11 @@
     <sheet name="Legs" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$T$227</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Schedule'!$A$1:$T$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$T$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Schedule'!$A$1:$T$243</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ideas (parked)'!$A$1:$G$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Moves'!$A$1:$F$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Legs'!$A$1:$I$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Legs'!$A$1:$I$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T227"/>
+  <dimension ref="A1:T228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16261,23 +16261,23 @@
       </c>
       <c r="J177" s="6" t="inlineStr">
         <is>
-          <t>Check in at Marriott</t>
+          <t>Shanghai Maglev</t>
         </is>
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L177" s="6" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M177" s="6" t="n">
-        <v>33.89</v>
+        <v>0</v>
       </c>
       <c r="N177" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O177" s="6" t="n">
@@ -16326,30 +16326,30 @@
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
+          <t>Shanghai Maglev</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J178" s="6" t="inlineStr">
+        <is>
           <t>Check in at Marriott</t>
-        </is>
-      </c>
-      <c r="F178" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G178" s="6" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="H178" s="6" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="I178" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J178" s="6" t="inlineStr">
-        <is>
-          <t>Shanghai Maglev</t>
         </is>
       </c>
       <c r="K178" s="6" t="inlineStr">
@@ -16373,25 +16373,25 @@
       </c>
       <c r="P178" s="6" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="Q178" s="6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R178" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:57 → 15:58; ORDER 40 → 30</t>
+          <t>RETIME 14:30 → 15:01; ORDER 20 → 30</t>
         </is>
       </c>
       <c r="S178" s="7" t="inlineStr">
         <is>
-          <t>Standard city-hotel check-in plus bag drop and a quick freshen-up; no evidence of unusual delays at this property.</t>
+          <t>Operator and airport guides: 8-minute run PVG-Longyang Road with departures every 15-20min, so ticket, platform wait, ride and exit total roughly 25min.</t>
         </is>
       </c>
       <c r="T178" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>Shanghai Maglev</t>
+          <t>Check in at Marriott</t>
         </is>
       </c>
       <c r="F179" s="6" t="inlineStr">
@@ -16424,16 +16424,16 @@
       </c>
       <c r="G179" s="6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="I179" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J179" s="6" t="inlineStr">
         <is>
@@ -16442,18 +16442,18 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L179" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M179" s="6" t="n">
-        <v>8.449999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="N179" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O179" s="6" t="n">
@@ -16461,25 +16461,25 @@
       </c>
       <c r="P179" s="6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="Q179" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R179" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:30 → 16:56; ORDER 20 → 40</t>
+          <t>RETIME 16:57 → 15:54</t>
         </is>
       </c>
       <c r="S179" s="7" t="inlineStr">
         <is>
-          <t>Operator and airport guides: 8-minute run PVG-Longyang Road with departures every 15-20min, so ticket, platform wait, ride and exit total roughly 25min.</t>
+          <t>Standard city-hotel check-in plus bag drop and a quick freshen-up; no evidence of unusual delays at this property.</t>
         </is>
       </c>
       <c r="T179" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -16512,12 +16512,12 @@
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
           <t>17:48</t>
-        </is>
-      </c>
-      <c r="H180" s="6" t="inlineStr">
-        <is>
-          <t>18:48</t>
         </is>
       </c>
       <c r="I180" s="6" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="R180" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:51 → 17:48</t>
+          <t>RETIME 17:51 → 16:48</t>
         </is>
       </c>
       <c r="S180" s="7" t="inlineStr">
@@ -16600,12 +16600,12 @@
       </c>
       <c r="G181" s="6" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I181" s="6" t="n">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="R181" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:16 → 18:56; ORDER 70 → 60</t>
+          <t>RETIME 21:16 → 17:56; ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S181" s="7" t="inlineStr">
@@ -16688,12 +16688,12 @@
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
           <t>20:53</t>
-        </is>
-      </c>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>21:53</t>
         </is>
       </c>
       <c r="I182" s="6" t="n">
@@ -16701,19 +16701,19 @@
       </c>
       <c r="J182" s="6" t="inlineStr">
         <is>
-          <t>Old Jazz Bar</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K182" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L182" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M182" s="6" t="n">
-        <v>0.34</v>
+        <v>2.04</v>
       </c>
       <c r="N182" s="6" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
       </c>
       <c r="R182" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:33 → 20:53; ORDER 60 → 70</t>
+          <t>RETIME 19:33 → 19:53; ORDER 60 → 70</t>
         </is>
       </c>
       <c r="S182" s="7" t="inlineStr">
@@ -16754,42 +16754,42 @@
         </is>
       </c>
       <c r="B183" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D183" s="6" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Old Jazz Bar</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I183" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="J183" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Recovery massage / spa</t>
         </is>
       </c>
       <c r="K183" s="6" t="inlineStr">
@@ -16798,10 +16798,10 @@
         </is>
       </c>
       <c r="L183" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M183" s="6" t="n">
-        <v>1.72</v>
+        <v>2.67</v>
       </c>
       <c r="N183" s="6" t="inlineStr">
         <is>
@@ -16809,24 +16809,24 @@
         </is>
       </c>
       <c r="O183" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P183" s="6" t="inlineStr">
         <is>
-          <t>01:51</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q183" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="R183" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 3 → 1; RETIME 01:51 → 22:13; ORDER 110 → 80</t>
+          <t>RETIME 07:30 → 07:00</t>
         </is>
       </c>
       <c r="S183" s="7" t="inlineStr">
         <is>
-          <t>The Fairmont Peace Hotel Old Jazz Band plays a long nightly run (from ~18:30, sets through 23:30); reviewers describe staying for a couple of sets over drinks, roughly 90min.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T183" s="6" t="inlineStr">
@@ -16850,34 +16850,34 @@
         </is>
       </c>
       <c r="D184" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Recovery massage / spa</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I184" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J184" s="6" t="inlineStr">
         <is>
-          <t>Recovery massage / spa</t>
+          <t>M50 Creative Park</t>
         </is>
       </c>
       <c r="K184" s="6" t="inlineStr">
@@ -16886,10 +16886,10 @@
         </is>
       </c>
       <c r="L184" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M184" s="6" t="n">
-        <v>2.67</v>
+        <v>3.34</v>
       </c>
       <c r="N184" s="6" t="inlineStr">
         <is>
@@ -16901,20 +16901,20 @@
       </c>
       <c r="P184" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="Q184" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R184" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 13:28 → 07:54; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S184" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Shanghai spa listings (Time Out, SmartShanghai, Culture Trip) show 60-80min foot/body packages as the standard tourist option; add foot bath, changing and tea for ~90min door to door.</t>
         </is>
       </c>
       <c r="T184" s="6" t="inlineStr">
@@ -16938,11 +16938,11 @@
         </is>
       </c>
       <c r="D185" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>Recovery massage / spa</t>
+          <t>M50 Creative Park</t>
         </is>
       </c>
       <c r="F185" s="6" t="inlineStr">
@@ -16952,57 +16952,57 @@
       </c>
       <c r="G185" s="6" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I185" s="6" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J185" s="6" t="inlineStr">
         <is>
-          <t>M50 Creative Park</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L185" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M185" s="6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N185" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O185" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P185" s="6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="Q185" s="6" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="R185" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:28 → 07:54; ORDER 30 → 20</t>
+          <t>MOVE day 4 → 2; RETIME 18:37 → 10:00; ORDER 80 → 30</t>
         </is>
       </c>
       <c r="S185" s="7" t="inlineStr">
         <is>
-          <t>Shanghai spa listings (Time Out, SmartShanghai, Culture Trip) show 60-80min foot/body packages as the standard tourist option; add foot bath, changing and tea for ~90min door to door.</t>
+          <t>Travel guides budget 2-4h (about 3h recommended) for 140+ studios and galleries plus the graffiti wall; 2h is a highlights-plus pass through the better galleries.</t>
         </is>
       </c>
       <c r="T185" s="6" t="inlineStr">
@@ -17026,30 +17026,30 @@
         </is>
       </c>
       <c r="D186" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>M50 Creative Park</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="H186" s="6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="I186" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="J186" s="6" t="inlineStr">
         <is>
@@ -17073,24 +17073,24 @@
         </is>
       </c>
       <c r="O186" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P186" s="6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q186" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="R186" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 18:37 → 09:44; ORDER 80 → 30</t>
+          <t>RETIME 12:00 → 12:08; ORDER 20 → 40</t>
         </is>
       </c>
       <c r="S186" s="7" t="inlineStr">
         <is>
-          <t>Travel guides budget 2-4h (about 3h recommended) for 140+ studios and galleries plus the graffiti wall; 2h is a highlights-plus pass through the better galleries.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T186" s="6" t="inlineStr">
@@ -17114,7 +17114,7 @@
         </is>
       </c>
       <c r="D187" s="6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
@@ -17128,12 +17128,12 @@
       </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="I187" s="6" t="n">
@@ -17141,23 +17141,23 @@
       </c>
       <c r="J187" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Nanjing Road West</t>
         </is>
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L187" s="6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M187" s="6" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="N187" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O187" s="6" t="n">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="R187" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:55 → 12:03</t>
+          <t>RETIME 15:55 → 13:27; ORDER 40 → 50</t>
         </is>
       </c>
       <c r="S187" s="7" t="inlineStr">
@@ -17202,34 +17202,34 @@
         </is>
       </c>
       <c r="D188" s="6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Nanjing Road West</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="H188" s="6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I188" s="6" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J188" s="6" t="inlineStr">
         <is>
-          <t>Nanjing Road West</t>
+          <t>Zhangyuan</t>
         </is>
       </c>
       <c r="K188" s="6" t="inlineStr">
@@ -17238,14 +17238,14 @@
         </is>
       </c>
       <c r="L188" s="6" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="M188" s="6" t="n">
-        <v>0.96</v>
+        <v>0.5</v>
       </c>
       <c r="N188" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O188" s="6" t="n">
@@ -17253,20 +17253,20 @@
       </c>
       <c r="P188" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="Q188" s="6" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="R188" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 13:11; ORDER 20 → 50</t>
+          <t>RETIME 19:32 → 14:58</t>
         </is>
       </c>
       <c r="S188" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Shopping guides: most visitors spend 1-2h on West Nanjing Road, 2-3h if working through Plaza 66 / HKRI Taikoo Hui; 75min covers the strip plus one mall.</t>
         </is>
       </c>
       <c r="T188" s="6" t="inlineStr">
@@ -17290,50 +17290,50 @@
         </is>
       </c>
       <c r="D189" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>Zhangyuan</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="I189" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
-        <is>
-          <t>Nanjing Road West</t>
-        </is>
-      </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G189" s="6" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="H189" s="6" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="I189" s="6" t="n">
-        <v>75</v>
-      </c>
       <c r="J189" s="6" t="inlineStr">
         <is>
-          <t>Zhangyuan</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L189" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M189" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N189" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O189" s="6" t="n">
@@ -17341,20 +17341,20 @@
       </c>
       <c r="P189" s="6" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="Q189" s="6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="R189" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:32 → 14:42</t>
+          <t>RETIME 17:47 → 16:28; ORDER 50 → 70</t>
         </is>
       </c>
       <c r="S189" s="7" t="inlineStr">
         <is>
-          <t>Shopping guides: most visitors spend 1-2h on West Nanjing Road, 2-3h if working through Plaza 66 / HKRI Taikoo Hui; 75min covers the strip plus one mall.</t>
+          <t>Reviews describe a restored shikumen retail precinct 'similar to Xintiandi but much quieter'; an unhurried wander of the lanes with a pop-up or two runs about an hour.</t>
         </is>
       </c>
       <c r="T189" s="6" t="inlineStr">
@@ -17378,50 +17378,50 @@
         </is>
       </c>
       <c r="D190" s="6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Zhangyuan</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H190" s="6" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I190" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J190" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K190" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L190" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M190" s="6" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="N190" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O190" s="6" t="n">
@@ -17429,20 +17429,20 @@
       </c>
       <c r="P190" s="6" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="Q190" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R190" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:47 → 16:12; ORDER 50 → 70</t>
+          <t>RETIME 21:15 → 18:00; ORDER 70 → 80</t>
         </is>
       </c>
       <c r="S190" s="7" t="inlineStr">
         <is>
-          <t>Reviews describe a restored shikumen retail precinct 'similar to Xintiandi but much quieter'; an unhurried wander of the lanes with a pop-up or two runs about an hour.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T190" s="6" t="inlineStr">
@@ -17458,19 +17458,19 @@
         </is>
       </c>
       <c r="B191" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D191" s="6" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="F191" s="6" t="inlineStr">
@@ -17480,20 +17480,20 @@
       </c>
       <c r="G191" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="H191" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I191" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="J191" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Wukang Building</t>
         </is>
       </c>
       <c r="K191" s="6" t="inlineStr">
@@ -17502,10 +17502,10 @@
         </is>
       </c>
       <c r="L191" s="6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M191" s="6" t="n">
-        <v>4.38</v>
+        <v>7.18</v>
       </c>
       <c r="N191" s="6" t="inlineStr">
         <is>
@@ -17513,24 +17513,24 @@
         </is>
       </c>
       <c r="O191" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P191" s="6" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="Q191" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="R191" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:15 → 18:00; ORDER 70 → 80</t>
+          <t>RETIME 09:00 → 07:00</t>
         </is>
       </c>
       <c r="S191" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T191" s="6" t="inlineStr">
@@ -17554,50 +17554,50 @@
         </is>
       </c>
       <c r="D192" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>Wukang Building</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="I192" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J192" s="6" t="inlineStr">
+        <is>
+          <t>Wukang Road</t>
+        </is>
+      </c>
+      <c r="K192" s="6" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="L192" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
-        <is>
-          <t>Breakfast</t>
-        </is>
-      </c>
-      <c r="F192" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G192" s="6" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="H192" s="6" t="inlineStr">
-        <is>
-          <t>07:35</t>
-        </is>
-      </c>
-      <c r="I192" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="J192" s="6" t="inlineStr">
-        <is>
-          <t>Wukang Building</t>
-        </is>
-      </c>
-      <c r="K192" s="6" t="inlineStr">
-        <is>
-          <t>didi</t>
-        </is>
-      </c>
-      <c r="L192" s="6" t="n">
-        <v>17</v>
-      </c>
       <c r="M192" s="6" t="n">
-        <v>7.18</v>
+        <v>0.7</v>
       </c>
       <c r="N192" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O192" s="6" t="n">
@@ -17605,20 +17605,20 @@
       </c>
       <c r="P192" s="6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="Q192" s="6" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="R192" s="7" t="inlineStr">
         <is>
-          <t>RETIME 09:00 → 07:00</t>
+          <t>RETIME 10:18 → 08:00</t>
         </is>
       </c>
       <c r="S192" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Walking guides treat Wukang Mansion as a photo landmark on the corner (best 16:00-17:30); it is exterior-only, so 15-25min including crowd jostling.</t>
         </is>
       </c>
       <c r="T192" s="6" t="inlineStr">
@@ -17642,11 +17642,11 @@
         </is>
       </c>
       <c r="D193" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>Wukang Building</t>
+          <t>Wukang Road</t>
         </is>
       </c>
       <c r="F193" s="6" t="inlineStr">
@@ -17656,20 +17656,20 @@
       </c>
       <c r="G193" s="6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="H193" s="6" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I193" s="6" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J193" s="6" t="inlineStr">
         <is>
-          <t>Wukang Road</t>
+          <t>Ferguson Lane</t>
         </is>
       </c>
       <c r="K193" s="6" t="inlineStr">
@@ -17678,10 +17678,10 @@
         </is>
       </c>
       <c r="L193" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M193" s="6" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="N193" s="6" t="inlineStr">
         <is>
@@ -17693,20 +17693,20 @@
       </c>
       <c r="P193" s="6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="Q193" s="6" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R193" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:18 → 08:00</t>
+          <t>RETIME 12:06 → 08:38</t>
         </is>
       </c>
       <c r="S193" s="7" t="inlineStr">
         <is>
-          <t>Walking guides treat Wukang Mansion as a photo landmark on the corner (best 16:00-17:30); it is exterior-only, so 15-25min including crowd jostling.</t>
+          <t>Guides quote 2-3h for Wukang Road with photos and coffee, but that bundles Ferguson Lane and cafes which are separate stops here; the 1.17km street alone walks in about an hour.</t>
         </is>
       </c>
       <c r="T193" s="6" t="inlineStr">
@@ -17730,11 +17730,11 @@
         </is>
       </c>
       <c r="D194" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Wukang Road</t>
+          <t>Ferguson Lane</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
@@ -17744,32 +17744,32 @@
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="H194" s="6" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I194" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J194" s="6" t="inlineStr">
         <is>
-          <t>Ferguson Lane</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="K194" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="L194" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M194" s="6" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="N194" s="6" t="inlineStr">
         <is>
@@ -17781,25 +17781,25 @@
       </c>
       <c r="P194" s="6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="Q194" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R194" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:06 → 08:38</t>
+          <t>RETIME 13:33 → 09:50</t>
         </is>
       </c>
       <c r="S194" s="7" t="inlineStr">
         <is>
-          <t>Guides quote 2-3h for Wukang Road with photos and coffee, but that bundles Ferguson Lane and cafes which are separate stops here; the 1.17km street alone walks in about an hour.</t>
+          <t>Ferguson Lane (376 Wukang Rd) is described as a small tucked-away courtyard of galleries and bistros — 15min to look, 45min if you actually sit for the coffee it exists for.</t>
         </is>
       </c>
       <c r="T194" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -17818,11 +17818,11 @@
         </is>
       </c>
       <c r="D195" s="6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Ferguson Lane</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="F195" s="6" t="inlineStr">
@@ -17832,12 +17832,12 @@
       </c>
       <c r="G195" s="6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="H195" s="6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I195" s="6" t="n">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="J195" s="6" t="inlineStr">
         <is>
-          <t>Anfu Road</t>
+          <t>Wulumuqi Road</t>
         </is>
       </c>
       <c r="K195" s="6" t="inlineStr">
@@ -17857,7 +17857,7 @@
         <v>14</v>
       </c>
       <c r="M195" s="6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="N195" s="6" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
       </c>
       <c r="P195" s="6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="Q195" s="6" t="n">
@@ -17877,17 +17877,17 @@
       </c>
       <c r="R195" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:33 → 09:50</t>
+          <t>RETIME 15:25 → 10:57</t>
         </is>
       </c>
       <c r="S195" s="7" t="inlineStr">
         <is>
-          <t>Ferguson Lane (376 Wukang Rd) is described as a small tucked-away courtyard of galleries and bistros — 15min to look, 45min if you actually sit for the coffee it exists for.</t>
+          <t>Wukang+Anfu combined walking routes are quoted at 3-4h over 2.5km; Anfu Road's own share, browsing a couple of shops, is roughly 45min.</t>
         </is>
       </c>
       <c r="T195" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -17906,11 +17906,11 @@
         </is>
       </c>
       <c r="D196" s="6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Anfu Road</t>
+          <t>Wulumuqi Road</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
@@ -17920,36 +17920,36 @@
       </c>
       <c r="G196" s="6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="H196" s="6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I196" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J196" s="6" t="inlineStr">
         <is>
-          <t>Wulumuqi Road</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K196" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L196" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M196" s="6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N196" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O196" s="6" t="n">
@@ -17957,25 +17957,25 @@
       </c>
       <c r="P196" s="6" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="Q196" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="R196" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:25 → 10:57</t>
+          <t>RETIME 17:02 → 12:04</t>
         </is>
       </c>
       <c r="S196" s="7" t="inlineStr">
         <is>
-          <t>Wukang+Anfu combined walking routes are quoted at 3-4h over 2.5km; Anfu Road's own share, browsing a couple of shops, is roughly 45min.</t>
+          <t>Guides frame Wulumuqi Middle Road as a short local-life detour (markets, Art Deco corner at Fuxing West Rd) rather than a destination; ~30min walk-through.</t>
         </is>
       </c>
       <c r="T196" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -17994,50 +17994,50 @@
         </is>
       </c>
       <c r="D197" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
-        <is>
-          <t>Wulumuqi Road</t>
-        </is>
-      </c>
-      <c r="F197" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G197" s="6" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="H197" s="6" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="I197" s="6" t="n">
-        <v>30</v>
-      </c>
       <c r="J197" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Fuxing Park</t>
         </is>
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L197" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M197" s="6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N197" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O197" s="6" t="n">
@@ -18045,25 +18045,25 @@
       </c>
       <c r="P197" s="6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="Q197" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="R197" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:02 → 12:04</t>
+          <t>RETIME 18:46 → 12:42</t>
         </is>
       </c>
       <c r="S197" s="7" t="inlineStr">
         <is>
-          <t>Guides frame Wulumuqi Middle Road as a short local-life detour (markets, Art Deco corner at Fuxing West Rd) rather than a destination; ~30min walk-through.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T197" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -18082,50 +18082,50 @@
         </is>
       </c>
       <c r="D198" s="6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Fuxing Park</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H198" s="6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I198" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J198" s="6" t="inlineStr">
         <is>
-          <t>Fuxing Park</t>
+          <t>Sinan Mansions</t>
         </is>
       </c>
       <c r="K198" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L198" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M198" s="6" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="N198" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O198" s="6" t="n">
@@ -18133,20 +18133,20 @@
       </c>
       <c r="P198" s="6" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q198" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R198" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:46 → 12:42</t>
+          <t>RETIME 21:42 → 14:00; ORDER 90 → 80</t>
         </is>
       </c>
       <c r="S198" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Guides say Fuxing Park is 'worth a 30-60 minute walk'; 45min lets you watch the dancing and chess without circling twice.</t>
         </is>
       </c>
       <c r="T198" s="6" t="inlineStr">
@@ -18170,11 +18170,11 @@
         </is>
       </c>
       <c r="D199" s="6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>Fuxing Park</t>
+          <t>Sinan Mansions</t>
         </is>
       </c>
       <c r="F199" s="6" t="inlineStr">
@@ -18184,36 +18184,36 @@
       </c>
       <c r="G199" s="6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="H199" s="6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I199" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J199" s="6" t="inlineStr">
         <is>
-          <t>Sinan Mansions</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L199" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M199" s="6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="N199" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O199" s="6" t="n">
@@ -18221,20 +18221,20 @@
       </c>
       <c r="P199" s="6" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="Q199" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R199" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:42 → 14:00; ORDER 90 → 80</t>
+          <t>RETIME 19:59 → 14:58; ORDER 80 → 90</t>
         </is>
       </c>
       <c r="S199" s="7" t="inlineStr">
         <is>
-          <t>Guides say Fuxing Park is 'worth a 30-60 minute walk'; 45min lets you watch the dancing and chess without circling twice.</t>
+          <t>Travel guides advise 1-2h to walk the estate, admire the facades and browse boutiques/side galleries; 60min is the lower, unhurried-but-not-lingering end.</t>
         </is>
       </c>
       <c r="T199" s="6" t="inlineStr">
@@ -18258,50 +18258,50 @@
         </is>
       </c>
       <c r="D200" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
-        <is>
-          <t>Sinan Mansions</t>
-        </is>
-      </c>
-      <c r="F200" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G200" s="6" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="H200" s="6" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="I200" s="6" t="n">
-        <v>60</v>
-      </c>
       <c r="J200" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K200" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L200" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M200" s="6" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N200" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O200" s="6" t="n">
@@ -18309,20 +18309,20 @@
       </c>
       <c r="P200" s="6" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="Q200" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R200" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:59 → 14:58; ORDER 80 → 90</t>
+          <t>RETIME 00:10 → 18:00</t>
         </is>
       </c>
       <c r="S200" s="7" t="inlineStr">
         <is>
-          <t>Travel guides advise 1-2h to walk the estate, admire the facades and browse boutiques/side galleries; 60min is the lower, unhurried-but-not-lingering end.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T200" s="6" t="inlineStr">
@@ -18338,19 +18338,19 @@
         </is>
       </c>
       <c r="B201" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D201" s="6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="F201" s="6" t="inlineStr">
@@ -18360,20 +18360,20 @@
       </c>
       <c r="G201" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H201" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I201" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="J201" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Yu Garden</t>
         </is>
       </c>
       <c r="K201" s="6" t="inlineStr">
@@ -18382,10 +18382,10 @@
         </is>
       </c>
       <c r="L201" s="6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M201" s="6" t="n">
-        <v>3.97</v>
+        <v>1.27</v>
       </c>
       <c r="N201" s="6" t="inlineStr">
         <is>
@@ -18393,24 +18393,24 @@
         </is>
       </c>
       <c r="O201" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P201" s="6" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q201" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="R201" s="7" t="inlineStr">
         <is>
-          <t>RETIME 00:10 → 18:00</t>
+          <t>RETIME 07:30 → 08:00</t>
         </is>
       </c>
       <c r="S201" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T201" s="6" t="inlineStr">
@@ -18434,46 +18434,46 @@
         </is>
       </c>
       <c r="D202" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Yu Garden</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="H202" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I202" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J202" s="6" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="K202" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L202" s="6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M202" s="6" t="n">
-        <v>1.27</v>
+        <v>0.47</v>
       </c>
       <c r="N202" s="6" t="inlineStr">
         <is>
@@ -18485,25 +18485,25 @@
       </c>
       <c r="P202" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q202" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R202" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 08:41 → 09:00</t>
         </is>
       </c>
       <c r="S202" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>TripAdvisor/guide consensus is ~2h for a complete visit and 45-60min for a fast loop; at opening with fewer crowds, a highlights-plus circuit of the rockeries and pavilions is ~90min.</t>
         </is>
       </c>
       <c r="T202" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -18522,11 +18522,11 @@
         </is>
       </c>
       <c r="D203" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="F203" s="6" t="inlineStr">
@@ -18536,20 +18536,20 @@
       </c>
       <c r="G203" s="6" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="H203" s="6" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I203" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J203" s="6" t="inlineStr">
         <is>
-          <t>Mid-Lake Teahouse</t>
+          <t>Yuyuan Bazaar</t>
         </is>
       </c>
       <c r="K203" s="6" t="inlineStr">
@@ -18558,14 +18558,14 @@
         </is>
       </c>
       <c r="L203" s="6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M203" s="6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="N203" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O203" s="6" t="n">
@@ -18573,25 +18573,25 @@
       </c>
       <c r="P203" s="6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q203" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R203" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:41 → 07:51</t>
+          <t>RETIME 12:21 → 10:52; ORDER 40 → 30</t>
         </is>
       </c>
       <c r="S203" s="7" t="inlineStr">
         <is>
-          <t>TripAdvisor/guide consensus is ~2h for a complete visit and 45-60min for a fast loop; at opening with fewer crowds, a highlights-plus circuit of the rockeries and pavilions is ~90min.</t>
+          <t>TripAdvisor reviewers report lingering 'an hour or two' over tea and the complimentary quail-egg/sweet snacks while watching the pond; 45min feels rushed for a set tea service.</t>
         </is>
       </c>
       <c r="T203" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -18610,11 +18610,11 @@
         </is>
       </c>
       <c r="D204" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>Mid-Lake Teahouse</t>
+          <t>Yuyuan Bazaar</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
@@ -18624,12 +18624,12 @@
       </c>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="H204" s="6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I204" s="6" t="n">
@@ -18637,23 +18637,23 @@
       </c>
       <c r="J204" s="6" t="inlineStr">
         <is>
-          <t>Yuyuan Bazaar</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K204" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L204" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M204" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N204" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O204" s="6" t="n">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="P204" s="6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="Q204" s="6" t="n">
@@ -18669,12 +18669,12 @@
       </c>
       <c r="R204" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:21 → 09:43; ORDER 40 → 30</t>
+          <t>RETIME 10:52 → 12:06; ORDER 30 → 40</t>
         </is>
       </c>
       <c r="S204" s="7" t="inlineStr">
         <is>
-          <t>TripAdvisor reviewers report lingering 'an hour or two' over tea and the complimentary quail-egg/sweet snacks while watching the pond; 45min feels rushed for a set tea service.</t>
+          <t>Guides say you can 'easily spend an hour or two' in the bazaar alone (4h if you do garden, bazaar and dumpling houses together); 60min covers snacks and a souvenir sweep.</t>
         </is>
       </c>
       <c r="T204" s="6" t="inlineStr">
@@ -18698,26 +18698,26 @@
         </is>
       </c>
       <c r="D205" s="6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>Yuyuan Bazaar</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G205" s="6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="H205" s="6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I205" s="6" t="n">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="P205" s="6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="Q205" s="6" t="n">
@@ -18757,12 +18757,12 @@
       </c>
       <c r="R205" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:52 → 10:57; ORDER 30 → 40</t>
+          <t>RETIME 15:27 → 13:14; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S205" s="7" t="inlineStr">
         <is>
-          <t>Guides say you can 'easily spend an hour or two' in the bazaar alone (4h if you do garden, bazaar and dumpling houses together); 60min covers snacks and a souvenir sweep.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T205" s="6" t="inlineStr">
@@ -18786,7 +18786,7 @@
         </is>
       </c>
       <c r="D206" s="6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
@@ -18800,12 +18800,12 @@
       </c>
       <c r="G206" s="6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="H206" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="I206" s="6" t="n">
@@ -18813,23 +18813,23 @@
       </c>
       <c r="J206" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>People’s Square</t>
         </is>
       </c>
       <c r="K206" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L206" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M206" s="6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="N206" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O206" s="6" t="n">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="R206" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:31 → 12:15</t>
+          <t>RETIME 13:31 → 14:32; ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S206" s="7" t="inlineStr">
@@ -18874,50 +18874,50 @@
         </is>
       </c>
       <c r="D207" s="6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>People’s Square</t>
         </is>
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G207" s="6" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="H207" s="6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I207" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J207" s="6" t="inlineStr">
         <is>
-          <t>People’s Square</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L207" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M207" s="6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="N207" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O207" s="6" t="n">
@@ -18925,20 +18925,20 @@
       </c>
       <c r="P207" s="6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="Q207" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R207" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:27 → 13:08</t>
+          <t>RETIME 16:39 → 15:34</t>
         </is>
       </c>
       <c r="S207" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>TripAdvisor reviews split between '10 minutes is plenty' for the plaza and 2-4h if you linger in People's Park; 45min suits its role here as a stroll-and-rest buffer.</t>
         </is>
       </c>
       <c r="T207" s="6" t="inlineStr">
@@ -18962,30 +18962,30 @@
         </is>
       </c>
       <c r="D208" s="6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>People’s Square</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G208" s="6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H208" s="6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I208" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="J208" s="6" t="inlineStr">
         <is>
@@ -19013,20 +19013,20 @@
       </c>
       <c r="P208" s="6" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q208" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R208" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:39 → 14:25</t>
+          <t>RETIME 21:13 → 17:30; ORDER 90 → 80</t>
         </is>
       </c>
       <c r="S208" s="7" t="inlineStr">
         <is>
-          <t>TripAdvisor reviews split between '10 minutes is plenty' for the plaza and 2-4h if you linger in People's Park; 45min suits its role here as a stroll-and-rest buffer.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T208" s="6" t="inlineStr">
@@ -19050,7 +19050,7 @@
         </is>
       </c>
       <c r="D209" s="6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
@@ -19064,12 +19064,12 @@
       </c>
       <c r="G209" s="6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="H209" s="6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I209" s="6" t="n">
@@ -19077,23 +19077,23 @@
       </c>
       <c r="J209" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L209" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M209" s="6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="N209" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O209" s="6" t="n">
@@ -19109,7 +19109,7 @@
       </c>
       <c r="R209" s="7" t="inlineStr">
         <is>
-          <t>RETIME 22:52 → 15:28; ORDER 100 → 80</t>
+          <t>RETIME 22:52 → 19:30; ORDER 100 → 90</t>
         </is>
       </c>
       <c r="S209" s="7" t="inlineStr">
@@ -19138,26 +19138,26 @@
         </is>
       </c>
       <c r="D210" s="6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G210" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="H210" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="I210" s="6" t="n">
@@ -19170,14 +19170,14 @@
       </c>
       <c r="K210" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L210" s="6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="M210" s="6" t="n">
-        <v>0.77</v>
+        <v>1.47</v>
       </c>
       <c r="N210" s="6" t="inlineStr">
         <is>
@@ -19185,11 +19185,11 @@
         </is>
       </c>
       <c r="O210" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P210" s="6" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>01:51</t>
         </is>
       </c>
       <c r="Q210" s="6" t="n">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="R210" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:13 → 18:00</t>
+          <t>MOVE day 3 → 4; RETIME 01:51 → 21:02; ORDER 110 → 100</t>
         </is>
       </c>
       <c r="S210" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>The Fairmont Peace Hotel Old Jazz Band plays a long nightly run (from ~18:30, sets through 23:30); reviewers describe staying for a couple of sets over drinks, roughly 90min.</t>
         </is>
       </c>
       <c r="T210" s="6" t="inlineStr">
@@ -19240,12 +19240,12 @@
       </c>
       <c r="G211" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="H211" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I211" s="6" t="n">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="R211" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 07:30 → 09:00</t>
         </is>
       </c>
       <c r="S211" s="7" t="inlineStr">
@@ -19328,12 +19328,12 @@
       </c>
       <c r="G212" s="6" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="H212" s="6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I212" s="6" t="n">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="R212" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:02 → 08:02; ORDER 50 → 20</t>
+          <t>RETIME 17:02 → 10:02; ORDER 50 → 20</t>
         </is>
       </c>
       <c r="S212" s="7" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="G213" s="6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="H213" s="6" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I213" s="6" t="n">
@@ -19429,23 +19429,23 @@
       </c>
       <c r="J213" s="6" t="inlineStr">
         <is>
-          <t>West Bund riverside</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L213" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M213" s="6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="N213" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O213" s="6" t="n">
@@ -19461,7 +19461,7 @@
       </c>
       <c r="R213" s="7" t="inlineStr">
         <is>
-          <t>RETIME 11:13 → 09:42</t>
+          <t>RETIME 11:13 → 11:42</t>
         </is>
       </c>
       <c r="S213" s="7" t="inlineStr">
@@ -19494,46 +19494,46 @@
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="H214" s="6" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="I214" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J214" s="6" t="inlineStr">
+        <is>
           <t>West Bund riverside</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G214" s="6" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="H214" s="6" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="I214" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J214" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K214" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="L214" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M214" s="6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="N214" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O214" s="6" t="n">
@@ -19541,25 +19541,25 @@
       </c>
       <c r="P214" s="6" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="Q214" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R214" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:50 → 11:35; ORDER 20 → 40</t>
+          <t>RETIME 19:48 → 13:20; ORDER 60 → 40</t>
         </is>
       </c>
       <c r="S214" s="7" t="inlineStr">
         <is>
-          <t>No dedicated dwell figure found; the Xuhui riverside corridor linking the museums is a 10-15min walk each way, so ~45min allows an unhurried stroll with stops between venues.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T214" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -19582,26 +19582,26 @@
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>West Bund riverside</t>
         </is>
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G215" s="6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="H215" s="6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="I215" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J215" s="6" t="inlineStr">
         <is>
@@ -19629,25 +19629,25 @@
       </c>
       <c r="P215" s="6" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q215" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R215" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:48 → 12:28; ORDER 60 → 50</t>
+          <t>RETIME 08:50 → 14:43; ORDER 20 → 50</t>
         </is>
       </c>
       <c r="S215" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>No dedicated dwell figure found; the Xuhui riverside corridor linking the museums is a 10-15min walk each way, so ~45min allows an unhurried stroll with stops between venues.</t>
         </is>
       </c>
       <c r="T215" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -19680,12 +19680,12 @@
       </c>
       <c r="G216" s="6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I216" s="6" t="n">
@@ -19693,23 +19693,23 @@
       </c>
       <c r="J216" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Check in — J Hotel (Tower)</t>
         </is>
       </c>
       <c r="K216" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L216" s="6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M216" s="6" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="N216" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O216" s="6" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="R216" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:06 → 13:53; ORDER 40 → 60</t>
+          <t>RETIME 14:06 → 15:53; ORDER 40 → 60</t>
         </is>
       </c>
       <c r="S216" s="7" t="inlineStr">
@@ -19758,46 +19758,46 @@
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
+          <t>Check in — J Hotel (Tower)</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="H217" s="6" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="I217" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J217" s="6" t="inlineStr">
+        <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G217" s="6" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="H217" s="6" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="I217" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J217" s="6" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L217" s="6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M217" s="6" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="N217" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O217" s="6" t="n">
@@ -19805,20 +19805,20 @@
       </c>
       <c r="P217" s="6" t="inlineStr">
         <is>
-          <t>02:44</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="Q217" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="R217" s="7" t="inlineStr">
         <is>
-          <t>RETIME 02:44 → 18:00; ORDER 110 → 70</t>
+          <t>RETIME 20:57 → 17:48</t>
         </is>
       </c>
       <c r="S217" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>J Hotel's reception is on floor 101 of Shanghai Tower (check-in 15:00), so lift-lobby routing, the shuttle-lift ride and a luxury check-in run longer than a street-level desk.</t>
         </is>
       </c>
       <c r="T217" s="6" t="inlineStr">
@@ -19834,19 +19834,19 @@
         </is>
       </c>
       <c r="B218" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D218" s="6" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F218" s="6" t="inlineStr">
@@ -19856,57 +19856,57 @@
       </c>
       <c r="G218" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="H218" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I218" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J218" s="6" t="inlineStr">
         <is>
-          <t>Shanghai Museum East</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K218" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L218" s="6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M218" s="6" t="n">
-        <v>6.62</v>
+        <v>0</v>
       </c>
       <c r="N218" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O218" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P218" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>02:44</t>
         </is>
       </c>
       <c r="Q218" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R218" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 02:44 → 18:41; ORDER 110 → 80</t>
         </is>
       </c>
       <c r="S218" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T218" s="6" t="inlineStr">
@@ -19930,46 +19930,46 @@
         </is>
       </c>
       <c r="D219" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G219" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="H219" s="6" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="I219" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J219" s="6" t="inlineStr">
+        <is>
           <t>Shanghai Museum East</t>
         </is>
       </c>
-      <c r="F219" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G219" s="6" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H219" s="6" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="I219" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="J219" s="6" t="inlineStr">
-        <is>
-          <t>Shanghai Tower base</t>
-        </is>
-      </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="L219" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M219" s="6" t="n">
-        <v>3.63</v>
+        <v>6.62</v>
       </c>
       <c r="N219" s="6" t="inlineStr">
         <is>
@@ -19981,25 +19981,25 @@
       </c>
       <c r="P219" s="6" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q219" s="6" t="n">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="R219" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:21 → 08:00; ORDER 30 → 20</t>
+          <t>RETIME 07:30 → 09:00</t>
         </is>
       </c>
       <c r="S219" s="7" t="inlineStr">
         <is>
-          <t>Guides advise at least 2-3h and recommend 3-4h (3-5h thorough) for 20 halls; 3 focused hours covers the headline galleries plus one temporary show.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T219" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -20018,11 +20018,11 @@
         </is>
       </c>
       <c r="D220" s="6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Shanghai Tower base</t>
+          <t>Shanghai Museum East</t>
         </is>
       </c>
       <c r="F220" s="6" t="inlineStr">
@@ -20032,62 +20032,62 @@
       </c>
       <c r="G220" s="6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="H220" s="6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="I220" s="6" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="J220" s="6" t="inlineStr">
         <is>
-          <t>World Financial Center</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K220" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L220" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M220" s="6" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="N220" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O220" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P220" s="6" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q220" s="6" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="R220" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 5 → 6; RETIME 21:36 → 11:20; ORDER 80 → 30</t>
+          <t>RETIME 13:21 → 10:00; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S220" s="7" t="inlineStr">
         <is>
-          <t>No published dwell time; the ground plaza and Exit 9A photo spot are the documented ground-level draws, and a walk around the base with photos is ~30min.</t>
+          <t>Guides advise at least 2-3h and recommend 3-4h (3-5h thorough) for 20 halls; 3 focused hours covers the headline galleries plus one temporary show.</t>
         </is>
       </c>
       <c r="T220" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -20106,71 +20106,71 @@
         </is>
       </c>
       <c r="D221" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>World Financial Center</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G221" s="6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="I221" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J221" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Shanghai Tower base</t>
         </is>
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L221" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M221" s="6" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N221" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O221" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P221" s="6" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q221" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="R221" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 5 → 6; RETIME 01:05 → 12:06; ORDER 100 → 40</t>
+          <t>RETIME 12:00 → 13:08; ORDER 20 → 30</t>
         </is>
       </c>
       <c r="S221" s="7" t="inlineStr">
         <is>
-          <t>Exterior stop per the note; the 94/97/100F observatory would instead need 1-2h (30min on 94F, 20min on 97F, 1-1.5h on 100F) plus ticket and lift queues.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T221" s="6" t="inlineStr">
@@ -20194,34 +20194,34 @@
         </is>
       </c>
       <c r="D222" s="6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Shanghai Tower base</t>
         </is>
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G222" s="6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="H222" s="6" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="I222" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J222" s="6" t="inlineStr">
         <is>
-          <t>Jin Mao Tower</t>
+          <t>World Financial Center</t>
         </is>
       </c>
       <c r="K222" s="6" t="inlineStr">
@@ -20233,37 +20233,37 @@
         <v>8</v>
       </c>
       <c r="M222" s="6" t="n">
-        <v>0.6</v>
+        <v>0.17</v>
       </c>
       <c r="N222" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O222" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P222" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="Q222" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="R222" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 12:44; ORDER 20 → 50</t>
+          <t>MOVE day 5 → 6; RETIME 21:36 → 14:28; ORDER 80 → 40</t>
         </is>
       </c>
       <c r="S222" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>No published dwell time; the ground plaza and Exit 9A photo spot are the documented ground-level draws, and a walk around the base with photos is ~30min.</t>
         </is>
       </c>
       <c r="T222" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -20282,11 +20282,11 @@
         </is>
       </c>
       <c r="D223" s="6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Jin Mao Tower</t>
+          <t>World Financial Center</t>
         </is>
       </c>
       <c r="F223" s="6" t="inlineStr">
@@ -20296,12 +20296,12 @@
       </c>
       <c r="G223" s="6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="H223" s="6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I223" s="6" t="n">
@@ -20309,7 +20309,7 @@
       </c>
       <c r="J223" s="6" t="inlineStr">
         <is>
-          <t>Oriental Pearl Tower</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="K223" s="6" t="inlineStr">
@@ -20318,14 +20318,14 @@
         </is>
       </c>
       <c r="L223" s="6" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M223" s="6" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="N223" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O223" s="6" t="n">
@@ -20333,7 +20333,7 @@
       </c>
       <c r="P223" s="6" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="Q223" s="6" t="n">
@@ -20341,12 +20341,12 @@
       </c>
       <c r="R223" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 5 → 6; RETIME 23:19 → 14:00; ORDER 90 → 60</t>
+          <t>MOVE day 5 → 6; RETIME 01:05 → 15:14; ORDER 100 → 50</t>
         </is>
       </c>
       <c r="S223" s="7" t="inlineStr">
         <is>
-          <t>Treated per the note as an exterior stop; going up would be different — the 88F deck is quoted at 2-3h and the Skywalk session alone is 45min plus 30min security check-in.</t>
+          <t>Exterior stop per the note; the 94/97/100F observatory would instead need 1-2h (30min on 94F, 20min on 97F, 1-1.5h on 100F) plus ticket and lift queues.</t>
         </is>
       </c>
       <c r="T223" s="6" t="inlineStr">
@@ -20370,11 +20370,11 @@
         </is>
       </c>
       <c r="D224" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Oriental Pearl Tower</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="F224" s="6" t="inlineStr">
@@ -20384,12 +20384,12 @@
       </c>
       <c r="G224" s="6" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H224" s="6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I224" s="6" t="n">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="J224" s="6" t="inlineStr">
         <is>
-          <t>Pudong promenade</t>
+          <t>Oriental Pearl Tower</t>
         </is>
       </c>
       <c r="K224" s="6" t="inlineStr">
@@ -20406,22 +20406,22 @@
         </is>
       </c>
       <c r="L224" s="6" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="M224" s="6" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="N224" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O224" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P224" s="6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="Q224" s="6" t="n">
@@ -20429,12 +20429,12 @@
       </c>
       <c r="R224" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:30 → 14:57; ORDER 50 → 70</t>
+          <t>MOVE day 5 → 6; RETIME 23:19 → 16:00; ORDER 90 → 60</t>
         </is>
       </c>
       <c r="S224" s="7" t="inlineStr">
         <is>
-          <t>Exterior-only per the note, so a photo stop at the base; ascending instead runs 1-2h on the decks and 2-3h with the museum, plus 15-60min ticket and 10-60min lift queues.</t>
+          <t>Treated per the note as an exterior stop; going up would be different — the 88F deck is quoted at 2-3h and the Skywalk session alone is 45min plus 30min security check-in.</t>
         </is>
       </c>
       <c r="T224" s="6" t="inlineStr">
@@ -20458,11 +20458,11 @@
         </is>
       </c>
       <c r="D225" s="6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Pudong promenade</t>
+          <t>Oriental Pearl Tower</t>
         </is>
       </c>
       <c r="F225" s="6" t="inlineStr">
@@ -20472,16 +20472,16 @@
       </c>
       <c r="G225" s="6" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="H225" s="6" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I225" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J225" s="6" t="inlineStr">
         <is>
@@ -20509,20 +20509,20 @@
       </c>
       <c r="P225" s="6" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="Q225" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="R225" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:21 → 15:36; ORDER 40 → 80</t>
+          <t>RETIME 17:30 → 16:57; ORDER 50 → 70</t>
         </is>
       </c>
       <c r="S225" s="7" t="inlineStr">
         <is>
-          <t>Binjiang Avenue full route logs are 7.7km/2h, but the Lujiazui section fronting the towers is a fraction of that; TripAdvisor describes it as a short skyline stroll of ~45min.</t>
+          <t>Exterior-only per the note, so a photo stop at the base; ascending instead runs 1-2h on the decks and 2-3h with the museum, plus 15-60min ticket and 10-60min lift queues.</t>
         </is>
       </c>
       <c r="T225" s="6" t="inlineStr">
@@ -20546,7 +20546,7 @@
         </is>
       </c>
       <c r="D226" s="6" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
@@ -20573,23 +20573,23 @@
       </c>
       <c r="J226" s="6" t="inlineStr">
         <is>
-          <t>Fly from PVG</t>
+          <t>Pudong promenade</t>
         </is>
       </c>
       <c r="K226" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L226" s="6" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M226" s="6" t="n">
-        <v>31.45</v>
+        <v>0</v>
       </c>
       <c r="N226" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O226" s="6" t="n">
@@ -20605,7 +20605,7 @@
       </c>
       <c r="R226" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:48 → 18:00; ORDER 60 → 90</t>
+          <t>RETIME 19:48 → 18:00; ORDER 60 → 80</t>
         </is>
       </c>
       <c r="S226" s="7" t="inlineStr">
@@ -20634,69 +20634,157 @@
         </is>
       </c>
       <c r="D227" s="6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
+          <t>Pudong promenade</t>
+        </is>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G227" s="6" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="H227" s="6" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="I227" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J227" s="6" t="inlineStr">
+        <is>
           <t>Fly from PVG</t>
         </is>
       </c>
-      <c r="F227" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="G227" s="6" t="inlineStr">
-        <is>
-          <t>23:10</t>
-        </is>
-      </c>
-      <c r="H227" s="6" t="inlineStr">
-        <is>
-          <t>02:10 (+1)</t>
-        </is>
-      </c>
-      <c r="I227" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="J227" s="6" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
-      <c r="K227" s="6" t="inlineStr"/>
-      <c r="L227" s="6" t="inlineStr"/>
-      <c r="M227" s="6" t="inlineStr"/>
-      <c r="N227" s="6" t="inlineStr"/>
+      <c r="K227" s="6" t="inlineStr">
+        <is>
+          <t>didi</t>
+        </is>
+      </c>
+      <c r="L227" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="M227" s="6" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="N227" s="6" t="inlineStr">
+        <is>
+          <t>estimated (fitted model)</t>
+        </is>
+      </c>
       <c r="O227" s="6" t="n">
         <v>6</v>
       </c>
       <c r="P227" s="6" t="inlineStr">
         <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="Q227" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="R227" s="7" t="inlineStr">
+        <is>
+          <t>RETIME 16:21 → 20:15; ORDER 40 → 90</t>
+        </is>
+      </c>
+      <c r="S227" s="7" t="inlineStr">
+        <is>
+          <t>Binjiang Avenue full route logs are 7.7km/2h, but the Lujiazui section fronting the towers is a fraction of that; TripAdvisor describes it as a short skyline stroll of ~45min.</t>
+        </is>
+      </c>
+      <c r="T227" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D228" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>Fly from PVG</t>
+        </is>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="G228" s="6" t="inlineStr">
+        <is>
           <t>23:10</t>
         </is>
       </c>
-      <c r="Q227" s="6" t="n">
+      <c r="H228" s="6" t="inlineStr">
+        <is>
+          <t>02:10 (+1)</t>
+        </is>
+      </c>
+      <c r="I228" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="R227" s="7" t="inlineStr">
+      <c r="J228" s="6" t="inlineStr">
+        <is>
+          <t>Hotel (home)</t>
+        </is>
+      </c>
+      <c r="K228" s="6" t="inlineStr"/>
+      <c r="L228" s="6" t="inlineStr"/>
+      <c r="M228" s="6" t="inlineStr"/>
+      <c r="N228" s="6" t="inlineStr"/>
+      <c r="O228" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P228" s="6" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="Q228" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="R228" s="7" t="inlineStr">
         <is>
           <t>ORDER 70 → 100</t>
         </is>
       </c>
-      <c r="S227" s="7" t="inlineStr">
+      <c r="S228" s="7" t="inlineStr">
         <is>
           <t>PVG guidance is to arrive 3h before an international departure (check-in closes 60min out), with Aug listed among the airport's busiest months; matches the note's 23:10 for a 02:10 flight.</t>
         </is>
       </c>
-      <c r="T227" s="6" t="inlineStr">
+      <c r="T228" s="6" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T227"/>
+  <autoFilter ref="A1:T228"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20707,7 +20795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T242"/>
+  <dimension ref="A1:T243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -37460,23 +37548,23 @@
       </c>
       <c r="J192" s="6" t="inlineStr">
         <is>
-          <t>Check in at Marriott</t>
+          <t>Shanghai Maglev</t>
         </is>
       </c>
       <c r="K192" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L192" s="6" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M192" s="6" t="n">
-        <v>33.89</v>
+        <v>0</v>
       </c>
       <c r="N192" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O192" s="6" t="n">
@@ -37525,30 +37613,30 @@
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
+          <t>Shanghai Maglev</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J193" s="6" t="inlineStr">
+        <is>
           <t>Check in at Marriott</t>
-        </is>
-      </c>
-      <c r="F193" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G193" s="6" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="H193" s="6" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="I193" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J193" s="6" t="inlineStr">
-        <is>
-          <t>Shanghai Maglev</t>
         </is>
       </c>
       <c r="K193" s="6" t="inlineStr">
@@ -37572,25 +37660,25 @@
       </c>
       <c r="P193" s="6" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="Q193" s="6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R193" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:57 → 15:58; ORDER 40 → 30</t>
+          <t>RETIME 14:30 → 15:01; ORDER 20 → 30</t>
         </is>
       </c>
       <c r="S193" s="7" t="inlineStr">
         <is>
-          <t>Standard city-hotel check-in plus bag drop and a quick freshen-up; no evidence of unusual delays at this property.</t>
+          <t>Operator and airport guides: 8-minute run PVG-Longyang Road with departures every 15-20min, so ticket, platform wait, ride and exit total roughly 25min.</t>
         </is>
       </c>
       <c r="T193" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -37613,7 +37701,7 @@
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Shanghai Maglev</t>
+          <t>Check in at Marriott</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
@@ -37623,16 +37711,16 @@
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="H194" s="6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="I194" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J194" s="6" t="inlineStr">
         <is>
@@ -37641,18 +37729,18 @@
       </c>
       <c r="K194" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L194" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M194" s="6" t="n">
-        <v>8.449999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="N194" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O194" s="6" t="n">
@@ -37660,25 +37748,25 @@
       </c>
       <c r="P194" s="6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="Q194" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R194" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:30 → 16:56; ORDER 20 → 40</t>
+          <t>RETIME 16:57 → 15:54</t>
         </is>
       </c>
       <c r="S194" s="7" t="inlineStr">
         <is>
-          <t>Operator and airport guides: 8-minute run PVG-Longyang Road with departures every 15-20min, so ticket, platform wait, ride and exit total roughly 25min.</t>
+          <t>Standard city-hotel check-in plus bag drop and a quick freshen-up; no evidence of unusual delays at this property.</t>
         </is>
       </c>
       <c r="T194" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -37711,12 +37799,12 @@
       </c>
       <c r="G195" s="6" t="inlineStr">
         <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="H195" s="6" t="inlineStr">
+        <is>
           <t>17:48</t>
-        </is>
-      </c>
-      <c r="H195" s="6" t="inlineStr">
-        <is>
-          <t>18:48</t>
         </is>
       </c>
       <c r="I195" s="6" t="n">
@@ -37756,7 +37844,7 @@
       </c>
       <c r="R195" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:51 → 17:48</t>
+          <t>RETIME 17:51 → 16:48</t>
         </is>
       </c>
       <c r="S195" s="7" t="inlineStr">
@@ -37799,12 +37887,12 @@
       </c>
       <c r="G196" s="6" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="H196" s="6" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I196" s="6" t="n">
@@ -37844,7 +37932,7 @@
       </c>
       <c r="R196" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:16 → 18:56; ORDER 70 → 60</t>
+          <t>RETIME 21:16 → 17:56; ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S196" s="7" t="inlineStr">
@@ -37887,12 +37975,12 @@
       </c>
       <c r="G197" s="6" t="inlineStr">
         <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
           <t>20:53</t>
-        </is>
-      </c>
-      <c r="H197" s="6" t="inlineStr">
-        <is>
-          <t>21:53</t>
         </is>
       </c>
       <c r="I197" s="6" t="n">
@@ -37900,19 +37988,19 @@
       </c>
       <c r="J197" s="6" t="inlineStr">
         <is>
-          <t>Old Jazz Bar</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L197" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M197" s="6" t="n">
-        <v>0.34</v>
+        <v>2.04</v>
       </c>
       <c r="N197" s="6" t="inlineStr">
         <is>
@@ -37932,7 +38020,7 @@
       </c>
       <c r="R197" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:33 → 20:53; ORDER 60 → 70</t>
+          <t>RETIME 19:33 → 19:53; ORDER 60 → 70</t>
         </is>
       </c>
       <c r="S197" s="7" t="inlineStr">
@@ -37953,42 +38041,42 @@
         </is>
       </c>
       <c r="B198" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D198" s="6" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Old Jazz Bar</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="H198" s="6" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I198" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="J198" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Recovery massage / spa</t>
         </is>
       </c>
       <c r="K198" s="6" t="inlineStr">
@@ -37997,10 +38085,10 @@
         </is>
       </c>
       <c r="L198" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M198" s="6" t="n">
-        <v>1.72</v>
+        <v>2.67</v>
       </c>
       <c r="N198" s="6" t="inlineStr">
         <is>
@@ -38008,24 +38096,24 @@
         </is>
       </c>
       <c r="O198" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P198" s="6" t="inlineStr">
         <is>
-          <t>01:51</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q198" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="R198" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 3 → 1; RETIME 01:51 → 22:13; ORDER 110 → 80</t>
+          <t>RETIME 07:30 → 07:00</t>
         </is>
       </c>
       <c r="S198" s="7" t="inlineStr">
         <is>
-          <t>The Fairmont Peace Hotel Old Jazz Band plays a long nightly run (from ~18:30, sets through 23:30); reviewers describe staying for a couple of sets over drinks, roughly 90min.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T198" s="6" t="inlineStr">
@@ -38049,34 +38137,34 @@
         </is>
       </c>
       <c r="D199" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Recovery massage / spa</t>
         </is>
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G199" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="H199" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I199" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J199" s="6" t="inlineStr">
         <is>
-          <t>Recovery massage / spa</t>
+          <t>M50 Creative Park</t>
         </is>
       </c>
       <c r="K199" s="6" t="inlineStr">
@@ -38085,10 +38173,10 @@
         </is>
       </c>
       <c r="L199" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M199" s="6" t="n">
-        <v>2.67</v>
+        <v>3.34</v>
       </c>
       <c r="N199" s="6" t="inlineStr">
         <is>
@@ -38100,20 +38188,20 @@
       </c>
       <c r="P199" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="Q199" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R199" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 13:28 → 07:54; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S199" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Shanghai spa listings (Time Out, SmartShanghai, Culture Trip) show 60-80min foot/body packages as the standard tourist option; add foot bath, changing and tea for ~90min door to door.</t>
         </is>
       </c>
       <c r="T199" s="6" t="inlineStr">
@@ -38137,11 +38225,11 @@
         </is>
       </c>
       <c r="D200" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Recovery massage / spa</t>
+          <t>M50 Creative Park</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
@@ -38151,57 +38239,57 @@
       </c>
       <c r="G200" s="6" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="H200" s="6" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I200" s="6" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J200" s="6" t="inlineStr">
         <is>
-          <t>M50 Creative Park</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K200" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L200" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M200" s="6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N200" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O200" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P200" s="6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="Q200" s="6" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="R200" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:28 → 07:54; ORDER 30 → 20</t>
+          <t>MOVE day 4 → 2; RETIME 18:37 → 10:00; ORDER 80 → 30</t>
         </is>
       </c>
       <c r="S200" s="7" t="inlineStr">
         <is>
-          <t>Shanghai spa listings (Time Out, SmartShanghai, Culture Trip) show 60-80min foot/body packages as the standard tourist option; add foot bath, changing and tea for ~90min door to door.</t>
+          <t>Travel guides budget 2-4h (about 3h recommended) for 140+ studios and galleries plus the graffiti wall; 2h is a highlights-plus pass through the better galleries.</t>
         </is>
       </c>
       <c r="T200" s="6" t="inlineStr">
@@ -38225,30 +38313,30 @@
         </is>
       </c>
       <c r="D201" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>M50 Creative Park</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G201" s="6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="H201" s="6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="I201" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="J201" s="6" t="inlineStr">
         <is>
@@ -38272,24 +38360,24 @@
         </is>
       </c>
       <c r="O201" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P201" s="6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q201" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="R201" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 4 → 2; RETIME 18:37 → 09:44; ORDER 80 → 30</t>
+          <t>RETIME 12:00 → 12:08; ORDER 20 → 40</t>
         </is>
       </c>
       <c r="S201" s="7" t="inlineStr">
         <is>
-          <t>Travel guides budget 2-4h (about 3h recommended) for 140+ studios and galleries plus the graffiti wall; 2h is a highlights-plus pass through the better galleries.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T201" s="6" t="inlineStr">
@@ -38313,7 +38401,7 @@
         </is>
       </c>
       <c r="D202" s="6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
@@ -38327,12 +38415,12 @@
       </c>
       <c r="G202" s="6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="H202" s="6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="I202" s="6" t="n">
@@ -38340,23 +38428,23 @@
       </c>
       <c r="J202" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Nanjing Road West</t>
         </is>
       </c>
       <c r="K202" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L202" s="6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M202" s="6" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="N202" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O202" s="6" t="n">
@@ -38372,7 +38460,7 @@
       </c>
       <c r="R202" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:55 → 12:03</t>
+          <t>RETIME 15:55 → 13:27; ORDER 40 → 50</t>
         </is>
       </c>
       <c r="S202" s="7" t="inlineStr">
@@ -38401,34 +38489,34 @@
         </is>
       </c>
       <c r="D203" s="6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Nanjing Road West</t>
         </is>
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G203" s="6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="H203" s="6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I203" s="6" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J203" s="6" t="inlineStr">
         <is>
-          <t>Nanjing Road West</t>
+          <t>Zhangyuan</t>
         </is>
       </c>
       <c r="K203" s="6" t="inlineStr">
@@ -38437,14 +38525,14 @@
         </is>
       </c>
       <c r="L203" s="6" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="M203" s="6" t="n">
-        <v>0.96</v>
+        <v>0.5</v>
       </c>
       <c r="N203" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O203" s="6" t="n">
@@ -38452,20 +38540,20 @@
       </c>
       <c r="P203" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="Q203" s="6" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="R203" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 13:11; ORDER 20 → 50</t>
+          <t>RETIME 19:32 → 14:58</t>
         </is>
       </c>
       <c r="S203" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Shopping guides: most visitors spend 1-2h on West Nanjing Road, 2-3h if working through Plaza 66 / HKRI Taikoo Hui; 75min covers the strip plus one mall.</t>
         </is>
       </c>
       <c r="T203" s="6" t="inlineStr">
@@ -38489,50 +38577,50 @@
         </is>
       </c>
       <c r="D204" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>Zhangyuan</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
-        <is>
-          <t>Nanjing Road West</t>
-        </is>
-      </c>
-      <c r="F204" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G204" s="6" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="H204" s="6" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="I204" s="6" t="n">
-        <v>75</v>
-      </c>
       <c r="J204" s="6" t="inlineStr">
         <is>
-          <t>Zhangyuan</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K204" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L204" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M204" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N204" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O204" s="6" t="n">
@@ -38540,20 +38628,20 @@
       </c>
       <c r="P204" s="6" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="Q204" s="6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="R204" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:32 → 14:42</t>
+          <t>RETIME 17:47 → 16:28; ORDER 50 → 70</t>
         </is>
       </c>
       <c r="S204" s="7" t="inlineStr">
         <is>
-          <t>Shopping guides: most visitors spend 1-2h on West Nanjing Road, 2-3h if working through Plaza 66 / HKRI Taikoo Hui; 75min covers the strip plus one mall.</t>
+          <t>Reviews describe a restored shikumen retail precinct 'similar to Xintiandi but much quieter'; an unhurried wander of the lanes with a pop-up or two runs about an hour.</t>
         </is>
       </c>
       <c r="T204" s="6" t="inlineStr">
@@ -38577,50 +38665,50 @@
         </is>
       </c>
       <c r="D205" s="6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>Zhangyuan</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G205" s="6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H205" s="6" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I205" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J205" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L205" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M205" s="6" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="N205" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O205" s="6" t="n">
@@ -38628,20 +38716,20 @@
       </c>
       <c r="P205" s="6" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="Q205" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R205" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:47 → 16:12; ORDER 50 → 70</t>
+          <t>RETIME 21:15 → 18:00; ORDER 70 → 80</t>
         </is>
       </c>
       <c r="S205" s="7" t="inlineStr">
         <is>
-          <t>Reviews describe a restored shikumen retail precinct 'similar to Xintiandi but much quieter'; an unhurried wander of the lanes with a pop-up or two runs about an hour.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T205" s="6" t="inlineStr">
@@ -38657,19 +38745,19 @@
         </is>
       </c>
       <c r="B206" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D206" s="6" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
@@ -38679,20 +38767,20 @@
       </c>
       <c r="G206" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="H206" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I206" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="J206" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Wukang Building</t>
         </is>
       </c>
       <c r="K206" s="6" t="inlineStr">
@@ -38701,10 +38789,10 @@
         </is>
       </c>
       <c r="L206" s="6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M206" s="6" t="n">
-        <v>4.38</v>
+        <v>7.18</v>
       </c>
       <c r="N206" s="6" t="inlineStr">
         <is>
@@ -38712,24 +38800,24 @@
         </is>
       </c>
       <c r="O206" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P206" s="6" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="Q206" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="R206" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:15 → 18:00; ORDER 70 → 80</t>
+          <t>RETIME 09:00 → 07:00</t>
         </is>
       </c>
       <c r="S206" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T206" s="6" t="inlineStr">
@@ -38753,50 +38841,50 @@
         </is>
       </c>
       <c r="D207" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>Wukang Building</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J207" s="6" t="inlineStr">
+        <is>
+          <t>Wukang Road</t>
+        </is>
+      </c>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="L207" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
-        <is>
-          <t>Breakfast</t>
-        </is>
-      </c>
-      <c r="F207" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G207" s="6" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="H207" s="6" t="inlineStr">
-        <is>
-          <t>07:35</t>
-        </is>
-      </c>
-      <c r="I207" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="J207" s="6" t="inlineStr">
-        <is>
-          <t>Wukang Building</t>
-        </is>
-      </c>
-      <c r="K207" s="6" t="inlineStr">
-        <is>
-          <t>didi</t>
-        </is>
-      </c>
-      <c r="L207" s="6" t="n">
-        <v>17</v>
-      </c>
       <c r="M207" s="6" t="n">
-        <v>7.18</v>
+        <v>0.7</v>
       </c>
       <c r="N207" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O207" s="6" t="n">
@@ -38804,20 +38892,20 @@
       </c>
       <c r="P207" s="6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="Q207" s="6" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="R207" s="7" t="inlineStr">
         <is>
-          <t>RETIME 09:00 → 07:00</t>
+          <t>RETIME 10:18 → 08:00</t>
         </is>
       </c>
       <c r="S207" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Walking guides treat Wukang Mansion as a photo landmark on the corner (best 16:00-17:30); it is exterior-only, so 15-25min including crowd jostling.</t>
         </is>
       </c>
       <c r="T207" s="6" t="inlineStr">
@@ -38841,11 +38929,11 @@
         </is>
       </c>
       <c r="D208" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Wukang Building</t>
+          <t>Wukang Road</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
@@ -38855,20 +38943,20 @@
       </c>
       <c r="G208" s="6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="H208" s="6" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I208" s="6" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J208" s="6" t="inlineStr">
         <is>
-          <t>Wukang Road</t>
+          <t>Ferguson Lane</t>
         </is>
       </c>
       <c r="K208" s="6" t="inlineStr">
@@ -38877,10 +38965,10 @@
         </is>
       </c>
       <c r="L208" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M208" s="6" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="N208" s="6" t="inlineStr">
         <is>
@@ -38892,20 +38980,20 @@
       </c>
       <c r="P208" s="6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="Q208" s="6" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R208" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:18 → 08:00</t>
+          <t>RETIME 12:06 → 08:38</t>
         </is>
       </c>
       <c r="S208" s="7" t="inlineStr">
         <is>
-          <t>Walking guides treat Wukang Mansion as a photo landmark on the corner (best 16:00-17:30); it is exterior-only, so 15-25min including crowd jostling.</t>
+          <t>Guides quote 2-3h for Wukang Road with photos and coffee, but that bundles Ferguson Lane and cafes which are separate stops here; the 1.17km street alone walks in about an hour.</t>
         </is>
       </c>
       <c r="T208" s="6" t="inlineStr">
@@ -38929,11 +39017,11 @@
         </is>
       </c>
       <c r="D209" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>Wukang Road</t>
+          <t>Ferguson Lane</t>
         </is>
       </c>
       <c r="F209" s="6" t="inlineStr">
@@ -38943,32 +39031,32 @@
       </c>
       <c r="G209" s="6" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="H209" s="6" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I209" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J209" s="6" t="inlineStr">
         <is>
-          <t>Ferguson Lane</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="L209" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M209" s="6" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="N209" s="6" t="inlineStr">
         <is>
@@ -38980,25 +39068,25 @@
       </c>
       <c r="P209" s="6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="Q209" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R209" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:06 → 08:38</t>
+          <t>RETIME 13:33 → 09:50</t>
         </is>
       </c>
       <c r="S209" s="7" t="inlineStr">
         <is>
-          <t>Guides quote 2-3h for Wukang Road with photos and coffee, but that bundles Ferguson Lane and cafes which are separate stops here; the 1.17km street alone walks in about an hour.</t>
+          <t>Ferguson Lane (376 Wukang Rd) is described as a small tucked-away courtyard of galleries and bistros — 15min to look, 45min if you actually sit for the coffee it exists for.</t>
         </is>
       </c>
       <c r="T209" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -39017,11 +39105,11 @@
         </is>
       </c>
       <c r="D210" s="6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Ferguson Lane</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
@@ -39031,12 +39119,12 @@
       </c>
       <c r="G210" s="6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="H210" s="6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I210" s="6" t="n">
@@ -39044,7 +39132,7 @@
       </c>
       <c r="J210" s="6" t="inlineStr">
         <is>
-          <t>Anfu Road</t>
+          <t>Wulumuqi Road</t>
         </is>
       </c>
       <c r="K210" s="6" t="inlineStr">
@@ -39056,7 +39144,7 @@
         <v>14</v>
       </c>
       <c r="M210" s="6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="N210" s="6" t="inlineStr">
         <is>
@@ -39068,7 +39156,7 @@
       </c>
       <c r="P210" s="6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="Q210" s="6" t="n">
@@ -39076,17 +39164,17 @@
       </c>
       <c r="R210" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:33 → 09:50</t>
+          <t>RETIME 15:25 → 10:57</t>
         </is>
       </c>
       <c r="S210" s="7" t="inlineStr">
         <is>
-          <t>Ferguson Lane (376 Wukang Rd) is described as a small tucked-away courtyard of galleries and bistros — 15min to look, 45min if you actually sit for the coffee it exists for.</t>
+          <t>Wukang+Anfu combined walking routes are quoted at 3-4h over 2.5km; Anfu Road's own share, browsing a couple of shops, is roughly 45min.</t>
         </is>
       </c>
       <c r="T210" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -39105,11 +39193,11 @@
         </is>
       </c>
       <c r="D211" s="6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>Anfu Road</t>
+          <t>Wulumuqi Road</t>
         </is>
       </c>
       <c r="F211" s="6" t="inlineStr">
@@ -39119,36 +39207,36 @@
       </c>
       <c r="G211" s="6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="H211" s="6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I211" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J211" s="6" t="inlineStr">
         <is>
-          <t>Wulumuqi Road</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L211" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M211" s="6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N211" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O211" s="6" t="n">
@@ -39156,25 +39244,25 @@
       </c>
       <c r="P211" s="6" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="Q211" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="R211" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:25 → 10:57</t>
+          <t>RETIME 17:02 → 12:04</t>
         </is>
       </c>
       <c r="S211" s="7" t="inlineStr">
         <is>
-          <t>Wukang+Anfu combined walking routes are quoted at 3-4h over 2.5km; Anfu Road's own share, browsing a couple of shops, is roughly 45min.</t>
+          <t>Guides frame Wulumuqi Middle Road as a short local-life detour (markets, Art Deco corner at Fuxing West Rd) rather than a destination; ~30min walk-through.</t>
         </is>
       </c>
       <c r="T211" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -39193,50 +39281,50 @@
         </is>
       </c>
       <c r="D212" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="H212" s="6" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="I212" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
-        <is>
-          <t>Wulumuqi Road</t>
-        </is>
-      </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G212" s="6" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="H212" s="6" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="I212" s="6" t="n">
-        <v>30</v>
-      </c>
       <c r="J212" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Fuxing Park</t>
         </is>
       </c>
       <c r="K212" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L212" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M212" s="6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N212" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O212" s="6" t="n">
@@ -39244,25 +39332,25 @@
       </c>
       <c r="P212" s="6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="Q212" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="R212" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:02 → 12:04</t>
+          <t>RETIME 18:46 → 12:42</t>
         </is>
       </c>
       <c r="S212" s="7" t="inlineStr">
         <is>
-          <t>Guides frame Wulumuqi Middle Road as a short local-life detour (markets, Art Deco corner at Fuxing West Rd) rather than a destination; ~30min walk-through.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T212" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -39281,50 +39369,50 @@
         </is>
       </c>
       <c r="D213" s="6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Fuxing Park</t>
         </is>
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G213" s="6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H213" s="6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I213" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J213" s="6" t="inlineStr">
         <is>
-          <t>Fuxing Park</t>
+          <t>Sinan Mansions</t>
         </is>
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L213" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M213" s="6" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="N213" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O213" s="6" t="n">
@@ -39332,20 +39420,20 @@
       </c>
       <c r="P213" s="6" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q213" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R213" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:46 → 12:42</t>
+          <t>RETIME 21:42 → 14:00; ORDER 90 → 80</t>
         </is>
       </c>
       <c r="S213" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>Guides say Fuxing Park is 'worth a 30-60 minute walk'; 45min lets you watch the dancing and chess without circling twice.</t>
         </is>
       </c>
       <c r="T213" s="6" t="inlineStr">
@@ -39369,11 +39457,11 @@
         </is>
       </c>
       <c r="D214" s="6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>Fuxing Park</t>
+          <t>Sinan Mansions</t>
         </is>
       </c>
       <c r="F214" s="6" t="inlineStr">
@@ -39383,36 +39471,36 @@
       </c>
       <c r="G214" s="6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="H214" s="6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I214" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J214" s="6" t="inlineStr">
         <is>
-          <t>Sinan Mansions</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K214" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L214" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M214" s="6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="N214" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O214" s="6" t="n">
@@ -39420,20 +39508,20 @@
       </c>
       <c r="P214" s="6" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="Q214" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R214" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:42 → 14:00; ORDER 90 → 80</t>
+          <t>RETIME 19:59 → 14:58; ORDER 80 → 90</t>
         </is>
       </c>
       <c r="S214" s="7" t="inlineStr">
         <is>
-          <t>Guides say Fuxing Park is 'worth a 30-60 minute walk'; 45min lets you watch the dancing and chess without circling twice.</t>
+          <t>Travel guides advise 1-2h to walk the estate, admire the facades and browse boutiques/side galleries; 60min is the lower, unhurried-but-not-lingering end.</t>
         </is>
       </c>
       <c r="T214" s="6" t="inlineStr">
@@ -39457,50 +39545,50 @@
         </is>
       </c>
       <c r="D215" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H215" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="I215" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
-        <is>
-          <t>Sinan Mansions</t>
-        </is>
-      </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G215" s="6" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="H215" s="6" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="I215" s="6" t="n">
-        <v>60</v>
-      </c>
       <c r="J215" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L215" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M215" s="6" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N215" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O215" s="6" t="n">
@@ -39508,20 +39596,20 @@
       </c>
       <c r="P215" s="6" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="Q215" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R215" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:59 → 14:58; ORDER 80 → 90</t>
+          <t>RETIME 00:10 → 18:00</t>
         </is>
       </c>
       <c r="S215" s="7" t="inlineStr">
         <is>
-          <t>Travel guides advise 1-2h to walk the estate, admire the facades and browse boutiques/side galleries; 60min is the lower, unhurried-but-not-lingering end.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T215" s="6" t="inlineStr">
@@ -39537,19 +39625,19 @@
         </is>
       </c>
       <c r="B216" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D216" s="6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="F216" s="6" t="inlineStr">
@@ -39559,20 +39647,20 @@
       </c>
       <c r="G216" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I216" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="J216" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Yu Garden</t>
         </is>
       </c>
       <c r="K216" s="6" t="inlineStr">
@@ -39581,10 +39669,10 @@
         </is>
       </c>
       <c r="L216" s="6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M216" s="6" t="n">
-        <v>3.97</v>
+        <v>1.27</v>
       </c>
       <c r="N216" s="6" t="inlineStr">
         <is>
@@ -39592,24 +39680,24 @@
         </is>
       </c>
       <c r="O216" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P216" s="6" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q216" s="6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="R216" s="7" t="inlineStr">
         <is>
-          <t>RETIME 00:10 → 18:00</t>
+          <t>RETIME 07:30 → 08:00</t>
         </is>
       </c>
       <c r="S216" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T216" s="6" t="inlineStr">
@@ -39633,46 +39721,46 @@
         </is>
       </c>
       <c r="D217" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Yu Garden</t>
         </is>
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G217" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="H217" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I217" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J217" s="6" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L217" s="6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M217" s="6" t="n">
-        <v>1.27</v>
+        <v>0.47</v>
       </c>
       <c r="N217" s="6" t="inlineStr">
         <is>
@@ -39684,25 +39772,25 @@
       </c>
       <c r="P217" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q217" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R217" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 08:41 → 09:00</t>
         </is>
       </c>
       <c r="S217" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>TripAdvisor/guide consensus is ~2h for a complete visit and 45-60min for a fast loop; at opening with fewer crowds, a highlights-plus circuit of the rockeries and pavilions is ~90min.</t>
         </is>
       </c>
       <c r="T217" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -39721,11 +39809,11 @@
         </is>
       </c>
       <c r="D218" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="F218" s="6" t="inlineStr">
@@ -39735,20 +39823,20 @@
       </c>
       <c r="G218" s="6" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="H218" s="6" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I218" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J218" s="6" t="inlineStr">
         <is>
-          <t>Mid-Lake Teahouse</t>
+          <t>Yuyuan Bazaar</t>
         </is>
       </c>
       <c r="K218" s="6" t="inlineStr">
@@ -39757,14 +39845,14 @@
         </is>
       </c>
       <c r="L218" s="6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M218" s="6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="N218" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O218" s="6" t="n">
@@ -39772,25 +39860,25 @@
       </c>
       <c r="P218" s="6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q218" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R218" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:41 → 07:51</t>
+          <t>RETIME 12:21 → 10:52; ORDER 40 → 30</t>
         </is>
       </c>
       <c r="S218" s="7" t="inlineStr">
         <is>
-          <t>TripAdvisor/guide consensus is ~2h for a complete visit and 45-60min for a fast loop; at opening with fewer crowds, a highlights-plus circuit of the rockeries and pavilions is ~90min.</t>
+          <t>TripAdvisor reviewers report lingering 'an hour or two' over tea and the complimentary quail-egg/sweet snacks while watching the pond; 45min feels rushed for a set tea service.</t>
         </is>
       </c>
       <c r="T218" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -39809,11 +39897,11 @@
         </is>
       </c>
       <c r="D219" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Mid-Lake Teahouse</t>
+          <t>Yuyuan Bazaar</t>
         </is>
       </c>
       <c r="F219" s="6" t="inlineStr">
@@ -39823,12 +39911,12 @@
       </c>
       <c r="G219" s="6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="H219" s="6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I219" s="6" t="n">
@@ -39836,23 +39924,23 @@
       </c>
       <c r="J219" s="6" t="inlineStr">
         <is>
-          <t>Yuyuan Bazaar</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L219" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M219" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N219" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O219" s="6" t="n">
@@ -39860,7 +39948,7 @@
       </c>
       <c r="P219" s="6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="Q219" s="6" t="n">
@@ -39868,12 +39956,12 @@
       </c>
       <c r="R219" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:21 → 09:43; ORDER 40 → 30</t>
+          <t>RETIME 10:52 → 12:06; ORDER 30 → 40</t>
         </is>
       </c>
       <c r="S219" s="7" t="inlineStr">
         <is>
-          <t>TripAdvisor reviewers report lingering 'an hour or two' over tea and the complimentary quail-egg/sweet snacks while watching the pond; 45min feels rushed for a set tea service.</t>
+          <t>Guides say you can 'easily spend an hour or two' in the bazaar alone (4h if you do garden, bazaar and dumpling houses together); 60min covers snacks and a souvenir sweep.</t>
         </is>
       </c>
       <c r="T219" s="6" t="inlineStr">
@@ -39897,26 +39985,26 @@
         </is>
       </c>
       <c r="D220" s="6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Yuyuan Bazaar</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G220" s="6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="H220" s="6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I220" s="6" t="n">
@@ -39948,7 +40036,7 @@
       </c>
       <c r="P220" s="6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="Q220" s="6" t="n">
@@ -39956,12 +40044,12 @@
       </c>
       <c r="R220" s="7" t="inlineStr">
         <is>
-          <t>RETIME 10:52 → 10:57; ORDER 30 → 40</t>
+          <t>RETIME 15:27 → 13:14; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S220" s="7" t="inlineStr">
         <is>
-          <t>Guides say you can 'easily spend an hour or two' in the bazaar alone (4h if you do garden, bazaar and dumpling houses together); 60min covers snacks and a souvenir sweep.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T220" s="6" t="inlineStr">
@@ -39985,7 +40073,7 @@
         </is>
       </c>
       <c r="D221" s="6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
@@ -39999,12 +40087,12 @@
       </c>
       <c r="G221" s="6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="I221" s="6" t="n">
@@ -40012,23 +40100,23 @@
       </c>
       <c r="J221" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>People’s Square</t>
         </is>
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L221" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M221" s="6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="N221" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O221" s="6" t="n">
@@ -40044,7 +40132,7 @@
       </c>
       <c r="R221" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:31 → 12:15</t>
+          <t>RETIME 13:31 → 14:32; ORDER 50 → 60</t>
         </is>
       </c>
       <c r="S221" s="7" t="inlineStr">
@@ -40073,50 +40161,50 @@
         </is>
       </c>
       <c r="D222" s="6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>People’s Square</t>
         </is>
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G222" s="6" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="H222" s="6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I222" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J222" s="6" t="inlineStr">
         <is>
-          <t>People’s Square</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K222" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L222" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M222" s="6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="N222" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O222" s="6" t="n">
@@ -40124,20 +40212,20 @@
       </c>
       <c r="P222" s="6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="Q222" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R222" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:27 → 13:08</t>
+          <t>RETIME 16:39 → 15:34</t>
         </is>
       </c>
       <c r="S222" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>TripAdvisor reviews split between '10 minutes is plenty' for the plaza and 2-4h if you linger in People's Park; 45min suits its role here as a stroll-and-rest buffer.</t>
         </is>
       </c>
       <c r="T222" s="6" t="inlineStr">
@@ -40161,30 +40249,30 @@
         </is>
       </c>
       <c r="D223" s="6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>People’s Square</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G223" s="6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H223" s="6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I223" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="J223" s="6" t="inlineStr">
         <is>
@@ -40212,20 +40300,20 @@
       </c>
       <c r="P223" s="6" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q223" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R223" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:39 → 14:25</t>
+          <t>RETIME 21:13 → 17:30; ORDER 90 → 80</t>
         </is>
       </c>
       <c r="S223" s="7" t="inlineStr">
         <is>
-          <t>TripAdvisor reviews split between '10 minutes is plenty' for the plaza and 2-4h if you linger in People's Park; 45min suits its role here as a stroll-and-rest buffer.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T223" s="6" t="inlineStr">
@@ -40249,7 +40337,7 @@
         </is>
       </c>
       <c r="D224" s="6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
@@ -40263,12 +40351,12 @@
       </c>
       <c r="G224" s="6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="H224" s="6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I224" s="6" t="n">
@@ -40276,23 +40364,23 @@
       </c>
       <c r="J224" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="K224" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L224" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M224" s="6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="N224" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O224" s="6" t="n">
@@ -40308,7 +40396,7 @@
       </c>
       <c r="R224" s="7" t="inlineStr">
         <is>
-          <t>RETIME 22:52 → 15:28; ORDER 100 → 80</t>
+          <t>RETIME 22:52 → 19:30; ORDER 100 → 90</t>
         </is>
       </c>
       <c r="S224" s="7" t="inlineStr">
@@ -40337,26 +40425,26 @@
         </is>
       </c>
       <c r="D225" s="6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G225" s="6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="H225" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="I225" s="6" t="n">
@@ -40369,14 +40457,14 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L225" s="6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="M225" s="6" t="n">
-        <v>0.77</v>
+        <v>1.47</v>
       </c>
       <c r="N225" s="6" t="inlineStr">
         <is>
@@ -40384,11 +40472,11 @@
         </is>
       </c>
       <c r="O225" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P225" s="6" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>01:51</t>
         </is>
       </c>
       <c r="Q225" s="6" t="n">
@@ -40396,12 +40484,12 @@
       </c>
       <c r="R225" s="7" t="inlineStr">
         <is>
-          <t>RETIME 21:13 → 18:00</t>
+          <t>MOVE day 3 → 4; RETIME 01:51 → 21:02; ORDER 110 → 100</t>
         </is>
       </c>
       <c r="S225" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>The Fairmont Peace Hotel Old Jazz Band plays a long nightly run (from ~18:30, sets through 23:30); reviewers describe staying for a couple of sets over drinks, roughly 90min.</t>
         </is>
       </c>
       <c r="T225" s="6" t="inlineStr">
@@ -40439,12 +40527,12 @@
       </c>
       <c r="G226" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="H226" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I226" s="6" t="n">
@@ -40484,7 +40572,7 @@
       </c>
       <c r="R226" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 07:30 → 09:00</t>
         </is>
       </c>
       <c r="S226" s="7" t="inlineStr">
@@ -40527,12 +40615,12 @@
       </c>
       <c r="G227" s="6" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="H227" s="6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I227" s="6" t="n">
@@ -40572,7 +40660,7 @@
       </c>
       <c r="R227" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:02 → 08:02; ORDER 50 → 20</t>
+          <t>RETIME 17:02 → 10:02; ORDER 50 → 20</t>
         </is>
       </c>
       <c r="S227" s="7" t="inlineStr">
@@ -40615,12 +40703,12 @@
       </c>
       <c r="G228" s="6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="H228" s="6" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I228" s="6" t="n">
@@ -40628,23 +40716,23 @@
       </c>
       <c r="J228" s="6" t="inlineStr">
         <is>
-          <t>West Bund riverside</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K228" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L228" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M228" s="6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="N228" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O228" s="6" t="n">
@@ -40660,7 +40748,7 @@
       </c>
       <c r="R228" s="7" t="inlineStr">
         <is>
-          <t>RETIME 11:13 → 09:42</t>
+          <t>RETIME 11:13 → 11:42</t>
         </is>
       </c>
       <c r="S228" s="7" t="inlineStr">
@@ -40693,46 +40781,46 @@
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="F229" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G229" s="6" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="H229" s="6" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="I229" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J229" s="6" t="inlineStr">
+        <is>
           <t>West Bund riverside</t>
         </is>
       </c>
-      <c r="F229" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G229" s="6" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="H229" s="6" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="I229" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J229" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="L229" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M229" s="6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="N229" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O229" s="6" t="n">
@@ -40740,25 +40828,25 @@
       </c>
       <c r="P229" s="6" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="Q229" s="6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="R229" s="7" t="inlineStr">
         <is>
-          <t>RETIME 08:50 → 11:35; ORDER 20 → 40</t>
+          <t>RETIME 19:48 → 13:20; ORDER 60 → 40</t>
         </is>
       </c>
       <c r="S229" s="7" t="inlineStr">
         <is>
-          <t>No dedicated dwell figure found; the Xuhui riverside corridor linking the museums is a 10-15min walk each way, so ~45min allows an unhurried stroll with stops between venues.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T229" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -40781,26 +40869,26 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>West Bund riverside</t>
         </is>
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G230" s="6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="H230" s="6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="I230" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J230" s="6" t="inlineStr">
         <is>
@@ -40828,25 +40916,25 @@
       </c>
       <c r="P230" s="6" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q230" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R230" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:48 → 12:28; ORDER 60 → 50</t>
+          <t>RETIME 08:50 → 14:43; ORDER 20 → 50</t>
         </is>
       </c>
       <c r="S230" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>No dedicated dwell figure found; the Xuhui riverside corridor linking the museums is a 10-15min walk each way, so ~45min allows an unhurried stroll with stops between venues.</t>
         </is>
       </c>
       <c r="T230" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -40879,12 +40967,12 @@
       </c>
       <c r="G231" s="6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="H231" s="6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I231" s="6" t="n">
@@ -40892,23 +40980,23 @@
       </c>
       <c r="J231" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Check in — J Hotel (Tower)</t>
         </is>
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L231" s="6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M231" s="6" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="N231" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O231" s="6" t="n">
@@ -40924,7 +41012,7 @@
       </c>
       <c r="R231" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:06 → 13:53; ORDER 40 → 60</t>
+          <t>RETIME 14:06 → 15:53; ORDER 40 → 60</t>
         </is>
       </c>
       <c r="S231" s="7" t="inlineStr">
@@ -40957,46 +41045,46 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
+          <t>Check in — J Hotel (Tower)</t>
+        </is>
+      </c>
+      <c r="F232" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G232" s="6" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="H232" s="6" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="I232" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J232" s="6" t="inlineStr">
+        <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F232" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G232" s="6" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="H232" s="6" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="I232" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J232" s="6" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
       <c r="K232" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L232" s="6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M232" s="6" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="N232" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O232" s="6" t="n">
@@ -41004,20 +41092,20 @@
       </c>
       <c r="P232" s="6" t="inlineStr">
         <is>
-          <t>02:44</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="Q232" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="R232" s="7" t="inlineStr">
         <is>
-          <t>RETIME 02:44 → 18:00; ORDER 110 → 70</t>
+          <t>RETIME 20:57 → 17:48</t>
         </is>
       </c>
       <c r="S232" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>J Hotel's reception is on floor 101 of Shanghai Tower (check-in 15:00), so lift-lobby routing, the shuttle-lift ride and a luxury check-in run longer than a street-level desk.</t>
         </is>
       </c>
       <c r="T232" s="6" t="inlineStr">
@@ -41033,19 +41121,19 @@
         </is>
       </c>
       <c r="B233" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D233" s="6" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F233" s="6" t="inlineStr">
@@ -41055,57 +41143,57 @@
       </c>
       <c r="G233" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="H233" s="6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I233" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J233" s="6" t="inlineStr">
         <is>
-          <t>Shanghai Museum East</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L233" s="6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M233" s="6" t="n">
-        <v>6.62</v>
+        <v>0</v>
       </c>
       <c r="N233" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O233" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P233" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>02:44</t>
         </is>
       </c>
       <c r="Q233" s="6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="R233" s="7" t="inlineStr">
         <is>
-          <t>RETIME 07:30 → 07:00</t>
+          <t>RETIME 02:44 → 18:41; ORDER 110 → 80</t>
         </is>
       </c>
       <c r="S233" s="7" t="inlineStr">
         <is>
-          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T233" s="6" t="inlineStr">
@@ -41129,46 +41217,46 @@
         </is>
       </c>
       <c r="D234" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F234" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G234" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="H234" s="6" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="I234" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J234" s="6" t="inlineStr">
+        <is>
           <t>Shanghai Museum East</t>
         </is>
       </c>
-      <c r="F234" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G234" s="6" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H234" s="6" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="I234" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="J234" s="6" t="inlineStr">
-        <is>
-          <t>Shanghai Tower base</t>
-        </is>
-      </c>
       <c r="K234" s="6" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="L234" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M234" s="6" t="n">
-        <v>3.63</v>
+        <v>6.62</v>
       </c>
       <c r="N234" s="6" t="inlineStr">
         <is>
@@ -41180,25 +41268,25 @@
       </c>
       <c r="P234" s="6" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="Q234" s="6" t="n">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="R234" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:21 → 08:00; ORDER 30 → 20</t>
+          <t>RETIME 07:30 → 09:00</t>
         </is>
       </c>
       <c r="S234" s="7" t="inlineStr">
         <is>
-          <t>Guides advise at least 2-3h and recommend 3-4h (3-5h thorough) for 20 halls; 3 focused hours covers the headline galleries plus one temporary show.</t>
+          <t>Hotel buffet breakfast; 35 min is enough to eat properly while still making a 07:00 gate slot if you start around 06:30.</t>
         </is>
       </c>
       <c r="T234" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -41217,11 +41305,11 @@
         </is>
       </c>
       <c r="D235" s="6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>Shanghai Tower base</t>
+          <t>Shanghai Museum East</t>
         </is>
       </c>
       <c r="F235" s="6" t="inlineStr">
@@ -41231,62 +41319,62 @@
       </c>
       <c r="G235" s="6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="H235" s="6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="I235" s="6" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="J235" s="6" t="inlineStr">
         <is>
-          <t>World Financial Center</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L235" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M235" s="6" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="N235" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O235" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P235" s="6" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q235" s="6" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="R235" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 5 → 6; RETIME 21:36 → 11:20; ORDER 80 → 30</t>
+          <t>RETIME 13:21 → 10:00; ORDER 30 → 20</t>
         </is>
       </c>
       <c r="S235" s="7" t="inlineStr">
         <is>
-          <t>No published dwell time; the ground plaza and Exit 9A photo spot are the documented ground-level draws, and a walk around the base with photos is ~30min.</t>
+          <t>Guides advise at least 2-3h and recommend 3-4h (3-5h thorough) for 20 halls; 3 focused hours covers the headline galleries plus one temporary show.</t>
         </is>
       </c>
       <c r="T235" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -41305,71 +41393,71 @@
         </is>
       </c>
       <c r="D236" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>World Financial Center</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G236" s="6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="H236" s="6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="I236" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J236" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Shanghai Tower base</t>
         </is>
       </c>
       <c r="K236" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L236" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M236" s="6" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N236" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O236" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P236" s="6" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q236" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="R236" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 5 → 6; RETIME 01:05 → 12:06; ORDER 100 → 40</t>
+          <t>RETIME 12:00 → 13:08; ORDER 20 → 30</t>
         </is>
       </c>
       <c r="S236" s="7" t="inlineStr">
         <is>
-          <t>Exterior stop per the note; the 94/97/100F observatory would instead need 1-2h (30min on 94F, 20min on 97F, 1-1.5h on 100F) plus ticket and lift queues.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T236" s="6" t="inlineStr">
@@ -41393,34 +41481,34 @@
         </is>
       </c>
       <c r="D237" s="6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Shanghai Tower base</t>
         </is>
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G237" s="6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="H237" s="6" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="I237" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J237" s="6" t="inlineStr">
         <is>
-          <t>Jin Mao Tower</t>
+          <t>World Financial Center</t>
         </is>
       </c>
       <c r="K237" s="6" t="inlineStr">
@@ -41432,37 +41520,37 @@
         <v>8</v>
       </c>
       <c r="M237" s="6" t="n">
-        <v>0.6</v>
+        <v>0.17</v>
       </c>
       <c r="N237" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O237" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P237" s="6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="Q237" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="R237" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:00 → 12:44; ORDER 20 → 50</t>
+          <t>MOVE day 5 → 6; RETIME 21:36 → 14:28; ORDER 80 → 40</t>
         </is>
       </c>
       <c r="S237" s="7" t="inlineStr">
         <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
+          <t>No published dwell time; the ground plaza and Exit 9A photo spot are the documented ground-level draws, and a walk around the base with photos is ~30min.</t>
         </is>
       </c>
       <c r="T237" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -41481,11 +41569,11 @@
         </is>
       </c>
       <c r="D238" s="6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Jin Mao Tower</t>
+          <t>World Financial Center</t>
         </is>
       </c>
       <c r="F238" s="6" t="inlineStr">
@@ -41495,12 +41583,12 @@
       </c>
       <c r="G238" s="6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="H238" s="6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I238" s="6" t="n">
@@ -41508,7 +41596,7 @@
       </c>
       <c r="J238" s="6" t="inlineStr">
         <is>
-          <t>Oriental Pearl Tower</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="K238" s="6" t="inlineStr">
@@ -41517,14 +41605,14 @@
         </is>
       </c>
       <c r="L238" s="6" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M238" s="6" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="N238" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O238" s="6" t="n">
@@ -41532,7 +41620,7 @@
       </c>
       <c r="P238" s="6" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="Q238" s="6" t="n">
@@ -41540,12 +41628,12 @@
       </c>
       <c r="R238" s="7" t="inlineStr">
         <is>
-          <t>MOVE day 5 → 6; RETIME 23:19 → 14:00; ORDER 90 → 60</t>
+          <t>MOVE day 5 → 6; RETIME 01:05 → 15:14; ORDER 100 → 50</t>
         </is>
       </c>
       <c r="S238" s="7" t="inlineStr">
         <is>
-          <t>Treated per the note as an exterior stop; going up would be different — the 88F deck is quoted at 2-3h and the Skywalk session alone is 45min plus 30min security check-in.</t>
+          <t>Exterior stop per the note; the 94/97/100F observatory would instead need 1-2h (30min on 94F, 20min on 97F, 1-1.5h on 100F) plus ticket and lift queues.</t>
         </is>
       </c>
       <c r="T238" s="6" t="inlineStr">
@@ -41569,11 +41657,11 @@
         </is>
       </c>
       <c r="D239" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>Oriental Pearl Tower</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="F239" s="6" t="inlineStr">
@@ -41583,12 +41671,12 @@
       </c>
       <c r="G239" s="6" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H239" s="6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I239" s="6" t="n">
@@ -41596,7 +41684,7 @@
       </c>
       <c r="J239" s="6" t="inlineStr">
         <is>
-          <t>Pudong promenade</t>
+          <t>Oriental Pearl Tower</t>
         </is>
       </c>
       <c r="K239" s="6" t="inlineStr">
@@ -41605,22 +41693,22 @@
         </is>
       </c>
       <c r="L239" s="6" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="M239" s="6" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="N239" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O239" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P239" s="6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="Q239" s="6" t="n">
@@ -41628,12 +41716,12 @@
       </c>
       <c r="R239" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:30 → 14:57; ORDER 50 → 70</t>
+          <t>MOVE day 5 → 6; RETIME 23:19 → 16:00; ORDER 90 → 60</t>
         </is>
       </c>
       <c r="S239" s="7" t="inlineStr">
         <is>
-          <t>Exterior-only per the note, so a photo stop at the base; ascending instead runs 1-2h on the decks and 2-3h with the museum, plus 15-60min ticket and 10-60min lift queues.</t>
+          <t>Treated per the note as an exterior stop; going up would be different — the 88F deck is quoted at 2-3h and the Skywalk session alone is 45min plus 30min security check-in.</t>
         </is>
       </c>
       <c r="T239" s="6" t="inlineStr">
@@ -41657,11 +41745,11 @@
         </is>
       </c>
       <c r="D240" s="6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>Pudong promenade</t>
+          <t>Oriental Pearl Tower</t>
         </is>
       </c>
       <c r="F240" s="6" t="inlineStr">
@@ -41671,16 +41759,16 @@
       </c>
       <c r="G240" s="6" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="H240" s="6" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I240" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J240" s="6" t="inlineStr">
         <is>
@@ -41708,20 +41796,20 @@
       </c>
       <c r="P240" s="6" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="Q240" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="R240" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:21 → 15:36; ORDER 40 → 80</t>
+          <t>RETIME 17:30 → 16:57; ORDER 50 → 70</t>
         </is>
       </c>
       <c r="S240" s="7" t="inlineStr">
         <is>
-          <t>Binjiang Avenue full route logs are 7.7km/2h, but the Lujiazui section fronting the towers is a fraction of that; TripAdvisor describes it as a short skyline stroll of ~45min.</t>
+          <t>Exterior-only per the note, so a photo stop at the base; ascending instead runs 1-2h on the decks and 2-3h with the museum, plus 15-60min ticket and 10-60min lift queues.</t>
         </is>
       </c>
       <c r="T240" s="6" t="inlineStr">
@@ -41745,7 +41833,7 @@
         </is>
       </c>
       <c r="D241" s="6" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
@@ -41772,23 +41860,23 @@
       </c>
       <c r="J241" s="6" t="inlineStr">
         <is>
-          <t>Fly from PVG</t>
+          <t>Pudong promenade</t>
         </is>
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L241" s="6" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M241" s="6" t="n">
-        <v>31.45</v>
+        <v>0</v>
       </c>
       <c r="N241" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O241" s="6" t="n">
@@ -41804,7 +41892,7 @@
       </c>
       <c r="R241" s="7" t="inlineStr">
         <is>
-          <t>RETIME 19:48 → 18:00; ORDER 60 → 90</t>
+          <t>RETIME 19:48 → 18:00; ORDER 60 → 80</t>
         </is>
       </c>
       <c r="S241" s="7" t="inlineStr">
@@ -41833,69 +41921,157 @@
         </is>
       </c>
       <c r="D242" s="6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
+          <t>Pudong promenade</t>
+        </is>
+      </c>
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="H242" s="6" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="I242" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J242" s="6" t="inlineStr">
+        <is>
           <t>Fly from PVG</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="G242" s="6" t="inlineStr">
-        <is>
-          <t>23:10</t>
-        </is>
-      </c>
-      <c r="H242" s="6" t="inlineStr">
-        <is>
-          <t>02:10 (+1)</t>
-        </is>
-      </c>
-      <c r="I242" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="J242" s="6" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
-      <c r="K242" s="6" t="inlineStr"/>
-      <c r="L242" s="6" t="inlineStr"/>
-      <c r="M242" s="6" t="inlineStr"/>
-      <c r="N242" s="6" t="inlineStr"/>
+      <c r="K242" s="6" t="inlineStr">
+        <is>
+          <t>didi</t>
+        </is>
+      </c>
+      <c r="L242" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="M242" s="6" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="N242" s="6" t="inlineStr">
+        <is>
+          <t>estimated (fitted model)</t>
+        </is>
+      </c>
       <c r="O242" s="6" t="n">
         <v>6</v>
       </c>
       <c r="P242" s="6" t="inlineStr">
         <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="Q242" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="R242" s="7" t="inlineStr">
+        <is>
+          <t>RETIME 16:21 → 20:15; ORDER 40 → 90</t>
+        </is>
+      </c>
+      <c r="S242" s="7" t="inlineStr">
+        <is>
+          <t>Binjiang Avenue full route logs are 7.7km/2h, but the Lujiazui section fronting the towers is a fraction of that; TripAdvisor describes it as a short skyline stroll of ~45min.</t>
+        </is>
+      </c>
+      <c r="T242" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E243" s="6" t="inlineStr">
+        <is>
+          <t>Fly from PVG</t>
+        </is>
+      </c>
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr">
+        <is>
           <t>23:10</t>
         </is>
       </c>
-      <c r="Q242" s="6" t="n">
+      <c r="H243" s="6" t="inlineStr">
+        <is>
+          <t>02:10 (+1)</t>
+        </is>
+      </c>
+      <c r="I243" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="R242" s="7" t="inlineStr">
+      <c r="J243" s="6" t="inlineStr">
+        <is>
+          <t>Hotel (home)</t>
+        </is>
+      </c>
+      <c r="K243" s="6" t="inlineStr"/>
+      <c r="L243" s="6" t="inlineStr"/>
+      <c r="M243" s="6" t="inlineStr"/>
+      <c r="N243" s="6" t="inlineStr"/>
+      <c r="O243" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P243" s="6" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="Q243" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="R243" s="7" t="inlineStr">
         <is>
           <t>ORDER 70 → 100</t>
         </is>
       </c>
-      <c r="S242" s="7" t="inlineStr">
+      <c r="S243" s="7" t="inlineStr">
         <is>
           <t>PVG guidance is to arrive 3h before an international departure (check-in closes 60min out), with Aug listed among the airport's busiest months; matches the note's 23:10 for a 02:10 flight.</t>
         </is>
       </c>
-      <c r="T242" s="6" t="inlineStr">
+      <c r="T243" s="6" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T242"/>
+  <autoFilter ref="A1:T243"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43056,14 +43232,14 @@
         <v>3</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>90</v>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Change this page's day: 3 → 1</t>
+          <t>Change this page's day: 3 → 4</t>
         </is>
       </c>
     </row>
@@ -43365,7 +43541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I159"/>
+  <dimension ref="A1:I158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -48321,7 +48497,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Shanghai Maglev</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -48335,10 +48511,10 @@
         </is>
       </c>
       <c r="G121" s="8" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>33.89</v>
+        <v>9.23</v>
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
@@ -48367,23 +48543,23 @@
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Maglev</t>
+          <t>Nanjing Road East</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G122" s="8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>9.23</v>
+        <v>0.9</v>
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48403,28 +48579,28 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Maglev</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Nanjing Road East</t>
+          <t>The Bund</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G123" s="8" t="n">
         <v>19</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>8.449999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48444,28 +48620,28 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>The Bund</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>The Bund</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G124" s="8" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>3.5</v>
+        <v>2.04</v>
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48476,33 +48652,33 @@
         </is>
       </c>
       <c r="B125" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>The Bund</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Old Jazz Bar</t>
+          <t>Recovery massage / spa</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G125" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>0.34</v>
+        <v>2.67</v>
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
@@ -48517,21 +48693,21 @@
         </is>
       </c>
       <c r="B126" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Old Jazz Bar</t>
+          <t>Recovery massage / spa</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>M50 Creative Park</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
@@ -48540,10 +48716,10 @@
         </is>
       </c>
       <c r="G126" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>1.72</v>
+        <v>3.34</v>
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
@@ -48567,12 +48743,12 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Recovery massage / spa</t>
+          <t>Jing’an Temple</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr">
@@ -48584,7 +48760,7 @@
         <v>11</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
@@ -48608,24 +48784,24 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Recovery massage / spa</t>
+          <t>Jing’an Temple</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>M50 Creative Park</t>
+          <t>Nanjing Road West</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G128" s="8" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>3.34</v>
+        <v>0.96</v>
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
@@ -48649,28 +48825,28 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>M50 Creative Park</t>
+          <t>Nanjing Road West</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Jing’an Temple</t>
+          <t>Zhangyuan</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G129" s="8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>2.83</v>
+        <v>0.5</v>
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48690,24 +48866,24 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Nanjing Road West</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G130" s="8" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>0.96</v>
+        <v>4.38</v>
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
@@ -48722,37 +48898,37 @@
         </is>
       </c>
       <c r="B131" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>Nanjing Road West</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Zhangyuan</t>
+          <t>Wukang Building</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G131" s="8" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H131" s="8" t="n">
-        <v>0.5</v>
+        <v>7.18</v>
       </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48763,37 +48939,37 @@
         </is>
       </c>
       <c r="B132" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Wukang Building</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Wukang Road</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G132" s="8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>4.38</v>
+        <v>0.7</v>
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48813,28 +48989,28 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Wukang Road</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Wukang Building</t>
+          <t>Ferguson Lane</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G133" s="8" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>7.18</v>
+        <v>0.3</v>
       </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -48854,24 +49030,24 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Wukang Building</t>
+          <t>Ferguson Lane</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Wukang Road</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G134" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
@@ -48895,24 +49071,24 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Wukang Road</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Ferguson Lane</t>
+          <t>Wulumuqi Road</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G135" s="8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
@@ -48936,28 +49112,28 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Ferguson Lane</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Anfu Road</t>
+          <t>Fuxing Park</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G136" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -48977,24 +49153,24 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Anfu Road</t>
+          <t>Fuxing Park</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Wulumuqi Road</t>
+          <t>Sinan Mansions</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G137" s="8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="I137" s="8" t="inlineStr">
         <is>
@@ -49018,12 +49194,12 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Fuxing Park</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
@@ -49032,10 +49208,10 @@
         </is>
       </c>
       <c r="G138" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>2.5</v>
+        <v>3.97</v>
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
@@ -49050,37 +49226,37 @@
         </is>
       </c>
       <c r="B139" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Fuxing Park</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Sinan Mansions</t>
+          <t>Yu Garden</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G139" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>0.3</v>
+        <v>1.27</v>
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -49091,33 +49267,33 @@
         </is>
       </c>
       <c r="B140" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Yu Garden</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G140" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>3.97</v>
+        <v>0.47</v>
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
@@ -49141,28 +49317,28 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Yuyuan Bazaar</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G141" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>1.27</v>
+        <v>0.5</v>
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -49182,12 +49358,12 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Mid-Lake Teahouse</t>
+          <t>City God Temple</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
@@ -49196,10 +49372,10 @@
         </is>
       </c>
       <c r="G142" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
@@ -49223,28 +49399,28 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>Mid-Lake Teahouse</t>
+          <t>City God Temple</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Yuyuan Bazaar</t>
+          <t>People’s Square</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G143" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H143" s="8" t="n">
-        <v>0.5</v>
+        <v>1.83</v>
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -49264,24 +49440,24 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Yuyuan Bazaar</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>City God Temple</t>
+          <t>Huangpu night cruise</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G144" s="8" t="n">
         <v>10</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>0.26</v>
+        <v>2.45</v>
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
@@ -49305,12 +49481,12 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Huangpu night cruise</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>People’s Square</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr">
@@ -49322,7 +49498,7 @@
         <v>9</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
@@ -49346,12 +49522,12 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>People’s Square</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Huangpu night cruise</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr">
@@ -49360,10 +49536,10 @@
         </is>
       </c>
       <c r="G146" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>2.45</v>
+        <v>1.47</v>
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
@@ -49378,33 +49554,33 @@
         </is>
       </c>
       <c r="B147" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>TANK Shanghai</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G147" s="8" t="n">
         <v>19</v>
       </c>
       <c r="H147" s="8" t="n">
-        <v>0.77</v>
+        <v>8.6</v>
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
@@ -49428,24 +49604,24 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>TANK Shanghai</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>TANK Shanghai</t>
+          <t>West Bund Museum</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G148" s="8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>8.6</v>
+        <v>0.64</v>
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
@@ -49469,28 +49645,28 @@
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>TANK Shanghai</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>West Bund Museum</t>
+          <t>West Bund riverside</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G149" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H149" s="8" t="n">
-        <v>0.64</v>
+        <v>1.8</v>
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -49510,28 +49686,28 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>West Bund Museum</t>
+          <t>West Bund riverside</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>West Bund riverside</t>
+          <t>Long Museum West Bund</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G150" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>1.8</v>
+        <v>0.66</v>
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -49551,24 +49727,24 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Long Museum West Bund</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Long Museum West Bund</t>
+          <t>Check in — J Hotel (Tower)</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G151" s="8" t="n">
         <v>17</v>
       </c>
       <c r="H151" s="8" t="n">
-        <v>0.66</v>
+        <v>6.75</v>
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
@@ -49583,21 +49759,21 @@
         </is>
       </c>
       <c r="B152" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Shanghai Museum East</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
@@ -49609,7 +49785,7 @@
         <v>17</v>
       </c>
       <c r="H152" s="8" t="n">
-        <v>6.75</v>
+        <v>6.62</v>
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
@@ -49633,12 +49809,12 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Museum East</t>
+          <t>Shanghai Tower base</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr">
@@ -49647,10 +49823,10 @@
         </is>
       </c>
       <c r="G153" s="8" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>6.62</v>
+        <v>3.63</v>
       </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
@@ -49674,24 +49850,24 @@
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Museum East</t>
+          <t>Shanghai Tower base</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Tower base</t>
+          <t>World Financial Center</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G154" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H154" s="8" t="n">
-        <v>3.63</v>
+        <v>0.17</v>
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
@@ -49715,12 +49891,12 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Tower base</t>
+          <t>World Financial Center</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>World Financial Center</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr">
@@ -49732,11 +49908,11 @@
         <v>8</v>
       </c>
       <c r="H155" s="8" t="n">
-        <v>0.17</v>
+        <v>0.6</v>
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -49756,12 +49932,12 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Jin Mao Tower</t>
+          <t>Oriental Pearl Tower</t>
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr">
@@ -49770,14 +49946,14 @@
         </is>
       </c>
       <c r="G156" s="8" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H156" s="8" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -49797,12 +49973,12 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Jin Mao Tower</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Oriental Pearl Tower</t>
+          <t>Pudong promenade</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr">
@@ -49811,14 +49987,14 @@
         </is>
       </c>
       <c r="G157" s="8" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -49838,74 +50014,33 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Oriental Pearl Tower</t>
+          <t>Pudong promenade</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Pudong promenade</t>
+          <t>Fly from PVG</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G158" s="8" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="H158" s="8" t="n">
-        <v>0</v>
+        <v>31.45</v>
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="8" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="B159" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C159" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D159" s="8" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
-      <c r="E159" s="8" t="inlineStr">
-        <is>
-          <t>Fly from PVG</t>
-        </is>
-      </c>
-      <c r="F159" s="8" t="inlineStr">
-        <is>
-          <t>didi</t>
-        </is>
-      </c>
-      <c r="G159" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="H159" s="8" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="I159" s="8" t="inlineStr">
-        <is>
           <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I159"/>
+  <autoFilter ref="A1:I158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/china-notion-sync.xlsx
+++ b/china-notion-sync.xlsx
@@ -1981,23 +1981,23 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Jingshan Park</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L14" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -2046,46 +2046,46 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
           <t>Jingshan Park</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -2093,20 +2093,20 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:40 → 17:25; ORDER 50 → 60</t>
+          <t>RETIME 18:04 → 17:05; ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>Trip.com and TripAdvisor reports give a 5-15 min climb each way (about 150 steps) and an average visit around 30 min, stretching to 2h only for dedicated photographers.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -2134,26 +2134,26 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Jingshan Park</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I16" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -2181,20 +2181,20 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:04 → 18:18</t>
+          <t>RETIME 13:40 → 19:05; ORDER 50 → 70</t>
         </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Trip.com and TripAdvisor reports give a 5-15 min climb each way (about 150 steps) and an average visit around 30 min, stretching to 2h only for dedicated photographers.</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -22196,23 +22196,23 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Jingshan Park</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L16" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -22261,46 +22261,46 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
           <t>Jingshan Park</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O17" s="6" t="n">
@@ -22308,20 +22308,20 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:40 → 17:25; ORDER 50 → 60</t>
+          <t>RETIME 18:04 → 17:05; ORDER 70 → 60</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>Trip.com and TripAdvisor reports give a 5-15 min climb each way (about 150 steps) and an average visit around 30 min, stretching to 2h only for dedicated photographers.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -22349,26 +22349,26 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Jingshan Park</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I18" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -22396,20 +22396,20 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:04 → 18:18</t>
+          <t>RETIME 13:40 → 19:05; ORDER 50 → 70</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Trip.com and TripAdvisor reports give a 5-15 min climb each way (about 150 steps) and an average visit around 30 min, stretching to 2h only for dedicated photographers.</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -44028,7 +44028,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>National Museum</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -44069,7 +44069,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Jingshan Park</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">

--- a/china-notion-sync.xlsx
+++ b/china-notion-sync.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Legs" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$T$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$T$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Schedule'!$A$1:$T$242</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ideas (parked)'!$A$1:$G$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Moves'!$A$1:$F$1</definedName>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1051,23 +1051,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>Chongqing</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Wuhou Shrine</t>
+          <t>Hongya Cave</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1077,32 +1077,32 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="I4" s="6" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Jinli Old Street</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L4" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
@@ -1110,75 +1110,75 @@
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:45 → 14:45</t>
+          <t>DURATION 105m → 83m</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>Chengdu guides state the main sights take about two hours, three if you linger in the gardens or the Three Kingdoms history.</t>
+          <t>CUT SHORT BY CLOSING TIME: closes 23:00, last entry 22:30; 22 min less than the 105 min advice. Guides put a full walk-through at 2-3h across 11 levels with the 19:30-22:00 window the most crowded and lift queues of 30-45min (stairs advised); trimmed because the bridge and riverbank photo stops are separate.</t>
         </is>
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>Zhangjiajie</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Jinli Old Street</t>
+          <t>Arrive Zhangjiajie West</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
@@ -1198,24 +1198,24 @@
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>RETIME 17:06 → 17:06</t>
+          <t>DURATION 30m → 15m</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>Guides suggest 2–3 h for Jinli at sunset; 1.5 h fits a walk plus snacks when Wuhou Shrine next door is visited the same evening.</t>
+          <t>Guides: Tourist Distributing Center is ~1 min from the station exit and Wulingyuan buses leave every ~10 min, so deboarding, ticketing and boarding runs ~30 min.</t>
         </is>
       </c>
       <c r="T5" s="6" t="inlineStr">
@@ -1227,134 +1227,134 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>Zhangjiajie</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
+          <t>Golden Whip Stream</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>123</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>20:14</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Taikoo Li</t>
-        </is>
-      </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>RETIME 18:44 → 18:44</t>
+          <t>DURATION 165m → 123m</t>
         </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>CUT SHORT BY CLOSING TIME: closes 19:00, last entry 17:30; 42 min less than the 165 min advice. Trail guides and trip reports put the full 7.5 km flat walk at 2.5-3 h at a relaxed pace with photo stops (some quote 3-4 h).</t>
         </is>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>Furong (Hibiscus)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Taikoo Li</t>
+          <t>Arrive Furongzhen</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I7" s="6" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Check in at Waterfall Bay</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -1363,35 +1363,35 @@
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>1.07</v>
+        <v>4.9</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>RETIME 20:33 → 20:33</t>
+          <t>DURATION 20m → 15m</t>
         </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>Chengdu guides put a relaxed walk through Taikoo Li at 1–2 hours, longer only if you stop to dine.</t>
+          <t>Chinese guides call Furongzhen one of China's closest HSR stations to its scenic area (~5 km, 7-10 min by car, taxi under ¥20, shuttle minibuses waiting at the exit), so only deboarding and finding transport happens here.</t>
         </is>
       </c>
       <c r="T7" s="6" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Furong (Hibiscus)</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -1411,15 +1411,15 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Hongya Cave</t>
+          <t>Wuli Stone Street</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1429,29 +1429,29 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I8" s="6" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Tuwang Palace</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>0</v>
@@ -1466,20 +1466,20 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>DURATION 105m → 83m</t>
+          <t>RETIME 13:21 → 12:41; ORDER 40 → 30</t>
         </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>CUT SHORT BY CLOSING TIME: closes 23:00, last entry 22:30; 22 min less than the 105 min advice. Guides put a full walk-through at 2-3h across 11 levels with the 19:30-22:00 window the most crowded and lift queues of 30-45min (stairs advised); trimmed because the bridge and riverbank photo stops are separate.</t>
+          <t>The 5-li (2.5 km) street is the town's spine, but guides say the whole core loop is walkable in about an hour brisk / two hours relaxed, so an unhurried first pass with shops and photos is about 60 min.</t>
         </is>
       </c>
       <c r="T8" s="6" t="inlineStr">
@@ -1491,7 +1491,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Zhangjiajie</t>
+          <t>Furong (Hibiscus)</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
@@ -1499,43 +1499,43 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Arrive Zhangjiajie West</t>
+          <t>Tuwang Palace</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="I9" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Furong waterfall</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="Q9" s="6" t="n">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>DURATION 30m → 15m</t>
+          <t>RETIME 14:30 → 13:50; ORDER 50 → 40</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>Guides: Tourist Distributing Center is ~1 min from the station exit and Wulingyuan buses leave every ~10 min, so deboarding, ticketing and boarding runs ~30 min.</t>
+          <t>Blogs treat 土司/土王行宫 as a compact clifftop wooden complex and 'another great photo spot' over the waterfall (part of it now a guesthouse) rather than a museum you work through.</t>
         </is>
       </c>
       <c r="T9" s="6" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Zhangjiajie</t>
+          <t>Furong (Hibiscus)</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Golden Whip Stream</t>
+          <t>Furong waterfall</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="I10" s="6" t="n">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Liu Xiaoqing rice tofu</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0</v>
+        <v>0.09993839083537745</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1642,25 +1642,25 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>DURATION 165m → 123m</t>
+          <t>RETIME 15:08 → 14:28; ORDER 60 → 50</t>
         </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>CUT SHORT BY CLOSING TIME: closes 19:00, last entry 17:30; 42 min less than the 165 min advice. Trail guides and trip reports put the full 7.5 km flat walk at 2.5-3 h at a relaxed pace with photo stops (some quote 3-4 h).</t>
+          <t>Guides advise 20-30 min to walk the full waterfall walkways before shooting seriously, and the loop here also takes in the viewing platform, water-curtain cave behind the 60 m falls and the covered bridge below.</t>
         </is>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>med</t>
         </is>
       </c>
     </row>
@@ -1679,50 +1679,50 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Arrive Furongzhen</t>
+          <t>Liu Xiaoqing rice tofu</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="I11" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Check in at Waterfall Bay</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1730,20 +1730,20 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>DURATION 20m → 15m</t>
+          <t>RETIME 12:42 → 16:30; ORDER 30 → 60</t>
         </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>Chinese guides call Furongzhen one of China's closest HSR stations to its scenic area (~5 km, 7-10 min by car, taxi under ¥20, shuttle minibuses waiting at the exit), so only deboarding and finding transport happens here.</t>
+          <t>Ctrip/Mafengwo reviews: ¥5 a bowl at No. 113 by the archway, shop is tiny and packed so people eat under the outdoor awning or walk with it — a snack stop, not a sit-down lunch.</t>
         </is>
       </c>
       <c r="T11" s="6" t="inlineStr">
@@ -1767,46 +1767,46 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Wuli Stone Street</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I12" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Tuwang Palace</t>
+          <t>Baishetang Square</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0</v>
+        <v>0.09993839083537745</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
@@ -1818,20 +1818,20 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:21 → 12:41; ORDER 40 → 30</t>
+          <t>RETIME 16:55 → 17:08; ORDER 80 → 70</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>The 5-li (2.5 km) street is the town's spine, but guides say the whole core loop is walkable in about an hour brisk / two hours relaxed, so an unhurried first pass with shops and photos is about 60 min.</t>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Tuwang Palace</t>
+          <t>Baishetang Square</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="I13" s="6" t="n">
@@ -1882,16 +1882,16 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Furong waterfall</t>
+          <t>Shenpu Camp Square</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="Q13" s="6" t="n">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:30 → 13:50; ORDER 50 → 40</t>
+          <t>ORDER 90 → 80</t>
         </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>Blogs treat 土司/土王行宫 as a compact clifftop wooden complex and 'another great photo spot' over the waterfall (part of it now a guesthouse) rather than a museum you work through.</t>
+          <t>Scheduled free performances at 摆手堂 run at 10:30, 16:30 and 19:30 (plus a 20:30 theatre show, moved indoors if raining); a square set of Tujia songs, 摆手舞 and 茅古斯 runs roughly half an hour.</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -1943,11 +1943,11 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Furong waterfall</t>
+          <t>Shenpu Camp Square</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="I14" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Liu Xiaoqing rice tofu</t>
+          <t>Far-bank platform</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>0.09993839083537745</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
@@ -1994,25 +1994,25 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:08 → 14:28; ORDER 60 → 50</t>
+          <t>ORDER 100 → 90</t>
         </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>Guides advise 20-30 min to walk the full waterfall walkways before shooting seriously, and the loop here also takes in the viewing platform, water-curtain cave behind the 60 m falls and the covered bridge below.</t>
+          <t>Could not verify this square by name in any Chinese or English source; treated as one more open viewpoint on the night circuit, and squares here read as short stand-and-look stops.</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -2031,26 +2031,26 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Liu Xiaoqing rice tofu</t>
+          <t>Far-bank platform</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Sight</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="I15" s="6" t="n">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>none (same place)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>co-located</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="Q15" s="6" t="n">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:42 → 16:30; ORDER 30 → 60</t>
+          <t>ORDER 110 → 100</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>Ctrip/Mafengwo reviews: ¥5 a bowl at No. 113 by the archway, shop is tiny and packed so people eat under the outdoor awning or walk with it — a snack stop, not a sit-down lunch.</t>
+          <t>Photo-spot roundups list the opposite-bank/观景台 as a single fixed vantage where visitors gather for sunset and the illuminated falls; it is a stand-and-shoot stop, not a walk.</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -2107,7 +2107,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Fenghuang</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -2115,50 +2115,50 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Fenghuang HSR station</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I16" s="6" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Baishetang Square</t>
+          <t>Check in at Jinshuian</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.09993839083537745</v>
+        <v>11.3</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
@@ -2170,20 +2170,20 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>RETIME 16:55 → 17:08; ORDER 80 → 70</t>
+          <t>DURATION 20m → 15m</t>
         </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+          <t>Fenghuanggucheng is a small line station ~10 km from town; arrival is deboarding, exiting and walking to the bus/taxi forecourt, not a visit.</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Guilin</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
@@ -2203,54 +2203,54 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Baishetang Square</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I17" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Shenpu Camp Square</t>
+          <t>Check in at RongShi</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0</v>
+        <v>6.68</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O17" s="6" t="n">
@@ -2258,20 +2258,20 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>ORDER 90 → 80</t>
+          <t>RETIME 15:00 → 14:58</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>Scheduled free performances at 摆手堂 run at 10:30, 16:30 and 19:30 (plus a 20:30 theatre show, moved indoors if raining); a square set of Tujia songs, 摆手舞 and 茅古斯 runs roughly half an hour.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -2283,7 +2283,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Yangshuo</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
@@ -2291,38 +2291,38 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Shenpu Camp Square</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="I18" s="6" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Far-bank platform</t>
+          <t>Fengqi Homestay</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -2331,14 +2331,14 @@
         </is>
       </c>
       <c r="L18" s="6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O18" s="6" t="n">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>ORDER 100 → 90</t>
+          <t>RETIME 14:00 → 13:53</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>Could not verify this square by name in any Chinese or English source; treated as one more open viewpoint on the night circuit, and squares here read as short stand-and-look stops.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -2379,43 +2379,43 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Far-bank platform</t>
+          <t>Land at PVG</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (same place)</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>co-located</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
@@ -2434,20 +2434,20 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>ORDER 110 → 100</t>
+          <t>DURATION 40m → 45m</t>
         </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>Photo-spot roundups list the opposite-bank/观景台 as a single fixed vantage where visitors gather for sunset and the illuminated falls; it is a stand-and-shoot stop, not a walk.</t>
+          <t>PVG guides put full international arrival at ~60min; a domestic arrival (HO1148 from Guilin, T2) skips immigration, leaving deplane, long terminal walk and belt wait at ~35-45min.</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -2456,360 +2456,8 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Fenghuang</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>Fenghuang HSR station</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Check in at Jinshuian</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>didi</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="M20" s="6" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-      <c r="O20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="R20" s="7" t="inlineStr">
-        <is>
-          <t>DURATION 20m → 15m</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>Fenghuanggucheng is a small line station ~10 km from town; arrival is deboarding, exiting and walking to the bus/taxi forecourt, not a visit.</t>
-        </is>
-      </c>
-      <c r="T20" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Guilin</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Check in at RongShi</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>didi</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="N21" s="6" t="inlineStr">
-        <is>
-          <t>estimated (fitted model)</t>
-        </is>
-      </c>
-      <c r="O21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 15:00 → 14:58</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
-        </is>
-      </c>
-      <c r="T21" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Yangshuo</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Fengqi Homestay</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="M22" s="6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>estimated (fitted model)</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="R22" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 14:00 → 13:53</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
-        </is>
-      </c>
-      <c r="T22" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Land at PVG</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>none (same place)</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>co-located</t>
-        </is>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="R23" s="7" t="inlineStr">
-        <is>
-          <t>DURATION 40m → 45m</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>PVG guides put full international arrival at ~60min; a domestic arrival (HO1148 from Guilin, T2) skips immigration, leaving deplane, long terminal walk and belt wait at ~35-45min.</t>
-        </is>
-      </c>
-      <c r="T23" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T23"/>
+  <autoFilter ref="A1:T19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10140,352 +9788,352 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>Chengdu</t>
         </is>
       </c>
-      <c r="B84" s="6" t="n">
+      <c r="B84" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D84" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>Wuhou Shrine</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="F84" s="8" t="inlineStr">
         <is>
           <t>Sight</t>
         </is>
       </c>
-      <c r="G84" s="6" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t>14:45</t>
         </is>
       </c>
-      <c r="H84" s="6" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="I84" s="6" t="n">
+      <c r="I84" s="8" t="n">
         <v>120</v>
       </c>
-      <c r="J84" s="6" t="inlineStr">
+      <c r="J84" s="8" t="inlineStr">
         <is>
           <t>Jinli Old Street</t>
         </is>
       </c>
-      <c r="K84" s="6" t="inlineStr">
+      <c r="K84" s="8" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="L84" s="6" t="n">
+      <c r="L84" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M84" s="6" t="n">
+      <c r="M84" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="N84" s="6" t="inlineStr">
+      <c r="N84" s="8" t="inlineStr">
         <is>
           <t>routed (real leg)</t>
         </is>
       </c>
-      <c r="O84" s="6" t="n">
+      <c r="O84" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="P84" s="6" t="inlineStr">
+      <c r="P84" s="8" t="inlineStr">
         <is>
           <t>14:45</t>
         </is>
       </c>
-      <c r="Q84" s="6" t="n">
+      <c r="Q84" s="8" t="n">
         <v>120</v>
       </c>
-      <c r="R84" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 14:45 → 14:45</t>
-        </is>
-      </c>
-      <c r="S84" s="7" t="inlineStr">
+      <c r="R84" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S84" s="9" t="inlineStr">
         <is>
           <t>Chengdu guides state the main sights take about two hours, three if you linger in the gardens or the Three Kingdoms history.</t>
         </is>
       </c>
-      <c r="T84" s="6" t="inlineStr">
+      <c r="T84" s="8" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>Chengdu</t>
         </is>
       </c>
-      <c r="B85" s="6" t="n">
+      <c r="B85" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D85" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>Jinli Old Street</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>Sight</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G85" s="8" t="inlineStr">
         <is>
           <t>17:06</t>
         </is>
       </c>
-      <c r="H85" s="6" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr">
         <is>
           <t>18:36</t>
         </is>
       </c>
-      <c r="I85" s="6" t="n">
+      <c r="I85" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="J85" s="6" t="inlineStr">
+      <c r="J85" s="8" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="K85" s="6" t="inlineStr">
+      <c r="K85" s="8" t="inlineStr">
         <is>
           <t>none (same place)</t>
         </is>
       </c>
-      <c r="L85" s="6" t="n">
+      <c r="L85" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M85" s="6" t="n">
+      <c r="M85" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N85" s="6" t="inlineStr">
+      <c r="N85" s="8" t="inlineStr">
         <is>
           <t>co-located</t>
         </is>
       </c>
-      <c r="O85" s="6" t="n">
+      <c r="O85" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="P85" s="6" t="inlineStr">
+      <c r="P85" s="8" t="inlineStr">
         <is>
           <t>17:06</t>
         </is>
       </c>
-      <c r="Q85" s="6" t="n">
+      <c r="Q85" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="R85" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 17:06 → 17:06</t>
-        </is>
-      </c>
-      <c r="S85" s="7" t="inlineStr">
+      <c r="R85" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S85" s="9" t="inlineStr">
         <is>
           <t>Guides suggest 2–3 h for Jinli at sunset; 1.5 h fits a walk plus snacks when Wuhou Shrine next door is visited the same evening.</t>
         </is>
       </c>
-      <c r="T85" s="6" t="inlineStr">
+      <c r="T85" s="8" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>Chengdu</t>
         </is>
       </c>
-      <c r="B86" s="6" t="n">
+      <c r="B86" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="G86" s="6" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>18:44</t>
         </is>
       </c>
-      <c r="H86" s="6" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>20:14</t>
         </is>
       </c>
-      <c r="I86" s="6" t="n">
+      <c r="I86" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="J86" s="6" t="inlineStr">
+      <c r="J86" s="8" t="inlineStr">
         <is>
           <t>Taikoo Li</t>
         </is>
       </c>
-      <c r="K86" s="6" t="inlineStr">
+      <c r="K86" s="8" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
-      <c r="L86" s="6" t="n">
+      <c r="L86" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="M86" s="6" t="n">
+      <c r="M86" s="8" t="n">
         <v>3.2</v>
       </c>
-      <c r="N86" s="6" t="inlineStr">
+      <c r="N86" s="8" t="inlineStr">
         <is>
           <t>estimated (fitted model)</t>
         </is>
       </c>
-      <c r="O86" s="6" t="n">
+      <c r="O86" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="P86" s="6" t="inlineStr">
+      <c r="P86" s="8" t="inlineStr">
         <is>
           <t>18:44</t>
         </is>
       </c>
-      <c r="Q86" s="6" t="n">
+      <c r="Q86" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="R86" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 18:44 → 18:44</t>
-        </is>
-      </c>
-      <c r="S86" s="7" t="inlineStr">
+      <c r="R86" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S86" s="9" t="inlineStr">
         <is>
           <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
         </is>
       </c>
-      <c r="T86" s="6" t="inlineStr">
+      <c r="T86" s="8" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>Chengdu</t>
         </is>
       </c>
-      <c r="B87" s="6" t="n">
+      <c r="B87" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>Taikoo Li</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>Sight</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>20:33</t>
         </is>
       </c>
-      <c r="H87" s="6" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>22:03</t>
         </is>
       </c>
-      <c r="I87" s="6" t="n">
+      <c r="I87" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="J87" s="6" t="inlineStr">
+      <c r="J87" s="8" t="inlineStr">
         <is>
           <t>Hotel (home)</t>
         </is>
       </c>
-      <c r="K87" s="6" t="inlineStr">
+      <c r="K87" s="8" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
-      <c r="L87" s="6" t="n">
+      <c r="L87" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="M87" s="6" t="n">
+      <c r="M87" s="8" t="n">
         <v>1.07</v>
       </c>
-      <c r="N87" s="6" t="inlineStr">
+      <c r="N87" s="8" t="inlineStr">
         <is>
           <t>estimated (fitted model)</t>
         </is>
       </c>
-      <c r="O87" s="6" t="n">
+      <c r="O87" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="P87" s="6" t="inlineStr">
+      <c r="P87" s="8" t="inlineStr">
         <is>
           <t>20:33</t>
         </is>
       </c>
-      <c r="Q87" s="6" t="n">
+      <c r="Q87" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="R87" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 20:33 → 20:33</t>
-        </is>
-      </c>
-      <c r="S87" s="7" t="inlineStr">
+      <c r="R87" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S87" s="9" t="inlineStr">
         <is>
           <t>Chengdu guides put a relaxed walk through Taikoo Li at 1–2 hours, longer only if you stop to dine.</t>
         </is>
       </c>
-      <c r="T87" s="6" t="inlineStr">
+      <c r="T87" s="8" t="inlineStr">
         <is>
           <t>med</t>
         </is>

--- a/china-notion-sync.xlsx
+++ b/china-notion-sync.xlsx
@@ -15,11 +15,11 @@
     <sheet name="Legs" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$T$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$T$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Schedule'!$A$1:$T$242</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ideas (parked)'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ideas (parked)'!$A$1:$G$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Moves'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Legs'!$A$1:$I$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Legs'!$A$1:$I$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1403,7 +1403,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Fenghuang</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -1411,50 +1411,50 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Wuli Stone Street</t>
+          <t>Fenghuang HSR station</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I8" s="6" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Tuwang Palace</t>
+          <t>Check in at Jinshuian</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L8" s="6" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
@@ -1466,20 +1466,20 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>RETIME 13:21 → 12:41; ORDER 40 → 30</t>
+          <t>DURATION 20m → 15m</t>
         </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>The 5-li (2.5 km) street is the town's spine, but guides say the whole core loop is walkable in about an hour brisk / two hours relaxed, so an unhurried first pass with shops and photos is about 60 min.</t>
+          <t>Fenghuanggucheng is a small line station ~10 km from town; arrival is deboarding, exiting and walking to the bus/taxi forecourt, not a visit.</t>
         </is>
       </c>
       <c r="T8" s="6" t="inlineStr">
@@ -1491,7 +1491,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Guilin</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
@@ -1499,54 +1499,54 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Tuwang Palace</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I9" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Furong waterfall</t>
+          <t>Check in at RongShi</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0</v>
+        <v>6.68</v>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1554,20 +1554,20 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>RETIME 14:30 → 13:50; ORDER 50 → 40</t>
+          <t>RETIME 15:00 → 14:58</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>Blogs treat 土司/土王行宫 as a compact clifftop wooden complex and 'another great photo spot' over the waterfall (part of it now a guesthouse) rather than a museum you work through.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T9" s="6" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Yangshuo</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
@@ -1587,30 +1587,30 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Furong waterfall</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="I10" s="6" t="n">
@@ -1618,23 +1618,23 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Liu Xiaoqing rice tofu</t>
+          <t>Fengqi Homestay</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.09993839083537745</v>
+        <v>0.52</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="Q10" s="6" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>RETIME 15:08 → 14:28; ORDER 60 → 50</t>
+          <t>RETIME 14:00 → 13:53</t>
         </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>Guides advise 20-30 min to walk the full waterfall walkways before shooting seriously, and the loop here also takes in the viewing platform, water-curtain cave behind the 60 m falls and the covered bridge below.</t>
+          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
         </is>
       </c>
       <c r="T10" s="6" t="inlineStr">
@@ -1667,7 +1667,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Furong (Hibiscus)</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
@@ -1675,38 +1675,38 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Liu Xiaoqing rice tofu</t>
+          <t>Land at PVG</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I11" s="6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1730,20 +1730,20 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>RETIME 12:42 → 16:30; ORDER 30 → 60</t>
+          <t>DURATION 40m → 45m</t>
         </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>Ctrip/Mafengwo reviews: ¥5 a bowl at No. 113 by the archway, shop is tiny and packed so people eat under the outdoor awning or walk with it — a snack stop, not a sit-down lunch.</t>
+          <t>PVG guides put full international arrival at ~60min; a domestic arrival (HO1148 from Guilin, T2) skips immigration, leaving deplane, long terminal walk and belt wait at ~35-45min.</t>
         </is>
       </c>
       <c r="T11" s="6" t="inlineStr">
@@ -1752,712 +1752,8 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Furong (Hibiscus)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Baishetang Square</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>0.09993839083537745</v>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-      <c r="O12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 16:55 → 17:08; ORDER 80 → 70</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
-        </is>
-      </c>
-      <c r="T12" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Furong (Hibiscus)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Baishetang Square</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Shenpu Camp Square</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-      <c r="O13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>ORDER 90 → 80</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>Scheduled free performances at 摆手堂 run at 10:30, 16:30 and 19:30 (plus a 20:30 theatre show, moved indoors if raining); a square set of Tujia songs, 摆手舞 and 茅古斯 runs roughly half an hour.</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Furong (Hibiscus)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Shenpu Camp Square</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>20:09</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Far-bank platform</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-      <c r="O14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>20:09</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="R14" s="7" t="inlineStr">
-        <is>
-          <t>ORDER 100 → 90</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>Could not verify this square by name in any Chinese or English source; treated as one more open viewpoint on the night circuit, and squares here read as short stand-and-look stops.</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Furong (Hibiscus)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Far-bank platform</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>20:38</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>20:38</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="R15" s="7" t="inlineStr">
-        <is>
-          <t>ORDER 110 → 100</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>Photo-spot roundups list the opposite-bank/观景台 as a single fixed vantage where visitors gather for sunset and the illuminated falls; it is a stand-and-shoot stop, not a walk.</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Fenghuang</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Fenghuang HSR station</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Check in at Jinshuian</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>didi</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-      <c r="O16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>DURATION 20m → 15m</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>Fenghuanggucheng is a small line station ~10 km from town; arrival is deboarding, exiting and walking to the bus/taxi forecourt, not a visit.</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Guilin</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Check in at RongShi</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>didi</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>estimated (fitted model)</t>
-        </is>
-      </c>
-      <c r="O17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 15:00 → 14:58</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
-        </is>
-      </c>
-      <c r="T17" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Yangshuo</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Fengqi Homestay</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="M18" s="6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>estimated (fitted model)</t>
-        </is>
-      </c>
-      <c r="O18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 14:00 → 13:53</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>Wulingyuan restaurants are ordered-at-table Hunan places at RMB80-120pp with no English menus; a proper unhurried meal is ~1 h.</t>
-        </is>
-      </c>
-      <c r="T18" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Land at PVG</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>none (same place)</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>co-located</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="R19" s="7" t="inlineStr">
-        <is>
-          <t>DURATION 40m → 45m</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>PVG guides put full international arrival at ~60min; a domestic arrival (HO1148 from Guilin, T2) skips immigration, leaving deplane, long terminal walk and belt wait at ~35-45min.</t>
-        </is>
-      </c>
-      <c r="T19" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T19"/>
+  <autoFilter ref="A1:T11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14320,704 +13616,704 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="inlineStr">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t>Furong (Hibiscus)</t>
         </is>
       </c>
-      <c r="B136" s="6" t="n">
+      <c r="B136" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C136" s="6" t="inlineStr">
+      <c r="C136" s="8" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D136" s="6" t="n">
+      <c r="D136" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="8" t="inlineStr">
         <is>
           <t>Wuli Stone Street</t>
         </is>
       </c>
-      <c r="F136" s="6" t="inlineStr">
+      <c r="F136" s="8" t="inlineStr">
         <is>
           <t>Sight</t>
         </is>
       </c>
-      <c r="G136" s="6" t="inlineStr">
+      <c r="G136" s="8" t="inlineStr">
         <is>
           <t>12:41</t>
         </is>
       </c>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="H136" s="8" t="inlineStr">
         <is>
           <t>13:41</t>
         </is>
       </c>
-      <c r="I136" s="6" t="n">
+      <c r="I136" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="J136" s="6" t="inlineStr">
+      <c r="J136" s="8" t="inlineStr">
         <is>
           <t>Tuwang Palace</t>
         </is>
       </c>
-      <c r="K136" s="6" t="inlineStr">
+      <c r="K136" s="8" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="L136" s="6" t="n">
+      <c r="L136" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M136" s="6" t="n">
+      <c r="M136" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N136" s="6" t="inlineStr">
+      <c r="N136" s="8" t="inlineStr">
         <is>
           <t>routed (real leg)</t>
         </is>
       </c>
-      <c r="O136" s="6" t="n">
+      <c r="O136" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P136" s="6" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="Q136" s="6" t="n">
+      <c r="P136" s="8" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="Q136" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="R136" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 13:21 → 12:41; ORDER 40 → 30</t>
-        </is>
-      </c>
-      <c r="S136" s="7" t="inlineStr">
+      <c r="R136" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S136" s="9" t="inlineStr">
         <is>
           <t>The 5-li (2.5 km) street is the town's spine, but guides say the whole core loop is walkable in about an hour brisk / two hours relaxed, so an unhurried first pass with shops and photos is about 60 min.</t>
         </is>
       </c>
-      <c r="T136" s="6" t="inlineStr">
+      <c r="T136" s="8" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="6" t="inlineStr">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>Furong (Hibiscus)</t>
         </is>
       </c>
-      <c r="B137" s="6" t="n">
+      <c r="B137" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="C137" s="8" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D137" s="6" t="n">
+      <c r="D137" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E137" s="8" t="inlineStr">
         <is>
           <t>Tuwang Palace</t>
         </is>
       </c>
-      <c r="F137" s="6" t="inlineStr">
+      <c r="F137" s="8" t="inlineStr">
         <is>
           <t>Sight</t>
         </is>
       </c>
-      <c r="G137" s="6" t="inlineStr">
+      <c r="G137" s="8" t="inlineStr">
         <is>
           <t>13:50</t>
         </is>
       </c>
-      <c r="H137" s="6" t="inlineStr">
+      <c r="H137" s="8" t="inlineStr">
         <is>
           <t>14:20</t>
         </is>
       </c>
-      <c r="I137" s="6" t="n">
+      <c r="I137" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="J137" s="6" t="inlineStr">
+      <c r="J137" s="8" t="inlineStr">
         <is>
           <t>Furong waterfall</t>
         </is>
       </c>
-      <c r="K137" s="6" t="inlineStr">
+      <c r="K137" s="8" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="L137" s="6" t="n">
+      <c r="L137" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M137" s="6" t="n">
+      <c r="M137" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N137" s="6" t="inlineStr">
+      <c r="N137" s="8" t="inlineStr">
         <is>
           <t>routed (real leg)</t>
         </is>
       </c>
-      <c r="O137" s="6" t="n">
+      <c r="O137" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P137" s="6" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="Q137" s="6" t="n">
+      <c r="P137" s="8" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="Q137" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R137" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 14:30 → 13:50; ORDER 50 → 40</t>
-        </is>
-      </c>
-      <c r="S137" s="7" t="inlineStr">
+      <c r="R137" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S137" s="9" t="inlineStr">
         <is>
           <t>Blogs treat 土司/土王行宫 as a compact clifftop wooden complex and 'another great photo spot' over the waterfall (part of it now a guesthouse) rather than a museum you work through.</t>
         </is>
       </c>
-      <c r="T137" s="6" t="inlineStr">
+      <c r="T137" s="8" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="6" t="inlineStr">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>Furong (Hibiscus)</t>
         </is>
       </c>
-      <c r="B138" s="6" t="n">
+      <c r="B138" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C138" s="8" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D138" s="6" t="n">
+      <c r="D138" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E138" s="8" t="inlineStr">
         <is>
           <t>Furong waterfall</t>
         </is>
       </c>
-      <c r="F138" s="6" t="inlineStr">
+      <c r="F138" s="8" t="inlineStr">
         <is>
           <t>Sight</t>
         </is>
       </c>
-      <c r="G138" s="6" t="inlineStr">
+      <c r="G138" s="8" t="inlineStr">
         <is>
           <t>14:28</t>
         </is>
       </c>
-      <c r="H138" s="6" t="inlineStr">
+      <c r="H138" s="8" t="inlineStr">
         <is>
           <t>15:28</t>
         </is>
       </c>
-      <c r="I138" s="6" t="n">
+      <c r="I138" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="J138" s="6" t="inlineStr">
-        <is>
-          <t>Liu Xiaoqing rice tofu</t>
-        </is>
-      </c>
-      <c r="K138" s="6" t="inlineStr">
+      <c r="J138" s="8" t="inlineStr">
+        <is>
+          <t>Youshui River cruise</t>
+        </is>
+      </c>
+      <c r="K138" s="8" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="L138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" s="8" t="inlineStr">
+        <is>
+          <t>routed (real leg)</t>
+        </is>
+      </c>
+      <c r="O138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" s="8" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="Q138" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="R138" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S138" s="9" t="inlineStr">
+        <is>
+          <t>Guides advise 20-30 min to walk the full waterfall walkways before shooting seriously, and the loop here also takes in the viewing platform, water-curtain cave behind the 60 m falls and the covered bridge below.</t>
+        </is>
+      </c>
+      <c r="T138" s="8" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>Furong (Hibiscus)</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E139" s="8" t="inlineStr">
+        <is>
+          <t>Youshui River cruise</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="I139" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J139" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="K139" s="8" t="inlineStr">
+        <is>
+          <t>none (same place)</t>
+        </is>
+      </c>
+      <c r="L139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" s="8" t="inlineStr">
+        <is>
+          <t>co-located</t>
+        </is>
+      </c>
+      <c r="O139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" s="8" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="Q139" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="R139" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S139" s="9" t="inlineStr">
+        <is>
+          <t>Trip reports describe the Youshui boat as 'a very short ferry' (bundled at ¥68 with the shuttle, running ~09:00-18:00); no source gives a duration, so 30 min covers boarding, wait and the run past the falls.</t>
+        </is>
+      </c>
+      <c r="T139" s="8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>Furong (Hibiscus)</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="I140" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="J140" s="8" t="inlineStr">
+        <is>
+          <t>Baishetang Square</t>
+        </is>
+      </c>
+      <c r="K140" s="8" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="L138" s="6" t="n">
+      <c r="L140" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M138" s="6" t="n">
-        <v>0.09993839083537745</v>
-      </c>
-      <c r="N138" s="6" t="inlineStr">
+      <c r="M140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" s="8" t="inlineStr">
         <is>
           <t>routed (real leg)</t>
         </is>
       </c>
-      <c r="O138" s="6" t="n">
+      <c r="O140" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P138" s="6" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="Q138" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="R138" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 15:08 → 14:28; ORDER 60 → 50</t>
-        </is>
-      </c>
-      <c r="S138" s="7" t="inlineStr">
-        <is>
-          <t>Guides advise 20-30 min to walk the full waterfall walkways before shooting seriously, and the loop here also takes in the viewing platform, water-curtain cave behind the 60 m falls and the covered bridge below.</t>
-        </is>
-      </c>
-      <c r="T138" s="6" t="inlineStr">
+      <c r="P140" s="8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="Q140" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="R140" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S140" s="9" t="inlineStr">
+        <is>
+          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
+        </is>
+      </c>
+      <c r="T140" s="8" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="6" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>Furong (Hibiscus)</t>
         </is>
       </c>
-      <c r="B139" s="6" t="n">
+      <c r="B141" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C139" s="6" t="inlineStr">
+      <c r="C141" s="8" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D139" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>Liu Xiaoqing rice tofu</t>
-        </is>
-      </c>
-      <c r="F139" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G139" s="6" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="H139" s="6" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I139" s="6" t="n">
+      <c r="D141" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>Baishetang Square</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="I141" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="J139" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
-      <c r="K139" s="6" t="inlineStr">
-        <is>
-          <t>none (same place)</t>
-        </is>
-      </c>
-      <c r="L139" s="6" t="n">
+      <c r="J141" s="8" t="inlineStr">
+        <is>
+          <t>Shenpu Camp Square</t>
+        </is>
+      </c>
+      <c r="K141" s="8" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="L141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M139" s="6" t="n">
+      <c r="N141" s="8" t="inlineStr">
+        <is>
+          <t>routed (real leg)</t>
+        </is>
+      </c>
+      <c r="O141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="Q141" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="R141" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S141" s="9" t="inlineStr">
+        <is>
+          <t>Scheduled free performances at 摆手堂 run at 10:30, 16:30 and 19:30 (plus a 20:30 theatre show, moved indoors if raining); a square set of Tujia songs, 摆手舞 and 茅古斯 runs roughly half an hour.</t>
+        </is>
+      </c>
+      <c r="T141" s="8" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>Furong (Hibiscus)</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t>Shenpu Camp Square</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="H142" s="8" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="I142" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J142" s="8" t="inlineStr">
+        <is>
+          <t>Far-bank platform</t>
+        </is>
+      </c>
+      <c r="K142" s="8" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="L142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N139" s="6" t="inlineStr">
-        <is>
-          <t>co-located</t>
-        </is>
-      </c>
-      <c r="O139" s="6" t="n">
+      <c r="N142" s="8" t="inlineStr">
+        <is>
+          <t>routed (real leg)</t>
+        </is>
+      </c>
+      <c r="O142" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P139" s="6" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="Q139" s="6" t="n">
+      <c r="P142" s="8" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="Q142" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="R142" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S142" s="9" t="inlineStr">
+        <is>
+          <t>Could not verify this square by name in any Chinese or English source; treated as one more open viewpoint on the night circuit, and squares here read as short stand-and-look stops.</t>
+        </is>
+      </c>
+      <c r="T142" s="8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>Furong (Hibiscus)</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>Far-bank platform</t>
+        </is>
+      </c>
+      <c r="F143" s="8" t="inlineStr">
+        <is>
+          <t>Sight</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="I143" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R139" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 12:42 → 16:30; ORDER 30 → 60</t>
-        </is>
-      </c>
-      <c r="S139" s="7" t="inlineStr">
-        <is>
-          <t>Ctrip/Mafengwo reviews: ¥5 a bowl at No. 113 by the archway, shop is tiny and packed so people eat under the outdoor awning or walk with it — a snack stop, not a sit-down lunch.</t>
-        </is>
-      </c>
-      <c r="T139" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>Furong (Hibiscus)</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="n">
+      <c r="J143" s="8" t="inlineStr">
+        <is>
+          <t>Hotel (home)</t>
+        </is>
+      </c>
+      <c r="K143" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" s="8" t="inlineStr">
+        <is>
+          <t>routed (real leg)</t>
+        </is>
+      </c>
+      <c r="O143" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
-      <c r="F140" s="6" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="H140" s="6" t="inlineStr">
-        <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="I140" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J140" s="6" t="inlineStr">
-        <is>
-          <t>Baishetang Square</t>
-        </is>
-      </c>
-      <c r="K140" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L140" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" s="6" t="n">
-        <v>0.09993839083537745</v>
-      </c>
-      <c r="N140" s="6" t="inlineStr">
-        <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-      <c r="O140" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P140" s="6" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="Q140" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="R140" s="7" t="inlineStr">
-        <is>
-          <t>RETIME 16:55 → 17:08; ORDER 80 → 70</t>
-        </is>
-      </c>
-      <c r="S140" s="7" t="inlineStr">
-        <is>
-          <t>Hunan dinner in Wulingyuan is a shared-dish sit-down affair; 1.5 h lets you order, wait and actually enjoy it rather than refuel.</t>
-        </is>
-      </c>
-      <c r="T140" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>Furong (Hibiscus)</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>Baishetang Square</t>
-        </is>
-      </c>
-      <c r="F141" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G141" s="6" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="H141" s="6" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="I141" s="6" t="n">
+      <c r="P143" s="8" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="Q143" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="J141" s="6" t="inlineStr">
-        <is>
-          <t>Shenpu Camp Square</t>
-        </is>
-      </c>
-      <c r="K141" s="6" t="inlineStr">
-        <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="L141" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M141" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" s="6" t="inlineStr">
-        <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-      <c r="O141" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P141" s="6" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="Q141" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="R141" s="7" t="inlineStr">
-        <is>
-          <t>ORDER 90 → 80</t>
-        </is>
-      </c>
-      <c r="S141" s="7" t="inlineStr">
-        <is>
-          <t>Scheduled free performances at 摆手堂 run at 10:30, 16:30 and 19:30 (plus a 20:30 theatre show, moved indoors if raining); a square set of Tujia songs, 摆手舞 and 茅古斯 runs roughly half an hour.</t>
-        </is>
-      </c>
-      <c r="T141" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>Furong (Hibiscus)</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>Shenpu Camp Square</t>
-        </is>
-      </c>
-      <c r="F142" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>20:09</t>
-        </is>
-      </c>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="I142" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J142" s="6" t="inlineStr">
-        <is>
-          <t>Far-bank platform</t>
-        </is>
-      </c>
-      <c r="K142" s="6" t="inlineStr">
-        <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="L142" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M142" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" s="6" t="inlineStr">
-        <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-      <c r="O142" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P142" s="6" t="inlineStr">
-        <is>
-          <t>20:09</t>
-        </is>
-      </c>
-      <c r="Q142" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="R142" s="7" t="inlineStr">
-        <is>
-          <t>ORDER 100 → 90</t>
-        </is>
-      </c>
-      <c r="S142" s="7" t="inlineStr">
-        <is>
-          <t>Could not verify this square by name in any Chinese or English source; treated as one more open viewpoint on the night circuit, and squares here read as short stand-and-look stops.</t>
-        </is>
-      </c>
-      <c r="T142" s="6" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>Furong (Hibiscus)</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>Far-bank platform</t>
-        </is>
-      </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
-          <t>Sight</t>
-        </is>
-      </c>
-      <c r="G143" s="6" t="inlineStr">
-        <is>
-          <t>20:38</t>
-        </is>
-      </c>
-      <c r="H143" s="6" t="inlineStr">
-        <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="I143" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J143" s="6" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
-      <c r="K143" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L143" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" s="6" t="inlineStr">
-        <is>
-          <t>routed (real leg)</t>
-        </is>
-      </c>
-      <c r="O143" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P143" s="6" t="inlineStr">
-        <is>
-          <t>20:38</t>
-        </is>
-      </c>
-      <c r="Q143" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="R143" s="7" t="inlineStr">
-        <is>
-          <t>ORDER 110 → 100</t>
-        </is>
-      </c>
-      <c r="S143" s="7" t="inlineStr">
+      <c r="R143" s="9" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="S143" s="9" t="inlineStr">
         <is>
           <t>Photo-spot roundups list the opposite-bank/观景台 as a single fixed vantage where visitors gather for sunset and the illuminated falls; it is a stand-and-shoot stop, not a walk.</t>
         </is>
       </c>
-      <c r="T143" s="6" t="inlineStr">
+      <c r="T143" s="8" t="inlineStr">
         <is>
           <t>med</t>
         </is>
@@ -23671,7 +22967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23727,11 +23023,11 @@
         </is>
       </c>
       <c r="B2" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -23760,11 +23056,11 @@
         </is>
       </c>
       <c r="B3" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -23868,11 +23164,11 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>SKP Chengdu</t>
+          <t>Hotpot alt · Shu Daxia</t>
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
@@ -23881,7 +23177,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Dropped outright. A luxury mall ~14 km south of the hotel, well off every other cluster, and the only argument for it is architecture and air conditioning — both of which Chengdu Museum gives you for free and centrally. The round-trip transit alone would cost most of a Kuanzhai.</t>
+          <t>This is a dinner, and you insert meals yourself. Kept as the recommendation for arrival night: it is in the Chunxi Road / Taikoo Li block near the hotel, so it fits the one slot day 1 actually has.</t>
         </is>
       </c>
     </row>
@@ -23892,20 +23188,20 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Hotpot alt · Shu Daxia</t>
+          <t>SKP Chengdu</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
@@ -23914,7 +23210,7 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>This is a dinner, and you insert meals yourself. Kept as the recommendation for arrival night: it is in the Chunxi Road / Taikoo Li block near the hotel, so it fits the one slot day 1 actually has.</t>
+          <t>Dropped outright. A luxury mall ~14 km south of the hotel, well off every other cluster, and the only argument for it is architecture and air conditioning — both of which Chengdu Museum gives you for free and centrally. The round-trip transit alone would cost most of a Kuanzhai.</t>
         </is>
       </c>
     </row>
@@ -23925,11 +23221,11 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -23991,11 +23287,11 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -24024,11 +23320,11 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -24057,11 +23353,11 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -24090,11 +23386,11 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -24255,11 +23551,11 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -24354,11 +23650,11 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -24387,34 +23683,67 @@
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
+          <t>Yangjiajie cableway</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>REMOVE from this day in Notion — keep the page, mark it unscheduled/idea</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>The lift that makes Yangjiajie reachable — cut with the area it serves. Only worth restoring if you add a fifth day or trade away the entire Tianzi/Ten-Mile half of day 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Zhangjiajie</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
           <t>Yangjiajie</t>
         </is>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E23" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>REMOVE from this day in Notion — keep the page, mark it unscheduled/idea</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>Genuinely excellent and much quieter than Yuanjiajie — Natural Great Wall and One Step to Heaven — but it sits at the far western end of the plateau. Reaching it costs its own cable car plus roughly an hour of extra shuttle each way, about 4 h of marginal cost against Ten-Mile Gallery's 90 min for zero extra transfer. With one afternoon and two full days it is the correct thing to lose. If you would rather have it than Tianmen, swap the whole of day 3 for it — do not try to squeeze it into day 2.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24480,7 +23809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I155"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28206,12 +27535,12 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Baishetang Square</t>
+          <t>Furong waterfall</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Shenpu Camp Square</t>
+          <t>Youshui River cruise</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
@@ -28247,12 +27576,12 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
+          <t>Baishetang Square</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
           <t>Shenpu Camp Square</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>Far-bank platform</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -28279,48 +27608,48 @@
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Shenpu Camp Square</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Train from Furongzhen</t>
+          <t>Far-bank platform</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G93" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>Fenghuang</t>
+          <t>Furong (Hibiscus)</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
@@ -28329,12 +27658,12 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Fenghuang HSR station</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Check in at Jinshuian</t>
+          <t>Train from Furongzhen</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
@@ -28343,14 +27672,14 @@
         </is>
       </c>
       <c r="G94" s="8" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>11.3</v>
+        <v>3.83</v>
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -28370,28 +27699,28 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
+          <t>Fenghuang HSR station</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
           <t>Check in at Jinshuian</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t>East Gate Tower</t>
-        </is>
-      </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G95" s="8" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>0.43</v>
+        <v>11.3</v>
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -28411,28 +27740,28 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
+          <t>Check in at Jinshuian</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
           <t>East Gate Tower</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>Hong Bridge</t>
-        </is>
-      </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
       <c r="G96" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>0.1</v>
+        <v>0.43</v>
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -28452,28 +27781,28 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
+          <t>East Gate Tower</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
           <t>Hong Bridge</t>
         </is>
       </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t>Fenghuang Ancient Town</t>
-        </is>
-      </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
       <c r="G97" s="8" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>0.77</v>
+        <v>0.1</v>
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -28493,12 +27822,12 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Hong Bridge</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Tuojiang night boat</t>
+          <t>Fenghuang Ancient Town</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -28507,10 +27836,10 @@
         </is>
       </c>
       <c r="G98" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
@@ -28534,12 +27863,12 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Snow Bridge (Xueqiao)</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Tuojiang night boat</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
@@ -28548,10 +27877,10 @@
         </is>
       </c>
       <c r="G99" s="8" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>0.22</v>
+        <v>0.8</v>
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
@@ -28566,33 +27895,33 @@
         </is>
       </c>
       <c r="B100" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Snow Bridge (Xueqiao)</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Train from Gucheng</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G100" s="8" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>8.050000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
@@ -28603,11 +27932,11 @@
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>Guilin</t>
+          <t>Fenghuang</t>
         </is>
       </c>
       <c r="B101" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
@@ -28616,12 +27945,12 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Check in at RongShi</t>
+          <t>Train from Gucheng</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
@@ -28630,10 +27959,10 @@
         </is>
       </c>
       <c r="G101" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>6.68</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
@@ -28657,24 +27986,24 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
           <t>Check in at RongShi</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>Elephant Trunk Hill</t>
-        </is>
-      </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G102" s="8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>0.23</v>
+        <v>6.68</v>
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
@@ -28698,12 +28027,12 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Check in at RongShi</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Two Rivers &amp; Four Lakes</t>
+          <t>Elephant Trunk Hill</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -28712,10 +28041,10 @@
         </is>
       </c>
       <c r="G103" s="8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>0.68</v>
+        <v>0.23</v>
       </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
@@ -28739,24 +28068,24 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
           <t>Two Rivers &amp; Four Lakes</t>
         </is>
       </c>
-      <c r="E104" s="8" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
       <c r="G104" s="8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
@@ -28771,33 +28100,33 @@
         </is>
       </c>
       <c r="B105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Two Rivers &amp; Four Lakes</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Zhujiang Wharf transfer</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G105" s="8" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>20.79</v>
+        <v>0.5</v>
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
@@ -28808,11 +28137,11 @@
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>Yangshuo</t>
+          <t>Guilin</t>
         </is>
       </c>
       <c r="B106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
@@ -28821,24 +28150,24 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Fengqi Homestay</t>
+          <t>Zhujiang Wharf transfer</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G106" s="8" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>0.52</v>
+        <v>20.79</v>
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
@@ -28862,28 +28191,28 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
           <t>Fengqi Homestay</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t>West Street</t>
-        </is>
-      </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G107" s="8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>0.8</v>
+        <v>0.52</v>
       </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -28903,28 +28232,28 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Fengqi Homestay</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Li River night walk</t>
+          <t>West Street</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G108" s="8" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -28935,33 +28264,33 @@
         </is>
       </c>
       <c r="B109" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Xingping Ancient Town</t>
+          <t>Li River night walk</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G109" s="8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>3.03</v>
+        <v>0.68</v>
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
@@ -28985,28 +28314,28 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
           <t>Xingping Ancient Town</t>
         </is>
       </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t>20-RMB viewpoint</t>
-        </is>
-      </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="G110" s="8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -29026,12 +28355,12 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Xingping Ancient Town</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Impression Liu Sanjie</t>
+          <t>20-RMB viewpoint</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
@@ -29040,14 +28369,14 @@
         </is>
       </c>
       <c r="G111" s="8" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>17.39</v>
+        <v>2.4</v>
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -29067,24 +28396,24 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
           <t>Impression Liu Sanjie</t>
         </is>
       </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="G112" s="8" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>1.42</v>
+        <v>17.39</v>
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
@@ -29099,21 +28428,21 @@
         </is>
       </c>
       <c r="B113" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Impression Liu Sanjie</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Yulong bamboo rafting</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F113" s="8" t="inlineStr">
@@ -29122,10 +28451,10 @@
         </is>
       </c>
       <c r="G113" s="8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>6.53</v>
+        <v>1.42</v>
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
@@ -29149,12 +28478,12 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
           <t>Yulong bamboo rafting</t>
-        </is>
-      </c>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
@@ -29190,12 +28519,12 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Yulong bamboo rafting</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Moon Hill</t>
+          <t>Yulong valley cycling</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
@@ -29204,14 +28533,14 @@
         </is>
       </c>
       <c r="G115" s="8" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>10.4</v>
+        <v>6.53</v>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -29231,12 +28560,12 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Lunch</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Moon Hill</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -29245,14 +28574,14 @@
         </is>
       </c>
       <c r="G116" s="8" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>6.23</v>
+        <v>10.4</v>
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -29263,21 +28592,21 @@
         </is>
       </c>
       <c r="B117" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Fly from KWL</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
@@ -29286,10 +28615,10 @@
         </is>
       </c>
       <c r="G117" s="8" t="n">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>67.09</v>
+        <v>6.23</v>
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
@@ -29300,11 +28629,11 @@
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Yangshuo</t>
         </is>
       </c>
       <c r="B118" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
@@ -29313,12 +28642,12 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Maglev</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Check in at Marriott</t>
+          <t>Fly from KWL</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -29327,10 +28656,10 @@
         </is>
       </c>
       <c r="G118" s="8" t="n">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>9.23</v>
+        <v>67.09</v>
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
@@ -29354,28 +28683,28 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
+          <t>Shanghai Maglev</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
           <t>Check in at Marriott</t>
         </is>
       </c>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t>Nanjing Road East</t>
-        </is>
-      </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G119" s="8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>0.9</v>
+        <v>9.23</v>
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -29395,24 +28724,24 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Check in at Marriott</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>The Bund</t>
+          <t>Nanjing Road East</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G120" s="8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
@@ -29436,28 +28765,28 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
           <t>The Bund</t>
         </is>
       </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
-        </is>
-      </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G121" s="8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -29468,21 +28797,21 @@
         </is>
       </c>
       <c r="B122" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>The Bund</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Recovery massage / spa</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
@@ -29491,10 +28820,10 @@
         </is>
       </c>
       <c r="G122" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>2.67</v>
+        <v>2.04</v>
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
@@ -29518,24 +28847,24 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
           <t>Recovery massage / spa</t>
         </is>
       </c>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t>M50 Creative Park</t>
-        </is>
-      </c>
       <c r="F123" s="8" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="G123" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>3.34</v>
+        <v>2.67</v>
       </c>
       <c r="I123" s="8" t="inlineStr">
         <is>
@@ -29559,12 +28888,12 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Recovery massage / spa</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Jing’an Temple</t>
+          <t>M50 Creative Park</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
@@ -29573,10 +28902,10 @@
         </is>
       </c>
       <c r="G124" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>2.83</v>
+        <v>3.34</v>
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
@@ -29600,24 +28929,24 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
           <t>Jing’an Temple</t>
         </is>
       </c>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t>Nanjing Road West</t>
-        </is>
-      </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G125" s="8" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>0.96</v>
+        <v>2.83</v>
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
@@ -29641,28 +28970,28 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
+          <t>Jing’an Temple</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
           <t>Nanjing Road West</t>
         </is>
       </c>
-      <c r="E126" s="8" t="inlineStr">
-        <is>
-          <t>Zhangyuan</t>
-        </is>
-      </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
       <c r="G126" s="8" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>0.5</v>
+        <v>0.96</v>
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -29682,28 +29011,28 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Nanjing Road West</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Zhangyuan</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G127" s="8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>4.38</v>
+        <v>0.5</v>
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -29714,21 +29043,21 @@
         </is>
       </c>
       <c r="B128" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Wukang Building</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
@@ -29737,10 +29066,10 @@
         </is>
       </c>
       <c r="G128" s="8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>7.18</v>
+        <v>4.38</v>
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
@@ -29764,28 +29093,28 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
           <t>Wukang Building</t>
         </is>
       </c>
-      <c r="E129" s="8" t="inlineStr">
-        <is>
-          <t>Wukang Road</t>
-        </is>
-      </c>
       <c r="F129" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G129" s="8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>0.7</v>
+        <v>7.18</v>
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -29805,24 +29134,24 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
+          <t>Wukang Building</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
           <t>Wukang Road</t>
         </is>
       </c>
-      <c r="E130" s="8" t="inlineStr">
-        <is>
-          <t>Ferguson Lane</t>
-        </is>
-      </c>
       <c r="F130" s="8" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
       <c r="G130" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
@@ -29846,24 +29175,24 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
+          <t>Wukang Road</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
           <t>Ferguson Lane</t>
         </is>
       </c>
-      <c r="E131" s="8" t="inlineStr">
-        <is>
-          <t>Anfu Road</t>
-        </is>
-      </c>
       <c r="F131" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G131" s="8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H131" s="8" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
@@ -29887,12 +29216,12 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
+          <t>Ferguson Lane</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
           <t>Anfu Road</t>
-        </is>
-      </c>
-      <c r="E132" s="8" t="inlineStr">
-        <is>
-          <t>Wulumuqi Road</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
@@ -29904,7 +29233,7 @@
         <v>14</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
@@ -29928,28 +29257,28 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Anfu Road</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Fuxing Park</t>
+          <t>Wulumuqi Road</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G133" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -29969,28 +29298,28 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
           <t>Fuxing Park</t>
         </is>
       </c>
-      <c r="E134" s="8" t="inlineStr">
-        <is>
-          <t>Sinan Mansions</t>
-        </is>
-      </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G134" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -30010,28 +29339,28 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Fuxing Park</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Hotel (home)</t>
+          <t>Sinan Mansions</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G135" s="8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>3.97</v>
+        <v>0.3</v>
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -30042,21 +29371,21 @@
         </is>
       </c>
       <c r="B136" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Yu Garden</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr">
@@ -30065,10 +29394,10 @@
         </is>
       </c>
       <c r="G136" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>1.27</v>
+        <v>3.97</v>
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
@@ -30092,24 +29421,24 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
           <t>Yu Garden</t>
         </is>
       </c>
-      <c r="E137" s="8" t="inlineStr">
-        <is>
-          <t>Mid-Lake Teahouse</t>
-        </is>
-      </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G137" s="8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>0.47</v>
+        <v>1.27</v>
       </c>
       <c r="I137" s="8" t="inlineStr">
         <is>
@@ -30133,28 +29462,28 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
+          <t>Yu Garden</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
           <t>Mid-Lake Teahouse</t>
         </is>
       </c>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t>Yuyuan Bazaar</t>
-        </is>
-      </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
       <c r="G138" s="8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -30174,12 +29503,12 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Mid-Lake Teahouse</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>City God Temple</t>
+          <t>Yuyuan Bazaar</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
@@ -30188,14 +29517,14 @@
         </is>
       </c>
       <c r="G139" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -30215,24 +29544,24 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
           <t>City God Temple</t>
         </is>
       </c>
-      <c r="E140" s="8" t="inlineStr">
-        <is>
-          <t>People’s Square</t>
-        </is>
-      </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G140" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>1.83</v>
+        <v>0.26</v>
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
@@ -30256,12 +29585,12 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>City God Temple</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Huangpu night cruise</t>
+          <t>People’s Square</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
@@ -30270,10 +29599,10 @@
         </is>
       </c>
       <c r="G141" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
@@ -30297,24 +29626,24 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
           <t>Huangpu night cruise</t>
         </is>
       </c>
-      <c r="E142" s="8" t="inlineStr">
-        <is>
-          <t>Old Jazz Bar</t>
-        </is>
-      </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
       <c r="G142" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>1.3</v>
+        <v>2.45</v>
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
@@ -30338,12 +29667,12 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
+          <t>Huangpu night cruise</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
           <t>Old Jazz Bar</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr">
@@ -30355,7 +29684,7 @@
         <v>9</v>
       </c>
       <c r="H143" s="8" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
@@ -30370,21 +29699,21 @@
         </is>
       </c>
       <c r="B144" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Old Jazz Bar</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>TANK Shanghai</t>
+          <t>Hotel (home)</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
@@ -30393,10 +29722,10 @@
         </is>
       </c>
       <c r="G144" s="8" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>8.6</v>
+        <v>1.47</v>
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
@@ -30420,24 +29749,24 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
           <t>TANK Shanghai</t>
         </is>
       </c>
-      <c r="E145" s="8" t="inlineStr">
-        <is>
-          <t>West Bund Museum</t>
-        </is>
-      </c>
       <c r="F145" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G145" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>0.64</v>
+        <v>8.6</v>
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
@@ -30461,28 +29790,28 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>TANK Shanghai</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>West Bund riverside</t>
+          <t>West Bund Museum</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G146" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>1.8</v>
+        <v>0.64</v>
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -30502,28 +29831,28 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
           <t>West Bund riverside</t>
         </is>
       </c>
-      <c r="E147" s="8" t="inlineStr">
-        <is>
-          <t>Long Museum West Bund</t>
-        </is>
-      </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="G147" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H147" s="8" t="n">
-        <v>0.66</v>
+        <v>1.8</v>
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -30543,24 +29872,24 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
+          <t>West Bund riverside</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
           <t>Long Museum West Bund</t>
         </is>
       </c>
-      <c r="E148" s="8" t="inlineStr">
-        <is>
-          <t>Check in — J Hotel (Tower)</t>
-        </is>
-      </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>didi</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="G148" s="8" t="n">
         <v>17</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>6.75</v>
+        <v>0.66</v>
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
@@ -30575,21 +29904,21 @@
         </is>
       </c>
       <c r="B149" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Long Museum West Bund</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Museum East</t>
+          <t>Check in — J Hotel (Tower)</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
@@ -30601,7 +29930,7 @@
         <v>17</v>
       </c>
       <c r="H149" s="8" t="n">
-        <v>6.62</v>
+        <v>6.75</v>
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
@@ -30625,12 +29954,12 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Shanghai Tower base</t>
+          <t>Shanghai Museum East</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
@@ -30639,10 +29968,10 @@
         </is>
       </c>
       <c r="G150" s="8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>3.63</v>
+        <v>6.62</v>
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
@@ -30666,24 +29995,24 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
           <t>Shanghai Tower base</t>
         </is>
       </c>
-      <c r="E151" s="8" t="inlineStr">
-        <is>
-          <t>World Financial Center</t>
-        </is>
-      </c>
       <c r="F151" s="8" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>didi</t>
         </is>
       </c>
       <c r="G151" s="8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H151" s="8" t="n">
-        <v>0.17</v>
+        <v>3.63</v>
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
@@ -30707,12 +30036,12 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
+          <t>Shanghai Tower base</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="inlineStr">
+        <is>
           <t>World Financial Center</t>
-        </is>
-      </c>
-      <c r="E152" s="8" t="inlineStr">
-        <is>
-          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
@@ -30724,11 +30053,11 @@
         <v>8</v>
       </c>
       <c r="H152" s="8" t="n">
-        <v>0.6</v>
+        <v>0.17</v>
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -30748,28 +30077,28 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
+          <t>World Financial Center</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
           <t>Jin Mao Tower</t>
         </is>
       </c>
-      <c r="E153" s="8" t="inlineStr">
-        <is>
-          <t>Oriental Pearl Tower</t>
-        </is>
-      </c>
       <c r="F153" s="8" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
       <c r="G153" s="8" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>estimated (fitted model)</t>
+          <t>routed (real leg)</t>
         </is>
       </c>
     </row>
@@ -30789,12 +30118,12 @@
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Jin Mao Tower</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Pudong promenade</t>
+          <t>Oriental Pearl Tower</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr">
@@ -30803,14 +30132,14 @@
         </is>
       </c>
       <c r="G154" s="8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H154" s="8" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>routed (real leg)</t>
+          <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
@@ -30830,33 +30159,74 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="inlineStr">
+        <is>
           <t>Pudong promenade</t>
         </is>
       </c>
-      <c r="E155" s="8" t="inlineStr">
+      <c r="F155" s="8" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="8" t="inlineStr">
+        <is>
+          <t>routed (real leg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>Pudong promenade</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
         <is>
           <t>Fly from PVG</t>
         </is>
       </c>
-      <c r="F155" s="8" t="inlineStr">
+      <c r="F156" s="8" t="inlineStr">
         <is>
           <t>didi</t>
         </is>
       </c>
-      <c r="G155" s="8" t="n">
+      <c r="G156" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="H155" s="8" t="n">
+      <c r="H156" s="8" t="n">
         <v>31.45</v>
       </c>
-      <c r="I155" s="8" t="inlineStr">
+      <c r="I156" s="8" t="inlineStr">
         <is>
           <t>estimated (fitted model)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I155"/>
+  <autoFilter ref="A1:I156"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>